--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="BuffInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="106">
   <si>
     <t>id</t>
   </si>
@@ -218,6 +218,9 @@
     <t>暴击50%</t>
   </si>
   <si>
+    <t>BuffEntityConditionalAttribute</t>
+  </si>
+  <si>
     <t>ATK</t>
   </si>
   <si>
@@ -287,6 +290,24 @@
     <t>每隔{Time_S}秒再攻击一次</t>
   </si>
   <si>
+    <t>GameFightLogic_UnderAttack_Dead</t>
+  </si>
+  <si>
+    <t>2001:10&amp;</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}生物，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}生物，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}生物，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}生物，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
     <t>BuffEntityPeriodicPickupCrystal</t>
   </si>
   <si>
@@ -320,7 +341,10 @@
     <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
   </si>
   <si>
-    <t>死亡后生成魔晶</t>
+    <t>BuffEntityConditionalDeadCreateCrystal</t>
+  </si>
+  <si>
+    <t>死亡后{Percentage}%生成魔晶</t>
   </si>
 </sst>
 </file>
@@ -1372,12 +1396,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24.25" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="4" width="21.25" customWidth="1"/>
+    <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="4" max="4" width="21.25" customWidth="1"/>
     <col min="5" max="5" width="51.875" customWidth="1"/>
     <col min="6" max="6" width="41.5" customWidth="1"/>
     <col min="7" max="8" width="42.625" customWidth="1"/>
@@ -1815,7 +1840,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" ht="14.25" spans="1:22">
       <c r="A11">
         <v>2000300001</v>
       </c>
@@ -1825,15 +1850,15 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>48</v>
+      <c r="F11" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="G11" s="6"/>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M11">
         <v>0.5</v>
@@ -1845,10 +1870,10 @@
         <v>20003000010000</v>
       </c>
       <c r="V11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" spans="1:22">
       <c r="A12">
         <v>2000400001</v>
       </c>
@@ -1858,15 +1883,15 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>48</v>
+      <c r="F12" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="G12" s="6"/>
       <c r="H12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M12">
         <v>-0.5</v>
@@ -1878,7 +1903,7 @@
         <v>20004000010000</v>
       </c>
       <c r="V12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1892,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="8"/>
       <c r="T13">
@@ -1902,7 +1927,7 @@
         <v>30001000010000</v>
       </c>
       <c r="V13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -1916,10 +1941,10 @@
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O14">
         <v>0.1</v>
@@ -1931,7 +1956,7 @@
         <v>30002000010000</v>
       </c>
       <c r="V14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1952,7 +1977,7 @@
       </c>
       <c r="G15" s="8"/>
       <c r="H15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M15">
         <v>0.1</v>
@@ -1964,7 +1989,7 @@
         <v>30003000010000</v>
       </c>
       <c r="V15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1982,7 +2007,7 @@
       </c>
       <c r="G16" s="8"/>
       <c r="H16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M16">
         <v>-0.1</v>
@@ -1994,7 +2019,7 @@
         <v>30004000010000</v>
       </c>
       <c r="V16" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -2012,7 +2037,7 @@
       </c>
       <c r="G17" s="9"/>
       <c r="H17" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M17">
         <v>0.2</v>
@@ -2027,7 +2052,7 @@
         <v>110001000010000</v>
       </c>
       <c r="V17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -2045,7 +2070,7 @@
       </c>
       <c r="G18" s="9"/>
       <c r="H18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M18">
         <v>0.2</v>
@@ -2060,7 +2085,7 @@
         <v>110002000010000</v>
       </c>
       <c r="V18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -2078,7 +2103,7 @@
       </c>
       <c r="G19" s="9"/>
       <c r="H19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M19">
         <v>0.2</v>
@@ -2093,7 +2118,7 @@
         <v>110003000010000</v>
       </c>
       <c r="V19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" ht="13" customHeight="1" spans="1:22">
@@ -2132,7 +2157,7 @@
         <v>120001000010000</v>
       </c>
       <c r="V20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:22">
@@ -2146,7 +2171,7 @@
         <v>3</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G21" s="4"/>
       <c r="M21">
@@ -2171,7 +2196,7 @@
         <v>120002000010000</v>
       </c>
       <c r="V21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="14.25" spans="1:22">
@@ -2185,7 +2210,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G22" s="4"/>
       <c r="Q22">
@@ -2201,70 +2226,74 @@
         <v>120003000010000</v>
       </c>
       <c r="V22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="1:22">
       <c r="A23">
-        <v>13000100001</v>
+        <v>12000400001</v>
       </c>
       <c r="C23">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" s="4"/>
-      <c r="K23">
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="Q23">
-        <v>-1</v>
-      </c>
-      <c r="R23">
-        <v>3</v>
+        <v>63</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" t="s">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23">
+        <v>0.25</v>
       </c>
       <c r="T23">
-        <v>13000100001</v>
+        <v>12000400001</v>
       </c>
       <c r="U23" s="3">
-        <v>130001000010000</v>
+        <v>120004000010000</v>
       </c>
       <c r="V23" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="14.25" spans="1:22">
       <c r="A24">
-        <v>13000300001</v>
+        <v>12000500001</v>
       </c>
       <c r="C24">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="F24" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" t="s">
+        <v>79</v>
+      </c>
+      <c r="J24" t="s">
         <v>88</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="10"/>
-      <c r="S24">
-        <v>500001</v>
+      <c r="M24">
+        <v>0.25</v>
       </c>
       <c r="T24">
-        <v>13000300001</v>
+        <v>12000500001</v>
       </c>
       <c r="U24" s="3">
-        <v>130003000010000</v>
+        <v>120005000010000</v>
       </c>
       <c r="V24" t="s">
         <v>90</v>
@@ -2272,77 +2301,77 @@
     </row>
     <row r="25" ht="14.25" spans="1:22">
       <c r="A25">
-        <v>13000400001</v>
+        <v>12000600001</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25">
-        <v>4</v>
-      </c>
-      <c r="F25" t="s">
+        <v>3</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" t="s">
+        <v>88</v>
+      </c>
+      <c r="M25">
+        <v>0.25</v>
+      </c>
+      <c r="T25">
+        <v>12000600001</v>
+      </c>
+      <c r="U25" s="3">
+        <v>120006000010000</v>
+      </c>
+      <c r="V25" t="s">
         <v>91</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25">
-        <v>300001</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="T25">
-        <v>13000400001</v>
-      </c>
-      <c r="U25" s="3">
-        <v>130004000010000</v>
-      </c>
-      <c r="V25" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="26" ht="14.25" spans="1:22">
       <c r="A26">
-        <v>13000500001</v>
+        <v>12000700001</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26">
-        <v>4</v>
-      </c>
-      <c r="F26" t="s">
-        <v>93</v>
+        <v>3</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="10">
-        <v>1</v>
+        <v>87</v>
+      </c>
+      <c r="H26" t="s">
+        <v>67</v>
+      </c>
+      <c r="J26" t="s">
+        <v>88</v>
       </c>
       <c r="M26">
-        <v>0.05</v>
-      </c>
-      <c r="N26">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="T26">
-        <v>13000500001</v>
+        <v>12000700001</v>
       </c>
       <c r="U26" s="3">
-        <v>130005000010000</v>
+        <v>120007000010000</v>
       </c>
       <c r="V26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="1:22">
       <c r="A27">
-        <v>13000600001</v>
+        <v>13000100001</v>
       </c>
       <c r="C27">
         <v>13</v>
@@ -2350,34 +2379,33 @@
       <c r="D27">
         <v>4</v>
       </c>
-      <c r="F27" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="10">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>0.05</v>
-      </c>
-      <c r="N27">
-        <v>0.01</v>
+      <c r="F27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27" s="4"/>
+      <c r="K27">
+        <v>2</v>
+      </c>
+      <c r="L27"/>
+      <c r="Q27">
+        <v>-1</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
       </c>
       <c r="T27">
-        <v>13000600001</v>
+        <v>13000100001</v>
       </c>
       <c r="U27" s="3">
-        <v>130006000010000</v>
+        <v>130001000010000</v>
       </c>
       <c r="V27" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" ht="14.25" spans="1:22">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" spans="1:22">
       <c r="A28">
-        <v>13000700001</v>
+        <v>13000300001</v>
       </c>
       <c r="C28">
         <v>13</v>
@@ -2385,23 +2413,159 @@
       <c r="D28">
         <v>4</v>
       </c>
+      <c r="F28" t="s">
+        <v>95</v>
+      </c>
       <c r="G28" s="10" t="s">
-        <v>89</v>
+        <v>96</v>
+      </c>
+      <c r="H28" s="10"/>
+      <c r="S28">
+        <v>500001</v>
       </c>
       <c r="T28">
-        <v>13000700001</v>
+        <v>13000300001</v>
       </c>
       <c r="U28" s="3">
-        <v>130007000010000</v>
+        <v>130003000010000</v>
       </c>
       <c r="V28" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1"/>
-    <row r="30" ht="15" customHeight="1"/>
-    <row r="31" ht="15" customHeight="1"/>
-    <row r="32" ht="15" customHeight="1"/>
+    <row r="29" ht="14.25" spans="1:22">
+      <c r="A29">
+        <v>13000400001</v>
+      </c>
+      <c r="C29">
+        <v>13</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29">
+        <v>300001</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29"/>
+      <c r="T29">
+        <v>13000400001</v>
+      </c>
+      <c r="U29" s="3">
+        <v>130004000010000</v>
+      </c>
+      <c r="V29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" spans="1:22">
+      <c r="A30">
+        <v>13000500001</v>
+      </c>
+      <c r="C30">
+        <v>13</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="F30" t="s">
+        <v>100</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="10">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>0.05</v>
+      </c>
+      <c r="N30">
+        <v>0.01</v>
+      </c>
+      <c r="T30">
+        <v>13000500001</v>
+      </c>
+      <c r="U30" s="3">
+        <v>130005000010000</v>
+      </c>
+      <c r="V30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="1:22">
+      <c r="A31">
+        <v>13000600001</v>
+      </c>
+      <c r="C31">
+        <v>13</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="F31" t="s">
+        <v>102</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>0.05</v>
+      </c>
+      <c r="N31">
+        <v>0.01</v>
+      </c>
+      <c r="T31">
+        <v>13000600001</v>
+      </c>
+      <c r="U31" s="3">
+        <v>130006000010000</v>
+      </c>
+      <c r="V31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="14.25" spans="1:22">
+      <c r="A32">
+        <v>13000700001</v>
+      </c>
+      <c r="C32">
+        <v>13</v>
+      </c>
+      <c r="D32">
+        <v>4</v>
+      </c>
+      <c r="F32" t="s">
+        <v>104</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="O32">
+        <v>0.2</v>
+      </c>
+      <c r="P32"/>
+      <c r="T32">
+        <v>13000700001</v>
+      </c>
+      <c r="U32" s="3">
+        <v>130007000010000</v>
+      </c>
+      <c r="V32" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="33" ht="15" customHeight="1"/>
     <row r="34" ht="15" customHeight="1"/>
     <row r="35" ht="15" customHeight="1"/>
@@ -2409,15 +2573,19 @@
     <row r="37" ht="15" customHeight="1"/>
     <row r="38" ht="15" customHeight="1"/>
     <row r="39" ht="15" customHeight="1"/>
-    <row r="71" ht="12" customHeight="1"/>
-    <row r="72" ht="12" customHeight="1"/>
-    <row r="73" ht="12" customHeight="1"/>
-    <row r="74" ht="12" customHeight="1"/>
+    <row r="40" ht="15" customHeight="1"/>
+    <row r="41" ht="15" customHeight="1"/>
+    <row r="42" ht="15" customHeight="1"/>
+    <row r="43" ht="15" customHeight="1"/>
     <row r="75" ht="12" customHeight="1"/>
     <row r="76" ht="12" customHeight="1"/>
     <row r="77" ht="12" customHeight="1"/>
     <row r="78" ht="12" customHeight="1"/>
     <row r="79" ht="12" customHeight="1"/>
+    <row r="80" ht="12" customHeight="1"/>
+    <row r="81" ht="12" customHeight="1"/>
+    <row r="82" ht="12" customHeight="1"/>
+    <row r="83" ht="12" customHeight="1"/>
   </sheetData>
   <sortState ref="A4:AE88">
     <sortCondition ref="A4"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuffInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="128">
   <si>
     <t>id</t>
   </si>
@@ -155,7 +155,7 @@
     <t>触发几率(最小值)</t>
   </si>
   <si>
-    <t>触发次数(0为触发一次 负数永久触发)</t>
+    <t>触发次数(小于等于0永久触发)</t>
   </si>
   <si>
     <t>触发时间</t>
@@ -242,7 +242,7 @@
     <t>增殖-随机复制一个已有的魔物</t>
   </si>
   <si>
-    <t>BuffEntityConditionalAddCrystal</t>
+    <t>BuffEntityConditionalAddDropCrystal</t>
   </si>
   <si>
     <t>GameFightLogic_CreatureDeadDropCrystal</t>
@@ -287,7 +287,7 @@
     <t>BuffEntityPeriodicAttackAgain</t>
   </si>
   <si>
-    <t>每隔{Time_S}秒再攻击一次</t>
+    <t>每隔{Time_S}秒立即攻击一次</t>
   </si>
   <si>
     <t>GameFightLogic_UnderAttack_Dead</t>
@@ -296,16 +296,82 @@
     <t>2001:10&amp;</t>
   </si>
   <si>
-    <t>击杀{KillNum}生物，生命增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}生物，护甲增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}生物，攻击力增加{Percentage}%</t>
-  </si>
-  <si>
-    <t>击杀{KillNum}生物，攻击速度增加{Percentage}%</t>
+    <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>GameFightLogic_UnderAttack</t>
+  </si>
+  <si>
+    <t>3001:1000&amp;</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+  </si>
+  <si>
+    <t>BuffEntityConditionalCreateCrystal</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>4001:1000&amp;</t>
+  </si>
+  <si>
+    <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>BuffEntityConditionalAttackAgain</t>
+  </si>
+  <si>
+    <t>2001:1&amp;</t>
+  </si>
+  <si>
+    <t>击杀{KillNum}次生物，立即攻击一次</t>
+  </si>
+  <si>
+    <t>3001:200&amp;</t>
+  </si>
+  <si>
+    <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+  </si>
+  <si>
+    <t>4001:200&amp;</t>
+  </si>
+  <si>
+    <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
   </si>
   <si>
     <t>BuffEntityPeriodicPickupCrystal</t>
@@ -358,7 +424,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -416,6 +482,36 @@
     <font>
       <sz val="10.5"/>
       <color theme="1"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="5"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="6"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFC00000"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="4"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
@@ -884,137 +980,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1046,6 +1142,21 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1396,7 +1507,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V83"/>
+  <dimension ref="A1:V97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24.25" customWidth="1"/>
@@ -1647,6 +1758,9 @@
       <c r="M4">
         <v>-0.5</v>
       </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
       <c r="R4">
         <v>10</v>
       </c>
@@ -1683,6 +1797,9 @@
       <c r="M5">
         <v>-0.2</v>
       </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
       <c r="R5">
         <v>1</v>
       </c>
@@ -1710,6 +1827,9 @@
         <v>54</v>
       </c>
       <c r="G6" s="5"/>
+      <c r="Q6">
+        <v>1</v>
+      </c>
       <c r="T6">
         <v>1000300001</v>
       </c>
@@ -1770,6 +1890,15 @@
         <v>54</v>
       </c>
       <c r="G8" s="5"/>
+      <c r="K8">
+        <v>-100</v>
+      </c>
+      <c r="Q8">
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <v>3</v>
+      </c>
       <c r="T8">
         <v>1000500001</v>
       </c>
@@ -2141,9 +2270,6 @@
       <c r="N20">
         <v>0.01</v>
       </c>
-      <c r="Q20">
-        <v>-1</v>
-      </c>
       <c r="R20">
         <v>5</v>
       </c>
@@ -2180,9 +2306,6 @@
       <c r="N21">
         <v>0.01</v>
       </c>
-      <c r="Q21">
-        <v>-1</v>
-      </c>
       <c r="R21">
         <v>5</v>
       </c>
@@ -2213,9 +2336,6 @@
         <v>85</v>
       </c>
       <c r="G22" s="4"/>
-      <c r="Q22">
-        <v>-1</v>
-      </c>
       <c r="R22">
         <v>5</v>
       </c>
@@ -2231,7 +2351,7 @@
     </row>
     <row r="23" ht="14.25" spans="1:22">
       <c r="A23">
-        <v>12000400001</v>
+        <v>12001100001</v>
       </c>
       <c r="C23">
         <v>12</v>
@@ -2255,10 +2375,10 @@
         <v>0.25</v>
       </c>
       <c r="T23">
-        <v>12000400001</v>
+        <v>12001100001</v>
       </c>
       <c r="U23" s="3">
-        <v>120004000010000</v>
+        <v>120011000010000</v>
       </c>
       <c r="V23" t="s">
         <v>89</v>
@@ -2266,7 +2386,7 @@
     </row>
     <row r="24" ht="14.25" spans="1:22">
       <c r="A24">
-        <v>12000500001</v>
+        <v>12001200001</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -2290,10 +2410,10 @@
         <v>0.25</v>
       </c>
       <c r="T24">
-        <v>12000500001</v>
+        <v>12001200001</v>
       </c>
       <c r="U24" s="3">
-        <v>120005000010000</v>
+        <v>120012000010000</v>
       </c>
       <c r="V24" t="s">
         <v>90</v>
@@ -2301,7 +2421,7 @@
     </row>
     <row r="25" ht="14.25" spans="1:22">
       <c r="A25">
-        <v>12000600001</v>
+        <v>12001300001</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -2325,10 +2445,10 @@
         <v>0.25</v>
       </c>
       <c r="T25">
-        <v>12000600001</v>
+        <v>12001300001</v>
       </c>
       <c r="U25" s="3">
-        <v>120006000010000</v>
+        <v>120013000010000</v>
       </c>
       <c r="V25" t="s">
         <v>91</v>
@@ -2336,7 +2456,7 @@
     </row>
     <row r="26" ht="14.25" spans="1:22">
       <c r="A26">
-        <v>12000700001</v>
+        <v>12001400001</v>
       </c>
       <c r="C26">
         <v>12</v>
@@ -2360,10 +2480,10 @@
         <v>0.25</v>
       </c>
       <c r="T26">
-        <v>12000700001</v>
+        <v>12001400001</v>
       </c>
       <c r="U26" s="3">
-        <v>120007000010000</v>
+        <v>120014000010000</v>
       </c>
       <c r="V26" t="s">
         <v>92</v>
@@ -2371,221 +2491,670 @@
     </row>
     <row r="27" ht="14.25" spans="1:22">
       <c r="A27">
-        <v>13000100001</v>
+        <v>12002100001</v>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27">
-        <v>4</v>
-      </c>
-      <c r="F27" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="K27">
-        <v>2</v>
-      </c>
-      <c r="L27"/>
-      <c r="Q27">
-        <v>-1</v>
-      </c>
-      <c r="R27">
-        <v>3</v>
+      <c r="H27" t="s">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s">
+        <v>94</v>
+      </c>
+      <c r="M27">
+        <v>0.25</v>
       </c>
       <c r="T27">
-        <v>13000100001</v>
+        <v>12002100001</v>
       </c>
       <c r="U27" s="3">
-        <v>130001000010000</v>
+        <v>120021000010000</v>
       </c>
       <c r="V27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" ht="14.25" spans="1:22">
       <c r="A28">
-        <v>13000300001</v>
+        <v>12002200001</v>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28">
-        <v>4</v>
-      </c>
-      <c r="F28" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H28" t="s">
+        <v>79</v>
+      </c>
+      <c r="J28" t="s">
+        <v>94</v>
+      </c>
+      <c r="M28">
+        <v>0.25</v>
+      </c>
+      <c r="T28">
+        <v>12002200001</v>
+      </c>
+      <c r="U28" s="3">
+        <v>120022000010000</v>
+      </c>
+      <c r="V28" t="s">
         <v>96</v>
-      </c>
-      <c r="H28" s="10"/>
-      <c r="S28">
-        <v>500001</v>
-      </c>
-      <c r="T28">
-        <v>13000300001</v>
-      </c>
-      <c r="U28" s="3">
-        <v>130003000010000</v>
-      </c>
-      <c r="V28" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="1:22">
       <c r="A29">
-        <v>13000400001</v>
+        <v>12002300001</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="F29" t="s">
-        <v>98</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H29">
-        <v>300001</v>
+        <v>3</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" t="s">
+        <v>64</v>
+      </c>
+      <c r="J29" t="s">
+        <v>94</v>
       </c>
       <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29"/>
+        <v>0.25</v>
+      </c>
       <c r="T29">
-        <v>13000400001</v>
+        <v>12002300001</v>
       </c>
       <c r="U29" s="3">
-        <v>130004000010000</v>
+        <v>120023000010000</v>
       </c>
       <c r="V29" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="14.25" spans="1:22">
       <c r="A30">
-        <v>13000500001</v>
+        <v>12002400001</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30">
-        <v>4</v>
-      </c>
-      <c r="F30" t="s">
-        <v>100</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H30" s="10">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H30" t="s">
+        <v>67</v>
+      </c>
+      <c r="J30" t="s">
+        <v>94</v>
       </c>
       <c r="M30">
-        <v>0.05</v>
-      </c>
-      <c r="N30">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="T30">
-        <v>13000500001</v>
+        <v>12002400001</v>
       </c>
       <c r="U30" s="3">
-        <v>130005000010000</v>
+        <v>120024000010000</v>
       </c>
       <c r="V30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="1:22">
       <c r="A31">
+        <v>12003100001</v>
+      </c>
+      <c r="C31">
+        <v>12</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H31" t="s">
+        <v>74</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M31">
+        <v>0.25</v>
+      </c>
+      <c r="T31">
+        <v>12003100001</v>
+      </c>
+      <c r="U31" s="3">
+        <v>120031000010000</v>
+      </c>
+      <c r="V31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" spans="1:22">
+      <c r="A32">
+        <v>12003200001</v>
+      </c>
+      <c r="C32">
+        <v>12</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H32" t="s">
+        <v>79</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M32">
+        <v>0.25</v>
+      </c>
+      <c r="T32">
+        <v>12003200001</v>
+      </c>
+      <c r="U32" s="3">
+        <v>120032000010000</v>
+      </c>
+      <c r="V32" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="1:22">
+      <c r="A33">
+        <v>12003300001</v>
+      </c>
+      <c r="C33">
+        <v>12</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H33" t="s">
+        <v>64</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33">
+        <v>0.25</v>
+      </c>
+      <c r="T33">
+        <v>12003300001</v>
+      </c>
+      <c r="U33" s="3">
+        <v>120033000010000</v>
+      </c>
+      <c r="V33" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" spans="1:22">
+      <c r="A34">
+        <v>12003400001</v>
+      </c>
+      <c r="C34">
+        <v>12</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" t="s">
+        <v>67</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="M34">
+        <v>0.25</v>
+      </c>
+      <c r="T34">
+        <v>12003400001</v>
+      </c>
+      <c r="U34" s="3">
+        <v>120034000010000</v>
+      </c>
+      <c r="V34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="1:22">
+      <c r="A35">
+        <v>12010100001</v>
+      </c>
+      <c r="C35">
+        <v>12</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J35" t="s">
+        <v>88</v>
+      </c>
+      <c r="T35">
+        <v>12010100001</v>
+      </c>
+      <c r="U35" s="3">
+        <v>120101000010000</v>
+      </c>
+      <c r="V35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="1:22">
+      <c r="A36">
+        <v>12010200001</v>
+      </c>
+      <c r="C36">
+        <v>12</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J36" t="s">
+        <v>94</v>
+      </c>
+      <c r="T36">
+        <v>12010200001</v>
+      </c>
+      <c r="U36" s="3">
+        <v>120102000010000</v>
+      </c>
+      <c r="V36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" spans="1:22">
+      <c r="A37">
+        <v>12010300001</v>
+      </c>
+      <c r="C37">
+        <v>12</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J37" t="s">
+        <v>106</v>
+      </c>
+      <c r="T37">
+        <v>12010300001</v>
+      </c>
+      <c r="U37" s="3">
+        <v>120103000010000</v>
+      </c>
+      <c r="V37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" spans="1:22">
+      <c r="A38">
+        <v>12011100001</v>
+      </c>
+      <c r="C38">
+        <v>12</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="J38" t="s">
+        <v>109</v>
+      </c>
+      <c r="T38">
+        <v>12011100001</v>
+      </c>
+      <c r="U38" s="3">
+        <v>120111000010000</v>
+      </c>
+      <c r="V38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" spans="1:22">
+      <c r="A39">
+        <v>12011200001</v>
+      </c>
+      <c r="C39">
+        <v>12</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J39" t="s">
+        <v>111</v>
+      </c>
+      <c r="T39">
+        <v>12011200001</v>
+      </c>
+      <c r="U39" s="3">
+        <v>120112000010000</v>
+      </c>
+      <c r="V39" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" spans="1:22">
+      <c r="A40">
+        <v>12011300001</v>
+      </c>
+      <c r="C40">
+        <v>12</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G40" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J40" t="s">
+        <v>113</v>
+      </c>
+      <c r="T40">
+        <v>12011300001</v>
+      </c>
+      <c r="U40" s="3">
+        <v>120113000010000</v>
+      </c>
+      <c r="V40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" spans="1:22">
+      <c r="A41">
+        <v>13000100001</v>
+      </c>
+      <c r="C41">
+        <v>13</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" s="4"/>
+      <c r="K41">
+        <v>2</v>
+      </c>
+      <c r="R41">
+        <v>3</v>
+      </c>
+      <c r="T41">
+        <v>13000100001</v>
+      </c>
+      <c r="U41" s="3">
+        <v>130001000010000</v>
+      </c>
+      <c r="V41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" spans="1:22">
+      <c r="A42">
+        <v>13000300001</v>
+      </c>
+      <c r="C42">
+        <v>13</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="F42" t="s">
+        <v>117</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H42" s="10"/>
+      <c r="S42">
+        <v>500001</v>
+      </c>
+      <c r="T42">
+        <v>13000300001</v>
+      </c>
+      <c r="U42" s="3">
+        <v>130003000010000</v>
+      </c>
+      <c r="V42" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" spans="1:22">
+      <c r="A43">
+        <v>13000400001</v>
+      </c>
+      <c r="C43">
+        <v>13</v>
+      </c>
+      <c r="D43">
+        <v>4</v>
+      </c>
+      <c r="F43" t="s">
+        <v>120</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H43">
+        <v>300001</v>
+      </c>
+      <c r="M43">
+        <v>1</v>
+      </c>
+      <c r="T43">
+        <v>13000400001</v>
+      </c>
+      <c r="U43" s="3">
+        <v>130004000010000</v>
+      </c>
+      <c r="V43" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" spans="1:22">
+      <c r="A44">
+        <v>13000500001</v>
+      </c>
+      <c r="C44">
+        <v>13</v>
+      </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="10">
+        <v>1</v>
+      </c>
+      <c r="M44">
+        <v>0.05</v>
+      </c>
+      <c r="N44">
+        <v>0.01</v>
+      </c>
+      <c r="T44">
+        <v>13000500001</v>
+      </c>
+      <c r="U44" s="3">
+        <v>130005000010000</v>
+      </c>
+      <c r="V44" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" spans="1:22">
+      <c r="A45">
         <v>13000600001</v>
       </c>
-      <c r="C31">
+      <c r="C45">
         <v>13</v>
       </c>
-      <c r="D31">
+      <c r="D45">
         <v>4</v>
       </c>
-      <c r="F31" t="s">
-        <v>102</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H31" s="10">
+      <c r="F45" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H45" s="10">
         <v>1</v>
       </c>
-      <c r="M31">
+      <c r="M45">
         <v>0.05</v>
       </c>
-      <c r="N31">
+      <c r="N45">
         <v>0.01</v>
       </c>
-      <c r="T31">
+      <c r="T45">
         <v>13000600001</v>
       </c>
-      <c r="U31" s="3">
+      <c r="U45" s="3">
         <v>130006000010000</v>
       </c>
-      <c r="V31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" ht="14.25" spans="1:22">
-      <c r="A32">
+      <c r="V45" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" ht="14.25" spans="1:22">
+      <c r="A46">
         <v>13000700001</v>
       </c>
-      <c r="C32">
+      <c r="C46">
         <v>13</v>
       </c>
-      <c r="D32">
+      <c r="D46">
         <v>4</v>
       </c>
-      <c r="F32" t="s">
-        <v>104</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="O32">
+      <c r="F46" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="O46">
         <v>0.2</v>
       </c>
-      <c r="P32"/>
-      <c r="T32">
+      <c r="P46"/>
+      <c r="T46">
         <v>13000700001</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U46" s="3">
         <v>130007000010000</v>
       </c>
-      <c r="V32" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1"/>
-    <row r="34" ht="15" customHeight="1"/>
-    <row r="35" ht="15" customHeight="1"/>
-    <row r="36" ht="15" customHeight="1"/>
-    <row r="37" ht="15" customHeight="1"/>
-    <row r="38" ht="15" customHeight="1"/>
-    <row r="39" ht="15" customHeight="1"/>
-    <row r="40" ht="15" customHeight="1"/>
-    <row r="41" ht="15" customHeight="1"/>
-    <row r="42" ht="15" customHeight="1"/>
-    <row r="43" ht="15" customHeight="1"/>
-    <row r="75" ht="12" customHeight="1"/>
-    <row r="76" ht="12" customHeight="1"/>
-    <row r="77" ht="12" customHeight="1"/>
-    <row r="78" ht="12" customHeight="1"/>
-    <row r="79" ht="12" customHeight="1"/>
-    <row r="80" ht="12" customHeight="1"/>
-    <row r="81" ht="12" customHeight="1"/>
-    <row r="82" ht="12" customHeight="1"/>
-    <row r="83" ht="12" customHeight="1"/>
+      <c r="V46" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1"/>
+    <row r="48" ht="15" customHeight="1"/>
+    <row r="49" ht="15" customHeight="1"/>
+    <row r="50" ht="15" customHeight="1"/>
+    <row r="51" ht="15" customHeight="1"/>
+    <row r="52" ht="15" customHeight="1"/>
+    <row r="53" ht="15" customHeight="1"/>
+    <row r="54" ht="15" customHeight="1"/>
+    <row r="55" ht="15" customHeight="1"/>
+    <row r="56" ht="15" customHeight="1"/>
+    <row r="57" ht="15" customHeight="1"/>
+    <row r="89" ht="12" customHeight="1"/>
+    <row r="90" ht="12" customHeight="1"/>
+    <row r="91" ht="12" customHeight="1"/>
+    <row r="92" ht="12" customHeight="1"/>
+    <row r="93" ht="12" customHeight="1"/>
+    <row r="94" ht="12" customHeight="1"/>
+    <row r="95" ht="12" customHeight="1"/>
+    <row r="96" ht="12" customHeight="1"/>
+    <row r="97" ht="12" customHeight="1"/>
   </sheetData>
   <sortState ref="A4:AE88">
     <sortCondition ref="A4"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuffInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="134">
   <si>
     <t>id</t>
   </si>
@@ -41,6 +41,12 @@
     <t>rarity</t>
   </si>
   <si>
+    <t>buff_parent_id</t>
+  </si>
+  <si>
+    <t>buff_level</t>
+  </si>
+  <si>
     <t>trigger_creature_type</t>
   </si>
   <si>
@@ -119,6 +125,12 @@
     <t>稀有度</t>
   </si>
   <si>
+    <t>父级buffID</t>
+  </si>
+  <si>
+    <t>buff等级</t>
+  </si>
+  <si>
     <t>buff触发对象类型0所有 1防御 2进攻 99防守核心</t>
   </si>
   <si>
@@ -248,7 +260,13 @@
     <t>GameFightLogic_CreatureDeadDropCrystal</t>
   </si>
   <si>
-    <t>钱多多-每一次击杀有10%的概率多掉落一次魔晶</t>
+    <t>钱多多LV1-每一次击杀有10%的概率多掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>钱多多LV2-每一次击杀有20%的概率多掉落一次魔晶</t>
+  </si>
+  <si>
+    <t>钱多多LV3-每一次击杀有30%的概率多掉落一次魔晶</t>
   </si>
   <si>
     <t>HP</t>
@@ -1507,31 +1525,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V97"/>
+  <dimension ref="A1:X99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24.25" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="31.5" customWidth="1"/>
-    <col min="4" max="4" width="21.25" customWidth="1"/>
-    <col min="5" max="5" width="51.875" customWidth="1"/>
-    <col min="6" max="6" width="41.5" customWidth="1"/>
-    <col min="7" max="8" width="42.625" customWidth="1"/>
-    <col min="9" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="11" width="14.875" customWidth="1"/>
-    <col min="12" max="12" width="19.375" customWidth="1"/>
-    <col min="13" max="13" width="20.375" customWidth="1"/>
-    <col min="14" max="14" width="24.875" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="21.375" customWidth="1"/>
-    <col min="17" max="17" width="36.125" customWidth="1"/>
-    <col min="18" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="17.125" customWidth="1"/>
-    <col min="21" max="21" width="28.625" customWidth="1"/>
-    <col min="22" max="22" width="61.875" customWidth="1"/>
+    <col min="4" max="5" width="21.25" customWidth="1"/>
+    <col min="6" max="6" width="27.25" customWidth="1"/>
+    <col min="7" max="7" width="51.875" customWidth="1"/>
+    <col min="8" max="8" width="41.5" customWidth="1"/>
+    <col min="9" max="10" width="42.625" customWidth="1"/>
+    <col min="11" max="12" width="11.5" customWidth="1"/>
+    <col min="13" max="13" width="14.875" customWidth="1"/>
+    <col min="14" max="14" width="19.375" customWidth="1"/>
+    <col min="15" max="15" width="20.375" customWidth="1"/>
+    <col min="16" max="16" width="24.875" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="21.375" customWidth="1"/>
+    <col min="19" max="19" width="36.125" customWidth="1"/>
+    <col min="20" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="17.125" customWidth="1"/>
+    <col min="23" max="23" width="28.625" customWidth="1"/>
+    <col min="24" max="24" width="61.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1584,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -1583,7 +1602,7 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
@@ -1598,144 +1617,162 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>25</v>
       </c>
       <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" t="s">
+        <v>24</v>
+      </c>
+      <c r="W2" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
-      <c r="T2" t="s">
-        <v>22</v>
-      </c>
-      <c r="U2" t="s">
-        <v>22</v>
-      </c>
-      <c r="V2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K3" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="L3" t="s">
+        <v>39</v>
       </c>
       <c r="M3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q3" t="s">
-        <v>42</v>
-      </c>
-      <c r="R3" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="S3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
+        <v>49</v>
+      </c>
+      <c r="W3" t="s">
+        <v>50</v>
+      </c>
+      <c r="X3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>1000100001</v>
       </c>
@@ -1745,36 +1782,36 @@
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M4">
+      <c r="H4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4">
         <v>-0.5</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>1</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>10</v>
       </c>
-      <c r="T4">
+      <c r="V4">
         <v>1000100001</v>
       </c>
-      <c r="U4" s="3">
+      <c r="W4" s="3">
         <v>10001000010000</v>
       </c>
-      <c r="V4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="X4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5">
         <v>1000200001</v>
       </c>
@@ -1784,36 +1821,36 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="H5" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="M5">
+      <c r="I5" s="2"/>
+      <c r="J5" t="s">
+        <v>53</v>
+      </c>
+      <c r="K5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5">
         <v>-0.2</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>1</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>1</v>
       </c>
-      <c r="T5">
+      <c r="V5">
         <v>1000200001</v>
       </c>
-      <c r="U5" s="3">
+      <c r="W5" s="3">
         <v>10002000010000</v>
       </c>
-      <c r="V5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" ht="14.25" spans="1:22">
+      <c r="X5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" spans="1:24">
       <c r="A6">
         <v>1000300001</v>
       </c>
@@ -1823,24 +1860,24 @@
       <c r="D6">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="Q6">
+      <c r="H6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="5"/>
+      <c r="S6">
         <v>1</v>
       </c>
-      <c r="T6">
+      <c r="V6">
         <v>1000300001</v>
       </c>
-      <c r="U6" s="3">
+      <c r="W6" s="3">
         <v>10003000010000</v>
       </c>
-      <c r="V6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="1:22">
+      <c r="X6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:24">
       <c r="A7">
         <v>1000400001</v>
       </c>
@@ -1850,33 +1887,33 @@
       <c r="D7">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="I7" t="s">
-        <v>56</v>
-      </c>
-      <c r="K7">
+      <c r="H7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="5"/>
+      <c r="K7" t="s">
+        <v>60</v>
+      </c>
+      <c r="M7">
         <v>-100</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>5</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>3</v>
       </c>
-      <c r="T7">
+      <c r="V7">
         <v>1000400001</v>
       </c>
-      <c r="U7" s="3">
+      <c r="W7" s="3">
         <v>10004000010000</v>
       </c>
-      <c r="V7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" ht="14.25" spans="1:22">
+      <c r="X7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" spans="1:24">
       <c r="A8">
         <v>1000500001</v>
       </c>
@@ -1886,30 +1923,30 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="K8">
+      <c r="H8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="M8">
         <v>-100</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>3</v>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>3</v>
       </c>
-      <c r="T8">
+      <c r="V8">
         <v>1000500001</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>10005000010000</v>
       </c>
-      <c r="V8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
+      <c r="X8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9">
         <v>2000100001</v>
       </c>
@@ -1919,27 +1956,27 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="6"/>
-      <c r="H9" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9">
+      <c r="H9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
+      <c r="O9">
         <v>0.5</v>
       </c>
-      <c r="T9">
+      <c r="V9">
         <v>2000100001</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>20001000010000</v>
       </c>
-      <c r="V9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
+      <c r="X9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
       <c r="A10">
         <v>2000200001</v>
       </c>
@@ -1949,27 +1986,27 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="6"/>
-      <c r="H10" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10">
+      <c r="H10" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="6"/>
+      <c r="J10" t="s">
+        <v>65</v>
+      </c>
+      <c r="O10">
         <v>0.5</v>
       </c>
-      <c r="T10">
+      <c r="V10">
         <v>2000200001</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>20002000010000</v>
       </c>
-      <c r="V10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:22">
+      <c r="X10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="1:24">
       <c r="A11">
         <v>2000300001</v>
       </c>
@@ -1979,30 +2016,30 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11" s="6"/>
-      <c r="H11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M11">
+      <c r="H11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="6"/>
+      <c r="J11" t="s">
+        <v>68</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O11">
         <v>0.5</v>
       </c>
-      <c r="T11">
+      <c r="V11">
         <v>2000300001</v>
       </c>
-      <c r="U11" s="3">
+      <c r="W11" s="3">
         <v>20003000010000</v>
       </c>
-      <c r="V11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:22">
+      <c r="X11" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" spans="1:24">
       <c r="A12">
         <v>2000400001</v>
       </c>
@@ -2012,30 +2049,30 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="6"/>
-      <c r="H12" t="s">
+      <c r="H12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M12">
+      <c r="I12" s="6"/>
+      <c r="J12" t="s">
+        <v>71</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O12">
         <v>-0.5</v>
       </c>
-      <c r="T12">
+      <c r="V12">
         <v>2000400001</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>20004000010000</v>
       </c>
-      <c r="V12" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+      <c r="X12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
       <c r="A13">
         <v>3000100001</v>
       </c>
@@ -2045,21 +2082,21 @@
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="8"/>
-      <c r="T13">
+      <c r="H13" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="V13">
         <v>3000100001</v>
       </c>
-      <c r="U13" s="3">
+      <c r="W13" s="3">
         <v>30001000010000</v>
       </c>
-      <c r="V13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+      <c r="X13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
       <c r="A14">
         <v>3000200001</v>
       </c>
@@ -2069,28 +2106,34 @@
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" t="s">
-        <v>72</v>
-      </c>
-      <c r="O14">
+      <c r="E14">
+        <v>3000200001</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q14">
         <v>0.1</v>
       </c>
-      <c r="T14">
+      <c r="V14">
         <v>3000200001</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>30002000010000</v>
       </c>
-      <c r="V14" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+      <c r="X14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
       <c r="A15">
-        <v>3000300001</v>
+        <v>3000200002</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -2099,31 +2142,33 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="8"/>
-      <c r="H15" t="s">
-        <v>74</v>
-      </c>
-      <c r="M15">
-        <v>0.1</v>
-      </c>
-      <c r="T15">
-        <v>3000300001</v>
-      </c>
-      <c r="U15" s="3">
-        <v>30003000010000</v>
-      </c>
-      <c r="V15" t="s">
+        <v>3000200002</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="16" spans="1:22">
+      <c r="I15" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q15">
+        <v>0.2</v>
+      </c>
+      <c r="V15">
+        <v>3000200002</v>
+      </c>
+      <c r="W15" s="3">
+        <v>30002000020000</v>
+      </c>
+      <c r="X15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24">
       <c r="A16">
-        <v>3000400001</v>
+        <v>3000200003</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2131,95 +2176,97 @@
       <c r="D16">
         <v>1</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="8"/>
-      <c r="H16" t="s">
+      <c r="E16">
+        <v>3000200003</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" t="s">
         <v>76</v>
       </c>
-      <c r="M16">
+      <c r="Q16">
+        <v>0.3</v>
+      </c>
+      <c r="V16">
+        <v>3000200003</v>
+      </c>
+      <c r="W16" s="3">
+        <v>30002000030000</v>
+      </c>
+      <c r="X16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17">
+        <v>3000300001</v>
+      </c>
+      <c r="C17">
+        <v>3</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" s="8"/>
+      <c r="J17" t="s">
+        <v>80</v>
+      </c>
+      <c r="O17">
+        <v>0.1</v>
+      </c>
+      <c r="V17">
+        <v>3000300001</v>
+      </c>
+      <c r="W17" s="3">
+        <v>30003000010000</v>
+      </c>
+      <c r="X17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18">
+        <v>3000400001</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="8"/>
+      <c r="J18" t="s">
+        <v>82</v>
+      </c>
+      <c r="O18">
         <v>-0.1</v>
       </c>
-      <c r="T16">
+      <c r="V18">
         <v>3000400001</v>
       </c>
-      <c r="U16" s="3">
+      <c r="W18" s="3">
         <v>30004000010000</v>
       </c>
-      <c r="V16" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
-      <c r="A17">
+      <c r="X18" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19">
         <v>11000100001</v>
-      </c>
-      <c r="C17">
-        <v>11</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="9"/>
-      <c r="H17" t="s">
-        <v>74</v>
-      </c>
-      <c r="M17">
-        <v>0.2</v>
-      </c>
-      <c r="N17">
-        <v>0.1</v>
-      </c>
-      <c r="T17">
-        <v>11000100001</v>
-      </c>
-      <c r="U17" s="3">
-        <v>110001000010000</v>
-      </c>
-      <c r="V17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
-      <c r="A18">
-        <v>11000200001</v>
-      </c>
-      <c r="C18">
-        <v>11</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" t="s">
-        <v>79</v>
-      </c>
-      <c r="M18">
-        <v>0.2</v>
-      </c>
-      <c r="N18">
-        <v>0.1</v>
-      </c>
-      <c r="T18">
-        <v>11000200001</v>
-      </c>
-      <c r="U18" s="3">
-        <v>110002000010000</v>
-      </c>
-      <c r="V18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
-      <c r="A19">
-        <v>11000300001</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -2227,104 +2274,98 @@
       <c r="D19">
         <v>2</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="9"/>
-      <c r="H19" t="s">
-        <v>64</v>
-      </c>
-      <c r="M19">
+      <c r="H19" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" t="s">
+        <v>80</v>
+      </c>
+      <c r="O19">
         <v>0.2</v>
       </c>
-      <c r="N19">
+      <c r="P19">
         <v>0.1</v>
       </c>
-      <c r="T19">
+      <c r="V19">
+        <v>11000100001</v>
+      </c>
+      <c r="W19" s="3">
+        <v>110001000010000</v>
+      </c>
+      <c r="X19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20">
+        <v>11000200001</v>
+      </c>
+      <c r="C20">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" t="s">
+        <v>85</v>
+      </c>
+      <c r="O20">
+        <v>0.2</v>
+      </c>
+      <c r="P20">
+        <v>0.1</v>
+      </c>
+      <c r="V20">
+        <v>11000200001</v>
+      </c>
+      <c r="W20" s="3">
+        <v>110002000010000</v>
+      </c>
+      <c r="X20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21">
         <v>11000300001</v>
       </c>
-      <c r="U19" s="3">
+      <c r="C21">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" t="s">
+        <v>68</v>
+      </c>
+      <c r="O21">
+        <v>0.2</v>
+      </c>
+      <c r="P21">
+        <v>0.1</v>
+      </c>
+      <c r="V21">
+        <v>11000300001</v>
+      </c>
+      <c r="W21" s="3">
         <v>110003000010000</v>
       </c>
-      <c r="V19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" ht="13" customHeight="1" spans="1:22">
-      <c r="A20">
+      <c r="X21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" ht="13" customHeight="1" spans="1:24">
+      <c r="A22">
         <v>12000100001</v>
-      </c>
-      <c r="C20">
-        <v>12</v>
-      </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="4"/>
-      <c r="M20">
-        <v>0.05</v>
-      </c>
-      <c r="N20">
-        <v>0.01</v>
-      </c>
-      <c r="R20">
-        <v>5</v>
-      </c>
-      <c r="S20">
-        <v>500001</v>
-      </c>
-      <c r="T20">
-        <v>12000100001</v>
-      </c>
-      <c r="U20" s="3">
-        <v>120001000010000</v>
-      </c>
-      <c r="V20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="1:22">
-      <c r="A21">
-        <v>12000200001</v>
-      </c>
-      <c r="C21">
-        <v>12</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G21" s="4"/>
-      <c r="M21">
-        <v>0.05</v>
-      </c>
-      <c r="N21">
-        <v>0.01</v>
-      </c>
-      <c r="R21">
-        <v>5</v>
-      </c>
-      <c r="S21">
-        <v>500002</v>
-      </c>
-      <c r="T21">
-        <v>12000200001</v>
-      </c>
-      <c r="U21" s="3">
-        <v>120002000010000</v>
-      </c>
-      <c r="V21" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" spans="1:22">
-      <c r="A22">
-        <v>12000300001</v>
       </c>
       <c r="C22">
         <v>12</v>
@@ -2332,26 +2373,35 @@
       <c r="D22">
         <v>3</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="4"/>
-      <c r="R22">
+      <c r="H22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="O22">
+        <v>0.05</v>
+      </c>
+      <c r="P22">
+        <v>0.01</v>
+      </c>
+      <c r="T22">
         <v>5</v>
       </c>
-      <c r="T22">
-        <v>12000300001</v>
-      </c>
-      <c r="U22" s="3">
-        <v>120003000010000</v>
-      </c>
-      <c r="V22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="1:22">
+      <c r="U22">
+        <v>500001</v>
+      </c>
+      <c r="V22">
+        <v>12000100001</v>
+      </c>
+      <c r="W22" s="3">
+        <v>120001000010000</v>
+      </c>
+      <c r="X22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="1:24">
       <c r="A23">
-        <v>12001100001</v>
+        <v>12000200001</v>
       </c>
       <c r="C23">
         <v>12</v>
@@ -2359,34 +2409,35 @@
       <c r="D23">
         <v>3</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H23" t="s">
-        <v>74</v>
-      </c>
-      <c r="J23" t="s">
-        <v>88</v>
-      </c>
-      <c r="M23">
-        <v>0.25</v>
+      <c r="H23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="O23">
+        <v>0.05</v>
+      </c>
+      <c r="P23">
+        <v>0.01</v>
       </c>
       <c r="T23">
-        <v>12001100001</v>
-      </c>
-      <c r="U23" s="3">
-        <v>120011000010000</v>
-      </c>
-      <c r="V23" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" spans="1:22">
+        <v>5</v>
+      </c>
+      <c r="U23">
+        <v>500002</v>
+      </c>
+      <c r="V23">
+        <v>12000200001</v>
+      </c>
+      <c r="W23" s="3">
+        <v>120002000010000</v>
+      </c>
+      <c r="X23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" spans="1:24">
       <c r="A24">
-        <v>12001200001</v>
+        <v>12000300001</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -2394,34 +2445,26 @@
       <c r="D24">
         <v>3</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H24" t="s">
-        <v>79</v>
-      </c>
-      <c r="J24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M24">
-        <v>0.25</v>
-      </c>
+      <c r="H24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="4"/>
       <c r="T24">
-        <v>12001200001</v>
-      </c>
-      <c r="U24" s="3">
-        <v>120012000010000</v>
-      </c>
-      <c r="V24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="1:22">
+        <v>5</v>
+      </c>
+      <c r="V24">
+        <v>12000300001</v>
+      </c>
+      <c r="W24" s="3">
+        <v>120003000010000</v>
+      </c>
+      <c r="X24" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="1:24">
       <c r="A25">
-        <v>12001300001</v>
+        <v>12001100001</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -2429,34 +2472,34 @@
       <c r="D25">
         <v>3</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H25" t="s">
-        <v>64</v>
+      <c r="H25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="J25" t="s">
-        <v>88</v>
-      </c>
-      <c r="M25">
+        <v>80</v>
+      </c>
+      <c r="L25" t="s">
+        <v>94</v>
+      </c>
+      <c r="O25">
         <v>0.25</v>
       </c>
-      <c r="T25">
-        <v>12001300001</v>
-      </c>
-      <c r="U25" s="3">
-        <v>120013000010000</v>
-      </c>
-      <c r="V25" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" spans="1:22">
+      <c r="V25">
+        <v>12001100001</v>
+      </c>
+      <c r="W25" s="3">
+        <v>120011000010000</v>
+      </c>
+      <c r="X25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" spans="1:24">
       <c r="A26">
-        <v>12001400001</v>
+        <v>12001200001</v>
       </c>
       <c r="C26">
         <v>12</v>
@@ -2464,34 +2507,34 @@
       <c r="D26">
         <v>3</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" t="s">
+      <c r="H26" s="4" t="s">
         <v>67</v>
       </c>
+      <c r="I26" s="10" t="s">
+        <v>93</v>
+      </c>
       <c r="J26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M26">
+        <v>85</v>
+      </c>
+      <c r="L26" t="s">
+        <v>94</v>
+      </c>
+      <c r="O26">
         <v>0.25</v>
       </c>
-      <c r="T26">
-        <v>12001400001</v>
-      </c>
-      <c r="U26" s="3">
-        <v>120014000010000</v>
-      </c>
-      <c r="V26" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="1:22">
+      <c r="V26">
+        <v>12001200001</v>
+      </c>
+      <c r="W26" s="3">
+        <v>120012000010000</v>
+      </c>
+      <c r="X26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="1:24">
       <c r="A27">
-        <v>12002100001</v>
+        <v>12001300001</v>
       </c>
       <c r="C27">
         <v>12</v>
@@ -2499,34 +2542,34 @@
       <c r="D27">
         <v>3</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" s="12" t="s">
+      <c r="H27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="H27" t="s">
-        <v>74</v>
-      </c>
       <c r="J27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L27" t="s">
         <v>94</v>
       </c>
-      <c r="M27">
+      <c r="O27">
         <v>0.25</v>
       </c>
-      <c r="T27">
-        <v>12002100001</v>
-      </c>
-      <c r="U27" s="3">
-        <v>120021000010000</v>
-      </c>
-      <c r="V27" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" spans="1:22">
+      <c r="V27">
+        <v>12001300001</v>
+      </c>
+      <c r="W27" s="3">
+        <v>120013000010000</v>
+      </c>
+      <c r="X27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" spans="1:24">
       <c r="A28">
-        <v>12002200001</v>
+        <v>12001400001</v>
       </c>
       <c r="C28">
         <v>12</v>
@@ -2534,34 +2577,34 @@
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G28" s="12" t="s">
+      <c r="H28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="H28" t="s">
-        <v>79</v>
-      </c>
       <c r="J28" t="s">
+        <v>71</v>
+      </c>
+      <c r="L28" t="s">
         <v>94</v>
       </c>
-      <c r="M28">
+      <c r="O28">
         <v>0.25</v>
       </c>
-      <c r="T28">
-        <v>12002200001</v>
-      </c>
-      <c r="U28" s="3">
-        <v>120022000010000</v>
-      </c>
-      <c r="V28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="1:22">
+      <c r="V28">
+        <v>12001400001</v>
+      </c>
+      <c r="W28" s="3">
+        <v>120014000010000</v>
+      </c>
+      <c r="X28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="1:24">
       <c r="A29">
-        <v>12002300001</v>
+        <v>12002100001</v>
       </c>
       <c r="C29">
         <v>12</v>
@@ -2569,34 +2612,34 @@
       <c r="D29">
         <v>3</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H29" t="s">
-        <v>64</v>
+      <c r="H29" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>99</v>
       </c>
       <c r="J29" t="s">
-        <v>94</v>
-      </c>
-      <c r="M29">
+        <v>80</v>
+      </c>
+      <c r="L29" t="s">
+        <v>100</v>
+      </c>
+      <c r="O29">
         <v>0.25</v>
       </c>
-      <c r="T29">
-        <v>12002300001</v>
-      </c>
-      <c r="U29" s="3">
-        <v>120023000010000</v>
-      </c>
-      <c r="V29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" spans="1:22">
+      <c r="V29">
+        <v>12002100001</v>
+      </c>
+      <c r="W29" s="3">
+        <v>120021000010000</v>
+      </c>
+      <c r="X29" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" spans="1:24">
       <c r="A30">
-        <v>12002400001</v>
+        <v>12002200001</v>
       </c>
       <c r="C30">
         <v>12</v>
@@ -2604,34 +2647,34 @@
       <c r="D30">
         <v>3</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="H30" t="s">
+      <c r="H30" s="11" t="s">
         <v>67</v>
       </c>
+      <c r="I30" s="12" t="s">
+        <v>99</v>
+      </c>
       <c r="J30" t="s">
-        <v>94</v>
-      </c>
-      <c r="M30">
+        <v>85</v>
+      </c>
+      <c r="L30" t="s">
+        <v>100</v>
+      </c>
+      <c r="O30">
         <v>0.25</v>
       </c>
-      <c r="T30">
-        <v>12002400001</v>
-      </c>
-      <c r="U30" s="3">
-        <v>120024000010000</v>
-      </c>
-      <c r="V30" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="1:22">
+      <c r="V30">
+        <v>12002200001</v>
+      </c>
+      <c r="W30" s="3">
+        <v>120022000010000</v>
+      </c>
+      <c r="X30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="1:24">
       <c r="A31">
-        <v>12003100001</v>
+        <v>12002300001</v>
       </c>
       <c r="C31">
         <v>12</v>
@@ -2639,34 +2682,34 @@
       <c r="D31">
         <v>3</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H31" t="s">
-        <v>74</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M31">
+      <c r="H31" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="J31" t="s">
+        <v>68</v>
+      </c>
+      <c r="L31" t="s">
+        <v>100</v>
+      </c>
+      <c r="O31">
         <v>0.25</v>
       </c>
-      <c r="T31">
-        <v>12003100001</v>
-      </c>
-      <c r="U31" s="3">
-        <v>120031000010000</v>
-      </c>
-      <c r="V31" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" spans="1:22">
+      <c r="V31">
+        <v>12002300001</v>
+      </c>
+      <c r="W31" s="3">
+        <v>120023000010000</v>
+      </c>
+      <c r="X31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" spans="1:24">
       <c r="A32">
-        <v>12003200001</v>
+        <v>12002400001</v>
       </c>
       <c r="C32">
         <v>12</v>
@@ -2674,34 +2717,34 @@
       <c r="D32">
         <v>3</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H32" t="s">
-        <v>79</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M32">
+      <c r="H32" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="J32" t="s">
+        <v>71</v>
+      </c>
+      <c r="L32" t="s">
+        <v>100</v>
+      </c>
+      <c r="O32">
         <v>0.25</v>
       </c>
-      <c r="T32">
-        <v>12003200001</v>
-      </c>
-      <c r="U32" s="3">
-        <v>120032000010000</v>
-      </c>
-      <c r="V32" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="1:22">
+      <c r="V32">
+        <v>12002400001</v>
+      </c>
+      <c r="W32" s="3">
+        <v>120024000010000</v>
+      </c>
+      <c r="X32" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="1:24">
       <c r="A33">
-        <v>12003300001</v>
+        <v>12003100001</v>
       </c>
       <c r="C33">
         <v>12</v>
@@ -2709,34 +2752,34 @@
       <c r="D33">
         <v>3</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H33" t="s">
-        <v>64</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M33">
+      <c r="H33" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" t="s">
+        <v>80</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O33">
         <v>0.25</v>
       </c>
-      <c r="T33">
-        <v>12003300001</v>
-      </c>
-      <c r="U33" s="3">
-        <v>120033000010000</v>
-      </c>
-      <c r="V33" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" spans="1:22">
+      <c r="V33">
+        <v>12003100001</v>
+      </c>
+      <c r="W33" s="3">
+        <v>120031000010000</v>
+      </c>
+      <c r="X33" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" spans="1:24">
       <c r="A34">
-        <v>12003400001</v>
+        <v>12003200001</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -2744,34 +2787,34 @@
       <c r="D34">
         <v>3</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="H34" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="J34" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="M34">
+      <c r="I34" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J34" t="s">
+        <v>85</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O34">
         <v>0.25</v>
       </c>
-      <c r="T34">
-        <v>12003400001</v>
-      </c>
-      <c r="U34" s="3">
-        <v>120034000010000</v>
-      </c>
-      <c r="V34" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="1:22">
+      <c r="V34">
+        <v>12003200001</v>
+      </c>
+      <c r="W34" s="3">
+        <v>120032000010000</v>
+      </c>
+      <c r="X34" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" spans="1:24">
       <c r="A35">
-        <v>12010100001</v>
+        <v>12003300001</v>
       </c>
       <c r="C35">
         <v>12</v>
@@ -2779,28 +2822,34 @@
       <c r="D35">
         <v>3</v>
       </c>
-      <c r="F35" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>87</v>
+      <c r="H35" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="J35" t="s">
-        <v>88</v>
-      </c>
-      <c r="T35">
-        <v>12010100001</v>
-      </c>
-      <c r="U35" s="3">
-        <v>120101000010000</v>
-      </c>
-      <c r="V35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:22">
+        <v>68</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O35">
+        <v>0.25</v>
+      </c>
+      <c r="V35">
+        <v>12003300001</v>
+      </c>
+      <c r="W35" s="3">
+        <v>120033000010000</v>
+      </c>
+      <c r="X35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" spans="1:24">
       <c r="A36">
-        <v>12010200001</v>
+        <v>12003400001</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -2808,28 +2857,34 @@
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="F36" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>93</v>
+      <c r="H36" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="J36" t="s">
-        <v>94</v>
-      </c>
-      <c r="T36">
-        <v>12010200001</v>
-      </c>
-      <c r="U36" s="3">
-        <v>120102000010000</v>
-      </c>
-      <c r="V36" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" spans="1:22">
+        <v>71</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="O36">
+        <v>0.25</v>
+      </c>
+      <c r="V36">
+        <v>12003400001</v>
+      </c>
+      <c r="W36" s="3">
+        <v>120034000010000</v>
+      </c>
+      <c r="X36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:24">
       <c r="A37">
-        <v>12010300001</v>
+        <v>12010100001</v>
       </c>
       <c r="C37">
         <v>12</v>
@@ -2837,28 +2892,28 @@
       <c r="D37">
         <v>3</v>
       </c>
-      <c r="F37" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="G37" s="12" t="s">
+      <c r="H37" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I37" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="J37" t="s">
-        <v>106</v>
-      </c>
-      <c r="T37">
-        <v>12010300001</v>
-      </c>
-      <c r="U37" s="3">
-        <v>120103000010000</v>
-      </c>
-      <c r="V37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" spans="1:22">
+      <c r="L37" t="s">
+        <v>94</v>
+      </c>
+      <c r="V37">
+        <v>12010100001</v>
+      </c>
+      <c r="W37" s="3">
+        <v>120101000010000</v>
+      </c>
+      <c r="X37" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" spans="1:24">
       <c r="A38">
-        <v>12011100001</v>
+        <v>12010200001</v>
       </c>
       <c r="C38">
         <v>12</v>
@@ -2866,28 +2921,28 @@
       <c r="D38">
         <v>3</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="H38" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="T38">
-        <v>12011100001</v>
-      </c>
-      <c r="U38" s="3">
-        <v>120111000010000</v>
-      </c>
-      <c r="V38" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" spans="1:22">
+      <c r="I38" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L38" t="s">
+        <v>100</v>
+      </c>
+      <c r="V38">
+        <v>12010200001</v>
+      </c>
+      <c r="W38" s="3">
+        <v>120102000010000</v>
+      </c>
+      <c r="X38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" ht="14.25" spans="1:24">
       <c r="A39">
-        <v>12011200001</v>
+        <v>12010300001</v>
       </c>
       <c r="C39">
         <v>12</v>
@@ -2895,28 +2950,28 @@
       <c r="D39">
         <v>3</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G39" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="J39" t="s">
-        <v>111</v>
-      </c>
-      <c r="T39">
-        <v>12011200001</v>
-      </c>
-      <c r="U39" s="3">
-        <v>120112000010000</v>
-      </c>
-      <c r="V39" t="s">
+      <c r="H39" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L39" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="40" ht="14.25" spans="1:22">
+      <c r="V39">
+        <v>12010300001</v>
+      </c>
+      <c r="W39" s="3">
+        <v>120103000010000</v>
+      </c>
+      <c r="X39" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" spans="1:24">
       <c r="A40">
-        <v>12011300001</v>
+        <v>12011100001</v>
       </c>
       <c r="C40">
         <v>12</v>
@@ -2924,88 +2979,86 @@
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="G40" s="12" t="s">
+      <c r="H40" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I40" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="J40" t="s">
-        <v>113</v>
-      </c>
-      <c r="T40">
+      <c r="L40" t="s">
+        <v>115</v>
+      </c>
+      <c r="V40">
+        <v>12011100001</v>
+      </c>
+      <c r="W40" s="3">
+        <v>120111000010000</v>
+      </c>
+      <c r="X40" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" spans="1:24">
+      <c r="A41">
+        <v>12011200001</v>
+      </c>
+      <c r="C41">
+        <v>12</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L41" t="s">
+        <v>117</v>
+      </c>
+      <c r="V41">
+        <v>12011200001</v>
+      </c>
+      <c r="W41" s="3">
+        <v>120112000010000</v>
+      </c>
+      <c r="X41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" spans="1:24">
+      <c r="A42">
         <v>12011300001</v>
       </c>
-      <c r="U40" s="3">
+      <c r="C42">
+        <v>12</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="L42" t="s">
+        <v>119</v>
+      </c>
+      <c r="V42">
+        <v>12011300001</v>
+      </c>
+      <c r="W42" s="3">
         <v>120113000010000</v>
       </c>
-      <c r="V40" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" spans="1:22">
-      <c r="A41">
+      <c r="X42" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" spans="1:24">
+      <c r="A43">
         <v>13000100001</v>
-      </c>
-      <c r="C41">
-        <v>13</v>
-      </c>
-      <c r="D41">
-        <v>4</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="4"/>
-      <c r="K41">
-        <v>2</v>
-      </c>
-      <c r="R41">
-        <v>3</v>
-      </c>
-      <c r="T41">
-        <v>13000100001</v>
-      </c>
-      <c r="U41" s="3">
-        <v>130001000010000</v>
-      </c>
-      <c r="V41" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" spans="1:22">
-      <c r="A42">
-        <v>13000300001</v>
-      </c>
-      <c r="C42">
-        <v>13</v>
-      </c>
-      <c r="D42">
-        <v>4</v>
-      </c>
-      <c r="F42" t="s">
-        <v>117</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H42" s="10"/>
-      <c r="S42">
-        <v>500001</v>
-      </c>
-      <c r="T42">
-        <v>13000300001</v>
-      </c>
-      <c r="U42" s="3">
-        <v>130003000010000</v>
-      </c>
-      <c r="V42" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" spans="1:22">
-      <c r="A43">
-        <v>13000400001</v>
       </c>
       <c r="C43">
         <v>13</v>
@@ -3013,31 +3066,29 @@
       <c r="D43">
         <v>4</v>
       </c>
-      <c r="F43" t="s">
-        <v>120</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H43">
-        <v>300001</v>
-      </c>
+      <c r="H43" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="I43" s="4"/>
       <c r="M43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43">
-        <v>13000400001</v>
-      </c>
-      <c r="U43" s="3">
-        <v>130004000010000</v>
-      </c>
-      <c r="V43" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" spans="1:22">
+        <v>3</v>
+      </c>
+      <c r="V43">
+        <v>13000100001</v>
+      </c>
+      <c r="W43" s="3">
+        <v>130001000010000</v>
+      </c>
+      <c r="X43" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" spans="1:24">
       <c r="A44">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="C44">
         <v>13</v>
@@ -3045,34 +3096,29 @@
       <c r="D44">
         <v>4</v>
       </c>
-      <c r="F44" t="s">
-        <v>122</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" s="10">
-        <v>1</v>
-      </c>
-      <c r="M44">
-        <v>0.05</v>
-      </c>
-      <c r="N44">
-        <v>0.01</v>
-      </c>
-      <c r="T44">
-        <v>13000500001</v>
-      </c>
-      <c r="U44" s="3">
-        <v>130005000010000</v>
-      </c>
-      <c r="V44" t="s">
+      <c r="H44" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="45" ht="14.25" spans="1:22">
+      <c r="I44" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J44" s="10"/>
+      <c r="U44">
+        <v>500001</v>
+      </c>
+      <c r="V44">
+        <v>13000300001</v>
+      </c>
+      <c r="W44" s="3">
+        <v>130003000010000</v>
+      </c>
+      <c r="X44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="45" ht="14.25" spans="1:24">
       <c r="A45">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="C45">
         <v>13</v>
@@ -3080,34 +3126,31 @@
       <c r="D45">
         <v>4</v>
       </c>
-      <c r="F45" t="s">
+      <c r="H45" t="s">
+        <v>126</v>
+      </c>
+      <c r="I45" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="H45" s="10">
+      <c r="J45">
+        <v>300001</v>
+      </c>
+      <c r="O45">
         <v>1</v>
       </c>
-      <c r="M45">
-        <v>0.05</v>
-      </c>
-      <c r="N45">
-        <v>0.01</v>
-      </c>
-      <c r="T45">
-        <v>13000600001</v>
-      </c>
-      <c r="U45" s="3">
-        <v>130006000010000</v>
-      </c>
-      <c r="V45" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" ht="14.25" spans="1:22">
+      <c r="V45">
+        <v>13000400001</v>
+      </c>
+      <c r="W45" s="3">
+        <v>130004000010000</v>
+      </c>
+      <c r="X45" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" ht="14.25" spans="1:24">
       <c r="A46">
-        <v>13000700001</v>
+        <v>13000500001</v>
       </c>
       <c r="C46">
         <v>13</v>
@@ -3115,28 +3158,96 @@
       <c r="D46">
         <v>4</v>
       </c>
-      <c r="F46" t="s">
-        <v>126</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>118</v>
+      <c r="H46" t="s">
+        <v>128</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J46" s="10">
+        <v>1</v>
       </c>
       <c r="O46">
+        <v>0.05</v>
+      </c>
+      <c r="P46">
+        <v>0.01</v>
+      </c>
+      <c r="V46">
+        <v>13000500001</v>
+      </c>
+      <c r="W46" s="3">
+        <v>130005000010000</v>
+      </c>
+      <c r="X46" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="47" ht="14.25" spans="1:24">
+      <c r="A47">
+        <v>13000600001</v>
+      </c>
+      <c r="C47">
+        <v>13</v>
+      </c>
+      <c r="D47">
+        <v>4</v>
+      </c>
+      <c r="H47" t="s">
+        <v>130</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="J47" s="10">
+        <v>1</v>
+      </c>
+      <c r="O47">
+        <v>0.05</v>
+      </c>
+      <c r="P47">
+        <v>0.01</v>
+      </c>
+      <c r="V47">
+        <v>13000600001</v>
+      </c>
+      <c r="W47" s="3">
+        <v>130006000010000</v>
+      </c>
+      <c r="X47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A48">
+        <v>13000700001</v>
+      </c>
+      <c r="C48">
+        <v>13</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="H48" t="s">
+        <v>132</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q48">
         <v>0.2</v>
       </c>
-      <c r="P46"/>
-      <c r="T46">
+      <c r="R48"/>
+      <c r="V48">
         <v>13000700001</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W48" s="3">
         <v>130007000010000</v>
       </c>
-      <c r="V46" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1"/>
-    <row r="48" ht="15" customHeight="1"/>
+      <c r="X48" t="s">
+        <v>133</v>
+      </c>
+    </row>
     <row r="49" ht="15" customHeight="1"/>
     <row r="50" ht="15" customHeight="1"/>
     <row r="51" ht="15" customHeight="1"/>
@@ -3146,8 +3257,8 @@
     <row r="55" ht="15" customHeight="1"/>
     <row r="56" ht="15" customHeight="1"/>
     <row r="57" ht="15" customHeight="1"/>
-    <row r="89" ht="12" customHeight="1"/>
-    <row r="90" ht="12" customHeight="1"/>
+    <row r="58" ht="15" customHeight="1"/>
+    <row r="59" ht="15" customHeight="1"/>
     <row r="91" ht="12" customHeight="1"/>
     <row r="92" ht="12" customHeight="1"/>
     <row r="93" ht="12" customHeight="1"/>
@@ -3155,8 +3266,10 @@
     <row r="95" ht="12" customHeight="1"/>
     <row r="96" ht="12" customHeight="1"/>
     <row r="97" ht="12" customHeight="1"/>
+    <row r="98" ht="12" customHeight="1"/>
+    <row r="99" ht="12" customHeight="1"/>
   </sheetData>
-  <sortState ref="A4:AE88">
+  <sortState ref="A4:AG88">
     <sortCondition ref="A4"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="BuffInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="140">
   <si>
     <t>id</t>
   </si>
@@ -215,7 +215,28 @@
     <t>中毒</t>
   </si>
   <si>
-    <t>烧伤</t>
+    <t>#A92F2C</t>
+  </si>
+  <si>
+    <t>烧伤-每隔3秒扣除血量</t>
+  </si>
+  <si>
+    <t>ATK</t>
+  </si>
+  <si>
+    <t>#00BEDB</t>
+  </si>
+  <si>
+    <t>潮湿-减少攻击力</t>
+  </si>
+  <si>
+    <t>BuffEntityAttributeAttackTime</t>
+  </si>
+  <si>
+    <t>#DDFFFF</t>
+  </si>
+  <si>
+    <t>冰冻-减速</t>
   </si>
   <si>
     <t>EVA</t>
@@ -231,9 +252,6 @@
   </si>
   <si>
     <t>BuffEntityConditionalAttribute</t>
-  </si>
-  <si>
-    <t>ATK</t>
   </si>
   <si>
     <t>1001:0.5&amp;</t>
@@ -442,10 +460,17 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -458,8 +483,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color theme="4"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="8"/>
+      <color theme="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -469,33 +506,6 @@
       <color rgb="FF4EC9B0"/>
       <name val="Consolas"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="8"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="6"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -511,12 +521,6 @@
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FFFF0000"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
       <color theme="6"/>
       <name val="Consolas"/>
       <charset val="134"/>
@@ -524,12 +528,6 @@
     <font>
       <sz val="10.5"/>
       <color rgb="FFC00000"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color theme="4"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
@@ -998,133 +996,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1138,26 +1136,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="47" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1165,16 +1169,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1525,12 +1523,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X99"/>
+  <dimension ref="A1:X101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24.25" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="31.5" customWidth="1"/>
+    <col min="3" max="3" width="61.125" customWidth="1"/>
     <col min="4" max="5" width="21.25" customWidth="1"/>
     <col min="6" max="6" width="27.25" customWidth="1"/>
     <col min="7" max="7" width="51.875" customWidth="1"/>
@@ -1590,19 +1588,19 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
@@ -1664,19 +1662,19 @@
       <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O2" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="Q2" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>27</v>
       </c>
       <c r="S2" t="s">
@@ -1738,19 +1736,19 @@
       <c r="M3" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="2" t="s">
         <v>41</v>
       </c>
       <c r="O3" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" s="2" t="s">
         <v>43</v>
       </c>
       <c r="Q3" t="s">
         <v>44</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" s="2" t="s">
         <v>45</v>
       </c>
       <c r="S3" t="s">
@@ -1772,368 +1770,436 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
-      <c r="A4">
+    <row r="4" s="1" customFormat="1" spans="1:24">
+      <c r="A4" s="1">
         <v>1000100001</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="2"/>
-      <c r="J4" t="s">
+      <c r="I4" s="1"/>
+      <c r="J4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="1">
         <v>-0.5</v>
       </c>
-      <c r="S4">
+      <c r="S4" s="1">
         <v>1</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="1">
         <v>10</v>
       </c>
-      <c r="V4">
+      <c r="V4" s="1">
         <v>1000100001</v>
       </c>
       <c r="W4" s="3">
         <v>10001000010000</v>
       </c>
-      <c r="X4" t="s">
+      <c r="X4" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
-      <c r="A5">
+    <row r="5" s="1" customFormat="1" spans="1:24">
+      <c r="A5" s="1">
         <v>1000200001</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="2"/>
-      <c r="J5" t="s">
+      <c r="I5" s="1"/>
+      <c r="J5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="1">
         <v>-0.2</v>
       </c>
-      <c r="S5">
+      <c r="S5" s="1">
         <v>1</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="1">
         <v>1</v>
       </c>
-      <c r="V5">
+      <c r="V5" s="1">
         <v>1000200001</v>
       </c>
       <c r="W5" s="3">
         <v>10002000010000</v>
       </c>
-      <c r="X5" t="s">
+      <c r="X5" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:24">
-      <c r="A6">
+    <row r="6" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A6" s="1">
         <v>1000300001</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="5"/>
-      <c r="S6">
+      <c r="I6" s="4"/>
+      <c r="S6" s="1">
         <v>1</v>
       </c>
-      <c r="V6">
+      <c r="V6" s="1">
         <v>1000300001</v>
       </c>
       <c r="W6" s="3">
         <v>10003000010000</v>
       </c>
-      <c r="X6" t="s">
+      <c r="X6" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:24">
-      <c r="A7">
+    <row r="7" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A7" s="1">
         <v>1000400001</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="5"/>
-      <c r="K7" t="s">
+      <c r="I7" s="4"/>
+      <c r="K7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M7">
-        <v>-100</v>
-      </c>
-      <c r="S7">
-        <v>5</v>
-      </c>
-      <c r="T7">
-        <v>3</v>
-      </c>
-      <c r="V7">
+      <c r="O7" s="1">
+        <v>-0.01</v>
+      </c>
+      <c r="S7" s="1">
+        <v>10</v>
+      </c>
+      <c r="T7" s="1">
+        <v>1</v>
+      </c>
+      <c r="V7" s="1">
         <v>1000400001</v>
       </c>
       <c r="W7" s="3">
         <v>10004000010000</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X7" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:24">
-      <c r="A8">
+    <row r="8" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A8" s="1">
         <v>1000500001</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>1</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="M8">
-        <v>-100</v>
-      </c>
-      <c r="S8">
+      <c r="I8" s="4"/>
+      <c r="K8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O8" s="1">
+        <v>-0.05</v>
+      </c>
+      <c r="S8" s="1">
         <v>3</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="1">
         <v>3</v>
       </c>
-      <c r="V8">
+      <c r="V8" s="1">
         <v>1000500001</v>
       </c>
       <c r="W8" s="3">
         <v>10005000010000</v>
       </c>
-      <c r="X8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
-      <c r="A9">
+      <c r="X8" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A9" s="1">
+        <v>1000600001</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="1">
+        <v>-0.1</v>
+      </c>
+      <c r="T9" s="1">
+        <v>10</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1000600001</v>
+      </c>
+      <c r="W9" s="3">
+        <v>10006000010000</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A10" s="1">
+        <v>1000700001</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" s="1">
+        <v>2</v>
+      </c>
+      <c r="T10" s="1">
+        <v>5</v>
+      </c>
+      <c r="V10" s="1">
+        <v>1000700001</v>
+      </c>
+      <c r="W10" s="3">
+        <v>10007000010000</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" s="2">
         <v>2000100001</v>
       </c>
-      <c r="C9">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2">
         <v>2</v>
       </c>
-      <c r="D9">
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="6"/>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-      <c r="O9">
+      <c r="I11" s="2"/>
+      <c r="J11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2">
         <v>0.5</v>
       </c>
-      <c r="V9">
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2">
         <v>2000100001</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W11" s="5">
         <v>20001000010000</v>
       </c>
-      <c r="X9" t="s">
+      <c r="X11" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" s="2">
+        <v>2000200001</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2">
+        <v>2000200001</v>
+      </c>
+      <c r="W12" s="5">
+        <v>20002000010000</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:24">
+      <c r="A13" s="2">
+        <v>2000300001</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:24">
-      <c r="A10">
-        <v>2000200001</v>
-      </c>
-      <c r="C10">
+      <c r="K13" s="2"/>
+      <c r="L13" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2">
+        <v>2000300001</v>
+      </c>
+      <c r="W13" s="5">
+        <v>20003000010000</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" spans="1:24">
+      <c r="A14" s="2">
+        <v>2000400001</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2">
         <v>2</v>
       </c>
-      <c r="D10">
+      <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="H10" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="6"/>
-      <c r="J10" t="s">
-        <v>65</v>
-      </c>
-      <c r="O10">
-        <v>0.5</v>
-      </c>
-      <c r="V10">
-        <v>2000200001</v>
-      </c>
-      <c r="W10" s="3">
-        <v>20002000010000</v>
-      </c>
-      <c r="X10" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="1:24">
-      <c r="A11">
-        <v>2000300001</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="6"/>
-      <c r="J11" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="O11">
-        <v>0.5</v>
-      </c>
-      <c r="V11">
-        <v>2000300001</v>
-      </c>
-      <c r="W11" s="3">
-        <v>20003000010000</v>
-      </c>
-      <c r="X11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:24">
-      <c r="A12">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2">
         <v>2000400001</v>
       </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I12" s="6"/>
-      <c r="J12" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="O12">
-        <v>-0.5</v>
-      </c>
-      <c r="V12">
-        <v>2000400001</v>
-      </c>
-      <c r="W12" s="3">
+      <c r="W14" s="5">
         <v>20004000010000</v>
       </c>
-      <c r="X12" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
-      <c r="A13">
-        <v>3000100001</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="8"/>
-      <c r="V13">
-        <v>3000100001</v>
-      </c>
-      <c r="W13" s="3">
-        <v>30001000010000</v>
-      </c>
-      <c r="X13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
-      <c r="A14">
-        <v>3000200001</v>
-      </c>
-      <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>3000200001</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I14" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q14">
-        <v>0.1</v>
-      </c>
-      <c r="V14">
-        <v>3000200001</v>
-      </c>
-      <c r="W14" s="3">
-        <v>30002000010000</v>
-      </c>
-      <c r="X14" t="s">
-        <v>77</v>
+      <c r="X14" s="2" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15">
-        <v>3000200002</v>
+        <v>3000100001</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -2141,34 +2207,23 @@
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="E15">
-        <v>3000200002</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
       <c r="H15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I15" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q15">
-        <v>0.2</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="I15" s="8"/>
       <c r="V15">
-        <v>3000200002</v>
-      </c>
-      <c r="W15" s="3">
-        <v>30002000020000</v>
+        <v>3000100001</v>
+      </c>
+      <c r="W15" s="9">
+        <v>30001000010000</v>
       </c>
       <c r="X15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:24">
       <c r="A16">
-        <v>3000200003</v>
+        <v>3000200001</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2177,33 +2232,33 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>3000200003</v>
+        <v>3000200001</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I16" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="Q16">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="V16">
-        <v>3000200003</v>
-      </c>
-      <c r="W16" s="3">
-        <v>30002000030000</v>
+        <v>3000200001</v>
+      </c>
+      <c r="W16" s="9">
+        <v>30002000010000</v>
       </c>
       <c r="X16" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:24">
       <c r="A17">
-        <v>3000300001</v>
+        <v>3000200002</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -2211,32 +2266,34 @@
       <c r="D17">
         <v>1</v>
       </c>
-      <c r="G17">
-        <v>1</v>
+      <c r="E17">
+        <v>3000200002</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="8"/>
-      <c r="J17" t="s">
-        <v>80</v>
-      </c>
-      <c r="O17">
-        <v>0.1</v>
+        <v>81</v>
+      </c>
+      <c r="I17" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q17">
+        <v>0.2</v>
       </c>
       <c r="V17">
-        <v>3000300001</v>
-      </c>
-      <c r="W17" s="3">
-        <v>30003000010000</v>
+        <v>3000200002</v>
+      </c>
+      <c r="W17" s="9">
+        <v>30002000020000</v>
       </c>
       <c r="X17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:24">
       <c r="A18">
-        <v>3000400001</v>
+        <v>3000200003</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -2244,200 +2301,196 @@
       <c r="D18">
         <v>1</v>
       </c>
+      <c r="E18">
+        <v>3000200003</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
       <c r="H18" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="I18" s="8"/>
-      <c r="J18" t="s">
+        <v>81</v>
+      </c>
+      <c r="I18" t="s">
         <v>82</v>
       </c>
-      <c r="O18">
-        <v>-0.1</v>
+      <c r="Q18">
+        <v>0.3</v>
       </c>
       <c r="V18">
-        <v>3000400001</v>
-      </c>
-      <c r="W18" s="3">
-        <v>30004000010000</v>
+        <v>3000200003</v>
+      </c>
+      <c r="W18" s="9">
+        <v>30002000030000</v>
       </c>
       <c r="X18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:24">
       <c r="A19">
-        <v>11000100001</v>
+        <v>3000300001</v>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="H19" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="9"/>
+      <c r="I19" s="8"/>
       <c r="J19" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="O19">
-        <v>0.2</v>
-      </c>
-      <c r="P19">
         <v>0.1</v>
       </c>
       <c r="V19">
-        <v>11000100001</v>
-      </c>
-      <c r="W19" s="3">
-        <v>110001000010000</v>
+        <v>3000300001</v>
+      </c>
+      <c r="W19" s="9">
+        <v>30003000010000</v>
       </c>
       <c r="X19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:24">
       <c r="A20">
+        <v>3000400001</v>
+      </c>
+      <c r="C20">
+        <v>3</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="8"/>
+      <c r="J20" t="s">
+        <v>88</v>
+      </c>
+      <c r="O20">
+        <v>-0.1</v>
+      </c>
+      <c r="V20">
+        <v>3000400001</v>
+      </c>
+      <c r="W20" s="9">
+        <v>30004000010000</v>
+      </c>
+      <c r="X20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:24">
+      <c r="A21" s="2">
+        <v>11000100001</v>
+      </c>
+      <c r="C21" s="2">
+        <v>11</v>
+      </c>
+      <c r="D21" s="2">
+        <v>2</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="V21" s="2">
+        <v>11000100001</v>
+      </c>
+      <c r="W21" s="5">
+        <v>110001000010000</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:24">
+      <c r="A22" s="2">
         <v>11000200001</v>
       </c>
-      <c r="C20">
+      <c r="C22" s="2">
         <v>11</v>
       </c>
-      <c r="D20">
+      <c r="D22" s="2">
         <v>2</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="J20" t="s">
-        <v>85</v>
-      </c>
-      <c r="O20">
+      <c r="I22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="O22" s="2">
         <v>0.2</v>
       </c>
-      <c r="P20">
+      <c r="P22" s="2">
         <v>0.1</v>
       </c>
-      <c r="V20">
+      <c r="V22" s="2">
         <v>11000200001</v>
       </c>
-      <c r="W20" s="3">
+      <c r="W22" s="5">
         <v>110002000010000</v>
       </c>
-      <c r="X20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24">
-      <c r="A21">
+      <c r="X22" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:24">
+      <c r="A23" s="2">
         <v>11000300001</v>
       </c>
-      <c r="C21">
+      <c r="C23" s="2">
         <v>11</v>
       </c>
-      <c r="D21">
+      <c r="D23" s="2">
         <v>2</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H23" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="J21" t="s">
-        <v>68</v>
-      </c>
-      <c r="O21">
+      <c r="I23" s="2"/>
+      <c r="J23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O23" s="2">
         <v>0.2</v>
       </c>
-      <c r="P21">
+      <c r="P23" s="2">
         <v>0.1</v>
       </c>
-      <c r="V21">
+      <c r="V23" s="2">
         <v>11000300001</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W23" s="5">
         <v>110003000010000</v>
       </c>
-      <c r="X21" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" ht="13" customHeight="1" spans="1:24">
-      <c r="A22">
+      <c r="X23" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1" spans="1:24">
+      <c r="A24">
         <v>12000100001</v>
-      </c>
-      <c r="C22">
-        <v>12</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I22" s="4"/>
-      <c r="O22">
-        <v>0.05</v>
-      </c>
-      <c r="P22">
-        <v>0.01</v>
-      </c>
-      <c r="T22">
-        <v>5</v>
-      </c>
-      <c r="U22">
-        <v>500001</v>
-      </c>
-      <c r="V22">
-        <v>12000100001</v>
-      </c>
-      <c r="W22" s="3">
-        <v>120001000010000</v>
-      </c>
-      <c r="X22" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="1:24">
-      <c r="A23">
-        <v>12000200001</v>
-      </c>
-      <c r="C23">
-        <v>12</v>
-      </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="O23">
-        <v>0.05</v>
-      </c>
-      <c r="P23">
-        <v>0.01</v>
-      </c>
-      <c r="T23">
-        <v>5</v>
-      </c>
-      <c r="U23">
-        <v>500002</v>
-      </c>
-      <c r="V23">
-        <v>12000200001</v>
-      </c>
-      <c r="W23" s="3">
-        <v>120002000010000</v>
-      </c>
-      <c r="X23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" spans="1:24">
-      <c r="A24">
-        <v>12000300001</v>
       </c>
       <c r="C24">
         <v>12</v>
@@ -2445,26 +2498,35 @@
       <c r="D24">
         <v>3</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I24" s="4"/>
+      <c r="H24" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" s="10"/>
+      <c r="O24">
+        <v>0.05</v>
+      </c>
+      <c r="P24">
+        <v>0.01</v>
+      </c>
       <c r="T24">
         <v>5</v>
       </c>
+      <c r="U24">
+        <v>500001</v>
+      </c>
       <c r="V24">
-        <v>12000300001</v>
-      </c>
-      <c r="W24" s="3">
-        <v>120003000010000</v>
+        <v>12000100001</v>
+      </c>
+      <c r="W24" s="9">
+        <v>120001000010000</v>
       </c>
       <c r="X24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="1:24">
       <c r="A25">
-        <v>12001100001</v>
+        <v>12000200001</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -2472,34 +2534,35 @@
       <c r="D25">
         <v>3</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J25" t="s">
-        <v>80</v>
-      </c>
-      <c r="L25" t="s">
-        <v>94</v>
-      </c>
+      <c r="H25" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="I25" s="10"/>
       <c r="O25">
-        <v>0.25</v>
+        <v>0.05</v>
+      </c>
+      <c r="P25">
+        <v>0.01</v>
+      </c>
+      <c r="T25">
+        <v>5</v>
+      </c>
+      <c r="U25">
+        <v>500002</v>
       </c>
       <c r="V25">
-        <v>12001100001</v>
-      </c>
-      <c r="W25" s="3">
-        <v>120011000010000</v>
+        <v>12000200001</v>
+      </c>
+      <c r="W25" s="9">
+        <v>120002000010000</v>
       </c>
       <c r="X25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="14.25" spans="1:24">
       <c r="A26">
-        <v>12001200001</v>
+        <v>12000300001</v>
       </c>
       <c r="C26">
         <v>12</v>
@@ -2507,34 +2570,26 @@
       <c r="D26">
         <v>3</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="J26" t="s">
-        <v>85</v>
-      </c>
-      <c r="L26" t="s">
-        <v>94</v>
-      </c>
-      <c r="O26">
-        <v>0.25</v>
+      <c r="H26" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="I26" s="10"/>
+      <c r="T26">
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>12001200001</v>
-      </c>
-      <c r="W26" s="3">
-        <v>120012000010000</v>
+        <v>12000300001</v>
+      </c>
+      <c r="W26" s="9">
+        <v>120003000010000</v>
       </c>
       <c r="X26" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="1:24">
       <c r="A27">
-        <v>12001300001</v>
+        <v>12001100001</v>
       </c>
       <c r="C27">
         <v>12</v>
@@ -2542,34 +2597,34 @@
       <c r="D27">
         <v>3</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>93</v>
+      <c r="H27" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="J27" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="L27" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>0.25</v>
       </c>
       <c r="V27">
-        <v>12001300001</v>
-      </c>
-      <c r="W27" s="3">
-        <v>120013000010000</v>
+        <v>12001100001</v>
+      </c>
+      <c r="W27" s="9">
+        <v>120011000010000</v>
       </c>
       <c r="X27" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" ht="14.25" spans="1:24">
       <c r="A28">
-        <v>12001400001</v>
+        <v>12001200001</v>
       </c>
       <c r="C28">
         <v>12</v>
@@ -2577,34 +2632,34 @@
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="H28" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>93</v>
+      <c r="H28" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>99</v>
       </c>
       <c r="J28" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="L28" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="O28">
         <v>0.25</v>
       </c>
       <c r="V28">
-        <v>12001400001</v>
-      </c>
-      <c r="W28" s="3">
-        <v>120014000010000</v>
+        <v>12001200001</v>
+      </c>
+      <c r="W28" s="9">
+        <v>120012000010000</v>
       </c>
       <c r="X28" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="1:24">
       <c r="A29">
-        <v>12002100001</v>
+        <v>12001300001</v>
       </c>
       <c r="C29">
         <v>12</v>
@@ -2612,14 +2667,14 @@
       <c r="D29">
         <v>3</v>
       </c>
-      <c r="H29" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I29" s="12" t="s">
+      <c r="H29" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>99</v>
       </c>
       <c r="J29" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="L29" t="s">
         <v>100</v>
@@ -2628,18 +2683,18 @@
         <v>0.25</v>
       </c>
       <c r="V29">
-        <v>12002100001</v>
-      </c>
-      <c r="W29" s="3">
-        <v>120021000010000</v>
+        <v>12001300001</v>
+      </c>
+      <c r="W29" s="9">
+        <v>120013000010000</v>
       </c>
       <c r="X29" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" ht="14.25" spans="1:24">
       <c r="A30">
-        <v>12002200001</v>
+        <v>12001400001</v>
       </c>
       <c r="C30">
         <v>12</v>
@@ -2647,14 +2702,14 @@
       <c r="D30">
         <v>3</v>
       </c>
-      <c r="H30" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I30" s="12" t="s">
+      <c r="H30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>99</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="L30" t="s">
         <v>100</v>
@@ -2663,18 +2718,18 @@
         <v>0.25</v>
       </c>
       <c r="V30">
-        <v>12002200001</v>
-      </c>
-      <c r="W30" s="3">
-        <v>120022000010000</v>
+        <v>12001400001</v>
+      </c>
+      <c r="W30" s="9">
+        <v>120014000010000</v>
       </c>
       <c r="X30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="1:24">
       <c r="A31">
-        <v>12002300001</v>
+        <v>12002100001</v>
       </c>
       <c r="C31">
         <v>12</v>
@@ -2682,34 +2737,34 @@
       <c r="D31">
         <v>3</v>
       </c>
-      <c r="H31" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I31" s="12" t="s">
-        <v>99</v>
+      <c r="H31" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="J31" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="L31" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="O31">
         <v>0.25</v>
       </c>
       <c r="V31">
-        <v>12002300001</v>
-      </c>
-      <c r="W31" s="3">
-        <v>120023000010000</v>
+        <v>12002100001</v>
+      </c>
+      <c r="W31" s="9">
+        <v>120021000010000</v>
       </c>
       <c r="X31" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" ht="14.25" spans="1:24">
       <c r="A32">
-        <v>12002400001</v>
+        <v>12002200001</v>
       </c>
       <c r="C32">
         <v>12</v>
@@ -2717,34 +2772,34 @@
       <c r="D32">
         <v>3</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>99</v>
+      <c r="H32" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="J32" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="L32" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="O32">
         <v>0.25</v>
       </c>
       <c r="V32">
-        <v>12002400001</v>
-      </c>
-      <c r="W32" s="3">
-        <v>120024000010000</v>
+        <v>12002200001</v>
+      </c>
+      <c r="W32" s="9">
+        <v>120022000010000</v>
       </c>
       <c r="X32" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="1:24">
       <c r="A33">
-        <v>12003100001</v>
+        <v>12002300001</v>
       </c>
       <c r="C33">
         <v>12</v>
@@ -2752,34 +2807,34 @@
       <c r="D33">
         <v>3</v>
       </c>
-      <c r="H33" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>99</v>
+      <c r="H33" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="J33" t="s">
-        <v>80</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
+      </c>
+      <c r="L33" t="s">
+        <v>106</v>
       </c>
       <c r="O33">
         <v>0.25</v>
       </c>
       <c r="V33">
-        <v>12003100001</v>
-      </c>
-      <c r="W33" s="3">
-        <v>120031000010000</v>
+        <v>12002300001</v>
+      </c>
+      <c r="W33" s="9">
+        <v>120023000010000</v>
       </c>
       <c r="X33" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" ht="14.25" spans="1:24">
       <c r="A34">
-        <v>12003200001</v>
+        <v>12002400001</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -2787,34 +2842,34 @@
       <c r="D34">
         <v>3</v>
       </c>
-      <c r="H34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>99</v>
+      <c r="H34" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="J34" t="s">
-        <v>85</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>69</v>
+        <v>77</v>
+      </c>
+      <c r="L34" t="s">
+        <v>106</v>
       </c>
       <c r="O34">
         <v>0.25</v>
       </c>
       <c r="V34">
-        <v>12003200001</v>
-      </c>
-      <c r="W34" s="3">
-        <v>120032000010000</v>
+        <v>12002400001</v>
+      </c>
+      <c r="W34" s="9">
+        <v>120024000010000</v>
       </c>
       <c r="X34" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" ht="14.25" spans="1:24">
       <c r="A35">
-        <v>12003300001</v>
+        <v>12003100001</v>
       </c>
       <c r="C35">
         <v>12</v>
@@ -2822,34 +2877,34 @@
       <c r="D35">
         <v>3</v>
       </c>
-      <c r="H35" s="4" t="s">
-        <v>67</v>
+      <c r="H35" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J35" t="s">
-        <v>68</v>
-      </c>
-      <c r="L35" s="7" t="s">
-        <v>69</v>
+        <v>86</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="O35">
         <v>0.25</v>
       </c>
       <c r="V35">
-        <v>12003300001</v>
-      </c>
-      <c r="W35" s="3">
-        <v>120033000010000</v>
+        <v>12003100001</v>
+      </c>
+      <c r="W35" s="9">
+        <v>120031000010000</v>
       </c>
       <c r="X35" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" ht="14.25" spans="1:24">
       <c r="A36">
-        <v>12003400001</v>
+        <v>12003200001</v>
       </c>
       <c r="C36">
         <v>12</v>
@@ -2857,34 +2912,34 @@
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="H36" s="4" t="s">
-        <v>67</v>
+      <c r="H36" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J36" t="s">
-        <v>71</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>69</v>
+        <v>91</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="O36">
         <v>0.25</v>
       </c>
       <c r="V36">
-        <v>12003400001</v>
-      </c>
-      <c r="W36" s="3">
-        <v>120034000010000</v>
+        <v>12003200001</v>
+      </c>
+      <c r="W36" s="9">
+        <v>120032000010000</v>
       </c>
       <c r="X36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:24">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" spans="1:24">
       <c r="A37">
-        <v>12010100001</v>
+        <v>12003300001</v>
       </c>
       <c r="C37">
         <v>12</v>
@@ -2892,28 +2947,34 @@
       <c r="D37">
         <v>3</v>
       </c>
-      <c r="H37" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="L37" t="s">
-        <v>94</v>
+      <c r="H37" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I37" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J37" t="s">
+        <v>64</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="O37">
+        <v>0.25</v>
       </c>
       <c r="V37">
-        <v>12010100001</v>
-      </c>
-      <c r="W37" s="3">
-        <v>120101000010000</v>
+        <v>12003300001</v>
+      </c>
+      <c r="W37" s="9">
+        <v>120033000010000</v>
       </c>
       <c r="X37" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" ht="14.25" spans="1:24">
       <c r="A38">
-        <v>12010200001</v>
+        <v>12003400001</v>
       </c>
       <c r="C38">
         <v>12</v>
@@ -2921,28 +2982,34 @@
       <c r="D38">
         <v>3</v>
       </c>
-      <c r="H38" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="L38" t="s">
-        <v>100</v>
+      <c r="H38" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I38" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J38" t="s">
+        <v>77</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="O38">
+        <v>0.25</v>
       </c>
       <c r="V38">
-        <v>12010200001</v>
-      </c>
-      <c r="W38" s="3">
-        <v>120102000010000</v>
+        <v>12003400001</v>
+      </c>
+      <c r="W38" s="9">
+        <v>120034000010000</v>
       </c>
       <c r="X38" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" ht="14.25" spans="1:24">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:24">
       <c r="A39">
-        <v>12010300001</v>
+        <v>12010100001</v>
       </c>
       <c r="C39">
         <v>12</v>
@@ -2951,27 +3018,27 @@
         <v>3</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="I39" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="I39" s="15" t="s">
         <v>99</v>
       </c>
       <c r="L39" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="V39">
-        <v>12010300001</v>
-      </c>
-      <c r="W39" s="3">
-        <v>120103000010000</v>
+        <v>12010100001</v>
+      </c>
+      <c r="W39" s="9">
+        <v>120101000010000</v>
       </c>
       <c r="X39" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" ht="14.25" spans="1:24">
       <c r="A40">
-        <v>12011100001</v>
+        <v>12010200001</v>
       </c>
       <c r="C40">
         <v>12</v>
@@ -2979,28 +3046,28 @@
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>93</v>
+      <c r="H40" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="L40" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="V40">
-        <v>12011100001</v>
-      </c>
-      <c r="W40" s="3">
-        <v>120111000010000</v>
+        <v>12010200001</v>
+      </c>
+      <c r="W40" s="9">
+        <v>120102000010000</v>
       </c>
       <c r="X40" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" ht="14.25" spans="1:24">
       <c r="A41">
-        <v>12011200001</v>
+        <v>12010300001</v>
       </c>
       <c r="C41">
         <v>12</v>
@@ -3008,28 +3075,28 @@
       <c r="D41">
         <v>3</v>
       </c>
-      <c r="H41" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I41" s="12" t="s">
-        <v>99</v>
+      <c r="H41" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="L41" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="V41">
-        <v>12011200001</v>
-      </c>
-      <c r="W41" s="3">
-        <v>120112000010000</v>
+        <v>12010300001</v>
+      </c>
+      <c r="W41" s="9">
+        <v>120103000010000</v>
       </c>
       <c r="X41" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" ht="14.25" spans="1:24">
       <c r="A42">
-        <v>12011300001</v>
+        <v>12011100001</v>
       </c>
       <c r="C42">
         <v>12</v>
@@ -3037,219 +3104,275 @@
       <c r="D42">
         <v>3</v>
       </c>
-      <c r="H42" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I42" s="12" t="s">
+      <c r="H42" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15" t="s">
         <v>99</v>
       </c>
       <c r="L42" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="V42">
-        <v>12011300001</v>
-      </c>
-      <c r="W42" s="3">
-        <v>120113000010000</v>
+        <v>12011100001</v>
+      </c>
+      <c r="W42" s="9">
+        <v>120111000010000</v>
       </c>
       <c r="X42" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43" ht="14.25" spans="1:24">
       <c r="A43">
-        <v>13000100001</v>
+        <v>12011200001</v>
       </c>
       <c r="C43">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43">
-        <v>4</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="I43" s="4"/>
-      <c r="M43">
-        <v>2</v>
-      </c>
-      <c r="T43">
         <v>3</v>
       </c>
+      <c r="H43" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="L43" t="s">
+        <v>123</v>
+      </c>
       <c r="V43">
-        <v>13000100001</v>
-      </c>
-      <c r="W43" s="3">
-        <v>130001000010000</v>
+        <v>12011200001</v>
+      </c>
+      <c r="W43" s="9">
+        <v>120112000010000</v>
       </c>
       <c r="X43" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" ht="14.25" spans="1:24">
       <c r="A44">
+        <v>12011300001</v>
+      </c>
+      <c r="C44">
+        <v>12</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="L44" t="s">
+        <v>125</v>
+      </c>
+      <c r="V44">
+        <v>12011300001</v>
+      </c>
+      <c r="W44" s="9">
+        <v>120113000010000</v>
+      </c>
+      <c r="X44" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A45" s="2">
+        <v>13000100001</v>
+      </c>
+      <c r="C45" s="2">
+        <v>13</v>
+      </c>
+      <c r="D45" s="2">
+        <v>4</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I45" s="6"/>
+      <c r="M45" s="2">
+        <v>2</v>
+      </c>
+      <c r="T45" s="2">
+        <v>3</v>
+      </c>
+      <c r="V45" s="2">
+        <v>13000100001</v>
+      </c>
+      <c r="W45" s="5">
+        <v>130001000010000</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A46" s="2">
         <v>13000300001</v>
       </c>
-      <c r="C44">
+      <c r="C46" s="2">
         <v>13</v>
       </c>
-      <c r="D44">
+      <c r="D46" s="2">
         <v>4</v>
       </c>
-      <c r="H44" t="s">
-        <v>123</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="J44" s="10"/>
-      <c r="U44">
+      <c r="H46" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J46" s="6"/>
+      <c r="U46" s="2">
         <v>500001</v>
       </c>
-      <c r="V44">
+      <c r="V46" s="2">
         <v>13000300001</v>
       </c>
-      <c r="W44" s="3">
+      <c r="W46" s="5">
         <v>130003000010000</v>
       </c>
-      <c r="X44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" ht="14.25" spans="1:24">
-      <c r="A45">
+      <c r="X46" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A47" s="2">
         <v>13000400001</v>
       </c>
-      <c r="C45">
+      <c r="C47" s="2">
         <v>13</v>
       </c>
-      <c r="D45">
+      <c r="D47" s="2">
         <v>4</v>
       </c>
-      <c r="H45" t="s">
-        <v>126</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="J45">
+      <c r="H47" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J47" s="2">
         <v>300001</v>
       </c>
-      <c r="O45">
+      <c r="O47" s="2">
         <v>1</v>
       </c>
-      <c r="V45">
+      <c r="V47" s="2">
         <v>13000400001</v>
       </c>
-      <c r="W45" s="3">
+      <c r="W47" s="5">
         <v>130004000010000</v>
       </c>
-      <c r="X45" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="46" ht="14.25" spans="1:24">
-      <c r="A46">
+      <c r="X47" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A48" s="2">
         <v>13000500001</v>
       </c>
-      <c r="C46">
+      <c r="C48" s="2">
         <v>13</v>
       </c>
-      <c r="D46">
+      <c r="D48" s="2">
         <v>4</v>
       </c>
-      <c r="H46" t="s">
-        <v>128</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="J46" s="10">
+      <c r="H48" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J48" s="6">
         <v>1</v>
       </c>
-      <c r="O46">
+      <c r="O48" s="2">
         <v>0.05</v>
       </c>
-      <c r="P46">
+      <c r="P48" s="2">
         <v>0.01</v>
       </c>
-      <c r="V46">
+      <c r="V48" s="2">
         <v>13000500001</v>
       </c>
-      <c r="W46" s="3">
+      <c r="W48" s="5">
         <v>130005000010000</v>
       </c>
-      <c r="X46" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="47" ht="14.25" spans="1:24">
-      <c r="A47">
+      <c r="X48" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A49" s="2">
         <v>13000600001</v>
       </c>
-      <c r="C47">
+      <c r="C49" s="2">
         <v>13</v>
       </c>
-      <c r="D47">
+      <c r="D49" s="2">
         <v>4</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H49" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I49" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="I47" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="J47" s="10">
+      <c r="J49" s="6">
         <v>1</v>
       </c>
-      <c r="O47">
+      <c r="O49" s="2">
         <v>0.05</v>
       </c>
-      <c r="P47">
+      <c r="P49" s="2">
         <v>0.01</v>
       </c>
-      <c r="V47">
+      <c r="V49" s="2">
         <v>13000600001</v>
       </c>
-      <c r="W47" s="3">
+      <c r="W49" s="5">
         <v>130006000010000</v>
       </c>
-      <c r="X47" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" ht="14.25" spans="1:24">
-      <c r="A48">
+      <c r="X49" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="A50" s="2">
         <v>13000700001</v>
       </c>
-      <c r="C48">
+      <c r="C50" s="2">
         <v>13</v>
       </c>
-      <c r="D48">
+      <c r="D50" s="2">
         <v>4</v>
       </c>
-      <c r="H48" t="s">
-        <v>132</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q48">
+      <c r="H50" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q50" s="2">
         <v>0.2</v>
       </c>
-      <c r="R48"/>
-      <c r="V48">
+      <c r="R50" s="2"/>
+      <c r="V50" s="2">
         <v>13000700001</v>
       </c>
-      <c r="W48" s="3">
+      <c r="W50" s="5">
         <v>130007000010000</v>
       </c>
-      <c r="X48" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1"/>
-    <row r="50" ht="15" customHeight="1"/>
+      <c r="X50" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
     <row r="51" ht="15" customHeight="1"/>
     <row r="52" ht="15" customHeight="1"/>
     <row r="53" ht="15" customHeight="1"/>
@@ -3259,8 +3382,8 @@
     <row r="57" ht="15" customHeight="1"/>
     <row r="58" ht="15" customHeight="1"/>
     <row r="59" ht="15" customHeight="1"/>
-    <row r="91" ht="12" customHeight="1"/>
-    <row r="92" ht="12" customHeight="1"/>
+    <row r="60" ht="15" customHeight="1"/>
+    <row r="61" ht="15" customHeight="1"/>
     <row r="93" ht="12" customHeight="1"/>
     <row r="94" ht="12" customHeight="1"/>
     <row r="95" ht="12" customHeight="1"/>
@@ -3268,6 +3391,8 @@
     <row r="97" ht="12" customHeight="1"/>
     <row r="98" ht="12" customHeight="1"/>
     <row r="99" ht="12" customHeight="1"/>
+    <row r="100" ht="12" customHeight="1"/>
+    <row r="101" ht="12" customHeight="1"/>
   </sheetData>
   <sortState ref="A4:AG88">
     <sortCondition ref="A4"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="24045" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BuffInfo" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
     <t>name[language]</t>
   </si>
   <si>
-    <t>content[language]</t>
+    <t>content[language_1]</t>
   </si>
   <si>
     <t>remark</t>
@@ -453,12 +453,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -1126,7 +1125,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1134,17 +1133,11 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1152,9 +1145,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1802,8 +1792,8 @@
       <c r="V4" s="1">
         <v>1000100001</v>
       </c>
-      <c r="W4" s="3">
-        <v>10001000010000</v>
+      <c r="W4" s="1">
+        <v>1000100001</v>
       </c>
       <c r="X4" s="1" t="s">
         <v>55</v>
@@ -1841,8 +1831,8 @@
       <c r="V5" s="1">
         <v>1000200001</v>
       </c>
-      <c r="W5" s="3">
-        <v>10002000010000</v>
+      <c r="W5" s="1">
+        <v>1000200001</v>
       </c>
       <c r="X5" s="1" t="s">
         <v>57</v>
@@ -1858,18 +1848,18 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="4"/>
+      <c r="I6" s="3"/>
       <c r="S6" s="1">
         <v>1</v>
       </c>
       <c r="V6" s="1">
         <v>1000300001</v>
       </c>
-      <c r="W6" s="3">
-        <v>10003000010000</v>
+      <c r="W6" s="1">
+        <v>1000300001</v>
       </c>
       <c r="X6" s="1" t="s">
         <v>59</v>
@@ -1885,10 +1875,10 @@
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="3"/>
       <c r="K7" s="1" t="s">
         <v>60</v>
       </c>
@@ -1904,8 +1894,8 @@
       <c r="V7" s="1">
         <v>1000400001</v>
       </c>
-      <c r="W7" s="3">
-        <v>10004000010000</v>
+      <c r="W7" s="1">
+        <v>1000400001</v>
       </c>
       <c r="X7" s="1" t="s">
         <v>61</v>
@@ -1921,10 +1911,10 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="4"/>
+      <c r="I8" s="3"/>
       <c r="K8" s="1" t="s">
         <v>62</v>
       </c>
@@ -1940,8 +1930,8 @@
       <c r="V8" s="1">
         <v>1000500001</v>
       </c>
-      <c r="W8" s="3">
-        <v>10005000010000</v>
+      <c r="W8" s="1">
+        <v>1000500001</v>
       </c>
       <c r="X8" s="1" t="s">
         <v>63</v>
@@ -1960,7 +1950,7 @@
       <c r="H9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="4"/>
+      <c r="I9" s="3"/>
       <c r="J9" s="1" t="s">
         <v>64</v>
       </c>
@@ -1976,8 +1966,8 @@
       <c r="V9" s="1">
         <v>1000600001</v>
       </c>
-      <c r="W9" s="3">
-        <v>10006000010000</v>
+      <c r="W9" s="1">
+        <v>1000600001</v>
       </c>
       <c r="X9" s="1" t="s">
         <v>66</v>
@@ -1996,7 +1986,7 @@
       <c r="H10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="4"/>
+      <c r="I10" s="3"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
         <v>68</v>
@@ -2010,8 +2000,8 @@
       <c r="V10" s="1">
         <v>1000700001</v>
       </c>
-      <c r="W10" s="3">
-        <v>10007000010000</v>
+      <c r="W10" s="1">
+        <v>1000700001</v>
       </c>
       <c r="X10" s="1" t="s">
         <v>69</v>
@@ -2054,8 +2044,8 @@
       <c r="V11" s="2">
         <v>2000100001</v>
       </c>
-      <c r="W11" s="5">
-        <v>20001000010000</v>
+      <c r="W11" s="2">
+        <v>2000100001</v>
       </c>
       <c r="X11" s="2" t="s">
         <v>71</v>
@@ -2098,8 +2088,8 @@
       <c r="V12" s="2">
         <v>2000200001</v>
       </c>
-      <c r="W12" s="5">
-        <v>20002000010000</v>
+      <c r="W12" s="2">
+        <v>2000200001</v>
       </c>
       <c r="X12" s="2" t="s">
         <v>73</v>
@@ -2119,7 +2109,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="4" t="s">
         <v>74</v>
       </c>
       <c r="I13" s="2"/>
@@ -2127,7 +2117,7 @@
         <v>64</v>
       </c>
       <c r="K13" s="2"/>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="5" t="s">
         <v>75</v>
       </c>
       <c r="M13" s="2"/>
@@ -2144,8 +2134,8 @@
       <c r="V13" s="2">
         <v>2000300001</v>
       </c>
-      <c r="W13" s="5">
-        <v>20003000010000</v>
+      <c r="W13" s="2">
+        <v>2000300001</v>
       </c>
       <c r="X13" s="2" t="s">
         <v>76</v>
@@ -2165,7 +2155,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="4" t="s">
         <v>74</v>
       </c>
       <c r="I14" s="2"/>
@@ -2173,7 +2163,7 @@
         <v>77</v>
       </c>
       <c r="K14" s="2"/>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="5" t="s">
         <v>75</v>
       </c>
       <c r="M14" s="2"/>
@@ -2190,8 +2180,8 @@
       <c r="V14" s="2">
         <v>2000400001</v>
       </c>
-      <c r="W14" s="5">
-        <v>20004000010000</v>
+      <c r="W14" s="2">
+        <v>2000400001</v>
       </c>
       <c r="X14" s="2" t="s">
         <v>78</v>
@@ -2207,15 +2197,15 @@
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="I15" s="8"/>
+      <c r="I15" s="6"/>
       <c r="V15">
         <v>3000100001</v>
       </c>
-      <c r="W15" s="9">
-        <v>30001000010000</v>
+      <c r="W15">
+        <v>3000100001</v>
       </c>
       <c r="X15" t="s">
         <v>80</v>
@@ -2237,7 +2227,7 @@
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I16" t="s">
@@ -2249,8 +2239,8 @@
       <c r="V16">
         <v>3000200001</v>
       </c>
-      <c r="W16" s="9">
-        <v>30002000010000</v>
+      <c r="W16">
+        <v>3000200001</v>
       </c>
       <c r="X16" t="s">
         <v>83</v>
@@ -2272,7 +2262,7 @@
       <c r="F17">
         <v>2</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I17" t="s">
@@ -2284,8 +2274,8 @@
       <c r="V17">
         <v>3000200002</v>
       </c>
-      <c r="W17" s="9">
-        <v>30002000020000</v>
+      <c r="W17">
+        <v>3000200002</v>
       </c>
       <c r="X17" t="s">
         <v>84</v>
@@ -2307,7 +2297,7 @@
       <c r="F18">
         <v>3</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I18" t="s">
@@ -2319,8 +2309,8 @@
       <c r="V18">
         <v>3000200003</v>
       </c>
-      <c r="W18" s="9">
-        <v>30002000030000</v>
+      <c r="W18">
+        <v>3000200003</v>
       </c>
       <c r="X18" t="s">
         <v>85</v>
@@ -2339,10 +2329,10 @@
       <c r="G19">
         <v>1</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="8"/>
+      <c r="I19" s="6"/>
       <c r="J19" t="s">
         <v>86</v>
       </c>
@@ -2352,8 +2342,8 @@
       <c r="V19">
         <v>3000300001</v>
       </c>
-      <c r="W19" s="9">
-        <v>30003000010000</v>
+      <c r="W19">
+        <v>3000300001</v>
       </c>
       <c r="X19" t="s">
         <v>87</v>
@@ -2369,10 +2359,10 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="I20" s="8"/>
+      <c r="I20" s="6"/>
       <c r="J20" t="s">
         <v>88</v>
       </c>
@@ -2382,8 +2372,8 @@
       <c r="V20">
         <v>3000400001</v>
       </c>
-      <c r="W20" s="9">
-        <v>30004000010000</v>
+      <c r="W20">
+        <v>3000400001</v>
       </c>
       <c r="X20" t="s">
         <v>89</v>
@@ -2415,8 +2405,8 @@
       <c r="V21" s="2">
         <v>11000100001</v>
       </c>
-      <c r="W21" s="5">
-        <v>110001000010000</v>
+      <c r="W21" s="2">
+        <v>11000100001</v>
       </c>
       <c r="X21" s="2" t="s">
         <v>90</v>
@@ -2448,8 +2438,8 @@
       <c r="V22" s="2">
         <v>11000200001</v>
       </c>
-      <c r="W22" s="5">
-        <v>110002000010000</v>
+      <c r="W22" s="2">
+        <v>11000200001</v>
       </c>
       <c r="X22" s="2" t="s">
         <v>92</v>
@@ -2481,8 +2471,8 @@
       <c r="V23" s="2">
         <v>11000300001</v>
       </c>
-      <c r="W23" s="5">
-        <v>110003000010000</v>
+      <c r="W23" s="2">
+        <v>11000300001</v>
       </c>
       <c r="X23" s="2" t="s">
         <v>93</v>
@@ -2498,10 +2488,10 @@
       <c r="D24">
         <v>3</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I24" s="10"/>
+      <c r="I24" s="7"/>
       <c r="O24">
         <v>0.05</v>
       </c>
@@ -2517,8 +2507,8 @@
       <c r="V24">
         <v>12000100001</v>
       </c>
-      <c r="W24" s="9">
-        <v>120001000010000</v>
+      <c r="W24">
+        <v>12000100001</v>
       </c>
       <c r="X24" t="s">
         <v>94</v>
@@ -2534,10 +2524,10 @@
       <c r="D25">
         <v>3</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="10"/>
+      <c r="I25" s="7"/>
       <c r="O25">
         <v>0.05</v>
       </c>
@@ -2553,8 +2543,8 @@
       <c r="V25">
         <v>12000200001</v>
       </c>
-      <c r="W25" s="9">
-        <v>120002000010000</v>
+      <c r="W25">
+        <v>12000200001</v>
       </c>
       <c r="X25" t="s">
         <v>96</v>
@@ -2570,18 +2560,18 @@
       <c r="D26">
         <v>3</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I26" s="10"/>
+      <c r="I26" s="7"/>
       <c r="T26">
         <v>5</v>
       </c>
       <c r="V26">
         <v>12000300001</v>
       </c>
-      <c r="W26" s="9">
-        <v>120003000010000</v>
+      <c r="W26">
+        <v>12000300001</v>
       </c>
       <c r="X26" t="s">
         <v>98</v>
@@ -2597,10 +2587,10 @@
       <c r="D27">
         <v>3</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="8" t="s">
         <v>99</v>
       </c>
       <c r="J27" t="s">
@@ -2615,8 +2605,8 @@
       <c r="V27">
         <v>12001100001</v>
       </c>
-      <c r="W27" s="9">
-        <v>120011000010000</v>
+      <c r="W27">
+        <v>12001100001</v>
       </c>
       <c r="X27" t="s">
         <v>101</v>
@@ -2632,10 +2622,10 @@
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="8" t="s">
         <v>99</v>
       </c>
       <c r="J28" t="s">
@@ -2650,8 +2640,8 @@
       <c r="V28">
         <v>12001200001</v>
       </c>
-      <c r="W28" s="9">
-        <v>120012000010000</v>
+      <c r="W28">
+        <v>12001200001</v>
       </c>
       <c r="X28" t="s">
         <v>102</v>
@@ -2667,10 +2657,10 @@
       <c r="D29">
         <v>3</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="8" t="s">
         <v>99</v>
       </c>
       <c r="J29" t="s">
@@ -2685,8 +2675,8 @@
       <c r="V29">
         <v>12001300001</v>
       </c>
-      <c r="W29" s="9">
-        <v>120013000010000</v>
+      <c r="W29">
+        <v>12001300001</v>
       </c>
       <c r="X29" t="s">
         <v>103</v>
@@ -2702,10 +2692,10 @@
       <c r="D30">
         <v>3</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="8" t="s">
         <v>99</v>
       </c>
       <c r="J30" t="s">
@@ -2720,8 +2710,8 @@
       <c r="V30">
         <v>12001400001</v>
       </c>
-      <c r="W30" s="9">
-        <v>120014000010000</v>
+      <c r="W30">
+        <v>12001400001</v>
       </c>
       <c r="X30" t="s">
         <v>104</v>
@@ -2737,10 +2727,10 @@
       <c r="D31">
         <v>3</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="4" t="s">
         <v>105</v>
       </c>
       <c r="J31" t="s">
@@ -2755,8 +2745,8 @@
       <c r="V31">
         <v>12002100001</v>
       </c>
-      <c r="W31" s="9">
-        <v>120021000010000</v>
+      <c r="W31">
+        <v>12002100001</v>
       </c>
       <c r="X31" t="s">
         <v>107</v>
@@ -2772,10 +2762,10 @@
       <c r="D32">
         <v>3</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="4" t="s">
         <v>105</v>
       </c>
       <c r="J32" t="s">
@@ -2790,8 +2780,8 @@
       <c r="V32">
         <v>12002200001</v>
       </c>
-      <c r="W32" s="9">
-        <v>120022000010000</v>
+      <c r="W32">
+        <v>12002200001</v>
       </c>
       <c r="X32" t="s">
         <v>108</v>
@@ -2807,10 +2797,10 @@
       <c r="D33">
         <v>3</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="4" t="s">
         <v>105</v>
       </c>
       <c r="J33" t="s">
@@ -2825,8 +2815,8 @@
       <c r="V33">
         <v>12002300001</v>
       </c>
-      <c r="W33" s="9">
-        <v>120023000010000</v>
+      <c r="W33">
+        <v>12002300001</v>
       </c>
       <c r="X33" t="s">
         <v>109</v>
@@ -2842,10 +2832,10 @@
       <c r="D34">
         <v>3</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="4" t="s">
         <v>105</v>
       </c>
       <c r="J34" t="s">
@@ -2860,8 +2850,8 @@
       <c r="V34">
         <v>12002400001</v>
       </c>
-      <c r="W34" s="9">
-        <v>120024000010000</v>
+      <c r="W34">
+        <v>12002400001</v>
       </c>
       <c r="X34" t="s">
         <v>110</v>
@@ -2877,16 +2867,16 @@
       <c r="D35">
         <v>3</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I35" s="13" t="s">
+      <c r="I35" s="10" t="s">
         <v>105</v>
       </c>
       <c r="J35" t="s">
         <v>86</v>
       </c>
-      <c r="L35" s="14" t="s">
+      <c r="L35" s="11" t="s">
         <v>75</v>
       </c>
       <c r="O35">
@@ -2895,8 +2885,8 @@
       <c r="V35">
         <v>12003100001</v>
       </c>
-      <c r="W35" s="9">
-        <v>120031000010000</v>
+      <c r="W35">
+        <v>12003100001</v>
       </c>
       <c r="X35" t="s">
         <v>111</v>
@@ -2912,16 +2902,16 @@
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I36" s="13" t="s">
+      <c r="I36" s="10" t="s">
         <v>105</v>
       </c>
       <c r="J36" t="s">
         <v>91</v>
       </c>
-      <c r="L36" s="14" t="s">
+      <c r="L36" s="11" t="s">
         <v>75</v>
       </c>
       <c r="O36">
@@ -2930,8 +2920,8 @@
       <c r="V36">
         <v>12003200001</v>
       </c>
-      <c r="W36" s="9">
-        <v>120032000010000</v>
+      <c r="W36">
+        <v>12003200001</v>
       </c>
       <c r="X36" t="s">
         <v>112</v>
@@ -2947,16 +2937,16 @@
       <c r="D37">
         <v>3</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I37" s="13" t="s">
+      <c r="I37" s="10" t="s">
         <v>105</v>
       </c>
       <c r="J37" t="s">
         <v>64</v>
       </c>
-      <c r="L37" s="14" t="s">
+      <c r="L37" s="11" t="s">
         <v>75</v>
       </c>
       <c r="O37">
@@ -2965,8 +2955,8 @@
       <c r="V37">
         <v>12003300001</v>
       </c>
-      <c r="W37" s="9">
-        <v>120033000010000</v>
+      <c r="W37">
+        <v>12003300001</v>
       </c>
       <c r="X37" t="s">
         <v>113</v>
@@ -2982,16 +2972,16 @@
       <c r="D38">
         <v>3</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I38" s="13" t="s">
+      <c r="I38" s="10" t="s">
         <v>105</v>
       </c>
       <c r="J38" t="s">
         <v>77</v>
       </c>
-      <c r="L38" s="14" t="s">
+      <c r="L38" s="11" t="s">
         <v>75</v>
       </c>
       <c r="O38">
@@ -3000,8 +2990,8 @@
       <c r="V38">
         <v>12003400001</v>
       </c>
-      <c r="W38" s="9">
-        <v>120034000010000</v>
+      <c r="W38">
+        <v>12003400001</v>
       </c>
       <c r="X38" t="s">
         <v>114</v>
@@ -3017,10 +3007,10 @@
       <c r="D39">
         <v>3</v>
       </c>
-      <c r="H39" s="13" t="s">
+      <c r="H39" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="12" t="s">
         <v>99</v>
       </c>
       <c r="L39" t="s">
@@ -3029,8 +3019,8 @@
       <c r="V39">
         <v>12010100001</v>
       </c>
-      <c r="W39" s="9">
-        <v>120101000010000</v>
+      <c r="W39">
+        <v>12010100001</v>
       </c>
       <c r="X39" t="s">
         <v>116</v>
@@ -3046,10 +3036,10 @@
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="4" t="s">
         <v>105</v>
       </c>
       <c r="L40" t="s">
@@ -3058,8 +3048,8 @@
       <c r="V40">
         <v>12010200001</v>
       </c>
-      <c r="W40" s="9">
-        <v>120102000010000</v>
+      <c r="W40">
+        <v>12010200001</v>
       </c>
       <c r="X40" t="s">
         <v>117</v>
@@ -3075,10 +3065,10 @@
       <c r="D41">
         <v>3</v>
       </c>
-      <c r="H41" s="13" t="s">
+      <c r="H41" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="4" t="s">
         <v>105</v>
       </c>
       <c r="L41" t="s">
@@ -3087,8 +3077,8 @@
       <c r="V41">
         <v>12010300001</v>
       </c>
-      <c r="W41" s="9">
-        <v>120103000010000</v>
+      <c r="W41">
+        <v>12010300001</v>
       </c>
       <c r="X41" t="s">
         <v>119</v>
@@ -3104,10 +3094,10 @@
       <c r="D42">
         <v>3</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="I42" s="12" t="s">
         <v>99</v>
       </c>
       <c r="L42" t="s">
@@ -3116,8 +3106,8 @@
       <c r="V42">
         <v>12011100001</v>
       </c>
-      <c r="W42" s="9">
-        <v>120111000010000</v>
+      <c r="W42">
+        <v>12011100001</v>
       </c>
       <c r="X42" t="s">
         <v>122</v>
@@ -3133,10 +3123,10 @@
       <c r="D43">
         <v>3</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="4" t="s">
         <v>105</v>
       </c>
       <c r="L43" t="s">
@@ -3145,8 +3135,8 @@
       <c r="V43">
         <v>12011200001</v>
       </c>
-      <c r="W43" s="9">
-        <v>120112000010000</v>
+      <c r="W43">
+        <v>12011200001</v>
       </c>
       <c r="X43" t="s">
         <v>124</v>
@@ -3162,10 +3152,10 @@
       <c r="D44">
         <v>3</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" s="4" t="s">
         <v>105</v>
       </c>
       <c r="L44" t="s">
@@ -3174,8 +3164,8 @@
       <c r="V44">
         <v>12011300001</v>
       </c>
-      <c r="W44" s="9">
-        <v>120113000010000</v>
+      <c r="W44">
+        <v>12011300001</v>
       </c>
       <c r="X44" t="s">
         <v>126</v>
@@ -3191,10 +3181,10 @@
       <c r="D45" s="2">
         <v>4</v>
       </c>
-      <c r="H45" s="6" t="s">
+      <c r="H45" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I45" s="6"/>
+      <c r="I45" s="4"/>
       <c r="M45" s="2">
         <v>2</v>
       </c>
@@ -3204,8 +3194,8 @@
       <c r="V45" s="2">
         <v>13000100001</v>
       </c>
-      <c r="W45" s="5">
-        <v>130001000010000</v>
+      <c r="W45" s="2">
+        <v>13000100001</v>
       </c>
       <c r="X45" s="2" t="s">
         <v>128</v>
@@ -3224,18 +3214,18 @@
       <c r="H46" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J46" s="6"/>
+      <c r="J46" s="4"/>
       <c r="U46" s="2">
         <v>500001</v>
       </c>
       <c r="V46" s="2">
         <v>13000300001</v>
       </c>
-      <c r="W46" s="5">
-        <v>130003000010000</v>
+      <c r="W46" s="2">
+        <v>13000300001</v>
       </c>
       <c r="X46" s="2" t="s">
         <v>131</v>
@@ -3254,7 +3244,7 @@
       <c r="H47" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" s="4" t="s">
         <v>130</v>
       </c>
       <c r="J47" s="2">
@@ -3266,8 +3256,8 @@
       <c r="V47" s="2">
         <v>13000400001</v>
       </c>
-      <c r="W47" s="5">
-        <v>130004000010000</v>
+      <c r="W47" s="2">
+        <v>13000400001</v>
       </c>
       <c r="X47" s="2" t="s">
         <v>133</v>
@@ -3286,10 +3276,10 @@
       <c r="H48" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="I48" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J48" s="6">
+      <c r="J48" s="4">
         <v>1</v>
       </c>
       <c r="O48" s="2">
@@ -3301,8 +3291,8 @@
       <c r="V48" s="2">
         <v>13000500001</v>
       </c>
-      <c r="W48" s="5">
-        <v>130005000010000</v>
+      <c r="W48" s="2">
+        <v>13000500001</v>
       </c>
       <c r="X48" s="2" t="s">
         <v>135</v>
@@ -3321,10 +3311,10 @@
       <c r="H49" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="I49" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J49" s="6">
+      <c r="J49" s="4">
         <v>1</v>
       </c>
       <c r="O49" s="2">
@@ -3336,8 +3326,8 @@
       <c r="V49" s="2">
         <v>13000600001</v>
       </c>
-      <c r="W49" s="5">
-        <v>130006000010000</v>
+      <c r="W49" s="2">
+        <v>13000600001</v>
       </c>
       <c r="X49" s="2" t="s">
         <v>137</v>
@@ -3356,7 +3346,7 @@
       <c r="H50" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="I50" s="6" t="s">
+      <c r="I50" s="4" t="s">
         <v>130</v>
       </c>
       <c r="Q50" s="2">
@@ -3366,8 +3356,8 @@
       <c r="V50" s="2">
         <v>13000700001</v>
       </c>
-      <c r="W50" s="5">
-        <v>130007000010000</v>
+      <c r="W50" s="2">
+        <v>13000700001</v>
       </c>
       <c r="X50" s="2" t="s">
         <v>139</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BuffInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="144">
   <si>
     <t>id</t>
   </si>
@@ -89,6 +89,12 @@
     <t>trigger_time</t>
   </si>
   <si>
+    <t>stack_mode</t>
+  </si>
+  <si>
+    <t>stack_max</t>
+  </si>
+  <si>
     <t>trigger_effect</t>
   </si>
   <si>
@@ -171,6 +177,12 @@
   </si>
   <si>
     <t>触发时间</t>
+  </si>
+  <si>
+    <t>堆叠策略 0=Refresh 1=Stack 2=Independent 3=Ignore 4=ReplaceStrongest</t>
+  </si>
+  <si>
+    <t>最大堆叠层数 0=无上限 仅Stack模式生效</t>
   </si>
   <si>
     <t>触发时的粒子</t>
@@ -980,171 +992,172 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="47" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="47" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1159,7 +1172,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1513,32 +1526,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X101"/>
+  <dimension ref="A1:Z101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="24.25" customWidth="1"/>
-    <col min="2" max="2" width="17.5" customWidth="1"/>
-    <col min="3" max="3" width="61.125" customWidth="1"/>
-    <col min="4" max="5" width="21.25" customWidth="1"/>
-    <col min="6" max="6" width="27.25" customWidth="1"/>
-    <col min="7" max="7" width="51.875" customWidth="1"/>
-    <col min="8" max="8" width="41.5" customWidth="1"/>
-    <col min="9" max="10" width="42.625" customWidth="1"/>
-    <col min="11" max="12" width="11.5" customWidth="1"/>
-    <col min="13" max="13" width="14.875" customWidth="1"/>
-    <col min="14" max="14" width="19.375" customWidth="1"/>
-    <col min="15" max="15" width="20.375" customWidth="1"/>
-    <col min="16" max="16" width="24.875" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="21.375" customWidth="1"/>
-    <col min="19" max="19" width="36.125" customWidth="1"/>
-    <col min="20" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="17.125" customWidth="1"/>
-    <col min="23" max="23" width="28.625" customWidth="1"/>
-    <col min="24" max="24" width="61.875" customWidth="1"/>
+    <col min="1" max="1" width="24.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="3" customWidth="1"/>
+    <col min="3" max="3" width="61.125" style="3" customWidth="1"/>
+    <col min="4" max="5" width="21.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="27.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="51.875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="41.5" style="3" customWidth="1"/>
+    <col min="9" max="10" width="42.625" style="3" customWidth="1"/>
+    <col min="11" max="12" width="11.5" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.875" style="3" customWidth="1"/>
+    <col min="14" max="14" width="19.375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="20.375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="24.875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="16" style="3" customWidth="1"/>
+    <col min="18" max="18" width="21.375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="36.125" style="3" customWidth="1"/>
+    <col min="20" max="21" width="16" style="3" customWidth="1"/>
+    <col min="22" max="22" width="23.875" style="3" customWidth="1"/>
+    <col min="23" max="23" width="28.625" style="3" customWidth="1"/>
+    <col min="24" max="24" width="61.875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1611,156 +1624,174 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" t="s">
         <v>26</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="X2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
+      <c r="Y2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="Z2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>27</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>27</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>26</v>
-      </c>
-      <c r="T2" t="s">
-        <v>27</v>
-      </c>
-      <c r="U2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V2" t="s">
-        <v>24</v>
-      </c>
-      <c r="W2" t="s">
-        <v>24</v>
-      </c>
-      <c r="X2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="T3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="W3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="X3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:24">
+        <v>53</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:26">
       <c r="A4" s="1">
         <v>1000100001</v>
       </c>
@@ -1771,14 +1802,14 @@
         <v>1</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="O4" s="1">
         <v>-0.5</v>
@@ -1789,17 +1820,23 @@
       <c r="T4" s="1">
         <v>10</v>
       </c>
-      <c r="V4" s="1">
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1">
         <v>1000100001</v>
       </c>
-      <c r="W4" s="1">
+      <c r="Y4" s="1">
         <v>1000100001</v>
       </c>
-      <c r="X4" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:24">
+      <c r="Z4" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:26">
       <c r="A5" s="1">
         <v>1000200001</v>
       </c>
@@ -1810,14 +1847,14 @@
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="O5" s="1">
         <v>-0.2</v>
@@ -1828,17 +1865,23 @@
       <c r="T5" s="1">
         <v>1</v>
       </c>
-      <c r="V5" s="1">
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1">
         <v>1000200001</v>
       </c>
-      <c r="W5" s="1">
+      <c r="Y5" s="1">
         <v>1000200001</v>
       </c>
-      <c r="X5" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z5" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A6" s="1">
         <v>1000300001</v>
       </c>
@@ -1848,24 +1891,30 @@
       <c r="D6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I6" s="4"/>
       <c r="S6" s="1">
         <v>1</v>
       </c>
-      <c r="V6" s="1">
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
         <v>1000300001</v>
       </c>
-      <c r="W6" s="1">
+      <c r="Y6" s="1">
         <v>1000300001</v>
       </c>
-      <c r="X6" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z6" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A7" s="1">
         <v>1000400001</v>
       </c>
@@ -1875,12 +1924,12 @@
       <c r="D7" s="1">
         <v>1</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="4"/>
       <c r="K7" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O7" s="1">
         <v>-0.01</v>
@@ -1891,17 +1940,23 @@
       <c r="T7" s="1">
         <v>1</v>
       </c>
-      <c r="V7" s="1">
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
         <v>1000400001</v>
       </c>
-      <c r="W7" s="1">
+      <c r="Y7" s="1">
         <v>1000400001</v>
       </c>
-      <c r="X7" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z7" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A8" s="1">
         <v>1000500001</v>
       </c>
@@ -1911,12 +1966,12 @@
       <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="4"/>
       <c r="K8" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="O8" s="1">
         <v>-0.05</v>
@@ -1927,17 +1982,23 @@
       <c r="T8" s="1">
         <v>3</v>
       </c>
-      <c r="V8" s="1">
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
         <v>1000500001</v>
       </c>
-      <c r="W8" s="1">
+      <c r="Y8" s="1">
         <v>1000500001</v>
       </c>
-      <c r="X8" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z8" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A9" s="1">
         <v>1000600001</v>
       </c>
@@ -1948,14 +2009,14 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="O9" s="1">
         <v>-0.1</v>
@@ -1963,17 +2024,23 @@
       <c r="T9" s="1">
         <v>10</v>
       </c>
-      <c r="V9" s="1">
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
         <v>1000600001</v>
       </c>
-      <c r="W9" s="1">
+      <c r="Y9" s="1">
         <v>1000600001</v>
       </c>
-      <c r="X9" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z9" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A10" s="1">
         <v>1000700001</v>
       </c>
@@ -1984,12 +2051,12 @@
         <v>1</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="3"/>
+        <v>71</v>
+      </c>
+      <c r="I10" s="4"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O10" s="1">
         <v>2</v>
@@ -1997,17 +2064,23 @@
       <c r="T10" s="1">
         <v>5</v>
       </c>
-      <c r="V10" s="1">
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
         <v>1000700001</v>
       </c>
-      <c r="W10" s="1">
+      <c r="Y10" s="1">
         <v>1000700001</v>
       </c>
-      <c r="X10" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="Z10" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="2">
         <v>2000100001</v>
       </c>
@@ -2022,11 +2095,11 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
@@ -2040,18 +2113,24 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2">
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2">
         <v>2000100001</v>
       </c>
-      <c r="W11" s="2">
+      <c r="Y11" s="2">
         <v>2000100001</v>
       </c>
-      <c r="X11" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="Z11" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="2">
         <v>2000200001</v>
       </c>
@@ -2066,11 +2145,11 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
@@ -2084,18 +2163,24 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2">
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2">
         <v>2000200001</v>
       </c>
-      <c r="W12" s="2">
+      <c r="Y12" s="2">
         <v>2000200001</v>
       </c>
-      <c r="X12" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:24">
+      <c r="Z12" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1" spans="1:26">
       <c r="A13" s="2">
         <v>2000300001</v>
       </c>
@@ -2109,16 +2194,16 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="4" t="s">
-        <v>74</v>
+      <c r="H13" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K13" s="2"/>
-      <c r="L13" s="5" t="s">
-        <v>75</v>
+      <c r="L13" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -2130,18 +2215,24 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2">
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2">
         <v>2000300001</v>
       </c>
-      <c r="W13" s="2">
+      <c r="Y13" s="2">
         <v>2000300001</v>
       </c>
-      <c r="X13" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:24">
+      <c r="Z13" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1" spans="1:26">
       <c r="A14" s="2">
         <v>2000400001</v>
       </c>
@@ -2155,16 +2246,16 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="4" t="s">
-        <v>74</v>
+      <c r="H14" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K14" s="2"/>
-      <c r="L14" s="5" t="s">
-        <v>75</v>
+      <c r="L14" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2176,18 +2267,24 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2">
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2">
         <v>2000400001</v>
       </c>
-      <c r="W14" s="2">
+      <c r="Y14" s="2">
         <v>2000400001</v>
       </c>
-      <c r="X14" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="Z14" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15">
         <v>3000100001</v>
       </c>
@@ -2197,21 +2294,27 @@
       <c r="D15">
         <v>1</v>
       </c>
-      <c r="H15" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" s="6"/>
+      <c r="H15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="U15">
+        <v>0</v>
+      </c>
       <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="X15">
         <v>3000100001</v>
       </c>
-      <c r="W15">
+      <c r="Y15">
         <v>3000100001</v>
       </c>
-      <c r="X15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="Z15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16">
         <v>3000200001</v>
       </c>
@@ -2227,26 +2330,32 @@
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="H16" s="6" t="s">
-        <v>81</v>
+      <c r="H16" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="I16" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q16">
         <v>0.1</v>
       </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
       <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="X16">
         <v>3000200001</v>
       </c>
-      <c r="W16">
+      <c r="Y16">
         <v>3000200001</v>
       </c>
-      <c r="X16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24">
+      <c r="Z16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17">
         <v>3000200002</v>
       </c>
@@ -2262,26 +2371,32 @@
       <c r="F17">
         <v>2</v>
       </c>
-      <c r="H17" s="6" t="s">
-        <v>81</v>
+      <c r="H17" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="I17" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q17">
         <v>0.2</v>
       </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
       <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="X17">
         <v>3000200002</v>
       </c>
-      <c r="W17">
+      <c r="Y17">
         <v>3000200002</v>
       </c>
-      <c r="X17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24">
+      <c r="Z17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18">
         <v>3000200003</v>
       </c>
@@ -2297,26 +2412,32 @@
       <c r="F18">
         <v>3</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>81</v>
+      <c r="H18" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="I18" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q18">
         <v>0.3</v>
       </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
       <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="X18">
         <v>3000200003</v>
       </c>
-      <c r="W18">
+      <c r="Y18">
         <v>3000200003</v>
       </c>
-      <c r="X18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24">
+      <c r="Z18" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
       <c r="A19">
         <v>3000300001</v>
       </c>
@@ -2329,27 +2450,33 @@
       <c r="G19">
         <v>1</v>
       </c>
-      <c r="H19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I19" s="6"/>
+      <c r="H19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="7"/>
       <c r="J19" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="O19">
         <v>0.1</v>
       </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
       <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="X19">
         <v>3000300001</v>
       </c>
-      <c r="W19">
+      <c r="Y19">
         <v>3000300001</v>
       </c>
-      <c r="X19" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24">
+      <c r="Z19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
       <c r="A20">
         <v>3000400001</v>
       </c>
@@ -2359,27 +2486,33 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="I20" s="6"/>
+      <c r="H20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="7"/>
       <c r="J20" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="O20">
         <v>-0.1</v>
       </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
       <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="X20">
         <v>3000400001</v>
       </c>
-      <c r="W20">
+      <c r="Y20">
         <v>3000400001</v>
       </c>
-      <c r="X20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" spans="1:24">
+      <c r="Z20" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" spans="1:26">
       <c r="A21" s="2">
         <v>11000100001</v>
       </c>
@@ -2390,11 +2523,11 @@
         <v>2</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="O21" s="2">
         <v>0.2</v>
@@ -2402,17 +2535,23 @@
       <c r="P21" s="2">
         <v>0.1</v>
       </c>
-      <c r="V21" s="2">
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2">
         <v>11000100001</v>
       </c>
-      <c r="W21" s="2">
+      <c r="Y21" s="2">
         <v>11000100001</v>
       </c>
-      <c r="X21" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" spans="1:24">
+      <c r="Z21" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" spans="1:26">
       <c r="A22" s="2">
         <v>11000200001</v>
       </c>
@@ -2423,11 +2562,11 @@
         <v>2</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="O22" s="2">
         <v>0.2</v>
@@ -2435,17 +2574,23 @@
       <c r="P22" s="2">
         <v>0.1</v>
       </c>
-      <c r="V22" s="2">
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2">
         <v>11000200001</v>
       </c>
-      <c r="W22" s="2">
+      <c r="Y22" s="2">
         <v>11000200001</v>
       </c>
-      <c r="X22" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" spans="1:24">
+      <c r="Z22" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" spans="1:26">
       <c r="A23" s="2">
         <v>11000300001</v>
       </c>
@@ -2456,11 +2601,11 @@
         <v>2</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="O23" s="2">
         <v>0.2</v>
@@ -2468,17 +2613,23 @@
       <c r="P23" s="2">
         <v>0.1</v>
       </c>
-      <c r="V23" s="2">
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2">
         <v>11000300001</v>
       </c>
-      <c r="W23" s="2">
+      <c r="Y23" s="2">
         <v>11000300001</v>
       </c>
-      <c r="X23" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" ht="13" customHeight="1" spans="1:24">
+      <c r="Z23" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1" spans="1:26">
       <c r="A24">
         <v>12000100001</v>
       </c>
@@ -2488,10 +2639,10 @@
       <c r="D24">
         <v>3</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I24" s="7"/>
+      <c r="H24" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I24" s="8"/>
       <c r="O24">
         <v>0.05</v>
       </c>
@@ -2502,19 +2653,25 @@
         <v>5</v>
       </c>
       <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
         <v>500001</v>
       </c>
-      <c r="V24">
+      <c r="X24">
         <v>12000100001</v>
       </c>
-      <c r="W24">
+      <c r="Y24">
         <v>12000100001</v>
       </c>
-      <c r="X24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="1:24">
+      <c r="Z24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1" spans="1:26">
       <c r="A25">
         <v>12000200001</v>
       </c>
@@ -2524,10 +2681,10 @@
       <c r="D25">
         <v>3</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="I25" s="7"/>
+      <c r="H25" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="I25" s="8"/>
       <c r="O25">
         <v>0.05</v>
       </c>
@@ -2538,19 +2695,25 @@
         <v>5</v>
       </c>
       <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
         <v>500002</v>
       </c>
-      <c r="V25">
+      <c r="X25">
         <v>12000200001</v>
       </c>
-      <c r="W25">
+      <c r="Y25">
         <v>12000200001</v>
       </c>
-      <c r="X25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" spans="1:24">
+      <c r="Z25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1" spans="1:26">
       <c r="A26">
         <v>12000300001</v>
       </c>
@@ -2560,24 +2723,30 @@
       <c r="D26">
         <v>3</v>
       </c>
-      <c r="H26" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="I26" s="7"/>
+      <c r="H26" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="I26" s="8"/>
       <c r="T26">
         <v>5</v>
       </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
       <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="X26">
         <v>12000300001</v>
       </c>
-      <c r="W26">
+      <c r="Y26">
         <v>12000300001</v>
       </c>
-      <c r="X26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="1:24">
+      <c r="Z26" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" customHeight="1" spans="1:26">
       <c r="A27">
         <v>12001100001</v>
       </c>
@@ -2587,32 +2756,38 @@
       <c r="D27">
         <v>3</v>
       </c>
-      <c r="H27" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>99</v>
+      <c r="H27" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="J27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L27" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O27">
         <v>0.25</v>
       </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
       <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="X27">
         <v>12001100001</v>
       </c>
-      <c r="W27">
+      <c r="Y27">
         <v>12001100001</v>
       </c>
-      <c r="X27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" ht="14.25" spans="1:24">
+      <c r="Z27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" ht="14.25" customHeight="1" spans="1:26">
       <c r="A28">
         <v>12001200001</v>
       </c>
@@ -2622,32 +2797,38 @@
       <c r="D28">
         <v>3</v>
       </c>
-      <c r="H28" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>99</v>
+      <c r="H28" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="J28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O28">
         <v>0.25</v>
       </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
       <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="X28">
         <v>12001200001</v>
       </c>
-      <c r="W28">
+      <c r="Y28">
         <v>12001200001</v>
       </c>
-      <c r="X28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="1:24">
+      <c r="Z28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" customHeight="1" spans="1:26">
       <c r="A29">
         <v>12001300001</v>
       </c>
@@ -2657,32 +2838,38 @@
       <c r="D29">
         <v>3</v>
       </c>
-      <c r="H29" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>99</v>
+      <c r="H29" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I29" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="J29" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L29" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O29">
         <v>0.25</v>
       </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
       <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="X29">
         <v>12001300001</v>
       </c>
-      <c r="W29">
+      <c r="Y29">
         <v>12001300001</v>
       </c>
-      <c r="X29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" ht="14.25" spans="1:24">
+      <c r="Z29" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="30" ht="14.25" customHeight="1" spans="1:26">
       <c r="A30">
         <v>12001400001</v>
       </c>
@@ -2692,32 +2879,38 @@
       <c r="D30">
         <v>3</v>
       </c>
-      <c r="H30" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>99</v>
+      <c r="H30" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I30" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="J30" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L30" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="O30">
         <v>0.25</v>
       </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
       <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="X30">
         <v>12001400001</v>
       </c>
-      <c r="W30">
+      <c r="Y30">
         <v>12001400001</v>
       </c>
-      <c r="X30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="1:24">
+      <c r="Z30" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" customHeight="1" spans="1:26">
       <c r="A31">
         <v>12002100001</v>
       </c>
@@ -2727,32 +2920,38 @@
       <c r="D31">
         <v>3</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>105</v>
+      <c r="H31" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J31" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O31">
         <v>0.25</v>
       </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
       <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="X31">
         <v>12002100001</v>
       </c>
-      <c r="W31">
+      <c r="Y31">
         <v>12002100001</v>
       </c>
-      <c r="X31" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25" spans="1:24">
+      <c r="Z31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" ht="14.25" customHeight="1" spans="1:26">
       <c r="A32">
         <v>12002200001</v>
       </c>
@@ -2762,32 +2961,38 @@
       <c r="D32">
         <v>3</v>
       </c>
-      <c r="H32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>105</v>
+      <c r="H32" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J32" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L32" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O32">
         <v>0.25</v>
       </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
       <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="X32">
         <v>12002200001</v>
       </c>
-      <c r="W32">
+      <c r="Y32">
         <v>12002200001</v>
       </c>
-      <c r="X32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="1:24">
+      <c r="Z32" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" customHeight="1" spans="1:26">
       <c r="A33">
         <v>12002300001</v>
       </c>
@@ -2797,32 +3002,38 @@
       <c r="D33">
         <v>3</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>105</v>
+      <c r="H33" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J33" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L33" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O33">
         <v>0.25</v>
       </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
       <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="X33">
         <v>12002300001</v>
       </c>
-      <c r="W33">
+      <c r="Y33">
         <v>12002300001</v>
       </c>
-      <c r="X33" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="34" ht="14.25" spans="1:24">
+      <c r="Z33" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="34" ht="14.25" customHeight="1" spans="1:26">
       <c r="A34">
         <v>12002400001</v>
       </c>
@@ -2832,32 +3043,38 @@
       <c r="D34">
         <v>3</v>
       </c>
-      <c r="H34" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>105</v>
+      <c r="H34" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="J34" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L34" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="O34">
         <v>0.25</v>
       </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
       <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="X34">
         <v>12002400001</v>
       </c>
-      <c r="W34">
+      <c r="Y34">
         <v>12002400001</v>
       </c>
-      <c r="X34" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="35" ht="14.25" spans="1:24">
+      <c r="Z34" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="35" ht="14.25" customHeight="1" spans="1:26">
       <c r="A35">
         <v>12003100001</v>
       </c>
@@ -2867,32 +3084,38 @@
       <c r="D35">
         <v>3</v>
       </c>
-      <c r="H35" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>105</v>
+      <c r="H35" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="J35" t="s">
-        <v>86</v>
-      </c>
-      <c r="L35" s="11" t="s">
-        <v>75</v>
+        <v>90</v>
+      </c>
+      <c r="L35" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="O35">
         <v>0.25</v>
       </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
       <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="X35">
         <v>12003100001</v>
       </c>
-      <c r="W35">
+      <c r="Y35">
         <v>12003100001</v>
       </c>
-      <c r="X35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" ht="14.25" spans="1:24">
+      <c r="Z35" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" ht="14.25" customHeight="1" spans="1:26">
       <c r="A36">
         <v>12003200001</v>
       </c>
@@ -2902,32 +3125,38 @@
       <c r="D36">
         <v>3</v>
       </c>
-      <c r="H36" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>105</v>
+      <c r="H36" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="J36" t="s">
-        <v>91</v>
-      </c>
-      <c r="L36" s="11" t="s">
-        <v>75</v>
+        <v>95</v>
+      </c>
+      <c r="L36" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="O36">
         <v>0.25</v>
       </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
       <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="X36">
         <v>12003200001</v>
       </c>
-      <c r="W36">
+      <c r="Y36">
         <v>12003200001</v>
       </c>
-      <c r="X36" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" spans="1:24">
+      <c r="Z36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1" spans="1:26">
       <c r="A37">
         <v>12003300001</v>
       </c>
@@ -2937,32 +3166,38 @@
       <c r="D37">
         <v>3</v>
       </c>
-      <c r="H37" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>105</v>
+      <c r="H37" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>64</v>
-      </c>
-      <c r="L37" s="11" t="s">
-        <v>75</v>
+        <v>68</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="O37">
         <v>0.25</v>
       </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
       <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="X37">
         <v>12003300001</v>
       </c>
-      <c r="W37">
+      <c r="Y37">
         <v>12003300001</v>
       </c>
-      <c r="X37" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="38" ht="14.25" spans="1:24">
+      <c r="Z37" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1" spans="1:26">
       <c r="A38">
         <v>12003400001</v>
       </c>
@@ -2972,32 +3207,38 @@
       <c r="D38">
         <v>3</v>
       </c>
-      <c r="H38" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>105</v>
+      <c r="H38" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="J38" t="s">
-        <v>77</v>
-      </c>
-      <c r="L38" s="11" t="s">
-        <v>75</v>
+        <v>81</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="O38">
         <v>0.25</v>
       </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
       <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="X38">
         <v>12003400001</v>
       </c>
-      <c r="W38">
+      <c r="Y38">
         <v>12003400001</v>
       </c>
-      <c r="X38" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="1:24">
+      <c r="Z38" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" spans="1:26">
       <c r="A39">
         <v>12010100001</v>
       </c>
@@ -3007,26 +3248,32 @@
       <c r="D39">
         <v>3</v>
       </c>
-      <c r="H39" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="I39" s="12" t="s">
-        <v>99</v>
+      <c r="H39" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I39" s="13" t="s">
+        <v>103</v>
       </c>
       <c r="L39" t="s">
-        <v>100</v>
+        <v>104</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
       </c>
       <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="X39">
         <v>12010100001</v>
       </c>
-      <c r="W39">
+      <c r="Y39">
         <v>12010100001</v>
       </c>
-      <c r="X39" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40" ht="14.25" spans="1:24">
+      <c r="Z39" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1" spans="1:26">
       <c r="A40">
         <v>12010200001</v>
       </c>
@@ -3036,26 +3283,32 @@
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>105</v>
+      <c r="H40" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="L40" t="s">
-        <v>106</v>
+        <v>110</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
       </c>
       <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="X40">
         <v>12010200001</v>
       </c>
-      <c r="W40">
+      <c r="Y40">
         <v>12010200001</v>
       </c>
-      <c r="X40" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="41" ht="14.25" spans="1:24">
+      <c r="Z40" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1" spans="1:26">
       <c r="A41">
         <v>12010300001</v>
       </c>
@@ -3065,26 +3318,32 @@
       <c r="D41">
         <v>3</v>
       </c>
-      <c r="H41" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>105</v>
+      <c r="H41" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="L41" t="s">
-        <v>118</v>
+        <v>122</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
       </c>
       <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="X41">
         <v>12010300001</v>
       </c>
-      <c r="W41">
+      <c r="Y41">
         <v>12010300001</v>
       </c>
-      <c r="X41" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" ht="14.25" spans="1:24">
+      <c r="Z41" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1" spans="1:26">
       <c r="A42">
         <v>12011100001</v>
       </c>
@@ -3094,26 +3353,32 @@
       <c r="D42">
         <v>3</v>
       </c>
-      <c r="H42" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="I42" s="12" t="s">
-        <v>99</v>
+      <c r="H42" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I42" s="13" t="s">
+        <v>103</v>
       </c>
       <c r="L42" t="s">
-        <v>121</v>
+        <v>125</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
       </c>
       <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="X42">
         <v>12011100001</v>
       </c>
-      <c r="W42">
+      <c r="Y42">
         <v>12011100001</v>
       </c>
-      <c r="X42" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="43" ht="14.25" spans="1:24">
+      <c r="Z42" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1" spans="1:26">
       <c r="A43">
         <v>12011200001</v>
       </c>
@@ -3123,26 +3388,32 @@
       <c r="D43">
         <v>3</v>
       </c>
-      <c r="H43" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>105</v>
+      <c r="H43" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="L43" t="s">
-        <v>123</v>
+        <v>127</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
       </c>
       <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="X43">
         <v>12011200001</v>
       </c>
-      <c r="W43">
+      <c r="Y43">
         <v>12011200001</v>
       </c>
-      <c r="X43" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" spans="1:24">
+      <c r="Z43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1" spans="1:26">
       <c r="A44">
         <v>12011300001</v>
       </c>
@@ -3152,26 +3423,32 @@
       <c r="D44">
         <v>3</v>
       </c>
-      <c r="H44" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>105</v>
+      <c r="H44" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>109</v>
       </c>
       <c r="L44" t="s">
-        <v>125</v>
+        <v>129</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
       </c>
       <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="X44">
         <v>12011300001</v>
       </c>
-      <c r="W44">
+      <c r="Y44">
         <v>12011300001</v>
       </c>
-      <c r="X44" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z44" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A45" s="2">
         <v>13000100001</v>
       </c>
@@ -3181,27 +3458,33 @@
       <c r="D45" s="2">
         <v>4</v>
       </c>
-      <c r="H45" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I45" s="4"/>
+      <c r="H45" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I45" s="5"/>
       <c r="M45" s="2">
         <v>2</v>
       </c>
       <c r="T45" s="2">
         <v>3</v>
       </c>
-      <c r="V45" s="2">
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="X45" s="2">
         <v>13000100001</v>
       </c>
-      <c r="W45" s="2">
+      <c r="Y45" s="2">
         <v>13000100001</v>
       </c>
-      <c r="X45" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z45" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A46" s="2">
         <v>13000300001</v>
       </c>
@@ -3212,26 +3495,32 @@
         <v>4</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J46" s="4"/>
-      <c r="U46" s="2">
+        <v>133</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J46" s="5"/>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46" s="2">
         <v>500001</v>
       </c>
-      <c r="V46" s="2">
+      <c r="X46" s="2">
         <v>13000300001</v>
       </c>
-      <c r="W46" s="2">
+      <c r="Y46" s="2">
         <v>13000300001</v>
       </c>
-      <c r="X46" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z46" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A47" s="2">
         <v>13000400001</v>
       </c>
@@ -3242,10 +3531,10 @@
         <v>4</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>134</v>
       </c>
       <c r="J47" s="2">
         <v>300001</v>
@@ -3253,17 +3542,23 @@
       <c r="O47" s="2">
         <v>1</v>
       </c>
-      <c r="V47" s="2">
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="X47" s="2">
         <v>13000400001</v>
       </c>
-      <c r="W47" s="2">
+      <c r="Y47" s="2">
         <v>13000400001</v>
       </c>
-      <c r="X47" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z47" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A48" s="2">
         <v>13000500001</v>
       </c>
@@ -3274,12 +3569,12 @@
         <v>4</v>
       </c>
       <c r="H48" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I48" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="I48" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J48" s="4">
+      <c r="J48" s="5">
         <v>1</v>
       </c>
       <c r="O48" s="2">
@@ -3288,17 +3583,23 @@
       <c r="P48" s="2">
         <v>0.01</v>
       </c>
-      <c r="V48" s="2">
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="X48" s="2">
         <v>13000500001</v>
       </c>
-      <c r="W48" s="2">
+      <c r="Y48" s="2">
         <v>13000500001</v>
       </c>
-      <c r="X48" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z48" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A49" s="2">
         <v>13000600001</v>
       </c>
@@ -3309,12 +3610,12 @@
         <v>4</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="J49" s="4">
+        <v>140</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J49" s="5">
         <v>1</v>
       </c>
       <c r="O49" s="2">
@@ -3323,17 +3624,23 @@
       <c r="P49" s="2">
         <v>0.01</v>
       </c>
-      <c r="V49" s="2">
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="X49" s="2">
         <v>13000600001</v>
       </c>
-      <c r="W49" s="2">
+      <c r="Y49" s="2">
         <v>13000600001</v>
       </c>
-      <c r="X49" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" ht="14.25" spans="1:24">
+      <c r="Z49" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A50" s="2">
         <v>13000700001</v>
       </c>
@@ -3344,23 +3651,29 @@
         <v>4</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>130</v>
+        <v>142</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>134</v>
       </c>
       <c r="Q50" s="2">
         <v>0.2</v>
       </c>
       <c r="R50" s="2"/>
-      <c r="V50" s="2">
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="X50" s="2">
         <v>13000700001</v>
       </c>
-      <c r="W50" s="2">
+      <c r="Y50" s="2">
         <v>13000700001</v>
       </c>
-      <c r="X50" s="2" t="s">
-        <v>139</v>
+      <c r="Z50" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1"/>
@@ -3384,9 +3697,6 @@
     <row r="100" ht="12" customHeight="1"/>
     <row r="101" ht="12" customHeight="1"/>
   </sheetData>
-  <sortState ref="A4:AG88">
-    <sortCondition ref="A4"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z65"/>
+  <dimension ref="A1:Z70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2823,220 +2823,220 @@
       </c>
     </row>
     <row r="31" customFormat="1" s="2">
-      <c r="A31" t="n">
+      <c r="A31" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="C31" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="C31" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O31" t="n">
+      <c r="O31" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
+      <c r="U31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Y31" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z31" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV1-所有魔物攻击力增加10%</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="2">
-      <c r="A32" t="n">
+      <c r="A32" s="0" t="n">
         <v>3000500002</v>
       </c>
-      <c r="C32" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="C32" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O32" t="n">
+      <c r="O32" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
+      <c r="U32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Y32" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="Z32" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV2-所有魔物攻击力增加20%</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="2">
-      <c r="A33" t="n">
+      <c r="A33" s="0" t="n">
         <v>3000500003</v>
       </c>
-      <c r="C33" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="C33" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O33" t="n">
+      <c r="O33" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
+      <c r="U33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Y33" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="Z33" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV3-所有魔物攻击力增加30%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" s="3">
-      <c r="A34" t="n">
+      <c r="A34" s="0" t="n">
         <v>3000500004</v>
       </c>
-      <c r="C34" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="C34" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O34" t="n">
+      <c r="O34" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
+      <c r="U34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Y34" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="Z34" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV4-所有魔物攻击力增加40%</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="3">
-      <c r="A35" t="n">
+      <c r="A35" s="0" t="n">
         <v>3000500005</v>
       </c>
-      <c r="C35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="C35" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O35" t="n">
+      <c r="O35" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
+      <c r="U35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y35" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="Z35" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV5-所有魔物攻击力增加50%</t>
         </is>
@@ -4438,8 +4438,226 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="3"/>
-    <row r="70" ht="15" customHeight="1" s="3"/>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3000600002</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3000600003</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="3">
+      <c r="A69" t="n">
+        <v>3000600004</v>
+      </c>
+      <c r="C69" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="3">
+      <c r="A70" t="n">
+        <v>3000600005</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
+        </is>
+      </c>
+    </row>
     <row r="71" ht="15" customHeight="1" s="3"/>
     <row r="103" ht="12" customHeight="1" s="3"/>
     <row r="104" ht="12" customHeight="1" s="3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z70"/>
+  <dimension ref="A1:Z80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="Z21" s="0" t="inlineStr">
         <is>
-          <t>强征健体-所有魔物体力增加10%</t>
+          <t>强身健体-所有魔物体力增加10%</t>
         </is>
       </c>
     </row>
@@ -3043,884 +3043,803 @@
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
-      <c r="A36" s="2" t="n">
+      <c r="A36" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="14.25" customHeight="1" s="3">
+      <c r="A37" t="n">
+        <v>3000600002</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="14.25" customHeight="1" s="3">
+      <c r="A38" t="n">
+        <v>3000600003</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="14.25" customHeight="1" s="3">
+      <c r="A39" t="n">
+        <v>3000600004</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="14.25" customHeight="1" s="3">
+      <c r="A40" t="n">
+        <v>3000600005</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14.25" customHeight="1" s="3">
+      <c r="A41" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>唯快不破LV1-所有魔物攻击速度增加10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="14.25" customHeight="1" s="3">
+      <c r="A42" t="n">
+        <v>3000700002</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>唯快不破LV2-所有魔物攻击速度增加20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="14.25" customHeight="1" s="3">
+      <c r="A43" t="n">
+        <v>3000700003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>唯快不破LV3-所有魔物攻击速度增加30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14.25" customHeight="1" s="3">
+      <c r="A44" t="n">
+        <v>3000700004</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>唯快不破LV4-所有魔物攻击速度增加40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="14.25" customHeight="1" s="3">
+      <c r="A45" t="n">
+        <v>3000700005</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>3000700001</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>唯快不破LV5-所有魔物攻击速度增加50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1" s="3">
+      <c r="A46" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>坚不可摧LV1-所有魔物护甲增加10%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1" s="3">
+      <c r="A47" t="n">
+        <v>3000800002</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>坚不可摧LV2-所有魔物护甲增加20%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1" s="3">
+      <c r="A48" t="n">
+        <v>3000800003</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>坚不可摧LV3-所有魔物护甲增加30%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="3">
+      <c r="A49" t="n">
+        <v>3000800004</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>坚不可摧LV4-所有魔物护甲增加40%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14.25" customHeight="1" s="3">
+      <c r="A50" t="n">
+        <v>3000800005</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>坚不可摧LV5-所有魔物护甲增加50%(无护甲则无加成)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="14.25" customHeight="1" s="3">
+      <c r="A51" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C51" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D36" s="2" t="n">
+      <c r="D51" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="inlineStr">
+      <c r="I51" s="2" t="n"/>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="O36" s="2" t="n">
+      <c r="O51" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P36" s="2" t="n">
+      <c r="P51" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="U36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" s="2" t="n">
+      <c r="U51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="Y36" s="2" t="n">
+      <c r="Y51" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z51" s="2" t="inlineStr">
         <is>
           <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="14.25" customHeight="1" s="3">
-      <c r="A37" s="2" t="n">
+    <row r="52" ht="14.25" customHeight="1" s="3">
+      <c r="A52" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C52" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="I52" s="2" t="n"/>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O37" s="2" t="n">
+      <c r="O52" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P37" s="2" t="n">
+      <c r="P52" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="U37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" s="2" t="n">
+      <c r="U52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="Y37" s="2" t="n">
+      <c r="Y52" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
+      <c r="Z52" s="2" t="inlineStr">
         <is>
           <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="14.25" customHeight="1" s="3">
-      <c r="A38" s="2" t="n">
+    <row r="53" ht="14.25" customHeight="1" s="3">
+      <c r="A53" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C53" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D53" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="inlineStr">
+      <c r="I53" s="2" t="n"/>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O38" s="2" t="n">
+      <c r="O53" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P38" s="2" t="n">
+      <c r="P53" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="U38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" s="2" t="n">
+      <c r="U53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y38" s="2" t="n">
+      <c r="Y53" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Z38" s="2" t="inlineStr">
+      <c r="Z53" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="14.25" customHeight="1" s="3">
-      <c r="A39" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="C39" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D39" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityBaseHPChange</t>
-        </is>
-      </c>
-      <c r="I39" s="8" t="n"/>
-      <c r="O39" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P39" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T39" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="U39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" s="0" t="n">
-        <v>500001</v>
-      </c>
-      <c r="X39" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="Y39" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="Z39" s="0" t="inlineStr">
-        <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="14.25" customHeight="1" s="3">
-      <c r="A40" s="0" t="n">
-        <v>12000200001</v>
-      </c>
-      <c r="C40" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D40" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityBaseDRChange</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="n"/>
-      <c r="O40" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P40" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T40" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="U40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="0" t="n">
-        <v>500002</v>
-      </c>
-      <c r="X40" s="0" t="n">
-        <v>12000200001</v>
-      </c>
-      <c r="Y40" s="0" t="n">
-        <v>12000200001</v>
-      </c>
-      <c r="Z40" s="0" t="inlineStr">
-        <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="14.25" customHeight="1" s="3">
-      <c r="A41" s="0" t="n">
-        <v>12000300001</v>
-      </c>
-      <c r="C41" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D41" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="n"/>
-      <c r="T41" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="U41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" s="0" t="n">
-        <v>12000300001</v>
-      </c>
-      <c r="Y41" s="0" t="n">
-        <v>12000300001</v>
-      </c>
-      <c r="Z41" s="0" t="inlineStr">
-        <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="14.25" customHeight="1" s="3">
-      <c r="A42" s="0" t="n">
-        <v>12001100001</v>
-      </c>
-      <c r="C42" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D42" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J42" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L42" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O42" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" s="0" t="n">
-        <v>12001100001</v>
-      </c>
-      <c r="Y42" s="0" t="n">
-        <v>12001100001</v>
-      </c>
-      <c r="Z42" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="14.25" customHeight="1" s="3">
-      <c r="A43" s="0" t="n">
-        <v>12001200001</v>
-      </c>
-      <c r="C43" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D43" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J43" s="0" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L43" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O43" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U43" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="0" t="n">
-        <v>12001200001</v>
-      </c>
-      <c r="Y43" s="0" t="n">
-        <v>12001200001</v>
-      </c>
-      <c r="Z43" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1" s="3">
-      <c r="A44" s="0" t="n">
-        <v>12001300001</v>
-      </c>
-      <c r="C44" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D44" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J44" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L44" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O44" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U44" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="0" t="n">
-        <v>12001300001</v>
-      </c>
-      <c r="Y44" s="0" t="n">
-        <v>12001300001</v>
-      </c>
-      <c r="Z44" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="14.25" customHeight="1" s="3">
-      <c r="A45" s="0" t="n">
-        <v>12001400001</v>
-      </c>
-      <c r="C45" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D45" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J45" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L45" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O45" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U45" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="0" t="n">
-        <v>12001400001</v>
-      </c>
-      <c r="Y45" s="0" t="n">
-        <v>12001400001</v>
-      </c>
-      <c r="Z45" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="14.25" customHeight="1" s="3">
-      <c r="A46" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="C46" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D46" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J46" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L46" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O46" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="Y46" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="Z46" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="14.25" customHeight="1" s="3">
-      <c r="A47" s="0" t="n">
-        <v>12002200001</v>
-      </c>
-      <c r="C47" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D47" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J47" s="0" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L47" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O47" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U47" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="0" t="n">
-        <v>12002200001</v>
-      </c>
-      <c r="Y47" s="0" t="n">
-        <v>12002200001</v>
-      </c>
-      <c r="Z47" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1" s="3">
-      <c r="A48" s="0" t="n">
-        <v>12002300001</v>
-      </c>
-      <c r="C48" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D48" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J48" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L48" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O48" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="0" t="n">
-        <v>12002300001</v>
-      </c>
-      <c r="Y48" s="0" t="n">
-        <v>12002300001</v>
-      </c>
-      <c r="Z48" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="3">
-      <c r="A49" s="0" t="n">
-        <v>12002400001</v>
-      </c>
-      <c r="C49" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D49" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J49" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L49" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O49" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="0" t="n">
-        <v>12002400001</v>
-      </c>
-      <c r="Y49" s="0" t="n">
-        <v>12002400001</v>
-      </c>
-      <c r="Z49" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1" s="3">
-      <c r="A50" s="0" t="n">
-        <v>12003100001</v>
-      </c>
-      <c r="C50" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D50" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I50" s="11" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J50" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
-        </is>
-      </c>
-      <c r="O50" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" s="0" t="n">
-        <v>12003100001</v>
-      </c>
-      <c r="Y50" s="0" t="n">
-        <v>12003100001</v>
-      </c>
-      <c r="Z50" s="0" t="inlineStr">
-        <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="14.25" customHeight="1" s="3">
-      <c r="A51" s="0" t="n">
-        <v>12003200001</v>
-      </c>
-      <c r="C51" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D51" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I51" s="11" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J51" s="0" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
-        </is>
-      </c>
-      <c r="O51" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="0" t="n">
-        <v>12003200001</v>
-      </c>
-      <c r="Y51" s="0" t="n">
-        <v>12003200001</v>
-      </c>
-      <c r="Z51" s="0" t="inlineStr">
-        <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="14.25" customHeight="1" s="3">
-      <c r="A52" s="0" t="n">
-        <v>12003300001</v>
-      </c>
-      <c r="C52" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D52" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J52" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
-        </is>
-      </c>
-      <c r="O52" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" s="0" t="n">
-        <v>12003300001</v>
-      </c>
-      <c r="Y52" s="0" t="n">
-        <v>12003300001</v>
-      </c>
-      <c r="Z52" s="0" t="inlineStr">
-        <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="14.25" customHeight="1" s="3">
-      <c r="A53" s="0" t="n">
-        <v>12003400001</v>
-      </c>
-      <c r="C53" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D53" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J53" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
-        </is>
-      </c>
-      <c r="O53" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="0" t="n">
-        <v>12003400001</v>
-      </c>
-      <c r="Y53" s="0" t="n">
-        <v>12003400001</v>
-      </c>
-      <c r="Z53" s="0" t="inlineStr">
-        <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>12010100001</v>
+        <v>12000100001</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>12</v>
@@ -3928,20 +3847,20 @@
       <c r="D54" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H54" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L54" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityBaseHPChange</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="n"/>
+      <c r="O54" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P54" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T54" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="U54" s="0" t="n">
         <v>0</v>
@@ -3949,21 +3868,24 @@
       <c r="V54" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="W54" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="X54" s="0" t="n">
-        <v>12010100001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y54" s="0" t="n">
-        <v>12010100001</v>
+        <v>12000100001</v>
       </c>
       <c r="Z54" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>12010200001</v>
+        <v>12000200001</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>12</v>
@@ -3971,20 +3893,20 @@
       <c r="D55" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H55" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L55" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityBaseDRChange</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="n"/>
+      <c r="O55" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P55" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T55" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="U55" s="0" t="n">
         <v>0</v>
@@ -3992,21 +3914,24 @@
       <c r="V55" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="W55" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="X55" s="0" t="n">
-        <v>12010200001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y55" s="0" t="n">
-        <v>12010200001</v>
+        <v>12000200001</v>
       </c>
       <c r="Z55" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>12010300001</v>
+        <v>12000300001</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>12</v>
@@ -4014,20 +3939,14 @@
       <c r="D56" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H56" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L56" s="0" t="inlineStr">
-        <is>
-          <t>4001:1000&amp;</t>
-        </is>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="I56" s="8" t="n"/>
+      <c r="T56" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="U56" s="0" t="n">
         <v>0</v>
@@ -4036,20 +3955,20 @@
         <v>0</v>
       </c>
       <c r="X56" s="0" t="n">
-        <v>12010300001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y56" s="0" t="n">
-        <v>12010300001</v>
+        <v>12000300001</v>
       </c>
       <c r="Z56" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>12011100001</v>
+        <v>12001100001</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>12</v>
@@ -4059,18 +3978,26 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
+      <c r="J57" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
       <c r="L57" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
-        </is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O57" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="U57" s="0" t="n">
         <v>0</v>
@@ -4079,20 +4006,20 @@
         <v>0</v>
       </c>
       <c r="X57" s="0" t="n">
-        <v>12011100001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y57" s="0" t="n">
-        <v>12011100001</v>
+        <v>12001100001</v>
       </c>
       <c r="Z57" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="0" t="n">
-        <v>12011200001</v>
+        <v>12001200001</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>12</v>
@@ -4102,18 +4029,26 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
         </is>
       </c>
       <c r="L58" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
-        </is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O58" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="U58" s="0" t="n">
         <v>0</v>
@@ -4122,20 +4057,20 @@
         <v>0</v>
       </c>
       <c r="X58" s="0" t="n">
-        <v>12011200001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y58" s="0" t="n">
-        <v>12011200001</v>
+        <v>12001200001</v>
       </c>
       <c r="Z58" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="0" t="n">
-        <v>12011300001</v>
+        <v>12001300001</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>12</v>
@@ -4145,520 +4080,1024 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J59" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L59" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O59" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="0" t="n">
+        <v>12001300001</v>
+      </c>
+      <c r="Y59" s="0" t="n">
+        <v>12001300001</v>
+      </c>
+      <c r="Z59" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A60" s="0" t="n">
+        <v>12001400001</v>
+      </c>
+      <c r="C60" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L60" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O60" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="0" t="n">
+        <v>12001400001</v>
+      </c>
+      <c r="Y60" s="0" t="n">
+        <v>12001400001</v>
+      </c>
+      <c r="Z60" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="C61" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J61" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L61" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O61" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="Y61" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="Z61" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="C62" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D62" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J62" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L62" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O62" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="Y62" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="Z62" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="C63" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D63" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J63" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L63" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O63" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="Y63" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="Z63" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="C64" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J64" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L64" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O64" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="Y64" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="Z64" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="C65" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D65" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O65" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="Y65" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="Z65" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="C66" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D66" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J66" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L66" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O66" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="Y66" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="Z66" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="C67" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D67" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J67" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O67" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U67" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="Y67" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="Z67" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="C68" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D68" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J68" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L68" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O68" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="U68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="Y68" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="Z68" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="3">
+      <c r="A69" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="C69" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D69" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H69" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L69" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="U69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="Y69" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="Z69" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="3">
+      <c r="A70" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="C70" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D70" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L70" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="U70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="Y70" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="Z70" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="3">
+      <c r="A71" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="C71" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D71" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H71" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L71" s="0" t="inlineStr">
+        <is>
+          <t>4001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="U71" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="Y71" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="Z71" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="C72" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D72" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
           <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr">
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
+      </c>
+      <c r="U72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="Y72" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="Z72" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="C73" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D73" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
-      <c r="L59" s="0" t="inlineStr">
+      <c r="L73" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
+      </c>
+      <c r="U73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="Y73" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="Z73" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L74" s="0" t="inlineStr">
         <is>
           <t>4001:200&amp;</t>
         </is>
       </c>
-      <c r="U59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" s="0" t="n">
+      <c r="U74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="0" t="n">
         <v>12011300001</v>
       </c>
-      <c r="Y59" s="0" t="n">
+      <c r="Y74" s="0" t="n">
         <v>12011300001</v>
       </c>
-      <c r="Z59" s="0" t="inlineStr">
+      <c r="Z74" s="0" t="inlineStr">
         <is>
           <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A60" s="2" t="n">
+    <row r="75">
+      <c r="A75" s="2" t="n">
         <v>13000100001</v>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C75" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D60" s="2" t="n">
+      <c r="D75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>BuffEntityPeriodicPickupCrystal</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n"/>
-      <c r="M60" s="2" t="n">
+      <c r="I75" s="5" t="n"/>
+      <c r="M75" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="T60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" s="2" t="n">
+      <c r="T75" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="2" t="n">
         <v>13000100001</v>
       </c>
-      <c r="Y60" s="2" t="n">
+      <c r="Y75" s="2" t="n">
         <v>13000100001</v>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
         <is>
           <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
+    <row r="76">
+      <c r="A76" s="2" t="n">
         <v>13000300001</v>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C76" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D61" s="2" t="n">
+      <c r="D76" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>BuffEntityConditionalDeadRebirth</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J61" s="5" t="n"/>
-      <c r="U61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="2" t="n">
+      <c r="J76" s="5" t="n"/>
+      <c r="U76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="2" t="n">
         <v>500001</v>
       </c>
-      <c r="X61" s="2" t="n">
+      <c r="X76" s="2" t="n">
         <v>13000300001</v>
       </c>
-      <c r="Y61" s="2" t="n">
+      <c r="Y76" s="2" t="n">
         <v>13000300001</v>
       </c>
-      <c r="Z61" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>死亡后重生</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
+    <row r="77">
+      <c r="A77" s="2" t="n">
         <v>13000400001</v>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C77" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D62" s="2" t="n">
+      <c r="D77" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>BuffEntityConditionalDeadAttack</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J62" s="2" t="n">
+      <c r="J77" s="2" t="n">
         <v>300001</v>
       </c>
-      <c r="O62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" s="2" t="n">
+      <c r="O77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="2" t="n">
         <v>13000400001</v>
       </c>
-      <c r="Y62" s="2" t="n">
+      <c r="Y77" s="2" t="n">
         <v>13000400001</v>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z77" s="2" t="inlineStr">
         <is>
           <t>死亡后爆炸</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+    <row r="78">
+      <c r="A78" s="2" t="n">
         <v>13000500001</v>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C78" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D63" s="2" t="n">
+      <c r="D78" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>BuffEntityConditionalDeadAreaHPChange</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O63" s="2" t="n">
+      <c r="J78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="P63" s="2" t="n">
+      <c r="P78" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="U63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="2" t="n">
+      <c r="U78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="2" t="n">
         <v>13000500001</v>
       </c>
-      <c r="Y63" s="2" t="n">
+      <c r="Y78" s="2" t="n">
         <v>13000500001</v>
       </c>
-      <c r="Z63" s="2" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
+    <row r="79">
+      <c r="A79" s="2" t="n">
         <v>13000600001</v>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C79" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D64" s="2" t="n">
+      <c r="D79" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>BuffEntityConditionalDeadAreaDRChange</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" s="2" t="n">
+      <c r="J79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="P64" s="2" t="n">
+      <c r="P79" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="U64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X64" s="2" t="n">
+      <c r="U79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="2" t="n">
         <v>13000600001</v>
       </c>
-      <c r="Y64" s="2" t="n">
+      <c r="Y79" s="2" t="n">
         <v>13000600001</v>
       </c>
-      <c r="Z64" s="2" t="inlineStr">
+      <c r="Z79" s="2" t="inlineStr">
         <is>
           <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
+    <row r="80">
+      <c r="A80" s="2" t="n">
         <v>13000700001</v>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C80" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="D65" s="2" t="n">
+      <c r="D80" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>BuffEntityConditionalDeadCreateCrystal</t>
         </is>
       </c>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q65" s="2" t="n">
+      <c r="Q80" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="R65" s="2" t="n"/>
-      <c r="U65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X65" s="2" t="n">
+      <c r="R80" s="2" t="n"/>
+      <c r="U80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="2" t="n">
         <v>13000700001</v>
       </c>
-      <c r="Y65" s="2" t="n">
+      <c r="Y80" s="2" t="n">
         <v>13000700001</v>
       </c>
-      <c r="Z65" s="2" t="inlineStr">
+      <c r="Z80" s="2" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="C66" t="n">
-        <v>3</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>MSPD</t>
-        </is>
-      </c>
-      <c r="O66" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>3000600002</v>
-      </c>
-      <c r="C67" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>2</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>MSPD</t>
-        </is>
-      </c>
-      <c r="O67" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>3000600003</v>
-      </c>
-      <c r="C68" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="n">
-        <v>2</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>MSPD</t>
-        </is>
-      </c>
-      <c r="O68" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="3">
-      <c r="A69" t="n">
-        <v>3000600004</v>
-      </c>
-      <c r="C69" t="n">
-        <v>3</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>2</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>MSPD</t>
-        </is>
-      </c>
-      <c r="O69" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="3">
-      <c r="A70" t="n">
-        <v>3000600005</v>
-      </c>
-      <c r="C70" t="n">
-        <v>3</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>2</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>MSPD</t>
-        </is>
-      </c>
-      <c r="O70" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="X70" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="3"/>
     <row r="103" ht="12" customHeight="1" s="3"/>
     <row r="104" ht="12" customHeight="1" s="3"/>
     <row r="105" ht="12" customHeight="1" s="3"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z80"/>
+  <dimension ref="A1:Z85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -3043,660 +3043,660 @@
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
-      <c r="A36" t="n">
+      <c r="A36" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="C36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="C36" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t>MSPD</t>
         </is>
       </c>
-      <c r="O36" t="n">
+      <c r="O36" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
+      <c r="S36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Y36" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="Z36" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
-      <c r="A37" t="n">
+      <c r="A37" s="0" t="n">
         <v>3000600002</v>
       </c>
-      <c r="C37" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="C37" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t>MSPD</t>
         </is>
       </c>
-      <c r="O37" t="n">
+      <c r="O37" s="0" t="n">
         <v>-0.2</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
+      <c r="S37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y37" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="Z37" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
-      <c r="A38" t="n">
+      <c r="A38" s="0" t="n">
         <v>3000600003</v>
       </c>
-      <c r="C38" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="C38" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t>MSPD</t>
         </is>
       </c>
-      <c r="O38" t="n">
+      <c r="O38" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
+      <c r="S38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y38" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="Z38" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
-      <c r="A39" t="n">
+      <c r="A39" s="0" t="n">
         <v>3000600004</v>
       </c>
-      <c r="C39" t="n">
-        <v>3</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="C39" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="0" t="inlineStr">
         <is>
           <t>MSPD</t>
         </is>
       </c>
-      <c r="O39" t="n">
+      <c r="O39" s="0" t="n">
         <v>-0.4</v>
       </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
+      <c r="S39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Y39" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="Z39" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
-      <c r="A40" t="n">
+      <c r="A40" s="0" t="n">
         <v>3000600005</v>
       </c>
-      <c r="C40" t="n">
-        <v>3</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="C40" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="0" t="inlineStr">
         <is>
           <t>MSPD</t>
         </is>
       </c>
-      <c r="O40" t="n">
+      <c r="O40" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
+      <c r="S40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Y40" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="Z40" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
-      <c r="A41" t="n">
+      <c r="A41" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="C41" t="n">
-        <v>3</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="inlineStr">
+      <c r="C41" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="0" t="inlineStr">
         <is>
           <t>ASPD</t>
         </is>
       </c>
-      <c r="O41" t="n">
+      <c r="O41" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
+      <c r="U41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Y41" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV1-所有魔物攻击速度增加10%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
-      <c r="A42" t="n">
+      <c r="A42" s="0" t="n">
         <v>3000700002</v>
       </c>
-      <c r="C42" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="inlineStr">
+      <c r="C42" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="0" t="inlineStr">
         <is>
           <t>ASPD</t>
         </is>
       </c>
-      <c r="O42" t="n">
+      <c r="O42" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
+      <c r="U42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y42" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z42" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV2-所有魔物攻击速度增加20%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
-      <c r="A43" t="n">
+      <c r="A43" s="0" t="n">
         <v>3000700003</v>
       </c>
-      <c r="C43" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="C43" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="0" t="inlineStr">
         <is>
           <t>ASPD</t>
         </is>
       </c>
-      <c r="O43" t="n">
+      <c r="O43" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
+      <c r="U43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Y43" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z43" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV3-所有魔物攻击速度增加30%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
-      <c r="A44" t="n">
+      <c r="A44" s="0" t="n">
         <v>3000700004</v>
       </c>
-      <c r="C44" t="n">
-        <v>3</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="C44" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="0" t="inlineStr">
         <is>
           <t>ASPD</t>
         </is>
       </c>
-      <c r="O44" t="n">
+      <c r="O44" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
+      <c r="U44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Y44" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="Z44" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV4-所有魔物攻击速度增加40%</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
-      <c r="A45" t="n">
+      <c r="A45" s="0" t="n">
         <v>3000700005</v>
       </c>
-      <c r="C45" t="n">
-        <v>3</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="C45" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="0" t="inlineStr">
         <is>
           <t>ASPD</t>
         </is>
       </c>
-      <c r="O45" t="n">
+      <c r="O45" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
+      <c r="U45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Y45" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z45" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV5-所有魔物攻击速度增加50%</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="3">
-      <c r="A46" t="n">
+      <c r="A46" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="C46" t="n">
-        <v>3</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="C46" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="0" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O46" t="n">
+      <c r="O46" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
+      <c r="U46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Y46" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="Z46" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV1-所有魔物护甲增加10%(无护甲则无加成)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="3">
-      <c r="A47" t="n">
+      <c r="A47" s="0" t="n">
         <v>3000800002</v>
       </c>
-      <c r="C47" t="n">
-        <v>3</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="C47" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="0" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O47" t="n">
+      <c r="O47" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
+      <c r="U47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Y47" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="Z47" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV2-所有魔物护甲增加20%(无护甲则无加成)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="3">
-      <c r="A48" t="n">
+      <c r="A48" s="0" t="n">
         <v>3000800003</v>
       </c>
-      <c r="C48" t="n">
-        <v>3</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" t="inlineStr">
+      <c r="C48" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="0" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O48" t="n">
+      <c r="O48" s="0" t="n">
         <v>0.3</v>
       </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
+      <c r="U48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Y48" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="Z48" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV3-所有魔物护甲增加30%(无护甲则无加成)</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="3">
-      <c r="A49" t="n">
+      <c r="A49" s="0" t="n">
         <v>3000800004</v>
       </c>
-      <c r="C49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" t="inlineStr">
+      <c r="C49" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="0" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="O49" s="0" t="n">
         <v>0.4</v>
       </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
+      <c r="U49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y49" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="Z49" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV4-所有魔物护甲增加40%(无护甲则无加成)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="3">
-      <c r="A50" t="n">
+      <c r="A50" s="0" t="n">
         <v>3000800005</v>
       </c>
-      <c r="C50" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="inlineStr">
+      <c r="C50" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="0" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O50" t="n">
+      <c r="O50" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
+      <c r="U50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Y50" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="Z50" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV5-所有魔物护甲增加50%(无护甲则无加成)</t>
         </is>
@@ -3704,31 +3704,23 @@
     </row>
     <row r="51" ht="14.25" customHeight="1" s="3">
       <c r="A51" s="2" t="n">
-        <v>11000100001</v>
+        <v>3000900001</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityInstantRewardMoreItem</t>
         </is>
       </c>
       <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="J51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
       <c r="U51" s="0" t="n">
         <v>0</v>
       </c>
@@ -3736,44 +3728,36 @@
         <v>0</v>
       </c>
       <c r="X51" s="2" t="n">
-        <v>11000100001</v>
+        <v>3000900001</v>
       </c>
       <c r="Y51" s="2" t="n">
-        <v>11000100001</v>
+        <v>3000900001</v>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>生命增加{Percentage}%</t>
+          <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="3">
       <c r="A52" s="2" t="n">
-        <v>11000200001</v>
+        <v>3001000001</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityInstantRewardMoreSelect</t>
         </is>
       </c>
       <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P52" s="2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
       <c r="U52" s="0" t="n">
         <v>0</v>
       </c>
@@ -3781,20 +3765,20 @@
         <v>0</v>
       </c>
       <c r="X52" s="2" t="n">
-        <v>11000200001</v>
+        <v>3001000001</v>
       </c>
       <c r="Y52" s="2" t="n">
-        <v>11000200001</v>
+        <v>3001000001</v>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>护甲增加{Percentage}%</t>
+          <t>再来一瓶-通关奖励可选次数+1</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
       <c r="A53" s="2" t="n">
-        <v>11000300001</v>
+        <v>11000100001</v>
       </c>
       <c r="C53" s="2" t="n">
         <v>11</v>
@@ -3810,7 +3794,7 @@
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="O53" s="2" t="n">
@@ -3826,127 +3810,132 @@
         <v>0</v>
       </c>
       <c r="X53" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="Y53" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="14.25" customHeight="1" s="3">
+      <c r="A54" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="Y54" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A55" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y53" s="2" t="n">
+      <c r="C55" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Y55" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="14.25" customHeight="1" s="3">
-      <c r="A54" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="C54" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D54" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityBaseHPChange</t>
-        </is>
-      </c>
-      <c r="I54" s="8" t="n"/>
-      <c r="O54" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P54" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T54" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="U54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="0" t="n">
-        <v>500001</v>
-      </c>
-      <c r="X54" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="Y54" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="Z54" s="0" t="inlineStr">
-        <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A55" s="0" t="n">
-        <v>12000200001</v>
-      </c>
-      <c r="C55" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D55" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityBaseDRChange</t>
-        </is>
-      </c>
-      <c r="I55" s="8" t="n"/>
-      <c r="O55" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P55" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T55" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="U55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" s="0" t="n">
-        <v>500002</v>
-      </c>
-      <c r="X55" s="0" t="n">
-        <v>12000200001</v>
-      </c>
-      <c r="Y55" s="0" t="n">
-        <v>12000200001</v>
-      </c>
-      <c r="Z55" s="0" t="inlineStr">
-        <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000400001</v>
       </c>
       <c r="C56" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
-      </c>
-      <c r="I56" s="8" t="n"/>
-      <c r="T56" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J56" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="O56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" s="0" t="n">
+        <v>0.5</v>
       </c>
       <c r="U56" s="0" t="n">
         <v>0</v>
@@ -3955,49 +3944,42 @@
         <v>0</v>
       </c>
       <c r="X56" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000400001</v>
       </c>
       <c r="Y56" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000400001</v>
       </c>
       <c r="Z56" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000500001</v>
       </c>
       <c r="C57" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+        <v>2</v>
+      </c>
+      <c r="H57" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L57" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O57" s="0" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
+      </c>
+      <c r="P57" s="0" t="n">
+        <v>-0.5</v>
       </c>
       <c r="U57" s="0" t="n">
         <v>0</v>
@@ -4006,49 +3988,42 @@
         <v>0</v>
       </c>
       <c r="X57" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y57" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000500001</v>
       </c>
       <c r="Z57" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="0" t="n">
-        <v>12001200001</v>
+        <v>11000600001</v>
       </c>
       <c r="C58" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D58" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+        <v>2</v>
+      </c>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L58" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O58" s="0" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
+      </c>
+      <c r="P58" s="0" t="n">
+        <v>-0.5</v>
       </c>
       <c r="U58" s="0" t="n">
         <v>0</v>
@@ -4057,20 +4032,20 @@
         <v>0</v>
       </c>
       <c r="X58" s="0" t="n">
-        <v>12001200001</v>
+        <v>11000600001</v>
       </c>
       <c r="Y58" s="0" t="n">
-        <v>12001200001</v>
+        <v>11000600001</v>
       </c>
       <c r="Z58" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>12</v>
@@ -4080,26 +4055,18 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J59" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L59" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
+          <t>BuffEntityBaseHPChange</t>
+        </is>
+      </c>
+      <c r="I59" s="8" t="n"/>
       <c r="O59" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
+      </c>
+      <c r="P59" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T59" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="U59" s="0" t="n">
         <v>0</v>
@@ -4107,21 +4074,24 @@
       <c r="V59" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="W59" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="X59" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y59" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="Z59" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="C60" s="0" t="n">
         <v>12</v>
@@ -4131,26 +4101,18 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I60" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J60" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L60" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
+          <t>BuffEntityBaseDRChange</t>
+        </is>
+      </c>
+      <c r="I60" s="8" t="n"/>
       <c r="O60" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
+      </c>
+      <c r="P60" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T60" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="U60" s="0" t="n">
         <v>0</v>
@@ -4158,21 +4120,24 @@
       <c r="V60" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="W60" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="X60" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y60" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="Z60" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="C61" s="0" t="n">
         <v>12</v>
@@ -4180,28 +4145,14 @@
       <c r="D61" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J61" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L61" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O61" s="0" t="n">
-        <v>0.25</v>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="n"/>
+      <c r="T61" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="U61" s="0" t="n">
         <v>0</v>
@@ -4210,20 +4161,20 @@
         <v>0</v>
       </c>
       <c r="X61" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y61" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="Z61" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>12</v>
@@ -4231,24 +4182,24 @@
       <c r="D62" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L62" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O62" s="0" t="n">
@@ -4261,20 +4212,20 @@
         <v>0</v>
       </c>
       <c r="X62" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y62" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="Z62" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>12</v>
@@ -4282,24 +4233,24 @@
       <c r="D63" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L63" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O63" s="0" t="n">
@@ -4312,20 +4263,20 @@
         <v>0</v>
       </c>
       <c r="X63" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y63" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="Z63" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>12</v>
@@ -4333,24 +4284,24 @@
       <c r="D64" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L64" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O64" s="0" t="n">
@@ -4363,20 +4314,20 @@
         <v>0</v>
       </c>
       <c r="X64" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y64" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="Z64" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>12</v>
@@ -4389,19 +4340,19 @@
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J65" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L65" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L65" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O65" s="0" t="n">
@@ -4414,20 +4365,20 @@
         <v>0</v>
       </c>
       <c r="X65" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y65" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="Z65" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>12</v>
@@ -4435,24 +4386,24 @@
       <c r="D66" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I66" s="11" t="inlineStr">
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L66" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L66" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O66" s="0" t="n">
@@ -4465,20 +4416,20 @@
         <v>0</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y66" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="Z66" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>12</v>
@@ -4486,24 +4437,24 @@
       <c r="D67" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="8" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I67" s="11" t="inlineStr">
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L67" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L67" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O67" s="0" t="n">
@@ -4516,20 +4467,20 @@
         <v>0</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y67" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="Z67" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>12</v>
@@ -4537,24 +4488,24 @@
       <c r="D68" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I68" s="11" t="inlineStr">
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L68" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L68" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O68" s="0" t="n">
@@ -4567,20 +4518,20 @@
         <v>0</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y68" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="Z68" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>12010100001</v>
+        <v>12002400001</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>12</v>
@@ -4588,20 +4539,28 @@
       <c r="D69" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H69" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J69" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L69" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O69" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="U69" s="0" t="n">
         <v>0</v>
@@ -4610,20 +4569,20 @@
         <v>0</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>12010100001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y69" s="0" t="n">
-        <v>12010100001</v>
+        <v>12002400001</v>
       </c>
       <c r="Z69" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>12010200001</v>
+        <v>12003100001</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>12</v>
@@ -4631,20 +4590,28 @@
       <c r="D70" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
-      <c r="L70" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
+      <c r="J70" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L70" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O70" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="U70" s="0" t="n">
         <v>0</v>
@@ -4653,20 +4620,20 @@
         <v>0</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>12010200001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y70" s="0" t="n">
-        <v>12010200001</v>
+        <v>12003100001</v>
       </c>
       <c r="Z70" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>12010300001</v>
+        <v>12003200001</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>12</v>
@@ -4674,20 +4641,28 @@
       <c r="D71" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H71" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
-      <c r="L71" s="0" t="inlineStr">
-        <is>
-          <t>4001:1000&amp;</t>
-        </is>
+      <c r="J71" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O71" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="U71" s="0" t="n">
         <v>0</v>
@@ -4696,20 +4671,20 @@
         <v>0</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>12010300001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y71" s="0" t="n">
-        <v>12010300001</v>
+        <v>12003200001</v>
       </c>
       <c r="Z71" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>12011100001</v>
+        <v>12003300001</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>12</v>
@@ -4719,18 +4694,26 @@
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L72" s="0" t="inlineStr">
-        <is>
-          <t>2001:1&amp;</t>
-        </is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L72" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O72" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="U72" s="0" t="n">
         <v>0</v>
@@ -4739,20 +4722,20 @@
         <v>0</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>12011100001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y72" s="0" t="n">
-        <v>12011100001</v>
+        <v>12003300001</v>
       </c>
       <c r="Z72" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>12011200001</v>
+        <v>12003400001</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>12</v>
@@ -4762,18 +4745,26 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
-      <c r="L73" s="0" t="inlineStr">
-        <is>
-          <t>3001:200&amp;</t>
-        </is>
+      <c r="J73" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O73" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="U73" s="0" t="n">
         <v>0</v>
@@ -4782,20 +4773,20 @@
         <v>0</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>12011200001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y73" s="0" t="n">
-        <v>12011200001</v>
+        <v>12003400001</v>
       </c>
       <c r="Z73" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010100001</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>12</v>
@@ -4803,262 +4794,257 @@
       <c r="D74" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H74" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L74" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="U74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="Y74" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="Z74" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="C75" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D75" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L75" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="U75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="Y75" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="Z75" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="C76" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H76" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L76" s="0" t="inlineStr">
+        <is>
+          <t>4001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="U76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="Y76" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="Z76" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="C77" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
-      <c r="I74" s="5" t="inlineStr">
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L77" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
+      </c>
+      <c r="U77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="Y77" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="Z77" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="C78" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
-      <c r="L74" s="0" t="inlineStr">
+      <c r="L78" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
+      </c>
+      <c r="U78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="Y78" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="Z78" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="C79" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L79" s="0" t="inlineStr">
         <is>
           <t>4001:200&amp;</t>
         </is>
       </c>
-      <c r="U74" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X74" s="0" t="n">
+      <c r="U79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" s="0" t="n">
         <v>12011300001</v>
       </c>
-      <c r="Y74" s="0" t="n">
+      <c r="Y79" s="0" t="n">
         <v>12011300001</v>
       </c>
-      <c r="Z74" s="0" t="inlineStr">
+      <c r="Z79" s="0" t="inlineStr">
         <is>
           <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D75" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="n"/>
-      <c r="M75" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T75" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="U75" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" s="2" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="Y75" s="2" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="Z75" s="2" t="inlineStr">
-        <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D76" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="n"/>
-      <c r="U76" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" s="2" t="n">
-        <v>500001</v>
-      </c>
-      <c r="X76" s="2" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="Y76" s="2" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="Z76" s="2" t="inlineStr">
-        <is>
-          <t>死亡后重生</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalDeadAttack</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U77" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" s="2" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="Y77" s="2" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="Z77" s="2" t="inlineStr">
-        <is>
-          <t>死亡后爆炸</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P78" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U78" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V78" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X78" s="2" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="Y78" s="2" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="Z78" s="2" t="inlineStr">
-        <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>13000600001</v>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O79" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P79" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="U79" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" s="2" t="n">
-        <v>13000600001</v>
-      </c>
-      <c r="Y79" s="2" t="n">
-        <v>13000600001</v>
-      </c>
-      <c r="Z79" s="2" t="inlineStr">
-        <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>13000700001</v>
+        <v>13000100001</v>
       </c>
       <c r="C80" s="2" t="n">
         <v>13</v>
@@ -5066,33 +5052,253 @@
       <c r="D80" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="n"/>
+      <c r="M80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" s="2" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="Y80" s="2" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="n"/>
+      <c r="U81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="2" t="n">
+        <v>500001</v>
+      </c>
+      <c r="X81" s="2" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Y81" s="2" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAttack</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" s="2" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Y82" s="2" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P83" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" s="2" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Y83" s="2" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P84" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="U84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" s="2" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="Y84" s="2" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>BuffEntityConditionalDeadCreateCrystal</t>
         </is>
       </c>
-      <c r="I80" s="5" t="inlineStr">
+      <c r="I85" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q80" s="2" t="n">
+      <c r="Q85" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="R80" s="2" t="n"/>
-      <c r="U80" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" s="2" t="n">
+      <c r="R85" s="2" t="n"/>
+      <c r="U85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" s="2" t="n">
         <v>13000700001</v>
       </c>
-      <c r="Y80" s="2" t="n">
+      <c r="Y85" s="2" t="n">
         <v>13000700001</v>
       </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Z85" s="2" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z85"/>
+  <dimension ref="A1:Y85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -1249,47 +1249,42 @@
           <t>trigger_chance</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>trigger_chance_min</t>
+      <c r="R1" s="0" t="inlineStr">
+        <is>
+          <t>trigger_num</t>
         </is>
       </c>
       <c r="S1" s="0" t="inlineStr">
         <is>
-          <t>trigger_num</t>
+          <t>trigger_time</t>
         </is>
       </c>
       <c r="T1" s="0" t="inlineStr">
         <is>
-          <t>trigger_time</t>
+          <t>stack_mode</t>
         </is>
       </c>
       <c r="U1" s="0" t="inlineStr">
         <is>
-          <t>stack_mode</t>
+          <t>stack_max</t>
         </is>
       </c>
       <c r="V1" s="0" t="inlineStr">
         <is>
-          <t>stack_max</t>
+          <t>trigger_effect</t>
         </is>
       </c>
       <c r="W1" s="0" t="inlineStr">
         <is>
-          <t>trigger_effect</t>
+          <t>name[language]</t>
         </is>
       </c>
       <c r="X1" s="0" t="inlineStr">
         <is>
-          <t>name[language]</t>
+          <t>content[language_1]</t>
         </is>
       </c>
       <c r="Y1" s="0" t="inlineStr">
-        <is>
-          <t>content[language_1]</t>
-        </is>
-      </c>
-      <c r="Z1" s="0" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -1381,21 +1376,21 @@
           <t>float</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" s="0" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="S2" s="0" t="inlineStr">
+      <c r="T2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="T2" s="0" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
       <c r="U2" s="0" t="inlineStr">
         <is>
           <t>int</t>
@@ -1403,7 +1398,7 @@
       </c>
       <c r="V2" s="0" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>long</t>
         </is>
       </c>
       <c r="W2" s="0" t="inlineStr">
@@ -1417,11 +1412,6 @@
         </is>
       </c>
       <c r="Y2" s="0" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="Z2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1513,47 +1503,42 @@
           <t>触发几率</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>触发几率(最小值)</t>
+      <c r="R3" s="0" t="inlineStr">
+        <is>
+          <t>触发次数(小于等于0永久触发)</t>
         </is>
       </c>
       <c r="S3" s="0" t="inlineStr">
         <is>
-          <t>触发次数(小于等于0永久触发)</t>
+          <t>触发时间</t>
         </is>
       </c>
       <c r="T3" s="0" t="inlineStr">
         <is>
-          <t>触发时间</t>
+          <t>堆叠策略 0=Refresh 1=Stack 2=Independent 3=Ignore 4=ReplaceStrongest</t>
         </is>
       </c>
       <c r="U3" s="0" t="inlineStr">
         <is>
-          <t>堆叠策略 0=Refresh 1=Stack 2=Independent 3=Ignore 4=ReplaceStrongest</t>
+          <t>最大堆叠层数 0=无上限 仅Stack模式生效</t>
         </is>
       </c>
       <c r="V3" s="0" t="inlineStr">
         <is>
-          <t>最大堆叠层数 0=无上限 仅Stack模式生效</t>
+          <t>触发时的粒子</t>
         </is>
       </c>
       <c r="W3" s="0" t="inlineStr">
         <is>
-          <t>触发时的粒子</t>
+          <t>名字</t>
         </is>
       </c>
       <c r="X3" s="0" t="inlineStr">
         <is>
-          <t>名字</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="Y3" s="0" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="Z3" s="0" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1588,25 +1573,25 @@
       <c r="O4" s="1" t="n">
         <v>-0.5</v>
       </c>
+      <c r="R4" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="S4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="T4" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="0" t="n">
-        <v>0</v>
+      <c r="W4" s="1" t="n">
+        <v>1000100001</v>
       </c>
       <c r="X4" s="1" t="n">
         <v>1000100001</v>
       </c>
-      <c r="Y4" s="1" t="n">
-        <v>1000100001</v>
-      </c>
-      <c r="Z4" s="1" t="inlineStr">
+      <c r="Y4" s="1" t="inlineStr">
         <is>
           <t>减速-冰</t>
         </is>
@@ -1641,25 +1626,25 @@
       <c r="O5" s="1" t="n">
         <v>-0.2</v>
       </c>
+      <c r="R5" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="S5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T5" s="1" t="n">
-        <v>1</v>
+      <c r="T5" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="0" t="n">
-        <v>0</v>
+      <c r="W5" s="1" t="n">
+        <v>1000200001</v>
       </c>
       <c r="X5" s="1" t="n">
         <v>1000200001</v>
       </c>
-      <c r="Y5" s="1" t="n">
-        <v>1000200001</v>
-      </c>
-      <c r="Z5" s="1" t="inlineStr">
+      <c r="Y5" s="1" t="inlineStr">
         <is>
           <t>减速-粘液</t>
         </is>
@@ -1681,22 +1666,22 @@
         </is>
       </c>
       <c r="I6" s="4" t="n"/>
-      <c r="S6" s="1" t="n">
-        <v>1</v>
+      <c r="R6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U6" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="0" t="n">
-        <v>0</v>
+      <c r="W6" s="1" t="n">
+        <v>1000300001</v>
       </c>
       <c r="X6" s="1" t="n">
         <v>1000300001</v>
       </c>
-      <c r="Y6" s="1" t="n">
-        <v>1000300001</v>
-      </c>
-      <c r="Z6" s="1" t="inlineStr">
+      <c r="Y6" s="1" t="inlineStr">
         <is>
           <t>流血</t>
         </is>
@@ -1726,25 +1711,25 @@
       <c r="O7" s="1" t="n">
         <v>-0.01</v>
       </c>
+      <c r="R7" s="1" t="n">
+        <v>10</v>
+      </c>
       <c r="S7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T7" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="0" t="n">
-        <v>0</v>
+      <c r="W7" s="1" t="n">
+        <v>1000400001</v>
       </c>
       <c r="X7" s="1" t="n">
         <v>1000400001</v>
       </c>
-      <c r="Y7" s="1" t="n">
-        <v>1000400001</v>
-      </c>
-      <c r="Z7" s="1" t="inlineStr">
+      <c r="Y7" s="1" t="inlineStr">
         <is>
           <t>中毒</t>
         </is>
@@ -1774,25 +1759,25 @@
       <c r="O8" s="1" t="n">
         <v>-0.05</v>
       </c>
+      <c r="R8" s="1" t="n">
+        <v>3</v>
+      </c>
       <c r="S8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="T8" s="1" t="n">
-        <v>3</v>
+      <c r="T8" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U8" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="0" t="n">
-        <v>0</v>
+      <c r="W8" s="1" t="n">
+        <v>1000500001</v>
       </c>
       <c r="X8" s="1" t="n">
         <v>1000500001</v>
       </c>
-      <c r="Y8" s="1" t="n">
-        <v>1000500001</v>
-      </c>
-      <c r="Z8" s="1" t="inlineStr">
+      <c r="Y8" s="1" t="inlineStr">
         <is>
           <t>烧伤-每隔3秒扣除血量</t>
         </is>
@@ -1827,22 +1812,22 @@
       <c r="O9" s="1" t="n">
         <v>-0.1</v>
       </c>
-      <c r="T9" s="1" t="n">
+      <c r="S9" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="T9" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U9" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="0" t="n">
-        <v>0</v>
+      <c r="W9" s="1" t="n">
+        <v>1000600001</v>
       </c>
       <c r="X9" s="1" t="n">
         <v>1000600001</v>
       </c>
-      <c r="Y9" s="1" t="n">
-        <v>1000600001</v>
-      </c>
-      <c r="Z9" s="1" t="inlineStr">
+      <c r="Y9" s="1" t="inlineStr">
         <is>
           <t>潮湿-减少攻击力</t>
         </is>
@@ -1873,22 +1858,22 @@
       <c r="O10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="T10" s="1" t="n">
+      <c r="S10" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="T10" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U10" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="0" t="n">
-        <v>0</v>
+      <c r="W10" s="1" t="n">
+        <v>1000700001</v>
       </c>
       <c r="X10" s="1" t="n">
         <v>1000700001</v>
       </c>
-      <c r="Y10" s="1" t="n">
-        <v>1000700001</v>
-      </c>
-      <c r="Z10" s="1" t="inlineStr">
+      <c r="Y10" s="1" t="inlineStr">
         <is>
           <t>冰冻-减速</t>
         </is>
@@ -1930,21 +1915,20 @@
       <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n"/>
+      <c r="T11" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U11" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
+      <c r="W11" s="2" t="n">
+        <v>2000100001</v>
+      </c>
       <c r="X11" s="2" t="n">
         <v>2000100001</v>
       </c>
-      <c r="Y11" s="2" t="n">
-        <v>2000100001</v>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
+      <c r="Y11" s="2" t="inlineStr">
         <is>
           <t>闪避50%</t>
         </is>
@@ -1986,21 +1970,20 @@
       <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n"/>
+      <c r="T12" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U12" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
+      <c r="W12" s="2" t="n">
+        <v>2000200001</v>
+      </c>
       <c r="X12" s="2" t="n">
         <v>2000200001</v>
       </c>
-      <c r="Y12" s="2" t="n">
-        <v>2000200001</v>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
+      <c r="Y12" s="2" t="inlineStr">
         <is>
           <t>暴击50%</t>
         </is>
@@ -2046,21 +2029,20 @@
       <c r="Q13" s="2" t="n"/>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="n"/>
+      <c r="T13" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U13" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="2" t="n"/>
+      <c r="V13" s="2" t="n"/>
+      <c r="W13" s="2" t="n">
+        <v>2000300001</v>
+      </c>
       <c r="X13" s="2" t="n">
         <v>2000300001</v>
       </c>
-      <c r="Y13" s="2" t="n">
-        <v>2000300001</v>
-      </c>
-      <c r="Z13" s="2" t="inlineStr">
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>血量低于50% 攻击力提升</t>
         </is>
@@ -2106,21 +2088,20 @@
       <c r="Q14" s="2" t="n"/>
       <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
-      <c r="T14" s="2" t="n"/>
+      <c r="T14" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U14" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2" t="n"/>
+      <c r="V14" s="2" t="n"/>
+      <c r="W14" s="2" t="n">
+        <v>2000400001</v>
+      </c>
       <c r="X14" s="2" t="n">
         <v>2000400001</v>
       </c>
-      <c r="Y14" s="2" t="n">
-        <v>2000400001</v>
-      </c>
-      <c r="Z14" s="2" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>血量低于50% 攻击速度提升</t>
         </is>
@@ -2142,19 +2123,19 @@
         </is>
       </c>
       <c r="I15" s="7" t="n"/>
+      <c r="T15" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U15" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="0" t="n">
-        <v>0</v>
+      <c r="W15" s="0" t="n">
+        <v>3000100001</v>
       </c>
       <c r="X15" s="0" t="n">
         <v>3000100001</v>
       </c>
-      <c r="Y15" s="0" t="n">
-        <v>3000100001</v>
-      </c>
-      <c r="Z15" s="0" t="inlineStr">
+      <c r="Y15" s="0" t="inlineStr">
         <is>
           <t>增殖-随机复制一个已有的魔物</t>
         </is>
@@ -2189,19 +2170,19 @@
       <c r="Q16" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="T16" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U16" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="0" t="n">
-        <v>0</v>
+      <c r="W16" s="0" t="n">
+        <v>3000200001</v>
       </c>
       <c r="X16" s="0" t="n">
         <v>3000200001</v>
       </c>
-      <c r="Y16" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="Z16" s="0" t="inlineStr">
+      <c r="Y16" s="0" t="inlineStr">
         <is>
           <t>钱多多LV1-每一次击杀有10%的概率多掉落一次魔晶</t>
         </is>
@@ -2236,19 +2217,19 @@
       <c r="Q17" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="T17" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U17" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="0" t="n">
-        <v>0</v>
+      <c r="W17" s="0" t="n">
+        <v>3000200001</v>
       </c>
       <c r="X17" s="0" t="n">
         <v>3000200001</v>
       </c>
-      <c r="Y17" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="Z17" s="0" t="inlineStr">
+      <c r="Y17" s="0" t="inlineStr">
         <is>
           <t>钱多多LV2-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
@@ -2283,19 +2264,19 @@
       <c r="Q18" s="0" t="n">
         <v>0.3</v>
       </c>
+      <c r="T18" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U18" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="0" t="n">
-        <v>0</v>
+      <c r="W18" s="0" t="n">
+        <v>3000200001</v>
       </c>
       <c r="X18" s="0" t="n">
         <v>3000200001</v>
       </c>
-      <c r="Y18" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="Z18" s="0" t="inlineStr">
+      <c r="Y18" s="0" t="inlineStr">
         <is>
           <t>钱多多LV3-每一次击杀有30%的概率多掉落一次魔晶</t>
         </is>
@@ -2330,19 +2311,19 @@
       <c r="Q19" s="0" t="n">
         <v>0.4</v>
       </c>
+      <c r="T19" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U19" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="0" t="n">
-        <v>0</v>
+      <c r="W19" s="0" t="n">
+        <v>3000200001</v>
       </c>
       <c r="X19" s="0" t="n">
         <v>3000200001</v>
       </c>
-      <c r="Y19" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="Z19" s="0" t="inlineStr">
+      <c r="Y19" s="0" t="inlineStr">
         <is>
           <t>钱多多LV4-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
@@ -2377,19 +2358,19 @@
       <c r="Q20" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="T20" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U20" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="0" t="n">
-        <v>0</v>
+      <c r="W20" s="0" t="n">
+        <v>3000200001</v>
       </c>
       <c r="X20" s="0" t="n">
         <v>3000200001</v>
       </c>
-      <c r="Y20" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="Z20" s="0" t="inlineStr">
+      <c r="Y20" s="0" t="inlineStr">
         <is>
           <t>钱多多LV5-每一次击杀有50%的概率多掉落一次魔晶</t>
         </is>
@@ -2422,19 +2403,19 @@
       <c r="O21" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="T21" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U21" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="0" t="n">
-        <v>0</v>
+      <c r="W21" s="0" t="n">
+        <v>3000300001</v>
       </c>
       <c r="X21" s="0" t="n">
         <v>3000300001</v>
       </c>
-      <c r="Y21" s="0" t="n">
-        <v>3000300001</v>
-      </c>
-      <c r="Z21" s="0" t="inlineStr">
+      <c r="Y21" s="0" t="inlineStr">
         <is>
           <t>强身健体-所有魔物体力增加10%</t>
         </is>
@@ -2466,19 +2447,19 @@
       <c r="O22" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="T22" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U22" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="0" t="n">
-        <v>0</v>
+      <c r="W22" s="0" t="n">
+        <v>3000300001</v>
       </c>
       <c r="X22" s="0" t="n">
         <v>3000300001</v>
       </c>
-      <c r="Y22" s="0" t="n">
-        <v>3000300001</v>
-      </c>
-      <c r="Z22" s="0" t="inlineStr">
+      <c r="Y22" s="0" t="inlineStr">
         <is>
           <t>强身健体LV2-所有魔物体力增加20%</t>
         </is>
@@ -2510,19 +2491,19 @@
       <c r="O23" s="0" t="n">
         <v>0.3</v>
       </c>
+      <c r="T23" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U23" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="0" t="n">
-        <v>0</v>
+      <c r="W23" s="0" t="n">
+        <v>3000300001</v>
       </c>
       <c r="X23" s="0" t="n">
         <v>3000300001</v>
       </c>
-      <c r="Y23" s="0" t="n">
-        <v>3000300001</v>
-      </c>
-      <c r="Z23" s="0" t="inlineStr">
+      <c r="Y23" s="0" t="inlineStr">
         <is>
           <t>强身健体LV3-所有魔物体力增加30%</t>
         </is>
@@ -2554,19 +2535,19 @@
       <c r="O24" s="0" t="n">
         <v>0.4</v>
       </c>
+      <c r="T24" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U24" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="0" t="n">
-        <v>0</v>
+      <c r="W24" s="0" t="n">
+        <v>3000300001</v>
       </c>
       <c r="X24" s="0" t="n">
         <v>3000300001</v>
       </c>
-      <c r="Y24" s="0" t="n">
-        <v>3000300001</v>
-      </c>
-      <c r="Z24" s="0" t="inlineStr">
+      <c r="Y24" s="0" t="inlineStr">
         <is>
           <t>强身健体LV4-所有魔物体力增加40%</t>
         </is>
@@ -2598,19 +2579,19 @@
       <c r="O25" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="T25" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U25" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="0" t="n">
-        <v>0</v>
+      <c r="W25" s="0" t="n">
+        <v>3000300001</v>
       </c>
       <c r="X25" s="0" t="n">
         <v>3000300001</v>
       </c>
-      <c r="Y25" s="0" t="n">
-        <v>3000300001</v>
-      </c>
-      <c r="Z25" s="0" t="inlineStr">
+      <c r="Y25" s="0" t="inlineStr">
         <is>
           <t>强身健体LV5-所有魔物体力增加50%</t>
         </is>
@@ -2640,19 +2621,19 @@
       <c r="O26" s="0" t="n">
         <v>-0.1</v>
       </c>
+      <c r="T26" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U26" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="0" t="n">
-        <v>0</v>
+      <c r="W26" s="0" t="n">
+        <v>3000400001</v>
       </c>
       <c r="X26" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y26" s="0" t="n">
-        <v>3000400001</v>
-      </c>
-      <c r="Z26" s="0" t="inlineStr">
+      <c r="Y26" s="0" t="inlineStr">
         <is>
           <t>时光沙漏-所有魔物放置CD减少10%</t>
         </is>
@@ -2681,19 +2662,19 @@
       <c r="O27" s="0" t="n">
         <v>-0.2</v>
       </c>
+      <c r="T27" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U27" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="0" t="n">
-        <v>0</v>
+      <c r="W27" s="0" t="n">
+        <v>3000400001</v>
       </c>
       <c r="X27" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y27" s="0" t="n">
-        <v>3000400001</v>
-      </c>
-      <c r="Z27" s="0" t="inlineStr">
+      <c r="Y27" s="0" t="inlineStr">
         <is>
           <t>时光沙漏LV2-所有魔物放置CD减少20%</t>
         </is>
@@ -2722,19 +2703,19 @@
       <c r="O28" s="0" t="n">
         <v>-0.3</v>
       </c>
+      <c r="T28" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U28" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="0" t="n">
-        <v>0</v>
+      <c r="W28" s="0" t="n">
+        <v>3000400001</v>
       </c>
       <c r="X28" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y28" s="0" t="n">
-        <v>3000400001</v>
-      </c>
-      <c r="Z28" s="0" t="inlineStr">
+      <c r="Y28" s="0" t="inlineStr">
         <is>
           <t>时光沙漏LV3-所有魔物放置CD减少30%</t>
         </is>
@@ -2763,19 +2744,19 @@
       <c r="O29" s="0" t="n">
         <v>-0.4</v>
       </c>
+      <c r="T29" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U29" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="0" t="n">
-        <v>0</v>
+      <c r="W29" s="0" t="n">
+        <v>3000400001</v>
       </c>
       <c r="X29" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y29" s="0" t="n">
-        <v>3000400001</v>
-      </c>
-      <c r="Z29" s="0" t="inlineStr">
+      <c r="Y29" s="0" t="inlineStr">
         <is>
           <t>时光沙漏LV4-所有魔物放置CD减少40%</t>
         </is>
@@ -2804,19 +2785,19 @@
       <c r="O30" s="0" t="n">
         <v>-0.5</v>
       </c>
+      <c r="T30" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U30" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="0" t="n">
-        <v>0</v>
+      <c r="W30" s="0" t="n">
+        <v>3000400001</v>
       </c>
       <c r="X30" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y30" s="0" t="n">
-        <v>3000400001</v>
-      </c>
-      <c r="Z30" s="0" t="inlineStr">
+      <c r="Y30" s="0" t="inlineStr">
         <is>
           <t>时光沙漏LV5-所有魔物放置CD减少50%</t>
         </is>
@@ -2848,19 +2829,19 @@
       <c r="O31" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="T31" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U31" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="0" t="n">
-        <v>0</v>
+      <c r="W31" s="0" t="n">
+        <v>3000500001</v>
       </c>
       <c r="X31" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y31" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="Z31" s="0" t="inlineStr">
+      <c r="Y31" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV1-所有魔物攻击力增加10%</t>
         </is>
@@ -2892,19 +2873,19 @@
       <c r="O32" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="T32" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U32" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="0" t="n">
-        <v>0</v>
+      <c r="W32" s="0" t="n">
+        <v>3000500001</v>
       </c>
       <c r="X32" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y32" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="Z32" s="0" t="inlineStr">
+      <c r="Y32" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV2-所有魔物攻击力增加20%</t>
         </is>
@@ -2936,19 +2917,19 @@
       <c r="O33" s="0" t="n">
         <v>0.3</v>
       </c>
+      <c r="T33" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U33" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="0" t="n">
-        <v>0</v>
+      <c r="W33" s="0" t="n">
+        <v>3000500001</v>
       </c>
       <c r="X33" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y33" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="Z33" s="0" t="inlineStr">
+      <c r="Y33" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV3-所有魔物攻击力增加30%</t>
         </is>
@@ -2980,19 +2961,19 @@
       <c r="O34" s="0" t="n">
         <v>0.4</v>
       </c>
+      <c r="T34" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U34" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="0" t="n">
-        <v>0</v>
+      <c r="W34" s="0" t="n">
+        <v>3000500001</v>
       </c>
       <c r="X34" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y34" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="Z34" s="0" t="inlineStr">
+      <c r="Y34" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV4-所有魔物攻击力增加40%</t>
         </is>
@@ -3024,19 +3005,19 @@
       <c r="O35" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="T35" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U35" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="0" t="n">
-        <v>0</v>
+      <c r="W35" s="0" t="n">
+        <v>3000500001</v>
       </c>
       <c r="X35" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y35" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="Z35" s="0" t="inlineStr">
+      <c r="Y35" s="0" t="inlineStr">
         <is>
           <t>伤害性极强LV5-所有魔物攻击力增加50%</t>
         </is>
@@ -3068,19 +3049,19 @@
       <c r="O36" s="0" t="n">
         <v>-0.1</v>
       </c>
-      <c r="S36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="0" t="n">
-        <v>0</v>
+      <c r="R36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="0" t="n">
+        <v>3000600001</v>
       </c>
       <c r="X36" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y36" s="0" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z36" s="0" t="inlineStr">
+      <c r="Y36" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV1-敌方进攻生物移动速度降低10%</t>
         </is>
@@ -3112,19 +3093,19 @@
       <c r="O37" s="0" t="n">
         <v>-0.2</v>
       </c>
-      <c r="S37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="0" t="n">
-        <v>0</v>
+      <c r="R37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="0" t="n">
+        <v>3000600001</v>
       </c>
       <c r="X37" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y37" s="0" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z37" s="0" t="inlineStr">
+      <c r="Y37" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV2-敌方进攻生物移动速度降低20%</t>
         </is>
@@ -3156,19 +3137,19 @@
       <c r="O38" s="0" t="n">
         <v>-0.3</v>
       </c>
-      <c r="S38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="0" t="n">
-        <v>0</v>
+      <c r="R38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="0" t="n">
+        <v>3000600001</v>
       </c>
       <c r="X38" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y38" s="0" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z38" s="0" t="inlineStr">
+      <c r="Y38" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV3-敌方进攻生物移动速度降低30%</t>
         </is>
@@ -3200,19 +3181,19 @@
       <c r="O39" s="0" t="n">
         <v>-0.4</v>
       </c>
-      <c r="S39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="0" t="n">
-        <v>0</v>
+      <c r="R39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="0" t="n">
+        <v>3000600001</v>
       </c>
       <c r="X39" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y39" s="0" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z39" s="0" t="inlineStr">
+      <c r="Y39" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV4-敌方进攻生物移动速度降低40%</t>
         </is>
@@ -3244,19 +3225,19 @@
       <c r="O40" s="0" t="n">
         <v>-0.5</v>
       </c>
-      <c r="S40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="0" t="n">
-        <v>0</v>
+      <c r="R40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="0" t="n">
+        <v>3000600001</v>
       </c>
       <c r="X40" s="0" t="n">
         <v>3000600001</v>
       </c>
-      <c r="Y40" s="0" t="n">
-        <v>3000600001</v>
-      </c>
-      <c r="Z40" s="0" t="inlineStr">
+      <c r="Y40" s="0" t="inlineStr">
         <is>
           <t>慢条斯理LV5-敌方进攻生物移动速度降低50%</t>
         </is>
@@ -3288,19 +3269,19 @@
       <c r="O41" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="T41" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U41" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="0" t="n">
-        <v>0</v>
+      <c r="W41" s="0" t="n">
+        <v>3000700001</v>
       </c>
       <c r="X41" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y41" s="0" t="n">
-        <v>3000700001</v>
-      </c>
-      <c r="Z41" s="0" t="inlineStr">
+      <c r="Y41" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV1-所有魔物攻击速度增加10%</t>
         </is>
@@ -3332,19 +3313,19 @@
       <c r="O42" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="T42" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U42" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="0" t="n">
-        <v>0</v>
+      <c r="W42" s="0" t="n">
+        <v>3000700001</v>
       </c>
       <c r="X42" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y42" s="0" t="n">
-        <v>3000700001</v>
-      </c>
-      <c r="Z42" s="0" t="inlineStr">
+      <c r="Y42" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV2-所有魔物攻击速度增加20%</t>
         </is>
@@ -3376,19 +3357,19 @@
       <c r="O43" s="0" t="n">
         <v>0.3</v>
       </c>
+      <c r="T43" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U43" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="0" t="n">
-        <v>0</v>
+      <c r="W43" s="0" t="n">
+        <v>3000700001</v>
       </c>
       <c r="X43" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y43" s="0" t="n">
-        <v>3000700001</v>
-      </c>
-      <c r="Z43" s="0" t="inlineStr">
+      <c r="Y43" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV3-所有魔物攻击速度增加30%</t>
         </is>
@@ -3420,19 +3401,19 @@
       <c r="O44" s="0" t="n">
         <v>0.4</v>
       </c>
+      <c r="T44" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U44" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="0" t="n">
-        <v>0</v>
+      <c r="W44" s="0" t="n">
+        <v>3000700001</v>
       </c>
       <c r="X44" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y44" s="0" t="n">
-        <v>3000700001</v>
-      </c>
-      <c r="Z44" s="0" t="inlineStr">
+      <c r="Y44" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV4-所有魔物攻击速度增加40%</t>
         </is>
@@ -3464,19 +3445,19 @@
       <c r="O45" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="T45" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U45" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="0" t="n">
-        <v>0</v>
+      <c r="W45" s="0" t="n">
+        <v>3000700001</v>
       </c>
       <c r="X45" s="0" t="n">
         <v>3000700001</v>
       </c>
-      <c r="Y45" s="0" t="n">
-        <v>3000700001</v>
-      </c>
-      <c r="Z45" s="0" t="inlineStr">
+      <c r="Y45" s="0" t="inlineStr">
         <is>
           <t>唯快不破LV5-所有魔物攻击速度增加50%</t>
         </is>
@@ -3508,19 +3489,19 @@
       <c r="O46" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="T46" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U46" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="0" t="n">
-        <v>0</v>
+      <c r="W46" s="0" t="n">
+        <v>3000800001</v>
       </c>
       <c r="X46" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y46" s="0" t="n">
-        <v>3000800001</v>
-      </c>
-      <c r="Z46" s="0" t="inlineStr">
+      <c r="Y46" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV1-所有魔物护甲增加10%(无护甲则无加成)</t>
         </is>
@@ -3552,19 +3533,19 @@
       <c r="O47" s="0" t="n">
         <v>0.2</v>
       </c>
+      <c r="T47" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U47" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="0" t="n">
-        <v>0</v>
+      <c r="W47" s="0" t="n">
+        <v>3000800001</v>
       </c>
       <c r="X47" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y47" s="0" t="n">
-        <v>3000800001</v>
-      </c>
-      <c r="Z47" s="0" t="inlineStr">
+      <c r="Y47" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV2-所有魔物护甲增加20%(无护甲则无加成)</t>
         </is>
@@ -3596,19 +3577,19 @@
       <c r="O48" s="0" t="n">
         <v>0.3</v>
       </c>
+      <c r="T48" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U48" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="0" t="n">
-        <v>0</v>
+      <c r="W48" s="0" t="n">
+        <v>3000800001</v>
       </c>
       <c r="X48" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y48" s="0" t="n">
-        <v>3000800001</v>
-      </c>
-      <c r="Z48" s="0" t="inlineStr">
+      <c r="Y48" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV3-所有魔物护甲增加30%(无护甲则无加成)</t>
         </is>
@@ -3640,19 +3621,19 @@
       <c r="O49" s="0" t="n">
         <v>0.4</v>
       </c>
+      <c r="T49" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U49" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="0" t="n">
-        <v>0</v>
+      <c r="W49" s="0" t="n">
+        <v>3000800001</v>
       </c>
       <c r="X49" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y49" s="0" t="n">
-        <v>3000800001</v>
-      </c>
-      <c r="Z49" s="0" t="inlineStr">
+      <c r="Y49" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV4-所有魔物护甲增加40%(无护甲则无加成)</t>
         </is>
@@ -3684,19 +3665,19 @@
       <c r="O50" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="T50" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U50" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="0" t="n">
-        <v>0</v>
+      <c r="W50" s="0" t="n">
+        <v>3000800001</v>
       </c>
       <c r="X50" s="0" t="n">
         <v>3000800001</v>
       </c>
-      <c r="Y50" s="0" t="n">
-        <v>3000800001</v>
-      </c>
-      <c r="Z50" s="0" t="inlineStr">
+      <c r="Y50" s="0" t="inlineStr">
         <is>
           <t>坚不可摧LV5-所有魔物护甲增加50%(无护甲则无加成)</t>
         </is>
@@ -3721,19 +3702,19 @@
       <c r="J51" s="2" t="n"/>
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="n"/>
+      <c r="T51" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U51" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="0" t="n">
-        <v>0</v>
+      <c r="W51" s="2" t="n">
+        <v>3000900001</v>
       </c>
       <c r="X51" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="Y51" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="Z51" s="2" t="inlineStr">
+      <c r="Y51" s="2" t="inlineStr">
         <is>
           <t>奖励多多-通关奖励数量+1</t>
         </is>
@@ -3758,19 +3739,19 @@
       <c r="J52" s="2" t="n"/>
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="n"/>
+      <c r="T52" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U52" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="0" t="n">
-        <v>0</v>
+      <c r="W52" s="2" t="n">
+        <v>3001000001</v>
       </c>
       <c r="X52" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="Y52" s="2" t="n">
-        <v>3001000001</v>
-      </c>
-      <c r="Z52" s="2" t="inlineStr">
+      <c r="Y52" s="2" t="inlineStr">
         <is>
           <t>再来一瓶-通关奖励可选次数+1</t>
         </is>
@@ -3803,19 +3784,19 @@
       <c r="P53" s="2" t="n">
         <v>0.1</v>
       </c>
+      <c r="T53" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U53" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="0" t="n">
-        <v>0</v>
+      <c r="W53" s="2" t="n">
+        <v>11000100001</v>
       </c>
       <c r="X53" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="Y53" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Y53" s="2" t="inlineStr">
         <is>
           <t>生命增加{Percentage}%</t>
         </is>
@@ -3848,19 +3829,19 @@
       <c r="P54" s="2" t="n">
         <v>0.1</v>
       </c>
+      <c r="T54" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U54" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="0" t="n">
-        <v>0</v>
+      <c r="W54" s="2" t="n">
+        <v>11000200001</v>
       </c>
       <c r="X54" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="Y54" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="Z54" s="2" t="inlineStr">
+      <c r="Y54" s="2" t="inlineStr">
         <is>
           <t>护甲增加{Percentage}%</t>
         </is>
@@ -3893,19 +3874,19 @@
       <c r="P55" s="2" t="n">
         <v>0.1</v>
       </c>
+      <c r="T55" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U55" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="0" t="n">
-        <v>0</v>
+      <c r="W55" s="2" t="n">
+        <v>11000300001</v>
       </c>
       <c r="X55" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y55" s="2" t="n">
-        <v>11000300001</v>
-      </c>
-      <c r="Z55" s="2" t="inlineStr">
+      <c r="Y55" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
         </is>
@@ -3937,19 +3918,19 @@
       <c r="P56" s="0" t="n">
         <v>0.5</v>
       </c>
+      <c r="T56" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U56" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="0" t="n">
-        <v>0</v>
+      <c r="W56" s="0" t="n">
+        <v>11000400001</v>
       </c>
       <c r="X56" s="0" t="n">
         <v>11000400001</v>
       </c>
-      <c r="Y56" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="Z56" s="0" t="inlineStr">
+      <c r="Y56" s="0" t="inlineStr">
         <is>
           <t>攻击速度增加{Percentage}%</t>
         </is>
@@ -3981,19 +3962,19 @@
       <c r="P57" s="0" t="n">
         <v>-0.5</v>
       </c>
+      <c r="T57" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U57" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="0" t="n">
-        <v>0</v>
+      <c r="W57" s="0" t="n">
+        <v>11000500001</v>
       </c>
       <c r="X57" s="0" t="n">
         <v>11000500001</v>
       </c>
-      <c r="Y57" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="Z57" s="0" t="inlineStr">
+      <c r="Y57" s="0" t="inlineStr">
         <is>
           <t>召唤CD{Percentage}%</t>
         </is>
@@ -4025,19 +4006,19 @@
       <c r="P58" s="0" t="n">
         <v>-0.5</v>
       </c>
+      <c r="T58" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U58" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="0" t="n">
-        <v>0</v>
+      <c r="W58" s="0" t="n">
+        <v>11000600001</v>
       </c>
       <c r="X58" s="0" t="n">
         <v>11000600001</v>
       </c>
-      <c r="Y58" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="Z58" s="0" t="inlineStr">
+      <c r="Y58" s="0" t="inlineStr">
         <is>
           <t>召唤魔力消耗{Percentage}%</t>
         </is>
@@ -4065,25 +4046,25 @@
       <c r="P59" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="S59" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="T59" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="V59" s="0" t="n">
-        <v>0</v>
+        <v>500001</v>
       </c>
       <c r="W59" s="0" t="n">
-        <v>500001</v>
+        <v>12000100001</v>
       </c>
       <c r="X59" s="0" t="n">
         <v>12000100001</v>
       </c>
-      <c r="Y59" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="Z59" s="0" t="inlineStr">
+      <c r="Y59" s="0" t="inlineStr">
         <is>
           <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
@@ -4111,25 +4092,25 @@
       <c r="P60" s="0" t="n">
         <v>0.01</v>
       </c>
+      <c r="S60" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="T60" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="V60" s="0" t="n">
-        <v>0</v>
+        <v>500002</v>
       </c>
       <c r="W60" s="0" t="n">
-        <v>500002</v>
+        <v>12000200001</v>
       </c>
       <c r="X60" s="0" t="n">
         <v>12000200001</v>
       </c>
-      <c r="Y60" s="0" t="n">
-        <v>12000200001</v>
-      </c>
-      <c r="Z60" s="0" t="inlineStr">
+      <c r="Y60" s="0" t="inlineStr">
         <is>
           <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
@@ -4151,22 +4132,22 @@
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
+      <c r="S61" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="T61" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U61" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="0" t="n">
-        <v>0</v>
+      <c r="W61" s="0" t="n">
+        <v>12000300001</v>
       </c>
       <c r="X61" s="0" t="n">
         <v>12000300001</v>
       </c>
-      <c r="Y61" s="0" t="n">
-        <v>12000300001</v>
-      </c>
-      <c r="Z61" s="0" t="inlineStr">
+      <c r="Y61" s="0" t="inlineStr">
         <is>
           <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
@@ -4205,19 +4186,19 @@
       <c r="O62" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T62" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U62" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="0" t="n">
-        <v>0</v>
+      <c r="W62" s="0" t="n">
+        <v>12001100001</v>
       </c>
       <c r="X62" s="0" t="n">
         <v>12001100001</v>
       </c>
-      <c r="Y62" s="0" t="n">
-        <v>12001100001</v>
-      </c>
-      <c r="Z62" s="0" t="inlineStr">
+      <c r="Y62" s="0" t="inlineStr">
         <is>
           <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
@@ -4256,19 +4237,19 @@
       <c r="O63" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T63" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U63" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="0" t="n">
-        <v>0</v>
+      <c r="W63" s="0" t="n">
+        <v>12001200001</v>
       </c>
       <c r="X63" s="0" t="n">
         <v>12001200001</v>
       </c>
-      <c r="Y63" s="0" t="n">
-        <v>12001200001</v>
-      </c>
-      <c r="Z63" s="0" t="inlineStr">
+      <c r="Y63" s="0" t="inlineStr">
         <is>
           <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
@@ -4307,19 +4288,19 @@
       <c r="O64" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T64" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U64" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="0" t="n">
-        <v>0</v>
+      <c r="W64" s="0" t="n">
+        <v>12001300001</v>
       </c>
       <c r="X64" s="0" t="n">
         <v>12001300001</v>
       </c>
-      <c r="Y64" s="0" t="n">
-        <v>12001300001</v>
-      </c>
-      <c r="Z64" s="0" t="inlineStr">
+      <c r="Y64" s="0" t="inlineStr">
         <is>
           <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
@@ -4358,19 +4339,19 @@
       <c r="O65" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T65" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U65" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="0" t="n">
-        <v>0</v>
+      <c r="W65" s="0" t="n">
+        <v>12001400001</v>
       </c>
       <c r="X65" s="0" t="n">
         <v>12001400001</v>
       </c>
-      <c r="Y65" s="0" t="n">
-        <v>12001400001</v>
-      </c>
-      <c r="Z65" s="0" t="inlineStr">
+      <c r="Y65" s="0" t="inlineStr">
         <is>
           <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
@@ -4409,19 +4390,19 @@
       <c r="O66" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T66" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U66" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="0" t="n">
-        <v>0</v>
+      <c r="W66" s="0" t="n">
+        <v>12002100001</v>
       </c>
       <c r="X66" s="0" t="n">
         <v>12002100001</v>
       </c>
-      <c r="Y66" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="Z66" s="0" t="inlineStr">
+      <c r="Y66" s="0" t="inlineStr">
         <is>
           <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
@@ -4460,19 +4441,19 @@
       <c r="O67" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T67" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U67" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="0" t="n">
-        <v>0</v>
+      <c r="W67" s="0" t="n">
+        <v>12002200001</v>
       </c>
       <c r="X67" s="0" t="n">
         <v>12002200001</v>
       </c>
-      <c r="Y67" s="0" t="n">
-        <v>12002200001</v>
-      </c>
-      <c r="Z67" s="0" t="inlineStr">
+      <c r="Y67" s="0" t="inlineStr">
         <is>
           <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
@@ -4511,19 +4492,19 @@
       <c r="O68" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T68" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U68" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="0" t="n">
-        <v>0</v>
+      <c r="W68" s="0" t="n">
+        <v>12002300001</v>
       </c>
       <c r="X68" s="0" t="n">
         <v>12002300001</v>
       </c>
-      <c r="Y68" s="0" t="n">
-        <v>12002300001</v>
-      </c>
-      <c r="Z68" s="0" t="inlineStr">
+      <c r="Y68" s="0" t="inlineStr">
         <is>
           <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
@@ -4562,19 +4543,19 @@
       <c r="O69" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T69" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U69" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="0" t="n">
-        <v>0</v>
+      <c r="W69" s="0" t="n">
+        <v>12002400001</v>
       </c>
       <c r="X69" s="0" t="n">
         <v>12002400001</v>
       </c>
-      <c r="Y69" s="0" t="n">
-        <v>12002400001</v>
-      </c>
-      <c r="Z69" s="0" t="inlineStr">
+      <c r="Y69" s="0" t="inlineStr">
         <is>
           <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
@@ -4613,19 +4594,19 @@
       <c r="O70" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T70" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U70" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="0" t="n">
-        <v>0</v>
+      <c r="W70" s="0" t="n">
+        <v>12003100001</v>
       </c>
       <c r="X70" s="0" t="n">
         <v>12003100001</v>
       </c>
-      <c r="Y70" s="0" t="n">
-        <v>12003100001</v>
-      </c>
-      <c r="Z70" s="0" t="inlineStr">
+      <c r="Y70" s="0" t="inlineStr">
         <is>
           <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
@@ -4664,19 +4645,19 @@
       <c r="O71" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T71" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U71" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="0" t="n">
-        <v>0</v>
+      <c r="W71" s="0" t="n">
+        <v>12003200001</v>
       </c>
       <c r="X71" s="0" t="n">
         <v>12003200001</v>
       </c>
-      <c r="Y71" s="0" t="n">
-        <v>12003200001</v>
-      </c>
-      <c r="Z71" s="0" t="inlineStr">
+      <c r="Y71" s="0" t="inlineStr">
         <is>
           <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
@@ -4715,19 +4696,19 @@
       <c r="O72" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T72" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U72" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="0" t="n">
-        <v>0</v>
+      <c r="W72" s="0" t="n">
+        <v>12003300001</v>
       </c>
       <c r="X72" s="0" t="n">
         <v>12003300001</v>
       </c>
-      <c r="Y72" s="0" t="n">
-        <v>12003300001</v>
-      </c>
-      <c r="Z72" s="0" t="inlineStr">
+      <c r="Y72" s="0" t="inlineStr">
         <is>
           <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
@@ -4766,19 +4747,19 @@
       <c r="O73" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="T73" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U73" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="0" t="n">
-        <v>0</v>
+      <c r="W73" s="0" t="n">
+        <v>12003400001</v>
       </c>
       <c r="X73" s="0" t="n">
         <v>12003400001</v>
       </c>
-      <c r="Y73" s="0" t="n">
-        <v>12003400001</v>
-      </c>
-      <c r="Z73" s="0" t="inlineStr">
+      <c r="Y73" s="0" t="inlineStr">
         <is>
           <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
@@ -4809,19 +4790,19 @@
           <t>2001:10&amp;</t>
         </is>
       </c>
+      <c r="T74" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U74" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="0" t="n">
-        <v>0</v>
+      <c r="W74" s="0" t="n">
+        <v>12010100001</v>
       </c>
       <c r="X74" s="0" t="n">
         <v>12010100001</v>
       </c>
-      <c r="Y74" s="0" t="n">
-        <v>12010100001</v>
-      </c>
-      <c r="Z74" s="0" t="inlineStr">
+      <c r="Y74" s="0" t="inlineStr">
         <is>
           <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
@@ -4852,19 +4833,19 @@
           <t>3001:1000&amp;</t>
         </is>
       </c>
+      <c r="T75" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U75" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="0" t="n">
-        <v>0</v>
+      <c r="W75" s="0" t="n">
+        <v>12010200001</v>
       </c>
       <c r="X75" s="0" t="n">
         <v>12010200001</v>
       </c>
-      <c r="Y75" s="0" t="n">
-        <v>12010200001</v>
-      </c>
-      <c r="Z75" s="0" t="inlineStr">
+      <c r="Y75" s="0" t="inlineStr">
         <is>
           <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
@@ -4895,19 +4876,19 @@
           <t>4001:1000&amp;</t>
         </is>
       </c>
+      <c r="T76" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U76" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="0" t="n">
-        <v>0</v>
+      <c r="W76" s="0" t="n">
+        <v>12010300001</v>
       </c>
       <c r="X76" s="0" t="n">
         <v>12010300001</v>
       </c>
-      <c r="Y76" s="0" t="n">
-        <v>12010300001</v>
-      </c>
-      <c r="Z76" s="0" t="inlineStr">
+      <c r="Y76" s="0" t="inlineStr">
         <is>
           <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
@@ -4938,19 +4919,19 @@
           <t>2001:1&amp;</t>
         </is>
       </c>
+      <c r="T77" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U77" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="0" t="n">
-        <v>0</v>
+      <c r="W77" s="0" t="n">
+        <v>12011100001</v>
       </c>
       <c r="X77" s="0" t="n">
         <v>12011100001</v>
       </c>
-      <c r="Y77" s="0" t="n">
-        <v>12011100001</v>
-      </c>
-      <c r="Z77" s="0" t="inlineStr">
+      <c r="Y77" s="0" t="inlineStr">
         <is>
           <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
@@ -4981,19 +4962,19 @@
           <t>3001:200&amp;</t>
         </is>
       </c>
+      <c r="T78" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U78" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="0" t="n">
-        <v>0</v>
+      <c r="W78" s="0" t="n">
+        <v>12011200001</v>
       </c>
       <c r="X78" s="0" t="n">
         <v>12011200001</v>
       </c>
-      <c r="Y78" s="0" t="n">
-        <v>12011200001</v>
-      </c>
-      <c r="Z78" s="0" t="inlineStr">
+      <c r="Y78" s="0" t="inlineStr">
         <is>
           <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
@@ -5024,19 +5005,19 @@
           <t>4001:200&amp;</t>
         </is>
       </c>
+      <c r="T79" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U79" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="0" t="n">
-        <v>0</v>
+      <c r="W79" s="0" t="n">
+        <v>12011300001</v>
       </c>
       <c r="X79" s="0" t="n">
         <v>12011300001</v>
       </c>
-      <c r="Y79" s="0" t="n">
-        <v>12011300001</v>
-      </c>
-      <c r="Z79" s="0" t="inlineStr">
+      <c r="Y79" s="0" t="inlineStr">
         <is>
           <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
@@ -5059,24 +5040,27 @@
       </c>
       <c r="I80" s="5" t="n"/>
       <c r="M80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="T80" s="2" t="n">
-        <v>3</v>
+        <v>3</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T80" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="U80" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="0" t="n">
-        <v>0</v>
+      <c r="W80" s="2" t="n">
+        <v>13000100001</v>
       </c>
       <c r="X80" s="2" t="n">
         <v>13000100001</v>
       </c>
-      <c r="Y80" s="2" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Y80" s="2" t="inlineStr">
         <is>
           <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
@@ -5103,22 +5087,22 @@
         </is>
       </c>
       <c r="J81" s="5" t="n"/>
+      <c r="T81" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U81" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="0" t="n">
-        <v>0</v>
+      <c r="V81" s="2" t="n">
+        <v>500001</v>
       </c>
       <c r="W81" s="2" t="n">
-        <v>500001</v>
+        <v>13000300001</v>
       </c>
       <c r="X81" s="2" t="n">
         <v>13000300001</v>
       </c>
-      <c r="Y81" s="2" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="Z81" s="2" t="inlineStr">
+      <c r="Y81" s="2" t="inlineStr">
         <is>
           <t>死亡后重生</t>
         </is>
@@ -5150,19 +5134,19 @@
       <c r="O82" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="T82" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U82" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="0" t="n">
-        <v>0</v>
+      <c r="W82" s="2" t="n">
+        <v>13000400001</v>
       </c>
       <c r="X82" s="2" t="n">
         <v>13000400001</v>
       </c>
-      <c r="Y82" s="2" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Y82" s="2" t="inlineStr">
         <is>
           <t>死亡后爆炸</t>
         </is>
@@ -5197,19 +5181,19 @@
       <c r="P83" s="2" t="n">
         <v>0.01</v>
       </c>
+      <c r="T83" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U83" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="0" t="n">
-        <v>0</v>
+      <c r="W83" s="2" t="n">
+        <v>13000500001</v>
       </c>
       <c r="X83" s="2" t="n">
         <v>13000500001</v>
       </c>
-      <c r="Y83" s="2" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="Z83" s="2" t="inlineStr">
+      <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
@@ -5244,19 +5228,19 @@
       <c r="P84" s="2" t="n">
         <v>0.01</v>
       </c>
+      <c r="T84" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U84" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="0" t="n">
-        <v>0</v>
+      <c r="W84" s="2" t="n">
+        <v>13000600001</v>
       </c>
       <c r="X84" s="2" t="n">
         <v>13000600001</v>
       </c>
-      <c r="Y84" s="2" t="n">
-        <v>13000600001</v>
-      </c>
-      <c r="Z84" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
@@ -5285,20 +5269,19 @@
       <c r="Q85" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="R85" s="2" t="n"/>
+      <c r="T85" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="U85" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="0" t="n">
-        <v>0</v>
+      <c r="W85" s="2" t="n">
+        <v>13000700001</v>
       </c>
       <c r="X85" s="2" t="n">
         <v>13000700001</v>
       </c>
-      <c r="Y85" s="2" t="n">
-        <v>13000700001</v>
-      </c>
-      <c r="Z85" s="2" t="inlineStr">
+      <c r="Y85" s="2" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y85"/>
+  <dimension ref="A1:Y89"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -3758,342 +3758,336 @@
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
-      <c r="A53" s="2" t="n">
+      <c r="A53" t="n">
+        <v>3001100001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeRandomDefense</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>3001100001</v>
+      </c>
+      <c r="X53" t="n">
+        <v>3001100001</v>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>大力出奇迹-随机一只防守魔物攻击力翻倍(单级可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="14.25" customHeight="1" s="3">
+      <c r="A54" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeRandomDefense</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="X54" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>膘肥体壮-随机一只防守魔物生命翻倍(单级可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A55" t="n">
+        <v>3001300001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeRandomDefense</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>3001300001</v>
+      </c>
+      <c r="X55" t="n">
+        <v>3001300001</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>钢铁憨憨-随机一只防守魔物护甲翻倍(单级可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A56" t="n">
+        <v>3001400001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeAttackTimeRandomDefense</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>3001400001</v>
+      </c>
+      <c r="X56" t="n">
+        <v>3001400001</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>急性子-随机一只防守魔物攻击翻倍快(单级可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A57" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C57" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D57" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="I57" s="2" t="n"/>
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="O53" s="2" t="n">
+      <c r="O57" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P53" s="2" t="n">
+      <c r="P57" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" s="2" t="n">
+      <c r="T57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="X53" s="2" t="n">
+      <c r="X57" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="14.25" customHeight="1" s="3">
-      <c r="A54" s="2" t="n">
+    <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A58" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C58" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D54" s="2" t="n">
+      <c r="D58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="I58" s="2" t="n"/>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O54" s="2" t="n">
+      <c r="O58" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P54" s="2" t="n">
+      <c r="P58" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="2" t="n">
+      <c r="T58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="X54" s="2" t="n">
+      <c r="X58" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="Y54" s="2" t="inlineStr">
+      <c r="Y58" s="2" t="inlineStr">
         <is>
           <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A55" s="2" t="n">
+    <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A59" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C59" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D55" s="2" t="n">
+      <c r="D59" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="I59" s="2" t="n"/>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O55" s="2" t="n">
+      <c r="O59" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P55" s="2" t="n">
+      <c r="P59" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" s="2" t="n">
+      <c r="T59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="X55" s="2" t="n">
+      <c r="X59" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y55" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A56" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="C56" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D56" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H56" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J56" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="O56" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="X56" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="Y56" s="0" t="inlineStr">
-        <is>
-          <t>攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A57" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="C57" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D57" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H57" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J57" s="0" t="inlineStr">
-        <is>
-          <t>RCD</t>
-        </is>
-      </c>
-      <c r="O57" s="0" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P57" s="0" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="X57" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="Y57" s="0" t="inlineStr">
-        <is>
-          <t>召唤CD{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A58" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="C58" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D58" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J58" s="0" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
-      <c r="O58" s="0" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P58" s="0" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="X58" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="Y58" s="0" t="inlineStr">
-        <is>
-          <t>召唤魔力消耗{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A59" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="C59" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D59" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityBaseHPChange</t>
-        </is>
-      </c>
-      <c r="I59" s="8" t="n"/>
-      <c r="O59" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P59" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S59" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V59" s="0" t="n">
-        <v>500001</v>
-      </c>
-      <c r="W59" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="X59" s="0" t="n">
-        <v>12000100001</v>
-      </c>
-      <c r="Y59" s="0" t="inlineStr">
-        <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000400001</v>
       </c>
       <c r="C60" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityBaseDRChange</t>
-        </is>
-      </c>
-      <c r="I60" s="8" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
       <c r="O60" s="0" t="n">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="P60" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S60" s="0" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="T60" s="0" t="n">
         <v>0</v>
@@ -4101,39 +4095,43 @@
       <c r="U60" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="0" t="n">
-        <v>500002</v>
-      </c>
       <c r="W60" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000400001</v>
       </c>
       <c r="X60" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000400001</v>
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000500001</v>
       </c>
       <c r="C61" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="n"/>
-      <c r="S61" s="0" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="H61" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J61" s="0" t="inlineStr">
+        <is>
+          <t>RCD</t>
+        </is>
+      </c>
+      <c r="O61" s="0" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P61" s="0" t="n">
+        <v>-0.5</v>
       </c>
       <c r="T61" s="0" t="n">
         <v>0</v>
@@ -4142,49 +4140,42 @@
         <v>0</v>
       </c>
       <c r="W61" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000500001</v>
       </c>
       <c r="X61" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000600001</v>
       </c>
       <c r="C62" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+        <v>2</v>
+      </c>
+      <c r="H62" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L62" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O62" s="0" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
+      </c>
+      <c r="P62" s="0" t="n">
+        <v>-0.5</v>
       </c>
       <c r="T62" s="0" t="n">
         <v>0</v>
@@ -4193,20 +4184,20 @@
         <v>0</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000600001</v>
       </c>
       <c r="X62" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000600001</v>
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000100001</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>12</v>
@@ -4216,26 +4207,18 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J63" s="0" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L63" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
+          <t>BuffEntityBaseHPChange</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="n"/>
       <c r="O63" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
+      </c>
+      <c r="P63" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S63" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T63" s="0" t="n">
         <v>0</v>
@@ -4243,21 +4226,24 @@
       <c r="U63" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V63" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W63" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000100001</v>
       </c>
       <c r="X63" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000200001</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>12</v>
@@ -4267,26 +4253,18 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J64" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L64" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
+          <t>BuffEntityBaseDRChange</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="n"/>
       <c r="O64" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
+      </c>
+      <c r="P64" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S64" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T64" s="0" t="n">
         <v>0</v>
@@ -4294,21 +4272,24 @@
       <c r="U64" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V64" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W64" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000200001</v>
       </c>
       <c r="X64" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000300001</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>12</v>
@@ -4318,26 +4299,12 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J65" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L65" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O65" s="0" t="n">
-        <v>0.25</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="n"/>
+      <c r="S65" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T65" s="0" t="n">
         <v>0</v>
@@ -4346,20 +4313,20 @@
         <v>0</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000300001</v>
       </c>
       <c r="X65" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001100001</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>12</v>
@@ -4367,14 +4334,14 @@
       <c r="D66" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J66" s="0" t="inlineStr">
@@ -4384,7 +4351,7 @@
       </c>
       <c r="L66" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O66" s="0" t="n">
@@ -4397,20 +4364,20 @@
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001100001</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001200001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>12</v>
@@ -4418,14 +4385,14 @@
       <c r="D67" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="H67" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J67" s="0" t="inlineStr">
@@ -4435,7 +4402,7 @@
       </c>
       <c r="L67" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O67" s="0" t="n">
@@ -4448,20 +4415,20 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001200001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001300001</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>12</v>
@@ -4469,14 +4436,14 @@
       <c r="D68" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J68" s="0" t="inlineStr">
@@ -4486,7 +4453,7 @@
       </c>
       <c r="L68" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O68" s="0" t="n">
@@ -4499,20 +4466,20 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001300001</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001400001</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>12</v>
@@ -4520,14 +4487,14 @@
       <c r="D69" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="H69" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J69" s="0" t="inlineStr">
@@ -4537,7 +4504,7 @@
       </c>
       <c r="L69" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O69" s="0" t="n">
@@ -4550,20 +4517,20 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001400001</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002100001</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>12</v>
@@ -4571,12 +4538,12 @@
       <c r="D70" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I70" s="11" t="inlineStr">
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
@@ -4586,9 +4553,9 @@
           <t>HP</t>
         </is>
       </c>
-      <c r="L70" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+      <c r="L70" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O70" s="0" t="n">
@@ -4601,20 +4568,20 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002100001</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002200001</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>12</v>
@@ -4622,12 +4589,12 @@
       <c r="D71" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H71" s="8" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I71" s="11" t="inlineStr">
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
@@ -4637,9 +4604,9 @@
           <t>DR</t>
         </is>
       </c>
-      <c r="L71" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+      <c r="L71" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O71" s="0" t="n">
@@ -4652,20 +4619,20 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002200001</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002300001</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>12</v>
@@ -4673,12 +4640,12 @@
       <c r="D72" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I72" s="11" t="inlineStr">
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
@@ -4688,9 +4655,9 @@
           <t>ATK</t>
         </is>
       </c>
-      <c r="L72" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O72" s="0" t="n">
@@ -4703,20 +4670,20 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002300001</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002400001</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>12</v>
@@ -4724,12 +4691,12 @@
       <c r="D73" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H73" s="8" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
-      <c r="I73" s="11" t="inlineStr">
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
@@ -4739,9 +4706,9 @@
           <t>ASPD</t>
         </is>
       </c>
-      <c r="L73" s="12" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+      <c r="L73" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O73" s="0" t="n">
@@ -4754,20 +4721,20 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002400001</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003100001</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>12</v>
@@ -4775,20 +4742,28 @@
       <c r="D74" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L74" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L74" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O74" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="T74" s="0" t="n">
         <v>0</v>
@@ -4797,20 +4772,20 @@
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003100001</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>12010200001</v>
+        <v>12003200001</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>12</v>
@@ -4818,20 +4793,28 @@
       <c r="D75" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H75" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
-      <c r="L75" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
+      <c r="J75" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L75" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O75" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="T75" s="0" t="n">
         <v>0</v>
@@ -4840,20 +4823,20 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>12010200001</v>
+        <v>12003200001</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>12010200001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>12010300001</v>
+        <v>12003300001</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>12</v>
@@ -4861,20 +4844,28 @@
       <c r="D76" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H76" s="11" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
-      <c r="L76" s="0" t="inlineStr">
-        <is>
-          <t>4001:1000&amp;</t>
-        </is>
+      <c r="J76" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L76" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O76" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="T76" s="0" t="n">
         <v>0</v>
@@ -4883,20 +4874,20 @@
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>12010300001</v>
+        <v>12003300001</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>12010300001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>12011100001</v>
+        <v>12003400001</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>12</v>
@@ -4906,18 +4897,26 @@
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L77" s="0" t="inlineStr">
-        <is>
-          <t>2001:1&amp;</t>
-        </is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O77" s="0" t="n">
+        <v>0.25</v>
       </c>
       <c r="T77" s="0" t="n">
         <v>0</v>
@@ -4926,20 +4925,20 @@
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>12011100001</v>
+        <v>12003400001</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>12011100001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010100001</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>12</v>
@@ -4947,19 +4946,19 @@
       <c r="D78" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="H78" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L78" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="T78" s="0" t="n">
@@ -4969,20 +4968,20 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010100001</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010200001</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>12</v>
@@ -4990,218 +4989,214 @@
       <c r="D79" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L79" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="X79" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="Y79" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H80" s="11" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L80" s="0" t="inlineStr">
+        <is>
+          <t>4001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="X80" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="Y80" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="C81" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L81" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
+      </c>
+      <c r="T81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="X81" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="Y81" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="C82" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
-      <c r="L79" s="0" t="inlineStr">
+      <c r="L82" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
+      </c>
+      <c r="T82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="X82" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="Y82" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L83" s="0" t="inlineStr">
         <is>
           <t>4001:200&amp;</t>
         </is>
       </c>
-      <c r="T79" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" s="0" t="n">
+      <c r="T83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="0" t="n">
         <v>12011300001</v>
       </c>
-      <c r="X79" s="0" t="n">
+      <c r="X83" s="0" t="n">
         <v>12011300001</v>
       </c>
-      <c r="Y79" s="0" t="inlineStr">
+      <c r="Y83" s="0" t="inlineStr">
         <is>
           <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="n"/>
-      <c r="M80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T80" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" s="2" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="X80" s="2" t="n">
-        <v>13000100001</v>
-      </c>
-      <c r="Y80" s="2" t="inlineStr">
-        <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D81" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="n"/>
-      <c r="T81" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" s="2" t="n">
-        <v>500001</v>
-      </c>
-      <c r="W81" s="2" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="X81" s="2" t="n">
-        <v>13000300001</v>
-      </c>
-      <c r="Y81" s="2" t="inlineStr">
-        <is>
-          <t>死亡后重生</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="C82" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D82" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalDeadAttack</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T82" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" s="2" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="X82" s="2" t="n">
-        <v>13000400001</v>
-      </c>
-      <c r="Y82" s="2" t="inlineStr">
-        <is>
-          <t>死亡后爆炸</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="C83" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D83" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P83" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="T83" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" s="2" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="X83" s="2" t="n">
-        <v>13000500001</v>
-      </c>
-      <c r="Y83" s="2" t="inlineStr">
-        <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>13000600001</v>
+        <v>13000100001</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>13</v>
@@ -5209,24 +5204,20 @@
       <c r="D84" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P84" s="2" t="n">
-        <v>0.01</v>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="n"/>
+      <c r="M84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N84" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="T84" s="0" t="n">
         <v>0</v>
@@ -5235,20 +5226,20 @@
         <v>0</v>
       </c>
       <c r="W84" s="2" t="n">
-        <v>13000600001</v>
+        <v>13000100001</v>
       </c>
       <c r="X84" s="2" t="n">
-        <v>13000600001</v>
+        <v>13000100001</v>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>13000700001</v>
+        <v>13000300001</v>
       </c>
       <c r="C85" s="2" t="n">
         <v>13</v>
@@ -5258,30 +5249,210 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J85" s="5" t="n"/>
+      <c r="T85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>500001</v>
+      </c>
+      <c r="W85" s="2" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="X85" s="2" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAttack</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" s="2" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="X86" s="2" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P87" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="2" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="X87" s="2" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P88" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="2" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="X88" s="2" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
           <t>BuffEntityConditionalDeadCreateCrystal</t>
         </is>
       </c>
-      <c r="I85" s="5" t="inlineStr">
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q85" s="2" t="n">
+      <c r="Q89" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="T85" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" s="2" t="n">
+      <c r="T89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" s="2" t="n">
         <v>13000700001</v>
       </c>
-      <c r="X85" s="2" t="n">
+      <c r="X89" s="2" t="n">
         <v>13000700001</v>
       </c>
-      <c r="Y85" s="2" t="inlineStr">
+      <c r="Y89" s="2" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -3758,171 +3758,171 @@
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
-      <c r="A53" t="n">
+      <c r="A53" s="0" t="n">
         <v>3001100001</v>
       </c>
-      <c r="C53" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeRandomDefense</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
+      <c r="C53" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeSingleTarget</t>
+        </is>
+      </c>
+      <c r="J53" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
+      <c r="O53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="0" t="n">
         <v>3001100001</v>
       </c>
-      <c r="X53" t="n">
+      <c r="X53" s="0" t="n">
         <v>3001100001</v>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Y53" s="0" t="inlineStr">
         <is>
           <t>大力出奇迹-随机一只防守魔物攻击力翻倍(单级可重复)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
-      <c r="A54" t="n">
+      <c r="A54" s="0" t="n">
         <v>3001200001</v>
       </c>
-      <c r="C54" t="n">
-        <v>3</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeRandomDefense</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
+      <c r="C54" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeSingleTarget</t>
+        </is>
+      </c>
+      <c r="J54" s="0" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
+      <c r="O54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="0" t="n">
         <v>3001200001</v>
       </c>
-      <c r="X54" t="n">
+      <c r="X54" s="0" t="n">
         <v>3001200001</v>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Y54" s="0" t="inlineStr">
         <is>
           <t>膘肥体壮-随机一只防守魔物生命翻倍(单级可重复)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A55" t="n">
+      <c r="A55" s="0" t="n">
         <v>3001300001</v>
       </c>
-      <c r="C55" t="n">
-        <v>3</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeRandomDefense</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
+      <c r="C55" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeSingleTarget</t>
+        </is>
+      </c>
+      <c r="J55" s="0" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
+      <c r="O55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="0" t="n">
         <v>3001300001</v>
       </c>
-      <c r="X55" t="n">
+      <c r="X55" s="0" t="n">
         <v>3001300001</v>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Y55" s="0" t="inlineStr">
         <is>
           <t>钢铁憨憨-随机一只防守魔物护甲翻倍(单级可重复)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A56" t="n">
+      <c r="A56" s="0" t="n">
         <v>3001400001</v>
       </c>
-      <c r="C56" t="n">
-        <v>3</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeAttackTimeRandomDefense</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
+      <c r="C56" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeAttackTimeSingleTarget</t>
+        </is>
+      </c>
+      <c r="O56" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
+      <c r="T56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="0" t="n">
         <v>3001400001</v>
       </c>
-      <c r="X56" t="n">
+      <c r="X56" s="0" t="n">
         <v>3001400001</v>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Y56" s="0" t="inlineStr">
         <is>
           <t>急性子-随机一只防守魔物攻击翻倍快(单级可重复)</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y89"/>
+  <dimension ref="A1:Y131"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -3930,27 +3930,30 @@
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="2" t="n">
-        <v>11000100001</v>
+        <v>3001500001</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I57" s="2" t="n"/>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="O57" s="2" t="n">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="P57" s="2" t="n">
         <v>0.1</v>
@@ -3962,40 +3965,43 @@
         <v>0</v>
       </c>
       <c r="W57" s="2" t="n">
-        <v>11000100001</v>
+        <v>3001500001</v>
       </c>
       <c r="X57" s="2" t="n">
-        <v>11000100001</v>
+        <v>3001500001</v>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>生命增加{Percentage}%</t>
+          <t>都是兄弟·攻击Lv.1-每只1%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="2" t="n">
-        <v>11000200001</v>
+        <v>3001500002</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I58" s="2" t="n"/>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="O58" s="2" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="P58" s="2" t="n">
         <v>0.1</v>
@@ -4007,30 +4013,33 @@
         <v>0</v>
       </c>
       <c r="W58" s="2" t="n">
-        <v>11000200001</v>
+        <v>3001500001</v>
       </c>
       <c r="X58" s="2" t="n">
-        <v>11000200001</v>
+        <v>3001500001</v>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>护甲增加{Percentage}%</t>
+          <t>都是兄弟·攻击Lv.2-每只2%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="2" t="n">
-        <v>11000300001</v>
+        <v>3001500003</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I59" s="2" t="n"/>
@@ -4040,7 +4049,7 @@
         </is>
       </c>
       <c r="O59" s="2" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="P59" s="2" t="n">
         <v>0.1</v>
@@ -4052,39 +4061,42 @@
         <v>0</v>
       </c>
       <c r="W59" s="2" t="n">
-        <v>11000300001</v>
+        <v>3001500001</v>
       </c>
       <c r="X59" s="2" t="n">
-        <v>11000300001</v>
+        <v>3001500001</v>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>攻击力增加{Percentage}%</t>
+          <t>都是兄弟·攻击Lv.3-每只3%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="0" t="n">
-        <v>11000400001</v>
+        <v>3001500004</v>
       </c>
       <c r="C60" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D60" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="O60" s="0" t="n">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="P60" s="0" t="n">
         <v>0.5</v>
@@ -4096,39 +4108,42 @@
         <v>0</v>
       </c>
       <c r="W60" s="0" t="n">
-        <v>11000400001</v>
+        <v>3001500001</v>
       </c>
       <c r="X60" s="0" t="n">
-        <v>11000400001</v>
+        <v>3001500001</v>
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>攻击速度增加{Percentage}%</t>
+          <t>都是兄弟·攻击Lv.4-每只4%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>11000500001</v>
+        <v>3001500005</v>
       </c>
       <c r="C61" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>RCD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="O61" s="0" t="n">
-        <v>-0.25</v>
+        <v>0.05</v>
       </c>
       <c r="P61" s="0" t="n">
         <v>-0.5</v>
@@ -4140,39 +4155,42 @@
         <v>0</v>
       </c>
       <c r="W61" s="0" t="n">
-        <v>11000500001</v>
+        <v>3001500001</v>
       </c>
       <c r="X61" s="0" t="n">
-        <v>11000500001</v>
+        <v>3001500001</v>
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>召唤CD{Percentage}%</t>
+          <t>都是兄弟·攻击Lv.5-每只5%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>11000600001</v>
+        <v>3001600001</v>
       </c>
       <c r="C62" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G62" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="O62" s="0" t="n">
-        <v>-0.25</v>
+        <v>0.01</v>
       </c>
       <c r="P62" s="0" t="n">
         <v>-0.5</v>
@@ -4184,35 +4202,43 @@
         <v>0</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>11000600001</v>
+        <v>3001600001</v>
       </c>
       <c r="X62" s="0" t="n">
-        <v>11000600001</v>
+        <v>3001600001</v>
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>召唤魔力消耗{Percentage}%</t>
+          <t>都是兄弟·护甲Lv.1-每只1%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>12000100001</v>
+        <v>3001600002</v>
       </c>
       <c r="C63" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G63" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
+      <c r="J63" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
       <c r="O63" s="0" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="P63" s="0" t="n">
         <v>0.01</v>
@@ -4230,35 +4256,43 @@
         <v>500001</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>12000100001</v>
+        <v>3001600001</v>
       </c>
       <c r="X63" s="0" t="n">
-        <v>12000100001</v>
+        <v>3001600001</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>都是兄弟·护甲Lv.2-每只2%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>12000200001</v>
+        <v>3001600003</v>
       </c>
       <c r="C64" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G64" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
+      <c r="J64" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
       <c r="O64" s="0" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="P64" s="0" t="n">
         <v>0.01</v>
@@ -4276,33 +4310,44 @@
         <v>500002</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>12000200001</v>
+        <v>3001600001</v>
       </c>
       <c r="X64" s="0" t="n">
-        <v>12000200001</v>
+        <v>3001600001</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>都是兄弟·护甲Lv.3-每只3%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>12000300001</v>
+        <v>3001600004</v>
       </c>
       <c r="C65" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G65" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O65" s="0" t="n">
+        <v>0.04</v>
+      </c>
       <c r="S65" s="0" t="n">
         <v>5</v>
       </c>
@@ -4313,30 +4358,33 @@
         <v>0</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>12000300001</v>
+        <v>3001600001</v>
       </c>
       <c r="X65" s="0" t="n">
-        <v>12000300001</v>
+        <v>3001600001</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>都是兄弟·护甲Lv.4-每只4%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>12001100001</v>
+        <v>3001600005</v>
       </c>
       <c r="C66" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G66" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I66" s="9" t="inlineStr">
@@ -4346,7 +4394,7 @@
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
@@ -4355,7 +4403,7 @@
         </is>
       </c>
       <c r="O66" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="T66" s="0" t="n">
         <v>0</v>
@@ -4364,30 +4412,33 @@
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>12001100001</v>
+        <v>3001600001</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>12001100001</v>
+        <v>3001600001</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>都是兄弟·护甲Lv.5-每只5%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>12001200001</v>
+        <v>3001700001</v>
       </c>
       <c r="C67" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G67" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I67" s="9" t="inlineStr">
@@ -4397,7 +4448,7 @@
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L67" s="0" t="inlineStr">
@@ -4406,7 +4457,7 @@
         </is>
       </c>
       <c r="O67" s="0" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="T67" s="0" t="n">
         <v>0</v>
@@ -4415,30 +4466,33 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>12001200001</v>
+        <v>3001700001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>12001200001</v>
+        <v>3001700001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>都是兄弟·生命Lv.1-每只1%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>12001300001</v>
+        <v>3001700002</v>
       </c>
       <c r="C68" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G68" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I68" s="9" t="inlineStr">
@@ -4448,7 +4502,7 @@
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L68" s="0" t="inlineStr">
@@ -4457,7 +4511,7 @@
         </is>
       </c>
       <c r="O68" s="0" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="T68" s="0" t="n">
         <v>0</v>
@@ -4466,30 +4520,33 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>12001300001</v>
+        <v>3001700001</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>12001300001</v>
+        <v>3001700001</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>都是兄弟·生命Lv.2-每只2%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>12001400001</v>
+        <v>3001700003</v>
       </c>
       <c r="C69" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G69" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I69" s="9" t="inlineStr">
@@ -4499,7 +4556,7 @@
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L69" s="0" t="inlineStr">
@@ -4508,7 +4565,7 @@
         </is>
       </c>
       <c r="O69" s="0" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="T69" s="0" t="n">
         <v>0</v>
@@ -4517,30 +4574,33 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>12001400001</v>
+        <v>3001700001</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>12001400001</v>
+        <v>3001700001</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>都是兄弟·生命Lv.3-每只3%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>12002100001</v>
+        <v>3001700004</v>
       </c>
       <c r="C70" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
@@ -4559,7 +4619,7 @@
         </is>
       </c>
       <c r="O70" s="0" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="T70" s="0" t="n">
         <v>0</v>
@@ -4568,30 +4628,33 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>12002100001</v>
+        <v>3001700001</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>12002100001</v>
+        <v>3001700001</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>都是兄弟·生命Lv.4-每只4%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>12002200001</v>
+        <v>3001700005</v>
       </c>
       <c r="C71" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G71" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByDefenseCount</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
@@ -4601,7 +4664,7 @@
       </c>
       <c r="J71" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L71" s="0" t="inlineStr">
@@ -4610,7 +4673,7 @@
         </is>
       </c>
       <c r="O71" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="T71" s="0" t="n">
         <v>0</v>
@@ -4619,30 +4682,33 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>12002200001</v>
+        <v>3001700001</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>12002200001</v>
+        <v>3001700001</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>都是兄弟·生命Lv.5-每只5%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>12002300001</v>
+        <v>3001800001</v>
       </c>
       <c r="C72" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G72" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I72" s="5" t="inlineStr">
@@ -4661,7 +4727,7 @@
         </is>
       </c>
       <c r="O72" s="0" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="T72" s="0" t="n">
         <v>0</v>
@@ -4670,30 +4736,33 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>12002300001</v>
+        <v>3001800001</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>12002300001</v>
+        <v>3001800001</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>杀红了眼·攻击Lv.1-每只1%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>12002400001</v>
+        <v>3001800002</v>
       </c>
       <c r="C73" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G73" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
@@ -4703,7 +4772,7 @@
       </c>
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L73" s="0" t="inlineStr">
@@ -4712,7 +4781,7 @@
         </is>
       </c>
       <c r="O73" s="0" t="n">
-        <v>0.25</v>
+        <v>0.02</v>
       </c>
       <c r="T73" s="0" t="n">
         <v>0</v>
@@ -4721,30 +4790,33 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>12002400001</v>
+        <v>3001800001</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>12002400001</v>
+        <v>3001800001</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>杀红了眼·攻击Lv.2-每只2%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>12003100001</v>
+        <v>3001800003</v>
       </c>
       <c r="C74" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G74" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
@@ -4754,7 +4826,7 @@
       </c>
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L74" s="12" t="inlineStr">
@@ -4763,7 +4835,7 @@
         </is>
       </c>
       <c r="O74" s="0" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="T74" s="0" t="n">
         <v>0</v>
@@ -4772,30 +4844,33 @@
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>12003100001</v>
+        <v>3001800001</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>12003100001</v>
+        <v>3001800001</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>杀红了眼·攻击Lv.3-每只3%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>12003200001</v>
+        <v>3001800004</v>
       </c>
       <c r="C75" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G75" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
@@ -4805,7 +4880,7 @@
       </c>
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L75" s="12" t="inlineStr">
@@ -4814,7 +4889,7 @@
         </is>
       </c>
       <c r="O75" s="0" t="n">
-        <v>0.25</v>
+        <v>0.04</v>
       </c>
       <c r="T75" s="0" t="n">
         <v>0</v>
@@ -4823,30 +4898,33 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>12003200001</v>
+        <v>3001800001</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>12003200001</v>
+        <v>3001800001</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>杀红了眼·攻击Lv.4-每只4%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>12003300001</v>
+        <v>3001800005</v>
       </c>
       <c r="C76" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G76" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
@@ -4865,7 +4943,7 @@
         </is>
       </c>
       <c r="O76" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="T76" s="0" t="n">
         <v>0</v>
@@ -4874,30 +4952,33 @@
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>12003300001</v>
+        <v>3001800001</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>12003300001</v>
+        <v>3001800001</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>杀红了眼·攻击Lv.5-每只5%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>12003400001</v>
+        <v>3001900001</v>
       </c>
       <c r="C77" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G77" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -4907,7 +4988,7 @@
       </c>
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L77" s="12" t="inlineStr">
@@ -4916,7 +4997,7 @@
         </is>
       </c>
       <c r="O77" s="0" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="T77" s="0" t="n">
         <v>0</v>
@@ -4925,30 +5006,33 @@
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>12003400001</v>
+        <v>3001900001</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>12003400001</v>
+        <v>3001900001</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>杀红了眼·护甲Lv.1-每只1%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>12010100001</v>
+        <v>3001900002</v>
       </c>
       <c r="C78" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G78" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I78" s="13" t="inlineStr">
@@ -4956,11 +5040,19 @@
           <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
       <c r="L78" s="0" t="inlineStr">
         <is>
           <t>2001:10&amp;</t>
         </is>
       </c>
+      <c r="O78" s="0" t="n">
+        <v>0.02</v>
+      </c>
       <c r="T78" s="0" t="n">
         <v>0</v>
       </c>
@@ -4968,30 +5060,33 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>12010100001</v>
+        <v>3001900001</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>12010100001</v>
+        <v>3001900001</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>杀红了眼·护甲Lv.2-每只2%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>12010200001</v>
+        <v>3001900003</v>
       </c>
       <c r="C79" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G79" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
@@ -4999,11 +5094,19 @@
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
+      <c r="J79" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
       <c r="L79" s="0" t="inlineStr">
         <is>
           <t>3001:1000&amp;</t>
         </is>
       </c>
+      <c r="O79" s="0" t="n">
+        <v>0.03</v>
+      </c>
       <c r="T79" s="0" t="n">
         <v>0</v>
       </c>
@@ -5011,30 +5114,33 @@
         <v>0</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>12010200001</v>
+        <v>3001900001</v>
       </c>
       <c r="X79" s="0" t="n">
-        <v>12010200001</v>
+        <v>3001900001</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>杀红了眼·护甲Lv.3-每只3%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>12010300001</v>
+        <v>3001900004</v>
       </c>
       <c r="C80" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G80" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
@@ -5042,11 +5148,19 @@
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
+      <c r="J80" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
       <c r="L80" s="0" t="inlineStr">
         <is>
           <t>4001:1000&amp;</t>
         </is>
       </c>
+      <c r="O80" s="0" t="n">
+        <v>0.04</v>
+      </c>
       <c r="T80" s="0" t="n">
         <v>0</v>
       </c>
@@ -5054,30 +5168,33 @@
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>12010300001</v>
+        <v>3001900001</v>
       </c>
       <c r="X80" s="0" t="n">
-        <v>12010300001</v>
+        <v>3001900001</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>杀红了眼·护甲Lv.4-每只4%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>12011100001</v>
+        <v>3001900005</v>
       </c>
       <c r="C81" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G81" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I81" s="13" t="inlineStr">
@@ -5085,11 +5202,19 @@
           <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
+      <c r="J81" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
       <c r="L81" s="0" t="inlineStr">
         <is>
           <t>2001:1&amp;</t>
         </is>
       </c>
+      <c r="O81" s="0" t="n">
+        <v>0.05</v>
+      </c>
       <c r="T81" s="0" t="n">
         <v>0</v>
       </c>
@@ -5097,30 +5222,33 @@
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>12011100001</v>
+        <v>3001900001</v>
       </c>
       <c r="X81" s="0" t="n">
-        <v>12011100001</v>
+        <v>3001900001</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>杀红了眼·护甲Lv.5-每只5%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>12011200001</v>
+        <v>3002000001</v>
       </c>
       <c r="C82" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G82" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr">
@@ -5128,11 +5256,19 @@
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
+      <c r="J82" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
       <c r="L82" s="0" t="inlineStr">
         <is>
           <t>3001:200&amp;</t>
         </is>
       </c>
+      <c r="O82" s="0" t="n">
+        <v>0.01</v>
+      </c>
       <c r="T82" s="0" t="n">
         <v>0</v>
       </c>
@@ -5140,30 +5276,33 @@
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>12011200001</v>
+        <v>3002000001</v>
       </c>
       <c r="X82" s="0" t="n">
-        <v>12011200001</v>
+        <v>3002000001</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>杀红了眼·生命Lv.1-每只1%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>12011300001</v>
+        <v>3002000002</v>
       </c>
       <c r="C83" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G83" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I83" s="5" t="inlineStr">
@@ -5171,11 +5310,19 @@
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
+      <c r="J83" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
       <c r="L83" s="0" t="inlineStr">
         <is>
           <t>4001:200&amp;</t>
         </is>
       </c>
+      <c r="O83" s="0" t="n">
+        <v>0.02</v>
+      </c>
       <c r="T83" s="0" t="n">
         <v>0</v>
       </c>
@@ -5183,39 +5330,50 @@
         <v>0</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>12011300001</v>
+        <v>3002000001</v>
       </c>
       <c r="X83" s="0" t="n">
-        <v>12011300001</v>
+        <v>3002000001</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>杀红了眼·生命Lv.2-每只2%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>13000100001</v>
+        <v>3002000003</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="G84" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
+      <c r="J84" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
       <c r="M84" s="2" t="n">
         <v>3</v>
       </c>
       <c r="N84" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="O84" s="0" t="n">
+        <v>0.03</v>
+      </c>
       <c r="S84" s="2" t="n">
         <v>3</v>
       </c>
@@ -5226,30 +5384,33 @@
         <v>0</v>
       </c>
       <c r="W84" s="2" t="n">
-        <v>13000100001</v>
+        <v>3002000001</v>
       </c>
       <c r="X84" s="2" t="n">
-        <v>13000100001</v>
+        <v>3002000001</v>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>杀红了眼·生命Lv.3-每只3%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>13000300001</v>
+        <v>3002000004</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="G85" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr">
@@ -5257,7 +5418,14 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J85" s="5" t="n"/>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="O85" s="0" t="n">
+        <v>0.04</v>
+      </c>
       <c r="T85" s="0" t="n">
         <v>0</v>
       </c>
@@ -5268,30 +5436,33 @@
         <v>500001</v>
       </c>
       <c r="W85" s="2" t="n">
-        <v>13000300001</v>
+        <v>3002000001</v>
       </c>
       <c r="X85" s="2" t="n">
-        <v>13000300001</v>
+        <v>3002000001</v>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>杀红了眼·生命Lv.4-每只4%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>13000400001</v>
+        <v>3002000005</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="G86" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityAttributeScaleByKillCount</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
@@ -5299,11 +5470,13 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J86" s="2" t="n">
-        <v>300001</v>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
       </c>
       <c r="O86" s="2" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="T86" s="0" t="n">
         <v>0</v>
@@ -5312,30 +5485,30 @@
         <v>0</v>
       </c>
       <c r="W86" s="2" t="n">
-        <v>13000400001</v>
+        <v>3002000001</v>
       </c>
       <c r="X86" s="2" t="n">
-        <v>13000400001</v>
+        <v>3002000001</v>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>杀红了眼·生命Lv.5-每只5%(动态,作用全体防守魔物)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>13000500001</v>
+        <v>11000100001</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
@@ -5343,14 +5516,16 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J87" s="5" t="n">
-        <v>1</v>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
       </c>
       <c r="O87" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="T87" s="0" t="n">
         <v>0</v>
@@ -5359,30 +5534,30 @@
         <v>0</v>
       </c>
       <c r="W87" s="2" t="n">
-        <v>13000500001</v>
+        <v>11000100001</v>
       </c>
       <c r="X87" s="2" t="n">
-        <v>13000500001</v>
+        <v>11000100001</v>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>13000600001</v>
+        <v>11000200001</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
@@ -5390,14 +5565,16 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J88" s="5" t="n">
-        <v>1</v>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
       </c>
       <c r="O88" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="T88" s="0" t="n">
         <v>0</v>
@@ -5406,36 +5583,47 @@
         <v>0</v>
       </c>
       <c r="W88" s="2" t="n">
-        <v>13000600001</v>
+        <v>11000200001</v>
       </c>
       <c r="X88" s="2" t="n">
-        <v>13000600001</v>
+        <v>11000200001</v>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>13000700001</v>
+        <v>11000300001</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadCreateCrystal</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
+      </c>
+      <c r="J89" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="O89" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P89" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="Q89" s="2" t="n">
         <v>0.2</v>
@@ -5447,26 +5635,2007 @@
         <v>0</v>
       </c>
       <c r="W89" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="X89" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="n">
+        <v>11000400001</v>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D90" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J90" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="O90" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="0" t="n">
+        <v>11000400001</v>
+      </c>
+      <c r="X90" s="0" t="n">
+        <v>11000400001</v>
+      </c>
+      <c r="Y90" s="0" t="inlineStr">
+        <is>
+          <t>攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="n">
+        <v>11000500001</v>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D91" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H91" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J91" s="0" t="inlineStr">
+        <is>
+          <t>RCD</t>
+        </is>
+      </c>
+      <c r="O91" s="0" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P91" s="0" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="0" t="n">
+        <v>11000500001</v>
+      </c>
+      <c r="X91" s="0" t="n">
+        <v>11000500001</v>
+      </c>
+      <c r="Y91" s="0" t="inlineStr">
+        <is>
+          <t>召唤CD{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="n">
+        <v>11000600001</v>
+      </c>
+      <c r="C92" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="D92" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H92" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J92" s="0" t="inlineStr">
+        <is>
+          <t>CMP</t>
+        </is>
+      </c>
+      <c r="O92" s="0" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="P92" s="0" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="T92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" s="0" t="n">
+        <v>11000600001</v>
+      </c>
+      <c r="X92" s="0" t="n">
+        <v>11000600001</v>
+      </c>
+      <c r="Y92" s="0" t="inlineStr">
+        <is>
+          <t>召唤魔力消耗{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>11000700001</v>
+      </c>
+      <c r="C93" t="n">
+        <v>11</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>ATK:1|HP:-1</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" t="n">
+        <v>11000700001</v>
+      </c>
+      <c r="X93" t="n">
+        <v>11000700001</v>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>狂战士-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>11000700002</v>
+      </c>
+      <c r="C94" t="n">
+        <v>11</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>ATK:1|DR:-1</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" t="n">
+        <v>11000700002</v>
+      </c>
+      <c r="X94" t="n">
+        <v>11000700002</v>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>狂战士-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>11000700003</v>
+      </c>
+      <c r="C95" t="n">
+        <v>11</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ATK:1|ASPD:-1</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" t="n">
+        <v>11000700003</v>
+      </c>
+      <c r="X95" t="n">
+        <v>11000700003</v>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>狂战士-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>11000800001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>11</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ASPD:1|DR:-1</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" t="n">
+        <v>11000800001</v>
+      </c>
+      <c r="X96" t="n">
+        <v>11000800001</v>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>快枪手-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>11000800002</v>
+      </c>
+      <c r="C97" t="n">
+        <v>11</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>ASPD:1|HP:-1</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" t="n">
+        <v>11000800002</v>
+      </c>
+      <c r="X97" t="n">
+        <v>11000800002</v>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>快枪手-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>11000800003</v>
+      </c>
+      <c r="C98" t="n">
+        <v>11</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>ASPD:1|ATK:-1</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" t="n">
+        <v>11000800003</v>
+      </c>
+      <c r="X98" t="n">
+        <v>11000800003</v>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>快枪手-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>11000900001</v>
+      </c>
+      <c r="C99" t="n">
+        <v>11</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>DR:1|HP:-1</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" t="n">
+        <v>11000900001</v>
+      </c>
+      <c r="X99" t="n">
+        <v>11000900001</v>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>铜墙铁壁-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>11000900002</v>
+      </c>
+      <c r="C100" t="n">
+        <v>11</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>DR:1|ATK:-1</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" t="n">
+        <v>11000900002</v>
+      </c>
+      <c r="X100" t="n">
+        <v>11000900002</v>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>铜墙铁壁-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>11000900003</v>
+      </c>
+      <c r="C101" t="n">
+        <v>11</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>DR:1|ASPD:-1</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" t="n">
+        <v>11000900003</v>
+      </c>
+      <c r="X101" t="n">
+        <v>11000900003</v>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>铜墙铁壁-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>11001000001</v>
+      </c>
+      <c r="C102" t="n">
+        <v>11</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>HP:1|ASPD:-1</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" t="n">
+        <v>11001000001</v>
+      </c>
+      <c r="X102" t="n">
+        <v>11001000001</v>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>大块头-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="12" customHeight="1" s="3">
+      <c r="A103" t="n">
+        <v>11001000002</v>
+      </c>
+      <c r="C103" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>HP:1|DR:-1</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>11001000002</v>
+      </c>
+      <c r="X103" t="n">
+        <v>11001000002</v>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>大块头-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="12" customHeight="1" s="3">
+      <c r="A104" t="n">
+        <v>11001000003</v>
+      </c>
+      <c r="C104" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>HP:1|ATK:-1</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>11001000003</v>
+      </c>
+      <c r="X104" t="n">
+        <v>11001000003</v>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>大块头-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="12" customHeight="1" s="3">
+      <c r="A105" s="0" t="n">
+        <v>12000100001</v>
+      </c>
+      <c r="C105" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H105" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityBaseHPChange</t>
+        </is>
+      </c>
+      <c r="O105" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P105" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S105" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="W105" s="0" t="n">
+        <v>12000100001</v>
+      </c>
+      <c r="X105" s="0" t="n">
+        <v>12000100001</v>
+      </c>
+      <c r="Y105" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="12" customHeight="1" s="3">
+      <c r="A106" s="0" t="n">
+        <v>12000200001</v>
+      </c>
+      <c r="C106" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityBaseDRChange</t>
+        </is>
+      </c>
+      <c r="O106" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P106" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S106" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="0" t="n">
+        <v>500002</v>
+      </c>
+      <c r="W106" s="0" t="n">
+        <v>12000200001</v>
+      </c>
+      <c r="X106" s="0" t="n">
+        <v>12000200001</v>
+      </c>
+      <c r="Y106" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="12" customHeight="1" s="3">
+      <c r="A107" s="0" t="n">
+        <v>12000300001</v>
+      </c>
+      <c r="C107" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H107" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="S107" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="0" t="n">
+        <v>12000300001</v>
+      </c>
+      <c r="X107" s="0" t="n">
+        <v>12000300001</v>
+      </c>
+      <c r="Y107" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒立即攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="12" customHeight="1" s="3">
+      <c r="A108" s="0" t="n">
+        <v>12001100001</v>
+      </c>
+      <c r="C108" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D108" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I108" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J108" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L108" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O108" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T108" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="0" t="n">
+        <v>12001100001</v>
+      </c>
+      <c r="X108" s="0" t="n">
+        <v>12001100001</v>
+      </c>
+      <c r="Y108" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="12" customHeight="1" s="3">
+      <c r="A109" s="0" t="n">
+        <v>12001200001</v>
+      </c>
+      <c r="C109" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J109" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L109" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O109" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="0" t="n">
+        <v>12001200001</v>
+      </c>
+      <c r="X109" s="0" t="n">
+        <v>12001200001</v>
+      </c>
+      <c r="Y109" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="12" customHeight="1" s="3">
+      <c r="A110" s="0" t="n">
+        <v>12001300001</v>
+      </c>
+      <c r="C110" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H110" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J110" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L110" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O110" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="0" t="n">
+        <v>12001300001</v>
+      </c>
+      <c r="X110" s="0" t="n">
+        <v>12001300001</v>
+      </c>
+      <c r="Y110" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="12" customHeight="1" s="3">
+      <c r="A111" s="0" t="n">
+        <v>12001400001</v>
+      </c>
+      <c r="C111" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J111" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L111" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O111" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" s="0" t="n">
+        <v>12001400001</v>
+      </c>
+      <c r="X111" s="0" t="n">
+        <v>12001400001</v>
+      </c>
+      <c r="Y111" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="C112" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D112" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J112" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O112" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="X112" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="Y112" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J113" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O113" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="X113" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="Y113" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J114" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O114" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T114" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="X114" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="Y114" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H115" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J115" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O115" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="X115" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="Y115" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="C116" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J116" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L116" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O116" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T116" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="X116" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="Y116" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="C117" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H117" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I117" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J117" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L117" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O117" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T117" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="X117" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="Y117" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="C118" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J118" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L118" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O118" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T118" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="X118" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="Y118" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="C119" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J119" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O119" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T119" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="X119" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="Y119" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="C120" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="T120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="X120" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="Y120" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="C121" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L121" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="X121" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="Y121" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="C122" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
+          <t>4001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T122" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="X122" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="Y122" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="C123" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
+      </c>
+      <c r="T123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="X123" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="Y123" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="C124" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H124" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L124" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
+      </c>
+      <c r="T124" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="X124" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="Y124" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="C125" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L125" s="0" t="inlineStr">
+        <is>
+          <t>4001:200&amp;</t>
+        </is>
+      </c>
+      <c r="T125" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="X125" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="Y125" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="C126" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H126" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M126" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N126" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S126" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T126" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="X126" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="Y126" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="C127" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I127" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="T127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="W127" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="X127" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Y127" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="C128" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H128" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAttack</t>
+        </is>
+      </c>
+      <c r="I128" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J128" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O128" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="X128" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Y128" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="C129" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D129" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H129" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
+        </is>
+      </c>
+      <c r="I129" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J129" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O129" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P129" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="X129" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Y129" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="C130" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D130" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H130" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I130" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J130" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P130" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="X130" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="Y130" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="n">
         <v>13000700001</v>
       </c>
-      <c r="X89" s="2" t="n">
+      <c r="C131" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D131" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H131" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I131" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="Q131" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" s="0" t="n">
         <v>13000700001</v>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="X131" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="Y131" s="0" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="12" customHeight="1" s="3"/>
-    <row r="104" ht="12" customHeight="1" s="3"/>
-    <row r="105" ht="12" customHeight="1" s="3"/>
-    <row r="106" ht="12" customHeight="1" s="3"/>
-    <row r="107" ht="12" customHeight="1" s="3"/>
-    <row r="108" ht="12" customHeight="1" s="3"/>
-    <row r="109" ht="12" customHeight="1" s="3"/>
-    <row r="110" ht="12" customHeight="1" s="3"/>
-    <row r="111" ht="12" customHeight="1" s="3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y131"/>
+  <dimension ref="A1:Y137"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -5779,600 +5779,600 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" s="0" t="n">
         <v>11000700001</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="inlineStr">
+      <c r="G93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="0" t="inlineStr">
         <is>
           <t>ATK:1|HP:-1</t>
         </is>
       </c>
-      <c r="O93" t="n">
+      <c r="O93" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P93" t="n">
+      <c r="P93" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>0</v>
-      </c>
-      <c r="U93" t="n">
-        <v>0</v>
-      </c>
-      <c r="W93" t="n">
+      <c r="R93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="0" t="n">
         <v>11000700001</v>
       </c>
-      <c r="X93" t="n">
+      <c r="X93" s="0" t="n">
         <v>11000700001</v>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Y93" s="0" t="inlineStr">
         <is>
           <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" s="0" t="n">
         <v>11000700002</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="inlineStr">
+      <c r="G94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="0" t="inlineStr">
         <is>
           <t>ATK:1|DR:-1</t>
         </is>
       </c>
-      <c r="O94" t="n">
+      <c r="O94" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P94" t="n">
+      <c r="P94" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" t="n">
-        <v>0</v>
-      </c>
-      <c r="W94" t="n">
+      <c r="R94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="0" t="n">
         <v>11000700002</v>
       </c>
-      <c r="X94" t="n">
+      <c r="X94" s="0" t="n">
         <v>11000700002</v>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Y94" s="0" t="inlineStr">
         <is>
           <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" s="0" t="n">
         <v>11000700003</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="inlineStr">
+      <c r="G95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" s="0" t="inlineStr">
         <is>
           <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
-      <c r="O95" t="n">
+      <c r="O95" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P95" t="n">
+      <c r="P95" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R95" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" t="n">
-        <v>0</v>
-      </c>
-      <c r="W95" t="n">
+      <c r="R95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="0" t="n">
         <v>11000700003</v>
       </c>
-      <c r="X95" t="n">
+      <c r="X95" s="0" t="n">
         <v>11000700003</v>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Y95" s="0" t="inlineStr">
         <is>
           <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" s="0" t="n">
         <v>11000800001</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="inlineStr">
+      <c r="G96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96" s="0" t="inlineStr">
         <is>
           <t>ASPD:1|DR:-1</t>
         </is>
       </c>
-      <c r="O96" t="n">
+      <c r="O96" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P96" t="n">
+      <c r="P96" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R96" t="n">
-        <v>0</v>
-      </c>
-      <c r="T96" t="n">
-        <v>0</v>
-      </c>
-      <c r="U96" t="n">
-        <v>0</v>
-      </c>
-      <c r="W96" t="n">
+      <c r="R96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="0" t="n">
         <v>11000800001</v>
       </c>
-      <c r="X96" t="n">
+      <c r="X96" s="0" t="n">
         <v>11000800001</v>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Y96" s="0" t="inlineStr">
         <is>
           <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="0" t="n">
         <v>11000800002</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="inlineStr">
+      <c r="G97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J97" s="0" t="inlineStr">
         <is>
           <t>ASPD:1|HP:-1</t>
         </is>
       </c>
-      <c r="O97" t="n">
+      <c r="O97" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P97" t="n">
+      <c r="P97" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R97" t="n">
-        <v>0</v>
-      </c>
-      <c r="T97" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" t="n">
+      <c r="R97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="0" t="n">
         <v>11000800002</v>
       </c>
-      <c r="X97" t="n">
+      <c r="X97" s="0" t="n">
         <v>11000800002</v>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Y97" s="0" t="inlineStr">
         <is>
           <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" s="0" t="n">
         <v>11000800003</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="inlineStr">
+      <c r="G98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J98" s="0" t="inlineStr">
         <is>
           <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
-      <c r="O98" t="n">
+      <c r="O98" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P98" t="n">
+      <c r="P98" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R98" t="n">
-        <v>0</v>
-      </c>
-      <c r="T98" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" t="n">
-        <v>0</v>
-      </c>
-      <c r="W98" t="n">
+      <c r="R98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="0" t="n">
         <v>11000800003</v>
       </c>
-      <c r="X98" t="n">
+      <c r="X98" s="0" t="n">
         <v>11000800003</v>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Y98" s="0" t="inlineStr">
         <is>
           <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="0" t="n">
         <v>11000900001</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="inlineStr">
+      <c r="G99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J99" s="0" t="inlineStr">
         <is>
           <t>DR:1|HP:-1</t>
         </is>
       </c>
-      <c r="O99" t="n">
+      <c r="O99" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P99" t="n">
+      <c r="P99" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R99" t="n">
-        <v>0</v>
-      </c>
-      <c r="T99" t="n">
-        <v>0</v>
-      </c>
-      <c r="U99" t="n">
-        <v>0</v>
-      </c>
-      <c r="W99" t="n">
+      <c r="R99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="0" t="n">
         <v>11000900001</v>
       </c>
-      <c r="X99" t="n">
+      <c r="X99" s="0" t="n">
         <v>11000900001</v>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Y99" s="0" t="inlineStr">
         <is>
           <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" s="0" t="n">
         <v>11000900002</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="G100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J100" s="0" t="inlineStr">
         <is>
           <t>DR:1|ATK:-1</t>
         </is>
       </c>
-      <c r="O100" t="n">
+      <c r="O100" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P100" t="n">
+      <c r="P100" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="T100" t="n">
-        <v>0</v>
-      </c>
-      <c r="U100" t="n">
-        <v>0</v>
-      </c>
-      <c r="W100" t="n">
+      <c r="R100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="0" t="n">
         <v>11000900002</v>
       </c>
-      <c r="X100" t="n">
+      <c r="X100" s="0" t="n">
         <v>11000900002</v>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Y100" s="0" t="inlineStr">
         <is>
           <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" s="0" t="n">
         <v>11000900003</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="inlineStr">
+      <c r="G101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J101" s="0" t="inlineStr">
         <is>
           <t>DR:1|ASPD:-1</t>
         </is>
       </c>
-      <c r="O101" t="n">
+      <c r="O101" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P101" t="n">
+      <c r="P101" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R101" t="n">
-        <v>0</v>
-      </c>
-      <c r="T101" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
+      <c r="R101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="0" t="n">
         <v>11000900003</v>
       </c>
-      <c r="X101" t="n">
+      <c r="X101" s="0" t="n">
         <v>11000900003</v>
       </c>
-      <c r="Y101" t="inlineStr">
+      <c r="Y101" s="0" t="inlineStr">
         <is>
           <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102" s="0" t="n">
         <v>11001000001</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="inlineStr">
+      <c r="G102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J102" s="0" t="inlineStr">
         <is>
           <t>HP:1|ASPD:-1</t>
         </is>
       </c>
-      <c r="O102" t="n">
+      <c r="O102" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P102" t="n">
+      <c r="P102" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
+      <c r="R102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="0" t="n">
         <v>11001000001</v>
       </c>
-      <c r="X102" t="n">
+      <c r="X102" s="0" t="n">
         <v>11001000001</v>
       </c>
-      <c r="Y102" t="inlineStr">
+      <c r="Y102" s="0" t="inlineStr">
         <is>
           <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="103" ht="12" customHeight="1" s="3">
-      <c r="A103" t="n">
+      <c r="A103" s="0" t="n">
         <v>11001000002</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="inlineStr">
+      <c r="G103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J103" s="0" t="inlineStr">
         <is>
           <t>HP:1|DR:-1</t>
         </is>
       </c>
-      <c r="O103" t="n">
+      <c r="O103" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P103" t="n">
+      <c r="P103" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
+      <c r="R103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="0" t="n">
         <v>11001000002</v>
       </c>
-      <c r="X103" t="n">
+      <c r="X103" s="0" t="n">
         <v>11001000002</v>
       </c>
-      <c r="Y103" t="inlineStr">
+      <c r="Y103" s="0" t="inlineStr">
         <is>
           <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="104" ht="12" customHeight="1" s="3">
-      <c r="A104" t="n">
+      <c r="A104" s="0" t="n">
         <v>11001000003</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="inlineStr">
+      <c r="G104" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J104" s="0" t="inlineStr">
         <is>
           <t>HP:1|ATK:-1</t>
         </is>
       </c>
-      <c r="O104" t="n">
+      <c r="O104" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P104" t="n">
+      <c r="P104" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
+      <c r="R104" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="0" t="n">
         <v>11001000003</v>
       </c>
-      <c r="X104" t="n">
+      <c r="X104" s="0" t="n">
         <v>11001000003</v>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Y104" s="0" t="inlineStr">
         <is>
           <t>大块头-C</t>
         </is>
@@ -6537,6 +6537,9 @@
       <c r="O108" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P108" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T108" s="0" t="n">
         <v>0</v>
       </c>
@@ -6588,6 +6591,9 @@
       <c r="O109" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P109" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T109" s="0" t="n">
         <v>0</v>
       </c>
@@ -6639,6 +6645,9 @@
       <c r="O110" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P110" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T110" s="0" t="n">
         <v>0</v>
       </c>
@@ -6690,6 +6699,9 @@
       <c r="O111" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P111" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T111" s="0" t="n">
         <v>0</v>
       </c>
@@ -6741,6 +6753,9 @@
       <c r="O112" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P112" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T112" s="0" t="n">
         <v>0</v>
       </c>
@@ -6792,6 +6807,9 @@
       <c r="O113" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P113" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T113" s="0" t="n">
         <v>0</v>
       </c>
@@ -6843,6 +6861,9 @@
       <c r="O114" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P114" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T114" s="0" t="n">
         <v>0</v>
       </c>
@@ -6894,6 +6915,9 @@
       <c r="O115" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P115" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T115" s="0" t="n">
         <v>0</v>
       </c>
@@ -6945,6 +6969,9 @@
       <c r="O116" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P116" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T116" s="0" t="n">
         <v>0</v>
       </c>
@@ -6996,6 +7023,9 @@
       <c r="O117" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P117" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T117" s="0" t="n">
         <v>0</v>
       </c>
@@ -7047,6 +7077,9 @@
       <c r="O118" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P118" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T118" s="0" t="n">
         <v>0</v>
       </c>
@@ -7098,6 +7131,9 @@
       <c r="O119" s="0" t="n">
         <v>0.25</v>
       </c>
+      <c r="P119" s="0" t="n">
+        <v>0.1</v>
+      </c>
       <c r="T119" s="0" t="n">
         <v>0</v>
       </c>
@@ -7117,180 +7153,208 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="0" t="n">
-        <v>12010100001</v>
-      </c>
-      <c r="C120" s="0" t="n">
+      <c r="A120" t="n">
+        <v>12004100001</v>
+      </c>
+      <c r="C120" t="n">
         <v>12</v>
       </c>
-      <c r="D120" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H120" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I120" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L120" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="T120" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" s="0" t="n">
-        <v>12010100001</v>
-      </c>
-      <c r="X120" s="0" t="n">
-        <v>12010100001</v>
-      </c>
-      <c r="Y120" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" t="n">
+        <v>12004100001</v>
+      </c>
+      <c r="X120" t="n">
+        <v>12004100001</v>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="0" t="n">
-        <v>12010200001</v>
-      </c>
-      <c r="C121" s="0" t="n">
+      <c r="A121" t="n">
+        <v>12004200001</v>
+      </c>
+      <c r="C121" t="n">
         <v>12</v>
       </c>
-      <c r="D121" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H121" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I121" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L121" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="T121" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" s="0" t="n">
-        <v>12010200001</v>
-      </c>
-      <c r="X121" s="0" t="n">
-        <v>12010200001</v>
-      </c>
-      <c r="Y121" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>12004200001</v>
+      </c>
+      <c r="X121" t="n">
+        <v>12004200001</v>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="0" t="n">
-        <v>12010300001</v>
-      </c>
-      <c r="C122" s="0" t="n">
+      <c r="A122" t="n">
+        <v>12004300001</v>
+      </c>
+      <c r="C122" t="n">
         <v>12</v>
       </c>
-      <c r="D122" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H122" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I122" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L122" s="0" t="inlineStr">
-        <is>
-          <t>4001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="T122" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" s="0" t="n">
-        <v>12010300001</v>
-      </c>
-      <c r="X122" s="0" t="n">
-        <v>12010300001</v>
-      </c>
-      <c r="Y122" s="0" t="inlineStr">
-        <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>12004300001</v>
+      </c>
+      <c r="X122" t="n">
+        <v>12004300001</v>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="0" t="n">
-        <v>12011100001</v>
-      </c>
-      <c r="C123" s="0" t="n">
+      <c r="A123" t="n">
+        <v>12004400001</v>
+      </c>
+      <c r="C123" t="n">
         <v>12</v>
       </c>
-      <c r="D123" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H123" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I123" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L123" s="0" t="inlineStr">
-        <is>
-          <t>2001:1&amp;</t>
-        </is>
-      </c>
-      <c r="T123" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" s="0" t="n">
-        <v>12011100001</v>
-      </c>
-      <c r="X123" s="0" t="n">
-        <v>12011100001</v>
-      </c>
-      <c r="Y123" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>12004400001</v>
+      </c>
+      <c r="X123" t="n">
+        <v>12004400001</v>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010100001</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>12</v>
@@ -7300,17 +7364,17 @@
       </c>
       <c r="H124" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="T124" s="0" t="n">
@@ -7320,20 +7384,20 @@
         <v>0</v>
       </c>
       <c r="W124" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010100001</v>
       </c>
       <c r="X124" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010200001</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>12</v>
@@ -7343,7 +7407,7 @@
       </c>
       <c r="H125" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I125" s="0" t="inlineStr">
@@ -7353,7 +7417,7 @@
       </c>
       <c r="L125" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="T125" s="0" t="n">
@@ -7363,40 +7427,41 @@
         <v>0</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010200001</v>
       </c>
       <c r="X125" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010200001</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010300001</v>
       </c>
       <c r="C126" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D126" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="M126" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N126" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S126" s="0" t="n">
-        <v>3</v>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L126" s="0" t="inlineStr">
+        <is>
+          <t>4001:1000&amp;</t>
+        </is>
       </c>
       <c r="T126" s="0" t="n">
         <v>0</v>
@@ -7405,35 +7470,40 @@
         <v>0</v>
       </c>
       <c r="W126" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010300001</v>
       </c>
       <c r="X126" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010300001</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>13000300001</v>
+        <v>12010400001</v>
       </c>
       <c r="C127" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H127" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I127" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L127" s="0" t="inlineStr">
+        <is>
+          <t>5001:500&amp;</t>
         </is>
       </c>
       <c r="T127" s="0" t="n">
@@ -7442,46 +7512,42 @@
       <c r="U127" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W127" s="0" t="n">
-        <v>13000300001</v>
+        <v>12010400001</v>
       </c>
       <c r="X127" s="0" t="n">
-        <v>13000300001</v>
+        <v>12010400001</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>13000400001</v>
+        <v>12010500001</v>
       </c>
       <c r="C128" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I128" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J128" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O128" s="0" t="n">
-        <v>1</v>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L128" s="0" t="inlineStr">
+        <is>
+          <t>6001:1000&amp;</t>
+        </is>
       </c>
       <c r="T128" s="0" t="n">
         <v>0</v>
@@ -7490,45 +7556,41 @@
         <v>0</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>13000400001</v>
+        <v>12010500001</v>
       </c>
       <c r="X128" s="0" t="n">
-        <v>13000400001</v>
+        <v>12010500001</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011100001</v>
       </c>
       <c r="C129" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H129" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I129" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J129" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O129" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P129" s="0" t="n">
-        <v>0.01</v>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L129" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
       </c>
       <c r="T129" s="0" t="n">
         <v>0</v>
@@ -7537,45 +7599,41 @@
         <v>0</v>
       </c>
       <c r="W129" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011100001</v>
       </c>
       <c r="X129" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011100001</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>13000600001</v>
+        <v>12011200001</v>
       </c>
       <c r="C130" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H130" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I130" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J130" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O130" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P130" s="0" t="n">
-        <v>0.01</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L130" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
       </c>
       <c r="T130" s="0" t="n">
         <v>0</v>
@@ -7584,53 +7642,317 @@
         <v>0</v>
       </c>
       <c r="W130" s="0" t="n">
-        <v>13000600001</v>
+        <v>12011200001</v>
       </c>
       <c r="X130" s="0" t="n">
-        <v>13000600001</v>
+        <v>12011200001</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="C131" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D131" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H131" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I131" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L131" s="0" t="inlineStr">
+        <is>
+          <t>4001:200&amp;</t>
+        </is>
+      </c>
+      <c r="T131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="X131" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="Y131" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="C132" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D132" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H132" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M132" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N132" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S132" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="X132" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="Y132" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="C133" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D133" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H133" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I133" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="T133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="W133" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="X133" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Y133" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="C134" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D134" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H134" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAttack</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J134" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O134" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="X134" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Y134" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="C135" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D135" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H135" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
+        </is>
+      </c>
+      <c r="I135" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J135" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O135" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P135" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="X135" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Y135" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="C136" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D136" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H136" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I136" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J136" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P136" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="X136" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="Y136" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="n">
         <v>13000700001</v>
       </c>
-      <c r="C131" s="0" t="n">
+      <c r="C137" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="D131" s="0" t="n">
+      <c r="D137" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="H131" s="0" t="inlineStr">
+      <c r="H137" s="0" t="inlineStr">
         <is>
           <t>BuffEntityConditionalDeadCreateCrystal</t>
         </is>
       </c>
-      <c r="I131" s="0" t="inlineStr">
+      <c r="I137" s="0" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q131" s="0" t="n">
+      <c r="Q137" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="T131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W131" s="0" t="n">
+      <c r="T137" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" s="0" t="n">
         <v>13000700001</v>
       </c>
-      <c r="X131" s="0" t="n">
+      <c r="X137" s="0" t="n">
         <v>13000700001</v>
       </c>
-      <c r="Y131" s="0" t="inlineStr">
+      <c r="Y137" s="0" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -7153,200 +7153,200 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" s="0" t="n">
         <v>12004100001</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="D120" t="n">
-        <v>3</v>
-      </c>
-      <c r="H120" t="inlineStr">
+      <c r="D120" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" s="0" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttributeTime</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr">
+      <c r="I120" s="0" t="inlineStr"/>
+      <c r="J120" s="0" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="L120" s="0" t="inlineStr">
         <is>
           <t>7001:300&amp;</t>
         </is>
       </c>
-      <c r="O120" t="n">
+      <c r="O120" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="P120" t="n">
+      <c r="P120" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="T120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-      <c r="W120" t="n">
+      <c r="T120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="0" t="n">
         <v>12004100001</v>
       </c>
-      <c r="X120" t="n">
+      <c r="X120" s="0" t="n">
         <v>12004100001</v>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Y120" s="0" t="inlineStr">
         <is>
           <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" s="0" t="n">
         <v>12004200001</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="D121" t="n">
-        <v>3</v>
-      </c>
-      <c r="H121" t="inlineStr">
+      <c r="D121" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" s="0" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttributeTime</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr">
+      <c r="I121" s="0" t="inlineStr"/>
+      <c r="J121" s="0" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="L121" s="0" t="inlineStr">
         <is>
           <t>7001:300&amp;</t>
         </is>
       </c>
-      <c r="O121" t="n">
+      <c r="O121" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="P121" t="n">
+      <c r="P121" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
+      <c r="T121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="0" t="n">
         <v>12004200001</v>
       </c>
-      <c r="X121" t="n">
+      <c r="X121" s="0" t="n">
         <v>12004200001</v>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Y121" s="0" t="inlineStr">
         <is>
           <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122" s="0" t="n">
         <v>12004300001</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="D122" t="n">
-        <v>3</v>
-      </c>
-      <c r="H122" t="inlineStr">
+      <c r="D122" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" s="0" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttributeTime</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr">
+      <c r="I122" s="0" t="inlineStr"/>
+      <c r="J122" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="L122" s="0" t="inlineStr">
         <is>
           <t>7001:300&amp;</t>
         </is>
       </c>
-      <c r="O122" t="n">
+      <c r="O122" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="P122" t="n">
+      <c r="P122" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" t="n">
+      <c r="T122" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="0" t="n">
         <v>12004300001</v>
       </c>
-      <c r="X122" t="n">
+      <c r="X122" s="0" t="n">
         <v>12004300001</v>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Y122" s="0" t="inlineStr">
         <is>
           <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" s="0" t="n">
         <v>12004400001</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="D123" t="n">
-        <v>3</v>
-      </c>
-      <c r="H123" t="inlineStr">
+      <c r="D123" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" s="0" t="inlineStr">
         <is>
           <t>BuffEntityConditionalAttributeTime</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr">
+      <c r="I123" s="0" t="inlineStr"/>
+      <c r="J123" s="0" t="inlineStr">
         <is>
           <t>ASPD</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="L123" s="0" t="inlineStr">
         <is>
           <t>7001:300&amp;</t>
         </is>
       </c>
-      <c r="O123" t="n">
+      <c r="O123" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="P123" t="n">
+      <c r="P123" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
+      <c r="T123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="0" t="n">
         <v>12004400001</v>
       </c>
-      <c r="X123" t="n">
+      <c r="X123" s="0" t="n">
         <v>12004400001</v>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Y123" s="0" t="inlineStr">
         <is>
           <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
@@ -7740,7 +7740,7 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="C133" s="0" t="n">
         <v>13</v>
@@ -7768,10 +7768,10 @@
         <v>500001</v>
       </c>
       <c r="W133" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="X133" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
@@ -7781,7 +7781,7 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="C134" s="0" t="n">
         <v>13</v>
@@ -7812,10 +7812,10 @@
         <v>0</v>
       </c>
       <c r="W134" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="X134" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="C135" s="0" t="n">
         <v>13</v>
@@ -7859,10 +7859,10 @@
         <v>0</v>
       </c>
       <c r="W135" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="X135" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="C136" s="0" t="n">
         <v>13</v>
@@ -7906,10 +7906,10 @@
         <v>0</v>
       </c>
       <c r="W136" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="X136" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="Y136" s="0" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>13000700001</v>
+        <v>13000600001</v>
       </c>
       <c r="C137" s="0" t="n">
         <v>13</v>
@@ -7947,10 +7947,10 @@
         <v>0</v>
       </c>
       <c r="W137" s="0" t="n">
-        <v>13000700001</v>
+        <v>13000600001</v>
       </c>
       <c r="X137" s="0" t="n">
-        <v>13000700001</v>
+        <v>13000600001</v>
       </c>
       <c r="Y137" s="0" t="inlineStr">
         <is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="O9" s="1" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="S9" s="1" t="n">
         <v>10</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -2168,7 +2168,7 @@
         </is>
       </c>
       <c r="Q16" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="T16" s="0" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Y16" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV1-每一次击杀有10%的概率多掉落一次魔晶</t>
+          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Q17" s="0" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="T17" s="0" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Y17" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV2-每一次击杀有20%的概率多掉落一次魔晶</t>
+          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="Q18" s="0" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="T18" s="0" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="Y18" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV3-每一次击杀有30%的概率多掉落一次魔晶</t>
+          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Q19" s="0" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="T19" s="0" t="n">
         <v>0</v>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="Y19" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV4-每一次击杀有40%的概率多掉落一次魔晶</t>
+          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
         </is>
       </c>
       <c r="Q20" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T20" s="0" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Y20" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV5-每一次击杀有50%的概率多掉落一次魔晶</t>
+          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:Y78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2377,464 +2377,467 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicMultiInstantAttack</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>1,0.2</t>
+        </is>
+      </c>
+      <c r="M21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="X21" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="Y21" s="0" t="inlineStr">
+        <is>
+          <t>闪电Lv1-每3秒1道落雷,范围0.2,伤害=魔王攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="3">
+      <c r="A22" s="0" t="n">
+        <v>3000300002</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicMultiInstantAttack</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="inlineStr">
+        <is>
+          <t>2,0.4</t>
+        </is>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="X22" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="Y22" s="0" t="inlineStr">
+        <is>
+          <t>闪电Lv2-每3秒2道落雷,范围0.4,伤害=魔王攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="3">
+      <c r="A23" s="0" t="n">
+        <v>3000300003</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicMultiInstantAttack</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="inlineStr">
+        <is>
+          <t>3,0.6</t>
+        </is>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="X23" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="Y23" s="0" t="inlineStr">
+        <is>
+          <t>闪电Lv3-每3秒3道落雷,范围0.6,伤害=魔王攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="3">
+      <c r="A24" s="0" t="n">
+        <v>3000300004</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicMultiInstantAttack</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>4,0.8</t>
+        </is>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="X24" s="0" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="Y24" s="0" t="inlineStr">
+        <is>
+          <t>闪电Lv4-每3秒4道落雷,范围0.8,伤害=魔王攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="3">
+      <c r="A25" t="n">
+        <v>3000300005</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicMultiInstantAttack</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5,1</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3000300001</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>闪电Lv5-每3秒5道落雷,范围1,伤害=魔王攻击力</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>BuffEntityInstantRewardMoreItem</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
-      <c r="T21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="2" t="n">
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="T26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="X21" s="2" t="n">
+      <c r="X26" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="Y26" s="2" t="inlineStr">
         <is>
           <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="3">
-      <c r="A22" s="2" t="n">
+    <row r="27" ht="15" customHeight="1" s="3">
+      <c r="A27" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>BuffEntityInstantRewardMoreSelect</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="n"/>
-      <c r="T22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="2" t="n">
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="T27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="X22" s="2" t="n">
+      <c r="X27" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>再来一瓶-通关奖励可选次数+1</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="3">
-      <c r="A23" s="2" t="n">
+    <row r="28" ht="15" customHeight="1" s="3">
+      <c r="A28" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C28" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="O23" s="2" t="n">
+      <c r="O28" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P23" s="2" t="n">
+      <c r="P28" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="2" t="n">
+      <c r="T28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="X23" s="2" t="n">
+      <c r="X28" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="3">
-      <c r="A24" s="2" t="n">
+    <row r="29" ht="15" customHeight="1" s="3">
+      <c r="A29" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C29" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O24" s="2" t="n">
+      <c r="O29" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P24" s="2" t="n">
+      <c r="P29" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="2" t="n">
+      <c r="T29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="X24" s="2" t="n">
+      <c r="X29" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="3">
-      <c r="A25" s="2" t="n">
+    <row r="30" ht="15" customHeight="1" s="3">
+      <c r="A30" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C30" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J25" s="0" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O25" s="0" t="n">
+      <c r="O30" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="P25" s="0" t="n">
+      <c r="P30" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q25" s="2" t="n">
+      <c r="Q30" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="T25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="2" t="n">
+      <c r="T30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="X25" s="2" t="n">
+      <c r="X30" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y25" s="2" t="inlineStr">
+      <c r="Y30" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="C26" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D26" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J26" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="O26" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="X26" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="Y26" s="0" t="inlineStr">
-        <is>
-          <t>攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="3">
-      <c r="A27" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="C27" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D27" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J27" s="0" t="inlineStr">
-        <is>
-          <t>RCD</t>
-        </is>
-      </c>
-      <c r="O27" s="0" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P27" s="0" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="X27" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="Y27" s="0" t="inlineStr">
-        <is>
-          <t>召唤CD{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="3">
-      <c r="A28" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="C28" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D28" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J28" s="0" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
-      <c r="O28" s="0" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P28" s="0" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="X28" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="Y28" s="0" t="inlineStr">
-        <is>
-          <t>召唤魔力消耗{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="3">
-      <c r="A29" s="0" t="n">
-        <v>11000700001</v>
-      </c>
-      <c r="C29" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeMulti</t>
-        </is>
-      </c>
-      <c r="J29" s="0" t="inlineStr">
-        <is>
-          <t>ATK:1|HP:-1</t>
-        </is>
-      </c>
-      <c r="O29" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P29" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="0" t="n">
-        <v>11000700001</v>
-      </c>
-      <c r="X29" s="0" t="n">
-        <v>11000700001</v>
-      </c>
-      <c r="Y29" s="0" t="inlineStr">
-        <is>
-          <t>狂战士-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="3">
-      <c r="A30" s="0" t="n">
-        <v>11000700002</v>
-      </c>
-      <c r="C30" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D30" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeMulti</t>
-        </is>
-      </c>
-      <c r="J30" s="0" t="inlineStr">
-        <is>
-          <t>ATK:1|DR:-1</t>
-        </is>
-      </c>
-      <c r="O30" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P30" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="0" t="n">
-        <v>11000700002</v>
-      </c>
-      <c r="X30" s="0" t="n">
-        <v>11000700002</v>
-      </c>
-      <c r="Y30" s="0" t="inlineStr">
-        <is>
-          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="1" s="2">
       <c r="A31" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000400001</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>11</v>
@@ -2842,28 +2845,22 @@
       <c r="D31" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G31" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|ASPD:-1</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="O31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P31" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R31" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="T31" s="0" t="n">
         <v>0</v>
       </c>
@@ -2871,20 +2868,20 @@
         <v>0</v>
       </c>
       <c r="W31" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000400001</v>
       </c>
       <c r="X31" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000400001</v>
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>狂战士-C</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="2">
       <c r="A32" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000500001</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>11</v>
@@ -2892,27 +2889,21 @@
       <c r="D32" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|DR:-1</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O32" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P32" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R32" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T32" s="0" t="n">
         <v>0</v>
@@ -2921,20 +2912,20 @@
         <v>0</v>
       </c>
       <c r="W32" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000500001</v>
       </c>
       <c r="X32" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>快枪手-A</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="2">
       <c r="A33" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000600001</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>11</v>
@@ -2942,27 +2933,21 @@
       <c r="D33" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|HP:-1</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O33" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P33" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R33" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T33" s="0" t="n">
         <v>0</v>
@@ -2971,20 +2956,20 @@
         <v>0</v>
       </c>
       <c r="W33" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000600001</v>
       </c>
       <c r="X33" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000600001</v>
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>快枪手-B</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" s="3">
       <c r="A34" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000700001</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>11</v>
@@ -3002,7 +2987,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|ATK:-1</t>
+          <t>ATK:1|HP:-1</t>
         </is>
       </c>
       <c r="O34" s="0" t="n">
@@ -3021,20 +3006,20 @@
         <v>0</v>
       </c>
       <c r="W34" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000700001</v>
       </c>
       <c r="X34" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000700001</v>
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>快枪手-C</t>
+          <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="3">
       <c r="A35" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000700002</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>11</v>
@@ -3052,7 +3037,7 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>DR:1|HP:-1</t>
+          <t>ATK:1|DR:-1</t>
         </is>
       </c>
       <c r="O35" s="0" t="n">
@@ -3071,20 +3056,20 @@
         <v>0</v>
       </c>
       <c r="W35" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000700002</v>
       </c>
       <c r="X35" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000700002</v>
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-A</t>
+          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
       <c r="A36" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000700003</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>11</v>
@@ -3102,7 +3087,7 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ATK:-1</t>
+          <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O36" s="0" t="n">
@@ -3121,20 +3106,20 @@
         <v>0</v>
       </c>
       <c r="W36" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000700003</v>
       </c>
       <c r="X36" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000700003</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-B</t>
+          <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
       <c r="A37" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000800001</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>11</v>
@@ -3152,7 +3137,7 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ASPD:-1</t>
+          <t>ASPD:1|DR:-1</t>
         </is>
       </c>
       <c r="O37" s="0" t="n">
@@ -3171,20 +3156,20 @@
         <v>0</v>
       </c>
       <c r="W37" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000800001</v>
       </c>
       <c r="X37" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000800001</v>
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-C</t>
+          <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
       <c r="A38" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000800002</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>11</v>
@@ -3202,7 +3187,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ASPD:-1</t>
+          <t>ASPD:1|HP:-1</t>
         </is>
       </c>
       <c r="O38" s="0" t="n">
@@ -3221,20 +3206,20 @@
         <v>0</v>
       </c>
       <c r="W38" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000800002</v>
       </c>
       <c r="X38" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000800002</v>
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>大块头-A</t>
+          <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
       <c r="A39" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000800003</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>11</v>
@@ -3252,7 +3237,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>HP:1|DR:-1</t>
+          <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
       <c r="O39" s="0" t="n">
@@ -3271,20 +3256,20 @@
         <v>0</v>
       </c>
       <c r="W39" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000800003</v>
       </c>
       <c r="X39" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000800003</v>
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>大块头-B</t>
+          <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
       <c r="A40" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000900001</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>11</v>
@@ -3302,7 +3287,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ATK:-1</t>
+          <t>DR:1|HP:-1</t>
         </is>
       </c>
       <c r="O40" s="0" t="n">
@@ -3321,40 +3306,48 @@
         <v>0</v>
       </c>
       <c r="W40" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000900001</v>
       </c>
       <c r="X40" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000900001</v>
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>大块头-C</t>
+          <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
       <c r="A41" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000900002</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>DR:1|ATK:-1</t>
         </is>
       </c>
       <c r="O41" s="0" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="P41" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S41" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
+      </c>
+      <c r="R41" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T41" s="0" t="n">
         <v>0</v>
@@ -3362,44 +3355,49 @@
       <c r="U41" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W41" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000900002</v>
       </c>
       <c r="X41" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000900002</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
       <c r="A42" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000900003</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G42" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>DR:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O42" s="0" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="P42" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S42" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
+      </c>
+      <c r="R42" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T42" s="0" t="n">
         <v>0</v>
@@ -3407,38 +3405,49 @@
       <c r="U42" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="0" t="n">
-        <v>500002</v>
-      </c>
       <c r="W42" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000900003</v>
       </c>
       <c r="X42" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000900003</v>
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
       <c r="A43" s="0" t="n">
-        <v>12000300001</v>
+        <v>11001000001</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D43" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G43" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
-      </c>
-      <c r="S43" s="0" t="n">
-        <v>5</v>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>HP:1|ASPD:-1</t>
+        </is>
+      </c>
+      <c r="O43" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P43" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R43" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T43" s="0" t="n">
         <v>0</v>
@@ -3447,52 +3456,48 @@
         <v>0</v>
       </c>
       <c r="W43" s="0" t="n">
-        <v>12000300001</v>
+        <v>11001000001</v>
       </c>
       <c r="X43" s="0" t="n">
-        <v>12000300001</v>
+        <v>11001000001</v>
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
       <c r="A44" s="0" t="n">
-        <v>12001100001</v>
+        <v>11001000002</v>
       </c>
       <c r="C44" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D44" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G44" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I44" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L44" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>HP:1|DR:-1</t>
         </is>
       </c>
       <c r="O44" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P44" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R44" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T44" s="0" t="n">
         <v>0</v>
@@ -3501,52 +3506,48 @@
         <v>0</v>
       </c>
       <c r="W44" s="0" t="n">
-        <v>12001100001</v>
+        <v>11001000002</v>
       </c>
       <c r="X44" s="0" t="n">
-        <v>12001100001</v>
+        <v>11001000002</v>
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
       <c r="A45" s="0" t="n">
-        <v>12001200001</v>
+        <v>11001000003</v>
       </c>
       <c r="C45" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D45" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G45" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I45" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L45" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>HP:1|ATK:-1</t>
         </is>
       </c>
       <c r="O45" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P45" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R45" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T45" s="0" t="n">
         <v>0</v>
@@ -3555,20 +3556,20 @@
         <v>0</v>
       </c>
       <c r="W45" s="0" t="n">
-        <v>12001200001</v>
+        <v>11001000003</v>
       </c>
       <c r="X45" s="0" t="n">
-        <v>12001200001</v>
+        <v>11001000003</v>
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>大块头-C</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="3">
       <c r="A46" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>12</v>
@@ -3578,29 +3579,17 @@
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I46" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J46" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L46" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>BuffEntityBaseHPChange</t>
         </is>
       </c>
       <c r="O46" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="P46" s="0" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
+      </c>
+      <c r="S46" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T46" s="0" t="n">
         <v>0</v>
@@ -3608,21 +3597,24 @@
       <c r="U46" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V46" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W46" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="X46" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="3">
       <c r="A47" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>12</v>
@@ -3632,29 +3624,17 @@
       </c>
       <c r="H47" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I47" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J47" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L47" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>BuffEntityBaseDRChange</t>
         </is>
       </c>
       <c r="O47" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="P47" s="0" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
+      </c>
+      <c r="S47" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T47" s="0" t="n">
         <v>0</v>
@@ -3662,21 +3642,24 @@
       <c r="U47" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V47" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W47" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="X47" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="3">
       <c r="A48" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="C48" s="0" t="n">
         <v>12</v>
@@ -3686,29 +3669,11 @@
       </c>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I48" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J48" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L48" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O48" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P48" s="0" t="n">
-        <v>0.1</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="S48" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T48" s="0" t="n">
         <v>0</v>
@@ -3717,20 +3682,20 @@
         <v>0</v>
       </c>
       <c r="W48" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="X48" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="3">
       <c r="A49" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="C49" s="0" t="n">
         <v>12</v>
@@ -3745,17 +3710,17 @@
       </c>
       <c r="I49" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L49" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O49" s="0" t="n">
@@ -3771,20 +3736,20 @@
         <v>0</v>
       </c>
       <c r="W49" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="X49" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y49" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="3">
       <c r="A50" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>12</v>
@@ -3799,17 +3764,17 @@
       </c>
       <c r="I50" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L50" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O50" s="0" t="n">
@@ -3825,20 +3790,20 @@
         <v>0</v>
       </c>
       <c r="W50" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="X50" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="3">
       <c r="A51" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="C51" s="0" t="n">
         <v>12</v>
@@ -3853,17 +3818,17 @@
       </c>
       <c r="I51" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J51" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L51" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O51" s="0" t="n">
@@ -3879,20 +3844,20 @@
         <v>0</v>
       </c>
       <c r="W51" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="X51" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y51" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="3">
       <c r="A52" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>12</v>
@@ -3907,17 +3872,17 @@
       </c>
       <c r="I52" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J52" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L52" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O52" s="0" t="n">
@@ -3933,20 +3898,20 @@
         <v>0</v>
       </c>
       <c r="W52" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="X52" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y52" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
       <c r="A53" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>12</v>
@@ -3966,12 +3931,12 @@
       </c>
       <c r="J53" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L53" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O53" s="0" t="n">
@@ -3987,20 +3952,20 @@
         <v>0</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="X53" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>12</v>
@@ -4020,12 +3985,12 @@
       </c>
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L54" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O54" s="0" t="n">
@@ -4041,20 +4006,20 @@
         <v>0</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="X54" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>12</v>
@@ -4074,12 +4039,12 @@
       </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L55" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O55" s="0" t="n">
@@ -4095,20 +4060,20 @@
         <v>0</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="X55" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>12004100001</v>
+        <v>12002400001</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>12</v>
@@ -4118,18 +4083,22 @@
       </c>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I56" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L56" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O56" s="0" t="n">
@@ -4145,20 +4114,20 @@
         <v>0</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>12004100001</v>
+        <v>12002400001</v>
       </c>
       <c r="X56" s="0" t="n">
-        <v>12004100001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003100001</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>12</v>
@@ -4168,18 +4137,22 @@
       </c>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I57" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L57" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O57" s="0" t="n">
@@ -4195,20 +4168,20 @@
         <v>0</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003100001</v>
       </c>
       <c r="X57" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="0" t="n">
-        <v>12004300001</v>
+        <v>12003200001</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>12</v>
@@ -4218,18 +4191,22 @@
       </c>
       <c r="H58" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I58" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L58" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O58" s="0" t="n">
@@ -4245,20 +4222,20 @@
         <v>0</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>12004300001</v>
+        <v>12003200001</v>
       </c>
       <c r="X58" s="0" t="n">
-        <v>12004300001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="0" t="n">
-        <v>12004400001</v>
+        <v>12003300001</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>12</v>
@@ -4268,18 +4245,22 @@
       </c>
       <c r="H59" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I59" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L59" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O59" s="0" t="n">
@@ -4295,20 +4276,20 @@
         <v>0</v>
       </c>
       <c r="W59" s="0" t="n">
-        <v>12004400001</v>
+        <v>12003300001</v>
       </c>
       <c r="X59" s="0" t="n">
-        <v>12004400001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003400001</v>
       </c>
       <c r="C60" s="0" t="n">
         <v>12</v>
@@ -4318,18 +4299,29 @@
       </c>
       <c r="H60" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I60" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L60" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O60" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P60" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T60" s="0" t="n">
         <v>0</v>
@@ -4338,20 +4330,20 @@
         <v>0</v>
       </c>
       <c r="W60" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003400001</v>
       </c>
       <c r="X60" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004100001</v>
       </c>
       <c r="C61" s="0" t="n">
         <v>12</v>
@@ -4361,18 +4353,25 @@
       </c>
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I61" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr"/>
+      <c r="J61" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="L61" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O61" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P61" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T61" s="0" t="n">
         <v>0</v>
@@ -4381,20 +4380,20 @@
         <v>0</v>
       </c>
       <c r="W61" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004100001</v>
       </c>
       <c r="X61" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004100001</v>
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>12010300001</v>
+        <v>12004200001</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>12</v>
@@ -4404,18 +4403,25 @@
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I62" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr"/>
+      <c r="J62" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
         </is>
       </c>
       <c r="L62" s="0" t="inlineStr">
         <is>
-          <t>4001:1000&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O62" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P62" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T62" s="0" t="n">
         <v>0</v>
@@ -4424,20 +4430,20 @@
         <v>0</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>12010300001</v>
+        <v>12004200001</v>
       </c>
       <c r="X62" s="0" t="n">
-        <v>12010300001</v>
+        <v>12004200001</v>
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>12010400001</v>
+        <v>12004300001</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>12</v>
@@ -4447,18 +4453,25 @@
       </c>
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I63" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr"/>
+      <c r="J63" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L63" s="0" t="inlineStr">
         <is>
-          <t>5001:500&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O63" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P63" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T63" s="0" t="n">
         <v>0</v>
@@ -4467,20 +4480,20 @@
         <v>0</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>12010400001</v>
+        <v>12004300001</v>
       </c>
       <c r="X63" s="0" t="n">
-        <v>12010400001</v>
+        <v>12004300001</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>12010500001</v>
+        <v>12004400001</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>12</v>
@@ -4490,18 +4503,25 @@
       </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I64" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="inlineStr"/>
+      <c r="J64" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L64" s="0" t="inlineStr">
         <is>
-          <t>6001:1000&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O64" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P64" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T64" s="0" t="n">
         <v>0</v>
@@ -4510,20 +4530,20 @@
         <v>0</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>12010500001</v>
+        <v>12004400001</v>
       </c>
       <c r="X64" s="0" t="n">
-        <v>12010500001</v>
+        <v>12004400001</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010100001</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>12</v>
@@ -4533,7 +4553,7 @@
       </c>
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I65" s="0" t="inlineStr">
@@ -4543,7 +4563,7 @@
       </c>
       <c r="L65" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="T65" s="0" t="n">
@@ -4553,20 +4573,20 @@
         <v>0</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010100001</v>
       </c>
       <c r="X65" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010200001</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>12</v>
@@ -4576,7 +4596,7 @@
       </c>
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I66" s="0" t="inlineStr">
@@ -4586,7 +4606,7 @@
       </c>
       <c r="L66" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="T66" s="0" t="n">
@@ -4596,20 +4616,20 @@
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010200001</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010200001</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010300001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>12</v>
@@ -4619,7 +4639,7 @@
       </c>
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I67" s="0" t="inlineStr">
@@ -4629,7 +4649,7 @@
       </c>
       <c r="L67" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
+          <t>4001:1000&amp;</t>
         </is>
       </c>
       <c r="T67" s="0" t="n">
@@ -4639,40 +4659,41 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010300001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010300001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010400001</v>
       </c>
       <c r="C68" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H68" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="M68" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N68" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S68" s="0" t="n">
-        <v>3</v>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L68" s="0" t="inlineStr">
+        <is>
+          <t>5001:500&amp;</t>
+        </is>
       </c>
       <c r="T68" s="0" t="n">
         <v>0</v>
@@ -4681,35 +4702,40 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010400001</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010400001</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>13000200001</v>
+        <v>12010500001</v>
       </c>
       <c r="C69" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I69" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L69" s="0" t="inlineStr">
+        <is>
+          <t>6001:1000&amp;</t>
         </is>
       </c>
       <c r="T69" s="0" t="n">
@@ -4718,46 +4744,42 @@
       <c r="U69" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W69" s="0" t="n">
-        <v>13000200001</v>
+        <v>12010500001</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>13000200001</v>
+        <v>12010500001</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>13000300001</v>
+        <v>12011100001</v>
       </c>
       <c r="C70" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I70" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J70" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O70" s="0" t="n">
-        <v>1</v>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L70" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
       </c>
       <c r="T70" s="0" t="n">
         <v>0</v>
@@ -4766,45 +4788,41 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>13000300001</v>
+        <v>12011100001</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>13000300001</v>
+        <v>12011100001</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>13000400001</v>
+        <v>12011200001</v>
       </c>
       <c r="C71" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H71" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I71" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J71" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O71" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P71" s="0" t="n">
-        <v>0.01</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L71" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
       </c>
       <c r="T71" s="0" t="n">
         <v>0</v>
@@ -4813,45 +4831,41 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>13000400001</v>
+        <v>12011200001</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>13000400001</v>
+        <v>12011200001</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011300001</v>
       </c>
       <c r="C72" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I72" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J72" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P72" s="0" t="n">
-        <v>0.01</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L72" s="0" t="inlineStr">
+        <is>
+          <t>4001:200&amp;</t>
+        </is>
       </c>
       <c r="T72" s="0" t="n">
         <v>0</v>
@@ -4860,20 +4874,20 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011300001</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011300001</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000100001</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>13</v>
@@ -4883,30 +4897,251 @@
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M73" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="X73" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="Y73" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="C74" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D74" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I74" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="T74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="W74" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="X74" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="Y74" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="C75" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D75" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H75" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAttack</t>
+        </is>
+      </c>
+      <c r="I75" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O75" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="X75" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Y75" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="C76" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D76" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
+        </is>
+      </c>
+      <c r="I76" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P76" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="X76" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Y76" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="C77" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D77" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H77" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P77" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="X77" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Y77" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="C78" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D78" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" s="0" t="inlineStr">
+        <is>
           <t>BuffEntityConditionalDeadCreateCrystal</t>
         </is>
       </c>
-      <c r="I73" s="0" t="inlineStr">
+      <c r="I78" s="0" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q73" s="0" t="n">
+      <c r="Q78" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="T73" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U73" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W73" s="0" t="n">
+      <c r="T78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="0" t="n">
         <v>13000600001</v>
       </c>
-      <c r="X73" s="0" t="n">
+      <c r="X78" s="0" t="n">
         <v>13000600001</v>
       </c>
-      <c r="Y73" s="0" t="inlineStr">
+      <c r="Y78" s="0" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -2393,7 +2393,7 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>1,0.2</t>
+          <t>1,0.2,1</t>
         </is>
       </c>
       <c r="M21" s="0" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="Y21" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv1-每3秒1道落雷,范围0.2,伤害=魔王攻击力</t>
+          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>2,0.4</t>
+          <t>2,0.4,2</t>
         </is>
       </c>
       <c r="M22" s="0" t="n">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Y22" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv2-每3秒2道落雷,范围0.4,伤害=魔王攻击力</t>
+          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>3,0.6</t>
+          <t>3,0.6,3</t>
         </is>
       </c>
       <c r="M23" s="0" t="n">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="Y23" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv3-每3秒3道落雷,范围0.6,伤害=魔王攻击力</t>
+          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>4,0.8</t>
+          <t>4,0.8,4</t>
         </is>
       </c>
       <c r="M24" s="0" t="n">
@@ -2560,54 +2560,54 @@
       </c>
       <c r="Y24" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv4-每3秒4道落雷,范围0.8,伤害=魔王攻击力</t>
+          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
-      <c r="A25" t="n">
+      <c r="A25" s="0" t="n">
         <v>3000300005</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>BuffEntityPeriodicMultiInstantAttack</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
+      <c r="J25" s="0" t="inlineStr">
+        <is>
+          <t>5,1,5</t>
+        </is>
+      </c>
+      <c r="M25" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="Q25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
+      <c r="T25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="0" t="n">
         <v>3000300001</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X25" s="0" t="n">
         <v>3000300001</v>
       </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>闪电Lv5-每3秒5道落雷,范围1,伤害=魔王攻击力</t>
+      <c r="Y25" s="0" t="inlineStr">
+        <is>
+          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -2393,7 +2393,7 @@
       </c>
       <c r="J21" s="0" t="inlineStr">
         <is>
-          <t>1,0.2,1</t>
+          <t>1,300031</t>
         </is>
       </c>
       <c r="M21" s="0" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J22" s="0" t="inlineStr">
         <is>
-          <t>2,0.4,2</t>
+          <t>2,300032</t>
         </is>
       </c>
       <c r="M22" s="0" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>3,0.6,3</t>
+          <t>3,300033</t>
         </is>
       </c>
       <c r="M23" s="0" t="n">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>4,0.8,4</t>
+          <t>4,300034</t>
         </is>
       </c>
       <c r="M24" s="0" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>5,1,5</t>
+          <t>5,300035</t>
         </is>
       </c>
       <c r="M25" s="0" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y78"/>
+  <dimension ref="A1:Y83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2612,464 +2612,467 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicRoadAttack</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1,300041</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="3">
+      <c r="A27" t="n">
+        <v>3000400002</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicRoadAttack</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2,300041</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="3">
+      <c r="A28" t="n">
+        <v>3000400003</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicRoadAttack</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>3,300041</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="3">
+      <c r="A29" t="n">
+        <v>3000400004</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicRoadAttack</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4,300041</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="3">
+      <c r="A30" t="n">
+        <v>3000400005</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicRoadAttack</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5,300041</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3000400001</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" customFormat="1" s="2">
+      <c r="A31" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="2" t="n">
+      <c r="C31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>BuffEntityInstantRewardMoreItem</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n"/>
-      <c r="T26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="2" t="n">
+      <c r="I31" s="2" t="n"/>
+      <c r="J31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
+      <c r="T31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="X26" s="2" t="n">
+      <c r="X31" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="3">
-      <c r="A27" s="2" t="n">
+    <row r="32" customFormat="1" s="2">
+      <c r="A32" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="2" t="n">
+      <c r="C32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>BuffEntityInstantRewardMoreSelect</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
-      <c r="T27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="2" t="n">
+      <c r="I32" s="2" t="n"/>
+      <c r="J32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="T32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="X27" s="2" t="n">
+      <c r="X32" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>再来一瓶-通关奖励可选次数+1</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="3">
-      <c r="A28" s="2" t="n">
+    <row r="33" customFormat="1" s="2">
+      <c r="A33" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C33" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D28" s="2" t="n">
+      <c r="D33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="O28" s="2" t="n">
+      <c r="O33" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P33" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" s="2" t="n">
+      <c r="T33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="X28" s="2" t="n">
+      <c r="X33" s="2" t="n">
         <v>11000100001</v>
       </c>
-      <c r="Y28" s="2" t="inlineStr">
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="3">
-      <c r="A29" s="2" t="n">
+    <row r="34" ht="13" customHeight="1" s="3">
+      <c r="A34" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C34" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="O29" s="2" t="n">
+      <c r="O34" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="P34" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="2" t="n">
+      <c r="T34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="X29" s="2" t="n">
+      <c r="X34" s="2" t="n">
         <v>11000200001</v>
       </c>
-      <c r="Y29" s="2" t="inlineStr">
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="3">
-      <c r="A30" s="2" t="n">
+    <row r="35" ht="14.25" customHeight="1" s="3">
+      <c r="A35" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C35" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J30" s="0" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O30" s="0" t="n">
+      <c r="O35" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="P30" s="0" t="n">
+      <c r="P35" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q30" s="2" t="n">
+      <c r="Q35" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="T30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="2" t="n">
+      <c r="T35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="X30" s="2" t="n">
+      <c r="X35" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" customFormat="1" s="2">
-      <c r="A31" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="C31" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D31" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J31" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="O31" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="X31" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="Y31" s="0" t="inlineStr">
-        <is>
-          <t>攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" customFormat="1" s="2">
-      <c r="A32" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="C32" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D32" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J32" s="0" t="inlineStr">
-        <is>
-          <t>RCD</t>
-        </is>
-      </c>
-      <c r="O32" s="0" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P32" s="0" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="X32" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="Y32" s="0" t="inlineStr">
-        <is>
-          <t>召唤CD{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" customFormat="1" s="2">
-      <c r="A33" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="C33" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D33" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J33" s="0" t="inlineStr">
-        <is>
-          <t>CMP</t>
-        </is>
-      </c>
-      <c r="O33" s="0" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P33" s="0" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="X33" s="0" t="n">
-        <v>11000600001</v>
-      </c>
-      <c r="Y33" s="0" t="inlineStr">
-        <is>
-          <t>召唤魔力消耗{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="13" customHeight="1" s="3">
-      <c r="A34" s="0" t="n">
-        <v>11000700001</v>
-      </c>
-      <c r="C34" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D34" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeMulti</t>
-        </is>
-      </c>
-      <c r="J34" s="0" t="inlineStr">
-        <is>
-          <t>ATK:1|HP:-1</t>
-        </is>
-      </c>
-      <c r="O34" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P34" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="0" t="n">
-        <v>11000700001</v>
-      </c>
-      <c r="X34" s="0" t="n">
-        <v>11000700001</v>
-      </c>
-      <c r="Y34" s="0" t="inlineStr">
-        <is>
-          <t>狂战士-A</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="14.25" customHeight="1" s="3">
-      <c r="A35" s="0" t="n">
-        <v>11000700002</v>
-      </c>
-      <c r="C35" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D35" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeMulti</t>
-        </is>
-      </c>
-      <c r="J35" s="0" t="inlineStr">
-        <is>
-          <t>ATK:1|DR:-1</t>
-        </is>
-      </c>
-      <c r="O35" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P35" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="0" t="n">
-        <v>11000700002</v>
-      </c>
-      <c r="X35" s="0" t="n">
-        <v>11000700002</v>
-      </c>
-      <c r="Y35" s="0" t="inlineStr">
-        <is>
-          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
       <c r="A36" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000400001</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>11</v>
@@ -3077,28 +3080,22 @@
       <c r="D36" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G36" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|ASPD:-1</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="O36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P36" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R36" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="T36" s="0" t="n">
         <v>0</v>
       </c>
@@ -3106,20 +3103,20 @@
         <v>0</v>
       </c>
       <c r="W36" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000400001</v>
       </c>
       <c r="X36" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000400001</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>狂战士-C</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
       <c r="A37" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000500001</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>11</v>
@@ -3127,27 +3124,21 @@
       <c r="D37" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|DR:-1</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O37" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P37" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R37" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T37" s="0" t="n">
         <v>0</v>
@@ -3156,20 +3147,20 @@
         <v>0</v>
       </c>
       <c r="W37" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000500001</v>
       </c>
       <c r="X37" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>快枪手-A</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
       <c r="A38" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000600001</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>11</v>
@@ -3177,27 +3168,21 @@
       <c r="D38" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|HP:-1</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O38" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P38" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R38" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T38" s="0" t="n">
         <v>0</v>
@@ -3206,20 +3191,20 @@
         <v>0</v>
       </c>
       <c r="W38" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000600001</v>
       </c>
       <c r="X38" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000600001</v>
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>快枪手-B</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
       <c r="A39" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000700001</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>11</v>
@@ -3237,7 +3222,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|ATK:-1</t>
+          <t>ATK:1|HP:-1</t>
         </is>
       </c>
       <c r="O39" s="0" t="n">
@@ -3256,20 +3241,20 @@
         <v>0</v>
       </c>
       <c r="W39" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000700001</v>
       </c>
       <c r="X39" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000700001</v>
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>快枪手-C</t>
+          <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
       <c r="A40" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000700002</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>11</v>
@@ -3287,7 +3272,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>DR:1|HP:-1</t>
+          <t>ATK:1|DR:-1</t>
         </is>
       </c>
       <c r="O40" s="0" t="n">
@@ -3306,20 +3291,20 @@
         <v>0</v>
       </c>
       <c r="W40" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000700002</v>
       </c>
       <c r="X40" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000700002</v>
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-A</t>
+          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
       <c r="A41" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000700003</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>11</v>
@@ -3337,7 +3322,7 @@
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ATK:-1</t>
+          <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O41" s="0" t="n">
@@ -3356,20 +3341,20 @@
         <v>0</v>
       </c>
       <c r="W41" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000700003</v>
       </c>
       <c r="X41" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000700003</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-B</t>
+          <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
       <c r="A42" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000800001</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>11</v>
@@ -3387,7 +3372,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ASPD:-1</t>
+          <t>ASPD:1|DR:-1</t>
         </is>
       </c>
       <c r="O42" s="0" t="n">
@@ -3406,20 +3391,20 @@
         <v>0</v>
       </c>
       <c r="W42" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000800001</v>
       </c>
       <c r="X42" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000800001</v>
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-C</t>
+          <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
       <c r="A43" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000800002</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>11</v>
@@ -3437,7 +3422,7 @@
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ASPD:-1</t>
+          <t>ASPD:1|HP:-1</t>
         </is>
       </c>
       <c r="O43" s="0" t="n">
@@ -3456,20 +3441,20 @@
         <v>0</v>
       </c>
       <c r="W43" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000800002</v>
       </c>
       <c r="X43" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000800002</v>
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>大块头-A</t>
+          <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
       <c r="A44" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000800003</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>11</v>
@@ -3487,7 +3472,7 @@
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>HP:1|DR:-1</t>
+          <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
       <c r="O44" s="0" t="n">
@@ -3506,20 +3491,20 @@
         <v>0</v>
       </c>
       <c r="W44" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000800003</v>
       </c>
       <c r="X44" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000800003</v>
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>大块头-B</t>
+          <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
       <c r="A45" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000900001</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>11</v>
@@ -3537,7 +3522,7 @@
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ATK:-1</t>
+          <t>DR:1|HP:-1</t>
         </is>
       </c>
       <c r="O45" s="0" t="n">
@@ -3556,40 +3541,48 @@
         <v>0</v>
       </c>
       <c r="W45" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000900001</v>
       </c>
       <c r="X45" s="0" t="n">
-        <v>11001000003</v>
+        <v>11000900001</v>
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>大块头-C</t>
+          <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="3">
       <c r="A46" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000900002</v>
       </c>
       <c r="C46" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D46" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H46" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t>DR:1|ATK:-1</t>
         </is>
       </c>
       <c r="O46" s="0" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="P46" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S46" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
+      </c>
+      <c r="R46" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T46" s="0" t="n">
         <v>0</v>
@@ -3597,44 +3590,49 @@
       <c r="U46" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W46" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000900002</v>
       </c>
       <c r="X46" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000900002</v>
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="3">
       <c r="A47" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000900003</v>
       </c>
       <c r="C47" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D47" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H47" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t>DR:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O47" s="0" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="P47" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S47" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
+      </c>
+      <c r="R47" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T47" s="0" t="n">
         <v>0</v>
@@ -3642,38 +3640,49 @@
       <c r="U47" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="0" t="n">
-        <v>500002</v>
-      </c>
       <c r="W47" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000900003</v>
       </c>
       <c r="X47" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000900003</v>
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="3">
       <c r="A48" s="0" t="n">
-        <v>12000300001</v>
+        <v>11001000001</v>
       </c>
       <c r="C48" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D48" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
-      </c>
-      <c r="S48" s="0" t="n">
-        <v>5</v>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t>HP:1|ASPD:-1</t>
+        </is>
+      </c>
+      <c r="O48" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P48" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R48" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T48" s="0" t="n">
         <v>0</v>
@@ -3682,52 +3691,48 @@
         <v>0</v>
       </c>
       <c r="W48" s="0" t="n">
-        <v>12000300001</v>
+        <v>11001000001</v>
       </c>
       <c r="X48" s="0" t="n">
-        <v>12000300001</v>
+        <v>11001000001</v>
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="3">
       <c r="A49" s="0" t="n">
-        <v>12001100001</v>
+        <v>11001000002</v>
       </c>
       <c r="C49" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G49" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I49" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L49" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>HP:1|DR:-1</t>
         </is>
       </c>
       <c r="O49" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P49" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R49" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T49" s="0" t="n">
         <v>0</v>
@@ -3736,52 +3741,48 @@
         <v>0</v>
       </c>
       <c r="W49" s="0" t="n">
-        <v>12001100001</v>
+        <v>11001000002</v>
       </c>
       <c r="X49" s="0" t="n">
-        <v>12001100001</v>
+        <v>11001000002</v>
       </c>
       <c r="Y49" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="3">
       <c r="A50" s="0" t="n">
-        <v>12001200001</v>
+        <v>11001000003</v>
       </c>
       <c r="C50" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D50" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G50" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I50" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L50" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>HP:1|ATK:-1</t>
         </is>
       </c>
       <c r="O50" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P50" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R50" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T50" s="0" t="n">
         <v>0</v>
@@ -3790,20 +3791,20 @@
         <v>0</v>
       </c>
       <c r="W50" s="0" t="n">
-        <v>12001200001</v>
+        <v>11001000003</v>
       </c>
       <c r="X50" s="0" t="n">
-        <v>12001200001</v>
+        <v>11001000003</v>
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>大块头-C</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="3">
       <c r="A51" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="C51" s="0" t="n">
         <v>12</v>
@@ -3813,29 +3814,17 @@
       </c>
       <c r="H51" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I51" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J51" s="0" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L51" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>BuffEntityBaseHPChange</t>
         </is>
       </c>
       <c r="O51" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="P51" s="0" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
+      </c>
+      <c r="S51" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T51" s="0" t="n">
         <v>0</v>
@@ -3843,21 +3832,24 @@
       <c r="U51" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V51" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W51" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="X51" s="0" t="n">
-        <v>12001300001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y51" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="3">
       <c r="A52" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>12</v>
@@ -3867,29 +3859,17 @@
       </c>
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I52" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J52" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L52" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>BuffEntityBaseDRChange</t>
         </is>
       </c>
       <c r="O52" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="P52" s="0" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
+      </c>
+      <c r="S52" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T52" s="0" t="n">
         <v>0</v>
@@ -3897,21 +3877,24 @@
       <c r="U52" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V52" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W52" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="X52" s="0" t="n">
-        <v>12001400001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y52" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
       <c r="A53" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>12</v>
@@ -3921,29 +3904,11 @@
       </c>
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I53" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J53" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L53" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O53" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P53" s="0" t="n">
-        <v>0.1</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="S53" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T53" s="0" t="n">
         <v>0</v>
@@ -3952,20 +3917,20 @@
         <v>0</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="X53" s="0" t="n">
-        <v>12002100001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>12</v>
@@ -3980,17 +3945,17 @@
       </c>
       <c r="I54" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L54" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O54" s="0" t="n">
@@ -4006,20 +3971,20 @@
         <v>0</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="X54" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="C55" s="0" t="n">
         <v>12</v>
@@ -4034,17 +3999,17 @@
       </c>
       <c r="I55" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L55" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O55" s="0" t="n">
@@ -4060,20 +4025,20 @@
         <v>0</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="X55" s="0" t="n">
-        <v>12002300001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="C56" s="0" t="n">
         <v>12</v>
@@ -4088,17 +4053,17 @@
       </c>
       <c r="I56" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L56" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O56" s="0" t="n">
@@ -4114,20 +4079,20 @@
         <v>0</v>
       </c>
       <c r="W56" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="X56" s="0" t="n">
-        <v>12002400001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="C57" s="0" t="n">
         <v>12</v>
@@ -4142,17 +4107,17 @@
       </c>
       <c r="I57" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L57" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O57" s="0" t="n">
@@ -4168,20 +4133,20 @@
         <v>0</v>
       </c>
       <c r="W57" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="X57" s="0" t="n">
-        <v>12003100001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="C58" s="0" t="n">
         <v>12</v>
@@ -4201,12 +4166,12 @@
       </c>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L58" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O58" s="0" t="n">
@@ -4222,20 +4187,20 @@
         <v>0</v>
       </c>
       <c r="W58" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="X58" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="C59" s="0" t="n">
         <v>12</v>
@@ -4255,12 +4220,12 @@
       </c>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L59" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O59" s="0" t="n">
@@ -4276,20 +4241,20 @@
         <v>0</v>
       </c>
       <c r="W59" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="X59" s="0" t="n">
-        <v>12003300001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="C60" s="0" t="n">
         <v>12</v>
@@ -4309,12 +4274,12 @@
       </c>
       <c r="J60" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L60" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O60" s="0" t="n">
@@ -4330,20 +4295,20 @@
         <v>0</v>
       </c>
       <c r="W60" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="X60" s="0" t="n">
-        <v>12003400001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>12004100001</v>
+        <v>12002400001</v>
       </c>
       <c r="C61" s="0" t="n">
         <v>12</v>
@@ -4353,18 +4318,22 @@
       </c>
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I61" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I61" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J61" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L61" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O61" s="0" t="n">
@@ -4380,20 +4349,20 @@
         <v>0</v>
       </c>
       <c r="W61" s="0" t="n">
-        <v>12004100001</v>
+        <v>12002400001</v>
       </c>
       <c r="X61" s="0" t="n">
-        <v>12004100001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003100001</v>
       </c>
       <c r="C62" s="0" t="n">
         <v>12</v>
@@ -4403,18 +4372,22 @@
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I62" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I62" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L62" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O62" s="0" t="n">
@@ -4430,20 +4403,20 @@
         <v>0</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003100001</v>
       </c>
       <c r="X62" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>12004300001</v>
+        <v>12003200001</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>12</v>
@@ -4453,18 +4426,22 @@
       </c>
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I63" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I63" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L63" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O63" s="0" t="n">
@@ -4480,20 +4457,20 @@
         <v>0</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>12004300001</v>
+        <v>12003200001</v>
       </c>
       <c r="X63" s="0" t="n">
-        <v>12004300001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>12004400001</v>
+        <v>12003300001</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>12</v>
@@ -4503,18 +4480,22 @@
       </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I64" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I64" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L64" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O64" s="0" t="n">
@@ -4530,20 +4511,20 @@
         <v>0</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>12004400001</v>
+        <v>12003300001</v>
       </c>
       <c r="X64" s="0" t="n">
-        <v>12004400001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003400001</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>12</v>
@@ -4553,18 +4534,29 @@
       </c>
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I65" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J65" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L65" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O65" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P65" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T65" s="0" t="n">
         <v>0</v>
@@ -4573,20 +4565,20 @@
         <v>0</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003400001</v>
       </c>
       <c r="X65" s="0" t="n">
-        <v>12010100001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004100001</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>12</v>
@@ -4596,18 +4588,25 @@
       </c>
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I66" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I66" s="0" t="inlineStr"/>
+      <c r="J66" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="L66" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O66" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P66" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T66" s="0" t="n">
         <v>0</v>
@@ -4616,20 +4615,20 @@
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004100001</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004100001</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>12010300001</v>
+        <v>12004200001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>12</v>
@@ -4639,18 +4638,25 @@
       </c>
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I67" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr"/>
+      <c r="J67" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
         </is>
       </c>
       <c r="L67" s="0" t="inlineStr">
         <is>
-          <t>4001:1000&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O67" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P67" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T67" s="0" t="n">
         <v>0</v>
@@ -4659,20 +4665,20 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>12010300001</v>
+        <v>12004200001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>12010300001</v>
+        <v>12004200001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>12010400001</v>
+        <v>12004300001</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>12</v>
@@ -4682,18 +4688,25 @@
       </c>
       <c r="H68" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I68" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr"/>
+      <c r="J68" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L68" s="0" t="inlineStr">
         <is>
-          <t>5001:500&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O68" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P68" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T68" s="0" t="n">
         <v>0</v>
@@ -4702,20 +4715,20 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>12010400001</v>
+        <v>12004300001</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>12010400001</v>
+        <v>12004300001</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>12010500001</v>
+        <v>12004400001</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>12</v>
@@ -4725,18 +4738,25 @@
       </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I69" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr"/>
+      <c r="J69" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L69" s="0" t="inlineStr">
         <is>
-          <t>6001:1000&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O69" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P69" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T69" s="0" t="n">
         <v>0</v>
@@ -4745,20 +4765,20 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>12010500001</v>
+        <v>12004400001</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>12010500001</v>
+        <v>12004400001</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010100001</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>12</v>
@@ -4768,7 +4788,7 @@
       </c>
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I70" s="0" t="inlineStr">
@@ -4778,7 +4798,7 @@
       </c>
       <c r="L70" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="T70" s="0" t="n">
@@ -4788,20 +4808,20 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010100001</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010200001</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>12</v>
@@ -4811,7 +4831,7 @@
       </c>
       <c r="H71" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I71" s="0" t="inlineStr">
@@ -4821,7 +4841,7 @@
       </c>
       <c r="L71" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="T71" s="0" t="n">
@@ -4831,20 +4851,20 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010200001</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010200001</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010300001</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>12</v>
@@ -4854,7 +4874,7 @@
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I72" s="0" t="inlineStr">
@@ -4864,7 +4884,7 @@
       </c>
       <c r="L72" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
+          <t>4001:1000&amp;</t>
         </is>
       </c>
       <c r="T72" s="0" t="n">
@@ -4874,40 +4894,41 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010300001</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>12011300001</v>
+        <v>12010300001</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010400001</v>
       </c>
       <c r="C73" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="M73" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N73" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S73" s="0" t="n">
-        <v>3</v>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L73" s="0" t="inlineStr">
+        <is>
+          <t>5001:500&amp;</t>
+        </is>
       </c>
       <c r="T73" s="0" t="n">
         <v>0</v>
@@ -4916,35 +4937,40 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010400001</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>13000100001</v>
+        <v>12010400001</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>13000200001</v>
+        <v>12010500001</v>
       </c>
       <c r="C74" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I74" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L74" s="0" t="inlineStr">
+        <is>
+          <t>6001:1000&amp;</t>
         </is>
       </c>
       <c r="T74" s="0" t="n">
@@ -4953,46 +4979,42 @@
       <c r="U74" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W74" s="0" t="n">
-        <v>13000200001</v>
+        <v>12010500001</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>13000200001</v>
+        <v>12010500001</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>13000300001</v>
+        <v>12011100001</v>
       </c>
       <c r="C75" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H75" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I75" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J75" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O75" s="0" t="n">
-        <v>1</v>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L75" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
       </c>
       <c r="T75" s="0" t="n">
         <v>0</v>
@@ -5001,45 +5023,41 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>13000300001</v>
+        <v>12011100001</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>13000300001</v>
+        <v>12011100001</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>13000400001</v>
+        <v>12011200001</v>
       </c>
       <c r="C76" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H76" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I76" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J76" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P76" s="0" t="n">
-        <v>0.01</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L76" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
       </c>
       <c r="T76" s="0" t="n">
         <v>0</v>
@@ -5048,45 +5066,41 @@
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>13000400001</v>
+        <v>12011200001</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>13000400001</v>
+        <v>12011200001</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011300001</v>
       </c>
       <c r="C77" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H77" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I77" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J77" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P77" s="0" t="n">
-        <v>0.01</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L77" s="0" t="inlineStr">
+        <is>
+          <t>4001:200&amp;</t>
+        </is>
       </c>
       <c r="T77" s="0" t="n">
         <v>0</v>
@@ -5095,20 +5109,20 @@
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011300001</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>13000500001</v>
+        <v>12011300001</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000100001</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>13</v>
@@ -5118,30 +5132,251 @@
       </c>
       <c r="H78" s="0" t="inlineStr">
         <is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M78" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="X78" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="Y78" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="C79" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D79" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I79" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="T79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="W79" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="X79" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="Y79" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="C80" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D80" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H80" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAttack</t>
+        </is>
+      </c>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O80" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="X80" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Y80" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="C81" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D81" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H81" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
+        </is>
+      </c>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J81" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P81" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="X81" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Y81" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="C82" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D82" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H82" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P82" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W82" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="X82" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Y82" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H83" s="0" t="inlineStr">
+        <is>
           <t>BuffEntityConditionalDeadCreateCrystal</t>
         </is>
       </c>
-      <c r="I78" s="0" t="inlineStr">
+      <c r="I83" s="0" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q78" s="0" t="n">
+      <c r="Q83" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="T78" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W78" s="0" t="n">
+      <c r="T83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="0" t="n">
         <v>13000600001</v>
       </c>
-      <c r="X78" s="0" t="n">
+      <c r="X83" s="0" t="n">
         <v>13000600001</v>
       </c>
-      <c r="Y78" s="0" t="inlineStr">
+      <c r="Y83" s="0" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y83"/>
+  <dimension ref="A1:Y113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2612,344 +2612,431 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="C26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="C26" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicRoadAttack</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRoad</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>1,300041</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="Q26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
+      <c r="T26" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X26" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y26" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
-      <c r="A27" t="n">
+      <c r="A27" s="0" t="n">
         <v>3000400002</v>
       </c>
-      <c r="C27" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="C27" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicRoadAttack</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRoad</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>2,300041</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="Q27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="T27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="X27" t="n">
+      <c r="X27" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y27" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
-      <c r="A28" t="n">
+      <c r="A28" s="0" t="n">
         <v>3000400003</v>
       </c>
-      <c r="C28" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="C28" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicRoadAttack</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRoad</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>3,300041</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="Q28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
+      <c r="T28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="X28" t="n">
+      <c r="X28" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y28" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
-      <c r="A29" t="n">
+      <c r="A29" s="0" t="n">
         <v>3000400004</v>
       </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="C29" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G29" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicRoadAttack</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRoad</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>4,300041</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="Q29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="T29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="X29" t="n">
+      <c r="X29" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y29" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
-      <c r="A30" t="n">
+      <c r="A30" s="0" t="n">
         <v>3000400005</v>
       </c>
-      <c r="C30" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" t="n">
+      <c r="C30" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G30" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicRoadAttack</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRoad</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>5,300041</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="Q30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
+      <c r="T30" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="X30" t="n">
+      <c r="X30" s="0" t="n">
         <v>3000400001</v>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" s="0" t="inlineStr">
         <is>
           <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="1" s="2">
-      <c r="A31" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" s="2" t="n">
+      <c r="A31" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="inlineStr">
+        <is>
+          <t>1,300061,0</t>
+        </is>
+      </c>
+      <c r="M31" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantRewardMoreItem</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="n"/>
+      <c r="N31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="T31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U31" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="X31" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
-        <is>
-          <t>奖励多多-通关奖励数量+1</t>
+      <c r="V31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="X31" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y31" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,不弹跳</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="2">
-      <c r="A32" s="2" t="n">
-        <v>3001000001</v>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="2" t="n">
+      <c r="A32" s="0" t="n">
+        <v>3000600002</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="inlineStr">
+        <is>
+          <t>2,300061,1</t>
+        </is>
+      </c>
+      <c r="M32" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantRewardMoreSelect</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n"/>
+      <c r="N32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="T32" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U32" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="2" t="n">
-        <v>3001000001</v>
-      </c>
-      <c r="X32" s="2" t="n">
-        <v>3001000001</v>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
-        <is>
-          <t>再来一瓶-通关奖励可选次数+1</t>
+      <c r="V32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="X32" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y32" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳1次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="2">
-      <c r="A33" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D33" s="2" t="n">
+      <c r="A33" s="0" t="n">
+        <v>3000600003</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P33" s="2" t="n">
-        <v>0.1</v>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="inlineStr">
+        <is>
+          <t>3,300061,2</t>
+        </is>
+      </c>
+      <c r="M33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T33" s="0" t="n">
         <v>0</v>
@@ -2957,48 +3044,70 @@
       <c r="U33" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="X33" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
-        <is>
-          <t>生命增加{Percentage}%</t>
+      <c r="V33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="X33" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y33" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" s="3">
-      <c r="A34" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D34" s="2" t="n">
+      <c r="A34" s="0" t="n">
+        <v>3000600004</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P34" s="2" t="n">
-        <v>0.1</v>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="inlineStr">
+        <is>
+          <t>4,300061,3</t>
+        </is>
+      </c>
+      <c r="M34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T34" s="0" t="n">
         <v>0</v>
@@ -3006,51 +3115,70 @@
       <c r="U34" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="X34" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
-        <is>
-          <t>护甲增加{Percentage}%</t>
+      <c r="V34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="X34" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y34" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="3">
-      <c r="A35" s="2" t="n">
-        <v>11000300001</v>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D35" s="2" t="n">
+      <c r="A35" s="0" t="n">
+        <v>3000600005</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
         </is>
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
+          <t>5,300061,4</t>
+        </is>
+      </c>
+      <c r="M35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O35" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P35" s="0" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q35" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T35" s="0" t="n">
         <v>0</v>
@@ -3058,43 +3186,70 @@
       <c r="U35" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W35" s="2" t="n">
-        <v>11000300001</v>
-      </c>
-      <c r="X35" s="2" t="n">
-        <v>11000300001</v>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t>攻击力增加{Percentage}%</t>
+      <c r="V35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="X35" s="0" t="n">
+        <v>3000600001</v>
+      </c>
+      <c r="Y35" s="0" t="inlineStr">
+        <is>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
       <c r="A36" s="0" t="n">
-        <v>11000400001</v>
+        <v>3000700001</v>
       </c>
       <c r="C36" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
-        </is>
+          <t>1,300071,0.6</t>
+        </is>
+      </c>
+      <c r="M36" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N36" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O36" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="0" t="n">
+        <v>9999</v>
       </c>
       <c r="T36" s="0" t="n">
         <v>0</v>
@@ -3102,43 +3257,70 @@
       <c r="U36" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V36" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W36" s="0" t="n">
-        <v>11000400001</v>
+        <v>3000700001</v>
       </c>
       <c r="X36" s="0" t="n">
-        <v>11000400001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>攻击速度增加{Percentage}%</t>
+          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力50%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
       <c r="A37" s="0" t="n">
-        <v>11000500001</v>
+        <v>3000700002</v>
       </c>
       <c r="C37" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>RCD</t>
-        </is>
+          <t>2,300071,1.2</t>
+        </is>
+      </c>
+      <c r="M37" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N37" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O37" s="0" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="P37" s="0" t="n">
-        <v>-0.5</v>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="0" t="n">
+        <v>9999</v>
       </c>
       <c r="T37" s="0" t="n">
         <v>0</v>
@@ -3146,43 +3328,70 @@
       <c r="U37" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V37" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W37" s="0" t="n">
-        <v>11000500001</v>
+        <v>3000700001</v>
       </c>
       <c r="X37" s="0" t="n">
-        <v>11000500001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>召唤CD{Percentage}%</t>
+          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力50%</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
       <c r="A38" s="0" t="n">
-        <v>11000600001</v>
+        <v>3000700003</v>
       </c>
       <c r="C38" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>CMP</t>
-        </is>
+          <t>3,300071,1.8</t>
+        </is>
+      </c>
+      <c r="M38" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N38" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O38" s="0" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="P38" s="0" t="n">
-        <v>-0.5</v>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="0" t="n">
+        <v>9999</v>
       </c>
       <c r="T38" s="0" t="n">
         <v>0</v>
@@ -3190,641 +3399,854 @@
       <c r="U38" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V38" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W38" s="0" t="n">
-        <v>11000600001</v>
+        <v>3000700001</v>
       </c>
       <c r="X38" s="0" t="n">
-        <v>11000600001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>召唤魔力消耗{Percentage}%</t>
+          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力50%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
       <c r="A39" s="0" t="n">
-        <v>11000700001</v>
+        <v>3000700004</v>
       </c>
       <c r="C39" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G39" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H39" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|HP:-1</t>
-        </is>
+          <t>4,300071,2.4</t>
+        </is>
+      </c>
+      <c r="M39" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N39" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O39" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P39" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R39" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S39" s="0" t="n">
+        <v>9999</v>
+      </c>
       <c r="T39" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U39" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V39" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W39" s="0" t="n">
-        <v>11000700001</v>
+        <v>3000700001</v>
       </c>
       <c r="X39" s="0" t="n">
-        <v>11000700001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>狂战士-A</t>
+          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力50%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
       <c r="A40" s="0" t="n">
-        <v>11000700002</v>
+        <v>3000700005</v>
       </c>
       <c r="C40" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|DR:-1</t>
-        </is>
+          <t>5,300071,3</t>
+        </is>
+      </c>
+      <c r="M40" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N40" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O40" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P40" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R40" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S40" s="0" t="n">
+        <v>9999</v>
+      </c>
       <c r="T40" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U40" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V40" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W40" s="0" t="n">
-        <v>11000700002</v>
+        <v>3000700001</v>
       </c>
       <c r="X40" s="0" t="n">
-        <v>11000700002</v>
+        <v>3000700001</v>
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>狂战士-B</t>
+          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力50%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
       <c r="A41" s="0" t="n">
-        <v>11000700003</v>
+        <v>3000800001</v>
       </c>
       <c r="C41" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackRebound</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|ASPD:-1</t>
-        </is>
+          <t>1,300081</t>
+        </is>
+      </c>
+      <c r="M41" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N41" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O41" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P41" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R41" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S41" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="T41" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U41" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V41" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W41" s="0" t="n">
-        <v>11000700003</v>
+        <v>3000800001</v>
       </c>
       <c r="X41" s="0" t="n">
-        <v>11000700003</v>
+        <v>3000800001</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>狂战士-C</t>
+          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力50%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
       <c r="A42" s="0" t="n">
-        <v>11000800001</v>
+        <v>3000800002</v>
       </c>
       <c r="C42" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G42" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackRebound</t>
         </is>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|DR:-1</t>
-        </is>
+          <t>2,300082</t>
+        </is>
+      </c>
+      <c r="M42" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N42" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O42" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P42" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R42" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S42" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="T42" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U42" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V42" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W42" s="0" t="n">
-        <v>11000800001</v>
+        <v>3000800001</v>
       </c>
       <c r="X42" s="0" t="n">
-        <v>11000800001</v>
+        <v>3000800001</v>
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>快枪手-A</t>
+          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力50%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
       <c r="A43" s="0" t="n">
-        <v>11000800002</v>
+        <v>3000800003</v>
       </c>
       <c r="C43" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackRebound</t>
         </is>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|HP:-1</t>
-        </is>
+          <t>3,300083</t>
+        </is>
+      </c>
+      <c r="M43" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N43" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O43" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P43" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R43" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S43" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="T43" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U43" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V43" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W43" s="0" t="n">
-        <v>11000800002</v>
+        <v>3000800001</v>
       </c>
       <c r="X43" s="0" t="n">
-        <v>11000800002</v>
+        <v>3000800001</v>
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>快枪手-B</t>
+          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力50%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
       <c r="A44" s="0" t="n">
-        <v>11000800003</v>
+        <v>3000800004</v>
       </c>
       <c r="C44" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackRebound</t>
         </is>
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|ATK:-1</t>
-        </is>
+          <t>4,300084</t>
+        </is>
+      </c>
+      <c r="M44" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N44" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O44" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P44" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R44" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S44" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="T44" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U44" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V44" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W44" s="0" t="n">
-        <v>11000800003</v>
+        <v>3000800001</v>
       </c>
       <c r="X44" s="0" t="n">
-        <v>11000800003</v>
+        <v>3000800001</v>
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>快枪手-C</t>
+          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力50%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
       <c r="A45" s="0" t="n">
-        <v>11000900001</v>
+        <v>3000800005</v>
       </c>
       <c r="C45" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G45" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackRebound</t>
         </is>
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>DR:1|HP:-1</t>
-        </is>
+          <t>5,300085</t>
+        </is>
+      </c>
+      <c r="M45" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N45" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O45" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P45" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R45" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S45" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="T45" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U45" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V45" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W45" s="0" t="n">
-        <v>11000900001</v>
+        <v>3000800001</v>
       </c>
       <c r="X45" s="0" t="n">
-        <v>11000900001</v>
+        <v>3000800001</v>
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-A</t>
+          <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力50%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="3">
-      <c r="A46" s="0" t="n">
-        <v>11000900002</v>
-      </c>
-      <c r="C46" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D46" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeMulti</t>
-        </is>
-      </c>
-      <c r="J46" s="0" t="inlineStr">
-        <is>
-          <t>DR:1|ATK:-1</t>
-        </is>
-      </c>
-      <c r="O46" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P46" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R46" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="A46" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityInstantRewardMoreItem</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
       <c r="T46" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U46" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W46" s="0" t="n">
-        <v>11000900002</v>
-      </c>
-      <c r="X46" s="0" t="n">
-        <v>11000900002</v>
-      </c>
-      <c r="Y46" s="0" t="inlineStr">
-        <is>
-          <t>铜墙铁壁-B</t>
+      <c r="W46" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="3">
-      <c r="A47" s="0" t="n">
-        <v>11000900003</v>
-      </c>
-      <c r="C47" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D47" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttributeMulti</t>
-        </is>
-      </c>
-      <c r="J47" s="0" t="inlineStr">
-        <is>
-          <t>DR:1|ASPD:-1</t>
-        </is>
-      </c>
-      <c r="O47" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P47" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R47" s="0" t="n">
-        <v>0</v>
-      </c>
+      <c r="A47" s="2" t="n">
+        <v>3001000001</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityInstantRewardMoreSelect</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
       <c r="T47" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U47" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="0" t="n">
-        <v>11000900003</v>
-      </c>
-      <c r="X47" s="0" t="n">
-        <v>11000900003</v>
-      </c>
-      <c r="Y47" s="0" t="inlineStr">
-        <is>
-          <t>铜墙铁壁-C</t>
+      <c r="W47" s="2" t="n">
+        <v>3001000001</v>
+      </c>
+      <c r="X47" s="2" t="n">
+        <v>3001000001</v>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>再来一瓶-通关奖励可选次数+1</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1" s="3">
       <c r="A48" s="0" t="n">
-        <v>11001000001</v>
+        <v>3001100005</v>
       </c>
       <c r="C48" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G48" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackShockwave</t>
         </is>
       </c>
       <c r="J48" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ASPD:-1</t>
-        </is>
+          <t>300091</t>
+        </is>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N48" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O48" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P48" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R48" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S48" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="T48" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U48" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V48" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W48" s="0" t="n">
-        <v>11001000001</v>
+        <v>3001100005</v>
       </c>
       <c r="X48" s="0" t="n">
-        <v>11001000001</v>
+        <v>3001100005</v>
       </c>
       <c r="Y48" s="0" t="inlineStr">
         <is>
-          <t>大块头-A</t>
+          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="3">
       <c r="A49" s="0" t="n">
-        <v>11001000002</v>
+        <v>3001100004</v>
       </c>
       <c r="C49" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G49" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H49" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackShockwave</t>
         </is>
       </c>
       <c r="J49" s="0" t="inlineStr">
         <is>
-          <t>HP:1|DR:-1</t>
-        </is>
+          <t>300091</t>
+        </is>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N49" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O49" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P49" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R49" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S49" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="T49" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U49" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V49" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W49" s="0" t="n">
-        <v>11001000002</v>
+        <v>3001100004</v>
       </c>
       <c r="X49" s="0" t="n">
-        <v>11001000002</v>
+        <v>3001100004</v>
       </c>
       <c r="Y49" s="0" t="inlineStr">
         <is>
-          <t>大块头-B</t>
+          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="3">
       <c r="A50" s="0" t="n">
-        <v>11001000003</v>
+        <v>3001100003</v>
       </c>
       <c r="C50" s="0" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G50" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H50" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityPeriodicAttackShockwave</t>
         </is>
       </c>
       <c r="J50" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ATK:-1</t>
-        </is>
+          <t>300091</t>
+        </is>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N50" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O50" s="0" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P50" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="R50" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="S50" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="T50" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U50" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V50" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W50" s="0" t="n">
-        <v>11001000003</v>
+        <v>3001100003</v>
       </c>
       <c r="X50" s="0" t="n">
-        <v>11001000003</v>
+        <v>3001100003</v>
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
-          <t>大块头-C</t>
+          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="3">
       <c r="A51" s="0" t="n">
-        <v>12000100001</v>
+        <v>3001100002</v>
       </c>
       <c r="C51" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D51" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H51" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
-        </is>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
+      <c r="J51" s="0" t="inlineStr">
+        <is>
+          <t>300091</t>
+        </is>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N51" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O51" s="0" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="P51" s="0" t="n">
-        <v>0.01</v>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="S51" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" s="0" t="n">
         <v>0</v>
@@ -3833,43 +4255,69 @@
         <v>0</v>
       </c>
       <c r="V51" s="0" t="n">
-        <v>500001</v>
+        <v>0</v>
       </c>
       <c r="W51" s="0" t="n">
-        <v>12000100001</v>
+        <v>3001100002</v>
       </c>
       <c r="X51" s="0" t="n">
-        <v>12000100001</v>
+        <v>3001100002</v>
       </c>
       <c r="Y51" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="3">
       <c r="A52" s="0" t="n">
-        <v>12000200001</v>
+        <v>3001100001</v>
       </c>
       <c r="C52" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D52" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H52" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
-        </is>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
+      <c r="J52" s="0" t="inlineStr">
+        <is>
+          <t>300091</t>
+        </is>
+      </c>
+      <c r="M52" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N52" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O52" s="0" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="P52" s="0" t="n">
-        <v>0.01</v>
+        <v>0</v>
+      </c>
+      <c r="Q52" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="S52" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" s="0" t="n">
         <v>0</v>
@@ -3878,37 +4326,73 @@
         <v>0</v>
       </c>
       <c r="V52" s="0" t="n">
-        <v>500002</v>
+        <v>0</v>
       </c>
       <c r="W52" s="0" t="n">
-        <v>12000200001</v>
+        <v>3001100001</v>
       </c>
       <c r="X52" s="0" t="n">
-        <v>12000200001</v>
+        <v>3001100001</v>
       </c>
       <c r="Y52" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
       <c r="A53" s="0" t="n">
-        <v>12000300001</v>
-      </c>
+        <v>3001200001</v>
+      </c>
+      <c r="B53" s="0" t="inlineStr"/>
       <c r="C53" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D53" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I53" s="0" t="inlineStr"/>
+      <c r="J53" s="0" t="inlineStr">
+        <is>
+          <t>1,300101</t>
+        </is>
+      </c>
+      <c r="K53" s="0" t="inlineStr"/>
+      <c r="L53" s="0" t="inlineStr"/>
+      <c r="M53" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="S53" s="0" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" s="0" t="n">
         <v>0</v>
@@ -3916,53 +4400,74 @@
       <c r="U53" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V53" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W53" s="0" t="n">
-        <v>12000300001</v>
+        <v>3001200001</v>
       </c>
       <c r="X53" s="0" t="n">
-        <v>12000300001</v>
+        <v>3001200001</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>12001100001</v>
-      </c>
+        <v>3001200002</v>
+      </c>
+      <c r="B54" s="0" t="inlineStr"/>
       <c r="C54" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D54" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H54" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I54" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I54" s="0" t="inlineStr"/>
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L54" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>2,300101</t>
+        </is>
+      </c>
+      <c r="K54" s="0" t="inlineStr"/>
+      <c r="L54" s="0" t="inlineStr"/>
+      <c r="M54" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N54" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O54" s="0" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P54" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="T54" s="0" t="n">
         <v>0</v>
@@ -3970,53 +4475,74 @@
       <c r="U54" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V54" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W54" s="0" t="n">
-        <v>12001100001</v>
+        <v>3001200001</v>
       </c>
       <c r="X54" s="0" t="n">
-        <v>12001100001</v>
+        <v>3001200001</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>12001200001</v>
-      </c>
+        <v>3001200003</v>
+      </c>
+      <c r="B55" s="0" t="inlineStr"/>
       <c r="C55" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D55" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I55" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I55" s="0" t="inlineStr"/>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L55" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>3,300101</t>
+        </is>
+      </c>
+      <c r="K55" s="0" t="inlineStr"/>
+      <c r="L55" s="0" t="inlineStr"/>
+      <c r="M55" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N55" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O55" s="0" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P55" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="T55" s="0" t="n">
         <v>0</v>
@@ -4024,53 +4550,74 @@
       <c r="U55" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V55" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W55" s="0" t="n">
-        <v>12001200001</v>
+        <v>3001200001</v>
       </c>
       <c r="X55" s="0" t="n">
-        <v>12001200001</v>
+        <v>3001200001</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>12001300001</v>
-      </c>
+        <v>3001200004</v>
+      </c>
+      <c r="B56" s="0" t="inlineStr"/>
       <c r="C56" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D56" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H56" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I56" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I56" s="0" t="inlineStr"/>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L56" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>4,300101</t>
+        </is>
+      </c>
+      <c r="K56" s="0" t="inlineStr"/>
+      <c r="L56" s="0" t="inlineStr"/>
+      <c r="M56" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N56" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O56" s="0" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P56" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="T56" s="0" t="n">
         <v>0</v>
@@ -4078,198 +4625,212 @@
       <c r="U56" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V56" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W56" s="0" t="n">
-        <v>12001300001</v>
+        <v>3001200001</v>
       </c>
       <c r="X56" s="0" t="n">
-        <v>12001300001</v>
+        <v>3001200001</v>
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>12001400001</v>
-      </c>
+        <v>3001200005</v>
+      </c>
+      <c r="B57" s="0" t="inlineStr"/>
       <c r="C57" s="0" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D57" s="0" t="n">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H57" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I57" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I57" s="0" t="inlineStr"/>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L57" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>5,300101</t>
+        </is>
+      </c>
+      <c r="K57" s="0" t="inlineStr"/>
+      <c r="L57" s="0" t="inlineStr"/>
+      <c r="M57" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N57" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O57" s="0" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="X57" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="Y57" s="0" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A58" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P58" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" s="0" t="n">
-        <v>12001400001</v>
-      </c>
-      <c r="X57" s="0" t="n">
-        <v>12001400001</v>
-      </c>
-      <c r="Y57" s="0" t="inlineStr">
-        <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A58" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="C58" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D58" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I58" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J58" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L58" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O58" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P58" s="0" t="n">
+      <c r="T58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="X58" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A59" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P59" s="2" t="n">
         <v>0.1</v>
       </c>
-      <c r="T58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="X58" s="0" t="n">
-        <v>12002100001</v>
-      </c>
-      <c r="Y58" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A59" s="0" t="n">
-        <v>12002200001</v>
-      </c>
-      <c r="C59" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D59" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I59" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="J59" s="0" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L59" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
-      <c r="O59" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P59" s="0" t="n">
-        <v>0.1</v>
-      </c>
       <c r="T59" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U59" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="0" t="n">
-        <v>12002200001</v>
-      </c>
-      <c r="X59" s="0" t="n">
-        <v>12002200001</v>
-      </c>
-      <c r="Y59" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+      <c r="W59" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="X59" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A60" s="0" t="n">
-        <v>12002300001</v>
-      </c>
-      <c r="C60" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="D60" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I60" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+      <c r="A60" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
       <c r="J60" s="0" t="inlineStr">
@@ -4277,53 +4838,46 @@
           <t>ATK</t>
         </is>
       </c>
-      <c r="L60" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
       <c r="O60" s="0" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="P60" s="0" t="n">
         <v>0.1</v>
       </c>
+      <c r="Q60" s="2" t="n">
+        <v>0.2</v>
+      </c>
       <c r="T60" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U60" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="0" t="n">
-        <v>12002300001</v>
-      </c>
-      <c r="X60" s="0" t="n">
-        <v>12002300001</v>
-      </c>
-      <c r="Y60" s="0" t="inlineStr">
-        <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+      <c r="W60" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="X60" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="n">
-        <v>12002400001</v>
+        <v>11000400001</v>
       </c>
       <c r="C61" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D61" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I61" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J61" s="0" t="inlineStr">
@@ -4331,16 +4885,11 @@
           <t>ASPD</t>
         </is>
       </c>
-      <c r="L61" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
-      </c>
       <c r="O61" s="0" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="P61" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="T61" s="0" t="n">
         <v>0</v>
@@ -4349,52 +4898,42 @@
         <v>0</v>
       </c>
       <c r="W61" s="0" t="n">
-        <v>12002400001</v>
+        <v>11000400001</v>
       </c>
       <c r="X61" s="0" t="n">
-        <v>12002400001</v>
+        <v>11000400001</v>
       </c>
       <c r="Y61" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="n">
-        <v>12003100001</v>
+        <v>11000500001</v>
       </c>
       <c r="C62" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D62" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I62" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J62" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L62" s="0" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O62" s="0" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="P62" s="0" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="T62" s="0" t="n">
         <v>0</v>
@@ -4403,52 +4942,42 @@
         <v>0</v>
       </c>
       <c r="W62" s="0" t="n">
-        <v>12003100001</v>
+        <v>11000500001</v>
       </c>
       <c r="X62" s="0" t="n">
-        <v>12003100001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y62" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>12003200001</v>
+        <v>11000600001</v>
       </c>
       <c r="C63" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D63" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I63" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L63" s="0" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O63" s="0" t="n">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="P63" s="0" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="T63" s="0" t="n">
         <v>0</v>
@@ -4457,52 +4986,48 @@
         <v>0</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>12003200001</v>
+        <v>11000600001</v>
       </c>
       <c r="X63" s="0" t="n">
-        <v>12003200001</v>
+        <v>11000600001</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>12003300001</v>
+        <v>11000700001</v>
       </c>
       <c r="C64" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D64" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G64" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I64" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L64" s="0" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>ATK:1|HP:-1</t>
         </is>
       </c>
       <c r="O64" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P64" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R64" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T64" s="0" t="n">
         <v>0</v>
@@ -4511,52 +5036,48 @@
         <v>0</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>12003300001</v>
+        <v>11000700001</v>
       </c>
       <c r="X64" s="0" t="n">
-        <v>12003300001</v>
+        <v>11000700001</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>12003400001</v>
+        <v>11000700002</v>
       </c>
       <c r="C65" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D65" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G65" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I65" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J65" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L65" s="0" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>ATK:1|DR:-1</t>
         </is>
       </c>
       <c r="O65" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P65" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R65" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T65" s="0" t="n">
         <v>0</v>
@@ -4565,48 +5086,48 @@
         <v>0</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>12003400001</v>
+        <v>11000700002</v>
       </c>
       <c r="X65" s="0" t="n">
-        <v>12003400001</v>
+        <v>11000700002</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>12004100001</v>
+        <v>11000700003</v>
       </c>
       <c r="C66" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D66" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G66" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I66" s="0" t="inlineStr"/>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L66" s="0" t="inlineStr">
-        <is>
-          <t>7001:300&amp;</t>
+          <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O66" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P66" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R66" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T66" s="0" t="n">
         <v>0</v>
@@ -4615,48 +5136,48 @@
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>12004100001</v>
+        <v>11000700003</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>12004100001</v>
+        <v>11000700003</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>12004200001</v>
+        <v>11000800001</v>
       </c>
       <c r="C67" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D67" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G67" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H67" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I67" s="0" t="inlineStr"/>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L67" s="0" t="inlineStr">
-        <is>
-          <t>7001:300&amp;</t>
+          <t>ASPD:1|DR:-1</t>
         </is>
       </c>
       <c r="O67" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P67" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R67" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T67" s="0" t="n">
         <v>0</v>
@@ -4665,48 +5186,48 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>12004200001</v>
+        <v>11000800001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>12004200001</v>
+        <v>11000800001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>12004300001</v>
+        <v>11000800002</v>
       </c>
       <c r="C68" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D68" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G68" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H68" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I68" s="0" t="inlineStr"/>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L68" s="0" t="inlineStr">
-        <is>
-          <t>7001:300&amp;</t>
+          <t>ASPD:1|HP:-1</t>
         </is>
       </c>
       <c r="O68" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P68" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R68" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T68" s="0" t="n">
         <v>0</v>
@@ -4715,48 +5236,48 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>12004300001</v>
+        <v>11000800002</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>12004300001</v>
+        <v>11000800002</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>12004400001</v>
+        <v>11000800003</v>
       </c>
       <c r="C69" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D69" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G69" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H69" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I69" s="0" t="inlineStr"/>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L69" s="0" t="inlineStr">
-        <is>
-          <t>7001:300&amp;</t>
+          <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
       <c r="O69" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P69" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R69" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T69" s="0" t="n">
         <v>0</v>
@@ -4765,41 +5286,48 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>12004400001</v>
+        <v>11000800003</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>12004400001</v>
+        <v>11000800003</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>12010100001</v>
+        <v>11000900001</v>
       </c>
       <c r="C70" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D70" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G70" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H70" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I70" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L70" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J70" s="0" t="inlineStr">
+        <is>
+          <t>DR:1|HP:-1</t>
+        </is>
+      </c>
+      <c r="O70" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P70" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R70" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T70" s="0" t="n">
         <v>0</v>
@@ -4808,41 +5336,48 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>12010100001</v>
+        <v>11000900001</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>12010100001</v>
+        <v>11000900001</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>12010200001</v>
+        <v>11000900002</v>
       </c>
       <c r="C71" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D71" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G71" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H71" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I71" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L71" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J71" s="0" t="inlineStr">
+        <is>
+          <t>DR:1|ATK:-1</t>
+        </is>
+      </c>
+      <c r="O71" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P71" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R71" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T71" s="0" t="n">
         <v>0</v>
@@ -4851,41 +5386,48 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>12010200001</v>
+        <v>11000900002</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>12010200001</v>
+        <v>11000900002</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>12010300001</v>
+        <v>11000900003</v>
       </c>
       <c r="C72" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D72" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G72" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H72" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I72" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L72" s="0" t="inlineStr">
-        <is>
-          <t>4001:1000&amp;</t>
-        </is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J72" s="0" t="inlineStr">
+        <is>
+          <t>DR:1|ASPD:-1</t>
+        </is>
+      </c>
+      <c r="O72" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P72" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R72" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T72" s="0" t="n">
         <v>0</v>
@@ -4894,41 +5436,48 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>12010300001</v>
+        <v>11000900003</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>12010300001</v>
+        <v>11000900003</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>12010400001</v>
+        <v>11001000001</v>
       </c>
       <c r="C73" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D73" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G73" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H73" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I73" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_RegainHP</t>
-        </is>
-      </c>
-      <c r="L73" s="0" t="inlineStr">
-        <is>
-          <t>5001:500&amp;</t>
-        </is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J73" s="0" t="inlineStr">
+        <is>
+          <t>HP:1|ASPD:-1</t>
+        </is>
+      </c>
+      <c r="O73" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P73" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R73" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T73" s="0" t="n">
         <v>0</v>
@@ -4937,41 +5486,48 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>12010400001</v>
+        <v>11001000001</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>12010400001</v>
+        <v>11001000001</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>12010500001</v>
+        <v>11001000002</v>
       </c>
       <c r="C74" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D74" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G74" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H74" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I74" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_RegainHP</t>
-        </is>
-      </c>
-      <c r="L74" s="0" t="inlineStr">
-        <is>
-          <t>6001:1000&amp;</t>
-        </is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J74" s="0" t="inlineStr">
+        <is>
+          <t>HP:1|DR:-1</t>
+        </is>
+      </c>
+      <c r="O74" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P74" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R74" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T74" s="0" t="n">
         <v>0</v>
@@ -4980,41 +5536,48 @@
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>12010500001</v>
+        <v>11001000002</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>12010500001</v>
+        <v>11001000002</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>12011100001</v>
+        <v>11001000003</v>
       </c>
       <c r="C75" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D75" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G75" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H75" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I75" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L75" s="0" t="inlineStr">
-        <is>
-          <t>2001:1&amp;</t>
-        </is>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J75" s="0" t="inlineStr">
+        <is>
+          <t>HP:1|ATK:-1</t>
+        </is>
+      </c>
+      <c r="O75" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P75" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R75" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T75" s="0" t="n">
         <v>0</v>
@@ -5023,20 +5586,20 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>12011100001</v>
+        <v>11001000003</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>12011100001</v>
+        <v>11001000003</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>大块头-C</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>12011200001</v>
+        <v>12000100001</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>12</v>
@@ -5046,18 +5609,17 @@
       </c>
       <c r="H76" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I76" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L76" s="0" t="inlineStr">
-        <is>
-          <t>3001:200&amp;</t>
-        </is>
+          <t>BuffEntityBaseHPChange</t>
+        </is>
+      </c>
+      <c r="O76" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P76" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S76" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T76" s="0" t="n">
         <v>0</v>
@@ -5065,21 +5627,24 @@
       <c r="U76" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V76" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W76" s="0" t="n">
-        <v>12011200001</v>
+        <v>12000100001</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>12011200001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>12011300001</v>
+        <v>12000200001</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>12</v>
@@ -5089,18 +5654,17 @@
       </c>
       <c r="H77" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
-        </is>
-      </c>
-      <c r="I77" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L77" s="0" t="inlineStr">
-        <is>
-          <t>4001:200&amp;</t>
-        </is>
+          <t>BuffEntityBaseDRChange</t>
+        </is>
+      </c>
+      <c r="O77" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P77" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S77" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T77" s="0" t="n">
         <v>0</v>
@@ -5108,41 +5672,38 @@
       <c r="U77" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V77" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W77" s="0" t="n">
-        <v>12011300001</v>
+        <v>12000200001</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>12011300001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>13000100001</v>
+        <v>12000300001</v>
       </c>
       <c r="C78" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H78" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="M78" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" s="0" t="n">
-        <v>1</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
       </c>
       <c r="S78" s="0" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T78" s="0" t="n">
         <v>0</v>
@@ -5151,36 +5712,52 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>13000100001</v>
+        <v>12000300001</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>13000100001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>13000200001</v>
+        <v>12001100001</v>
       </c>
       <c r="C79" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H79" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I79" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J79" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L79" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O79" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P79" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T79" s="0" t="n">
         <v>0</v>
@@ -5188,46 +5765,53 @@
       <c r="U79" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W79" s="0" t="n">
-        <v>13000200001</v>
+        <v>12001100001</v>
       </c>
       <c r="X79" s="0" t="n">
-        <v>13000200001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>13000300001</v>
+        <v>12001200001</v>
       </c>
       <c r="C80" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H80" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I80" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J80" s="0" t="n">
-        <v>300001</v>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J80" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L80" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
       </c>
       <c r="O80" s="0" t="n">
-        <v>1</v>
+        <v>0.25</v>
+      </c>
+      <c r="P80" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T80" s="0" t="n">
         <v>0</v>
@@ -5236,45 +5820,52 @@
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>13000300001</v>
+        <v>12001200001</v>
       </c>
       <c r="X80" s="0" t="n">
-        <v>13000300001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>13000400001</v>
+        <v>12001300001</v>
       </c>
       <c r="C81" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H81" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I81" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J81" s="0" t="n">
-        <v>1</v>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J81" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L81" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
       </c>
       <c r="O81" s="0" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="P81" s="0" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="T81" s="0" t="n">
         <v>0</v>
@@ -5283,45 +5874,52 @@
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>13000400001</v>
+        <v>12001300001</v>
       </c>
       <c r="X81" s="0" t="n">
-        <v>13000400001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>13000500001</v>
+        <v>12001400001</v>
       </c>
       <c r="C82" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H82" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I82" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J82" s="0" t="n">
-        <v>1</v>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J82" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L82" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
       </c>
       <c r="O82" s="0" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="P82" s="0" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="T82" s="0" t="n">
         <v>0</v>
@@ -5330,67 +5928,1630 @@
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>13000500001</v>
+        <v>12001400001</v>
       </c>
       <c r="X82" s="0" t="n">
-        <v>13000500001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="C83" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D83" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I83" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J83" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L83" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O83" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P83" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W83" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="X83" s="0" t="n">
+        <v>12002100001</v>
+      </c>
+      <c r="Y83" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="C84" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D84" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H84" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I84" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J84" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L84" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O84" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P84" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="X84" s="0" t="n">
+        <v>12002200001</v>
+      </c>
+      <c r="Y84" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="C85" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D85" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H85" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I85" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J85" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L85" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O85" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P85" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W85" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="X85" s="0" t="n">
+        <v>12002300001</v>
+      </c>
+      <c r="Y85" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="C86" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D86" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H86" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I86" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J86" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L86" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O86" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P86" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W86" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="X86" s="0" t="n">
+        <v>12002400001</v>
+      </c>
+      <c r="Y86" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="C87" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D87" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H87" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I87" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J87" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L87" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O87" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P87" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="X87" s="0" t="n">
+        <v>12003100001</v>
+      </c>
+      <c r="Y87" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="C88" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D88" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H88" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I88" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J88" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L88" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O88" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P88" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="X88" s="0" t="n">
+        <v>12003200001</v>
+      </c>
+      <c r="Y88" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="C89" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D89" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I89" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J89" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L89" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O89" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P89" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="X89" s="0" t="n">
+        <v>12003300001</v>
+      </c>
+      <c r="Y89" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="C90" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D90" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I90" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J90" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L90" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O90" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P90" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="X90" s="0" t="n">
+        <v>12003400001</v>
+      </c>
+      <c r="Y90" s="0" t="inlineStr">
+        <is>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0" t="n">
+        <v>12004100001</v>
+      </c>
+      <c r="C91" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D91" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H91" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I91" s="0" t="inlineStr"/>
+      <c r="J91" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L91" s="0" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O91" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P91" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W91" s="0" t="n">
+        <v>12004100001</v>
+      </c>
+      <c r="X91" s="0" t="n">
+        <v>12004100001</v>
+      </c>
+      <c r="Y91" s="0" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0" t="n">
+        <v>12004200001</v>
+      </c>
+      <c r="C92" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H92" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I92" s="0" t="inlineStr"/>
+      <c r="J92" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L92" s="0" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O92" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P92" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" s="0" t="n">
+        <v>12004200001</v>
+      </c>
+      <c r="X92" s="0" t="n">
+        <v>12004200001</v>
+      </c>
+      <c r="Y92" s="0" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0" t="n">
+        <v>12004300001</v>
+      </c>
+      <c r="C93" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D93" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H93" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I93" s="0" t="inlineStr"/>
+      <c r="J93" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L93" s="0" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O93" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P93" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W93" s="0" t="n">
+        <v>12004300001</v>
+      </c>
+      <c r="X93" s="0" t="n">
+        <v>12004300001</v>
+      </c>
+      <c r="Y93" s="0" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0" t="n">
+        <v>12004400001</v>
+      </c>
+      <c r="C94" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H94" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I94" s="0" t="inlineStr"/>
+      <c r="J94" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L94" s="0" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O94" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P94" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W94" s="0" t="n">
+        <v>12004400001</v>
+      </c>
+      <c r="X94" s="0" t="n">
+        <v>12004400001</v>
+      </c>
+      <c r="Y94" s="0" t="inlineStr">
+        <is>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="C95" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D95" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H95" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I95" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L95" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="T95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="X95" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="Y95" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="C96" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D96" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I96" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L96" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="X96" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="Y96" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="C97" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H97" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I97" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L97" s="0" t="inlineStr">
+        <is>
+          <t>4001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W97" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="X97" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="Y97" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0" t="n">
+        <v>12010400001</v>
+      </c>
+      <c r="C98" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H98" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I98" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L98" s="0" t="inlineStr">
+        <is>
+          <t>5001:500&amp;</t>
+        </is>
+      </c>
+      <c r="T98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="0" t="n">
+        <v>12010400001</v>
+      </c>
+      <c r="X98" s="0" t="n">
+        <v>12010400001</v>
+      </c>
+      <c r="Y98" s="0" t="inlineStr">
+        <is>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0" t="n">
+        <v>12010500001</v>
+      </c>
+      <c r="C99" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L99" s="0" t="inlineStr">
+        <is>
+          <t>6001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="0" t="n">
+        <v>12010500001</v>
+      </c>
+      <c r="X99" s="0" t="n">
+        <v>12010500001</v>
+      </c>
+      <c r="Y99" s="0" t="inlineStr">
+        <is>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="C100" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H100" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I100" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L100" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
+      </c>
+      <c r="T100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W100" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="X100" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="Y100" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="C101" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D101" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H101" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L101" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
+      </c>
+      <c r="T101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W101" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="X101" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="Y101" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="C102" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D102" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L102" s="0" t="inlineStr">
+        <is>
+          <t>4001:200&amp;</t>
+        </is>
+      </c>
+      <c r="T102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="X102" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="Y102" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="12" customHeight="1" s="3">
+      <c r="A103" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="C103" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D103" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H103" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M103" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N103" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="X103" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="Y103" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="12" customHeight="1" s="3">
+      <c r="A104" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="C104" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D104" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H104" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="T104" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="W104" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="X104" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="Y104" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="12" customHeight="1" s="3">
+      <c r="A105" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="C105" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D105" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H105" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAttack</t>
+        </is>
+      </c>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J105" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O105" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T105" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="X105" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Y105" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="12" customHeight="1" s="3">
+      <c r="A106" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="C106" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D106" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H106" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
+        </is>
+      </c>
+      <c r="I106" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J106" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P106" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T106" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="X106" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Y106" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="12" customHeight="1" s="3">
+      <c r="A107" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="C107" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D107" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I107" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J107" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P107" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T107" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="X107" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Y107" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="12" customHeight="1" s="3">
+      <c r="A108" s="0" t="n">
         <v>13000600001</v>
       </c>
-      <c r="C83" s="0" t="n">
+      <c r="C108" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="D83" s="0" t="n">
+      <c r="D108" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="H83" s="0" t="inlineStr">
+      <c r="H108" s="0" t="inlineStr">
         <is>
           <t>BuffEntityConditionalDeadCreateCrystal</t>
         </is>
       </c>
-      <c r="I83" s="0" t="inlineStr">
+      <c r="I108" s="0" t="inlineStr">
         <is>
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q83" s="0" t="n">
+      <c r="Q108" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="T83" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U83" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W83" s="0" t="n">
+      <c r="T108" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="0" t="n">
         <v>13000600001</v>
       </c>
-      <c r="X83" s="0" t="n">
+      <c r="X108" s="0" t="n">
         <v>13000600001</v>
       </c>
-      <c r="Y83" s="0" t="inlineStr">
+      <c r="Y108" s="0" t="inlineStr">
         <is>
           <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="12" customHeight="1" s="3"/>
-    <row r="104" ht="12" customHeight="1" s="3"/>
-    <row r="105" ht="12" customHeight="1" s="3"/>
-    <row r="106" ht="12" customHeight="1" s="3"/>
-    <row r="107" ht="12" customHeight="1" s="3"/>
-    <row r="108" ht="12" customHeight="1" s="3"/>
-    <row r="109" ht="12" customHeight="1" s="3"/>
-    <row r="110" ht="12" customHeight="1" s="3"/>
-    <row r="111" ht="12" customHeight="1" s="3"/>
+    <row r="109" ht="12" customHeight="1" s="3">
+      <c r="A109" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="B109" s="0" t="inlineStr"/>
+      <c r="C109" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H109" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I109" s="0" t="inlineStr"/>
+      <c r="J109" s="0" t="inlineStr">
+        <is>
+          <t>1,300051</t>
+        </is>
+      </c>
+      <c r="K109" s="0" t="inlineStr"/>
+      <c r="L109" s="0" t="inlineStr"/>
+      <c r="M109" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X109" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y109" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="12" customHeight="1" s="3">
+      <c r="A110" s="0" t="n">
+        <v>3000500002</v>
+      </c>
+      <c r="B110" s="0" t="inlineStr"/>
+      <c r="C110" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I110" s="0" t="inlineStr"/>
+      <c r="J110" s="0" t="inlineStr">
+        <is>
+          <t>2,300051</t>
+        </is>
+      </c>
+      <c r="K110" s="0" t="inlineStr"/>
+      <c r="L110" s="0" t="inlineStr"/>
+      <c r="M110" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X110" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y110" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="12" customHeight="1" s="3">
+      <c r="A111" s="0" t="n">
+        <v>3000500003</v>
+      </c>
+      <c r="B111" s="0" t="inlineStr"/>
+      <c r="C111" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I111" s="0" t="inlineStr"/>
+      <c r="J111" s="0" t="inlineStr">
+        <is>
+          <t>3,300051</t>
+        </is>
+      </c>
+      <c r="K111" s="0" t="inlineStr"/>
+      <c r="L111" s="0" t="inlineStr"/>
+      <c r="M111" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X111" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y111" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0" t="n">
+        <v>3000500004</v>
+      </c>
+      <c r="B112" s="0" t="inlineStr"/>
+      <c r="C112" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I112" s="0" t="inlineStr"/>
+      <c r="J112" s="0" t="inlineStr">
+        <is>
+          <t>4,300051</t>
+        </is>
+      </c>
+      <c r="K112" s="0" t="inlineStr"/>
+      <c r="L112" s="0" t="inlineStr"/>
+      <c r="M112" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X112" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y112" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0" t="n">
+        <v>3000500005</v>
+      </c>
+      <c r="B113" s="0" t="inlineStr"/>
+      <c r="C113" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H113" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr"/>
+      <c r="J113" s="0" t="inlineStr">
+        <is>
+          <t>5,300051</t>
+        </is>
+      </c>
+      <c r="K113" s="0" t="inlineStr"/>
+      <c r="L113" s="0" t="inlineStr"/>
+      <c r="M113" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X113" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y113" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -2388,7 +2388,7 @@
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicMultiInstantAttack</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J21" s="0" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicMultiInstantAttack</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J22" s="0" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicMultiInstantAttack</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J23" s="0" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="H24" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicMultiInstantAttack</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J24" s="0" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H25" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicMultiInstantAttack</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J25" s="0" t="inlineStr">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y113"/>
+  <dimension ref="A1:Y134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>1,300061,0</t>
+          <t>1,300061,1</t>
         </is>
       </c>
       <c r="M31" s="0" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,不弹跳</t>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>2,300061,1</t>
+          <t>2,300061,2</t>
         </is>
       </c>
       <c r="M32" s="0" t="n">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳1次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>3,300061,2</t>
+          <t>3,300061,3</t>
         </is>
       </c>
       <c r="M33" s="0" t="n">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>4,300061,3</t>
+          <t>4,300061,4</t>
         </is>
       </c>
       <c r="M34" s="0" t="n">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>5,300061,4</t>
+          <t>5,300061,5</t>
         </is>
       </c>
       <c r="M35" s="0" t="n">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="M36" s="0" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力50%</t>
+          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="M37" s="0" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>0</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力50%</t>
+          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="M38" s="0" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N38" s="0" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力50%</t>
+          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M39" s="0" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N39" s="0" t="n">
         <v>0</v>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力50%</t>
+          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="M40" s="0" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N40" s="0" t="n">
         <v>0</v>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力50%</t>
+          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
@@ -5599,27 +5599,35 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000700004</v>
       </c>
       <c r="C76" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D76" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G76" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H76" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J76" s="0" t="inlineStr">
+        <is>
+          <t>ATK:1|RCD:1</t>
         </is>
       </c>
       <c r="O76" s="0" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="P76" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S76" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
+      </c>
+      <c r="R76" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T76" s="0" t="n">
         <v>0</v>
@@ -5627,44 +5635,49 @@
       <c r="U76" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W76" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000700004</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>12000100001</v>
+        <v>11000700004</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>狂战士-D</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000700005</v>
       </c>
       <c r="C77" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D77" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G77" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H77" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J77" s="0" t="inlineStr">
+        <is>
+          <t>ATK:1|CMP:1</t>
         </is>
       </c>
       <c r="O77" s="0" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="P77" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S77" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
+      </c>
+      <c r="R77" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T77" s="0" t="n">
         <v>0</v>
@@ -5672,38 +5685,49 @@
       <c r="U77" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="0" t="n">
-        <v>500002</v>
-      </c>
       <c r="W77" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000700005</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>12000200001</v>
+        <v>11000700005</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>狂战士-E</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000800004</v>
       </c>
       <c r="C78" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D78" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G78" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H78" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
-      </c>
-      <c r="S78" s="0" t="n">
-        <v>5</v>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J78" s="0" t="inlineStr">
+        <is>
+          <t>ASPD:1|RCD:1</t>
+        </is>
+      </c>
+      <c r="O78" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P78" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R78" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T78" s="0" t="n">
         <v>0</v>
@@ -5712,52 +5736,48 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000800004</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>12000300001</v>
+        <v>11000800004</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>快枪手-D</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000800005</v>
       </c>
       <c r="C79" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D79" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G79" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H79" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I79" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L79" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>ASPD:1|CMP:1</t>
         </is>
       </c>
       <c r="O79" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P79" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R79" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T79" s="0" t="n">
         <v>0</v>
@@ -5766,52 +5786,48 @@
         <v>0</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000800005</v>
       </c>
       <c r="X79" s="0" t="n">
-        <v>12001100001</v>
+        <v>11000800005</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>快枪手-E</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>12001200001</v>
+        <v>11000900004</v>
       </c>
       <c r="C80" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D80" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G80" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H80" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I80" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L80" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>DR:1|RCD:1</t>
         </is>
       </c>
       <c r="O80" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P80" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R80" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T80" s="0" t="n">
         <v>0</v>
@@ -5820,52 +5836,48 @@
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>12001200001</v>
+        <v>11000900004</v>
       </c>
       <c r="X80" s="0" t="n">
-        <v>12001200001</v>
+        <v>11000900004</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>铜墙铁壁-D</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>12001300001</v>
+        <v>11000900005</v>
       </c>
       <c r="C81" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D81" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G81" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H81" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I81" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L81" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>DR:1|CMP:1</t>
         </is>
       </c>
       <c r="O81" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P81" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R81" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T81" s="0" t="n">
         <v>0</v>
@@ -5874,52 +5886,48 @@
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>12001300001</v>
+        <v>11000900005</v>
       </c>
       <c r="X81" s="0" t="n">
-        <v>12001300001</v>
+        <v>11000900005</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>铜墙铁壁-E</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>12001400001</v>
+        <v>11001000004</v>
       </c>
       <c r="C82" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D82" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G82" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H82" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I82" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L82" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>HP:1|RCD:1</t>
         </is>
       </c>
       <c r="O82" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P82" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R82" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T82" s="0" t="n">
         <v>0</v>
@@ -5928,52 +5936,48 @@
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>12001400001</v>
+        <v>11001000004</v>
       </c>
       <c r="X82" s="0" t="n">
-        <v>12001400001</v>
+        <v>11001000004</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>大块头-D</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>12002100001</v>
+        <v>11001000005</v>
       </c>
       <c r="C83" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D83" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G83" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H83" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I83" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L83" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
+          <t>HP:1|CMP:1</t>
         </is>
       </c>
       <c r="O83" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="P83" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="R83" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T83" s="0" t="n">
         <v>0</v>
@@ -5982,52 +5986,48 @@
         <v>0</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>12002100001</v>
+        <v>11001000005</v>
       </c>
       <c r="X83" s="0" t="n">
-        <v>12002100001</v>
+        <v>11001000005</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>大块头-E</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>12002200001</v>
+        <v>11001100001</v>
       </c>
       <c r="C84" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D84" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G84" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H84" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I84" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L84" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
+          <t>RCD:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O84" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P84" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R84" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T84" s="0" t="n">
         <v>0</v>
@@ -6036,52 +6036,48 @@
         <v>0</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>12002200001</v>
+        <v>11001100001</v>
       </c>
       <c r="X84" s="0" t="n">
-        <v>12002200001</v>
+        <v>11001100001</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>魂牵梦绕-A</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>12002300001</v>
+        <v>11001100002</v>
       </c>
       <c r="C85" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D85" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G85" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H85" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I85" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L85" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
+          <t>RCD:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O85" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P85" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R85" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T85" s="0" t="n">
         <v>0</v>
@@ -6090,52 +6086,48 @@
         <v>0</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>12002300001</v>
+        <v>11001100002</v>
       </c>
       <c r="X85" s="0" t="n">
-        <v>12002300001</v>
+        <v>11001100002</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>魂牵梦绕-B</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>12002400001</v>
+        <v>11001100003</v>
       </c>
       <c r="C86" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D86" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G86" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H86" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I86" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L86" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
+          <t>RCD:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O86" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P86" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R86" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T86" s="0" t="n">
         <v>0</v>
@@ -6144,52 +6136,48 @@
         <v>0</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>12002400001</v>
+        <v>11001100003</v>
       </c>
       <c r="X86" s="0" t="n">
-        <v>12002400001</v>
+        <v>11001100003</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>魂牵梦绕-C</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>12003100001</v>
+        <v>11001100004</v>
       </c>
       <c r="C87" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D87" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G87" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H87" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I87" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L87" s="0" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>RCD:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O87" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P87" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R87" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T87" s="0" t="n">
         <v>0</v>
@@ -6198,52 +6186,48 @@
         <v>0</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>12003100001</v>
+        <v>11001100004</v>
       </c>
       <c r="X87" s="0" t="n">
-        <v>12003100001</v>
+        <v>11001100004</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>魂牵梦绕-D</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>12003200001</v>
+        <v>11001100005</v>
       </c>
       <c r="C88" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D88" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G88" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H88" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I88" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L88" s="0" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>RCD:-1|CMP:0.5</t>
         </is>
       </c>
       <c r="O88" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P88" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R88" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T88" s="0" t="n">
         <v>0</v>
@@ -6252,52 +6236,48 @@
         <v>0</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>12003200001</v>
+        <v>11001100005</v>
       </c>
       <c r="X88" s="0" t="n">
-        <v>12003200001</v>
+        <v>11001100005</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>魂牵梦绕-E</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>12003300001</v>
+        <v>11001200001</v>
       </c>
       <c r="C89" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D89" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G89" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H89" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I89" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L89" s="0" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>CMP:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O89" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P89" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R89" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T89" s="0" t="n">
         <v>0</v>
@@ -6306,52 +6286,48 @@
         <v>0</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>12003300001</v>
+        <v>11001200001</v>
       </c>
       <c r="X89" s="0" t="n">
-        <v>12003300001</v>
+        <v>11001200001</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>折上折-A</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>12003400001</v>
+        <v>11001200002</v>
       </c>
       <c r="C90" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D90" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G90" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H90" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I90" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityAttributeMulti</t>
         </is>
       </c>
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L90" s="0" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
+          <t>CMP:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O90" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P90" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R90" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T90" s="0" t="n">
         <v>0</v>
@@ -6360,48 +6336,48 @@
         <v>0</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>12003400001</v>
+        <v>11001200002</v>
       </c>
       <c r="X90" s="0" t="n">
-        <v>12003400001</v>
+        <v>11001200002</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>折上折-B</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>12004100001</v>
+        <v>11001200003</v>
       </c>
       <c r="C91" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D91" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G91" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H91" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I91" s="0" t="inlineStr"/>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L91" s="0" t="inlineStr">
-        <is>
-          <t>7001:300&amp;</t>
+          <t>CMP:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O91" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P91" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R91" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T91" s="0" t="n">
         <v>0</v>
@@ -6410,48 +6386,48 @@
         <v>0</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>12004100001</v>
+        <v>11001200003</v>
       </c>
       <c r="X91" s="0" t="n">
-        <v>12004100001</v>
+        <v>11001200003</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>折上折-C</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>12004200001</v>
+        <v>11001200004</v>
       </c>
       <c r="C92" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D92" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G92" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H92" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I92" s="0" t="inlineStr"/>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L92" s="0" t="inlineStr">
-        <is>
-          <t>7001:300&amp;</t>
+          <t>CMP:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O92" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P92" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R92" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T92" s="0" t="n">
         <v>0</v>
@@ -6460,48 +6436,48 @@
         <v>0</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>12004200001</v>
+        <v>11001200004</v>
       </c>
       <c r="X92" s="0" t="n">
-        <v>12004200001</v>
+        <v>11001200004</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>折上折-D</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>12004300001</v>
+        <v>11001200005</v>
       </c>
       <c r="C93" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D93" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G93" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H93" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I93" s="0" t="inlineStr"/>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="L93" s="0" t="inlineStr">
-        <is>
-          <t>7001:300&amp;</t>
+          <t>CMP:-1|RCD:0.5</t>
         </is>
       </c>
       <c r="O93" s="0" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="P93" s="0" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
+      </c>
+      <c r="R93" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T93" s="0" t="n">
         <v>0</v>
@@ -6510,20 +6486,20 @@
         <v>0</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>12004300001</v>
+        <v>11001200005</v>
       </c>
       <c r="X93" s="0" t="n">
-        <v>12004300001</v>
+        <v>11001200005</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>折上折-E</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>12004400001</v>
+        <v>12000100001</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>12</v>
@@ -6533,25 +6509,17 @@
       </c>
       <c r="H94" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I94" s="0" t="inlineStr"/>
-      <c r="J94" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="L94" s="0" t="inlineStr">
-        <is>
-          <t>7001:300&amp;</t>
+          <t>BuffEntityBaseHPChange</t>
         </is>
       </c>
       <c r="O94" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="P94" s="0" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
+      </c>
+      <c r="S94" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T94" s="0" t="n">
         <v>0</v>
@@ -6559,21 +6527,24 @@
       <c r="U94" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V94" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W94" s="0" t="n">
-        <v>12004400001</v>
+        <v>12000100001</v>
       </c>
       <c r="X94" s="0" t="n">
-        <v>12004400001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>12010100001</v>
+        <v>12000200001</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>12</v>
@@ -6583,18 +6554,17 @@
       </c>
       <c r="H95" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I95" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="L95" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>BuffEntityBaseDRChange</t>
+        </is>
+      </c>
+      <c r="O95" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P95" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="S95" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T95" s="0" t="n">
         <v>0</v>
@@ -6602,21 +6572,24 @@
       <c r="U95" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V95" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W95" s="0" t="n">
-        <v>12010100001</v>
+        <v>12000200001</v>
       </c>
       <c r="X95" s="0" t="n">
-        <v>12010100001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>12010200001</v>
+        <v>12000300001</v>
       </c>
       <c r="C96" s="0" t="n">
         <v>12</v>
@@ -6626,18 +6599,11 @@
       </c>
       <c r="H96" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I96" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
-      </c>
-      <c r="L96" s="0" t="inlineStr">
-        <is>
-          <t>3001:1000&amp;</t>
-        </is>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="S96" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T96" s="0" t="n">
         <v>0</v>
@@ -6646,20 +6612,20 @@
         <v>0</v>
       </c>
       <c r="W96" s="0" t="n">
-        <v>12010200001</v>
+        <v>12000300001</v>
       </c>
       <c r="X96" s="0" t="n">
-        <v>12010200001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>12010300001</v>
+        <v>12001100001</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>12</v>
@@ -6669,18 +6635,29 @@
       </c>
       <c r="H97" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I97" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J97" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
         </is>
       </c>
       <c r="L97" s="0" t="inlineStr">
         <is>
-          <t>4001:1000&amp;</t>
-        </is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O97" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P97" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T97" s="0" t="n">
         <v>0</v>
@@ -6689,20 +6666,20 @@
         <v>0</v>
       </c>
       <c r="W97" s="0" t="n">
-        <v>12010300001</v>
+        <v>12001100001</v>
       </c>
       <c r="X97" s="0" t="n">
-        <v>12010300001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>12010400001</v>
+        <v>12001200001</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>12</v>
@@ -6712,18 +6689,29 @@
       </c>
       <c r="H98" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I98" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J98" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
         </is>
       </c>
       <c r="L98" s="0" t="inlineStr">
         <is>
-          <t>5001:500&amp;</t>
-        </is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O98" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P98" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T98" s="0" t="n">
         <v>0</v>
@@ -6732,20 +6720,20 @@
         <v>0</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>12010400001</v>
+        <v>12001200001</v>
       </c>
       <c r="X98" s="0" t="n">
-        <v>12010400001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>12010500001</v>
+        <v>12001300001</v>
       </c>
       <c r="C99" s="0" t="n">
         <v>12</v>
@@ -6755,18 +6743,29 @@
       </c>
       <c r="H99" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I99" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="J99" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
         <is>
-          <t>6001:1000&amp;</t>
-        </is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O99" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P99" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T99" s="0" t="n">
         <v>0</v>
@@ -6775,20 +6774,20 @@
         <v>0</v>
       </c>
       <c r="W99" s="0" t="n">
-        <v>12010500001</v>
+        <v>12001300001</v>
       </c>
       <c r="X99" s="0" t="n">
-        <v>12010500001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>12011100001</v>
+        <v>12001400001</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>12</v>
@@ -6798,7 +6797,7 @@
       </c>
       <c r="H100" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I100" s="0" t="inlineStr">
@@ -6806,10 +6805,21 @@
           <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
+      <c r="J100" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
       <c r="L100" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
-        </is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="O100" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P100" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T100" s="0" t="n">
         <v>0</v>
@@ -6818,20 +6828,20 @@
         <v>0</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>12011100001</v>
+        <v>12001400001</v>
       </c>
       <c r="X100" s="0" t="n">
-        <v>12011100001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>12011200001</v>
+        <v>12002100001</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>12</v>
@@ -6841,7 +6851,7 @@
       </c>
       <c r="H101" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I101" s="0" t="inlineStr">
@@ -6849,10 +6859,21 @@
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
+      <c r="J101" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
       <c r="L101" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
-        </is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O101" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P101" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T101" s="0" t="n">
         <v>0</v>
@@ -6861,20 +6882,20 @@
         <v>0</v>
       </c>
       <c r="W101" s="0" t="n">
-        <v>12011200001</v>
+        <v>12002100001</v>
       </c>
       <c r="X101" s="0" t="n">
-        <v>12011200001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>12011300001</v>
+        <v>12002200001</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>12</v>
@@ -6884,7 +6905,7 @@
       </c>
       <c r="H102" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I102" s="0" t="inlineStr">
@@ -6892,10 +6913,21 @@
           <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
+      <c r="J102" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
       <c r="L102" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
-        </is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O102" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P102" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T102" s="0" t="n">
         <v>0</v>
@@ -6904,40 +6936,52 @@
         <v>0</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>12011300001</v>
+        <v>12002200001</v>
       </c>
       <c r="X102" s="0" t="n">
-        <v>12011300001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="12" customHeight="1" s="3">
       <c r="A103" s="0" t="n">
-        <v>13000100001</v>
+        <v>12002300001</v>
       </c>
       <c r="C103" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D103" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H103" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="M103" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N103" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S103" s="0" t="n">
-        <v>3</v>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J103" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L103" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O103" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P103" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T103" s="0" t="n">
         <v>0</v>
@@ -6946,36 +6990,52 @@
         <v>0</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>13000100001</v>
+        <v>12002300001</v>
       </c>
       <c r="X103" s="0" t="n">
-        <v>13000100001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="12" customHeight="1" s="3">
       <c r="A104" s="0" t="n">
-        <v>13000200001</v>
+        <v>12002400001</v>
       </c>
       <c r="C104" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D104" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H104" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I104" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J104" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L104" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="O104" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P104" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T104" s="0" t="n">
         <v>0</v>
@@ -6983,46 +7043,53 @@
       <c r="U104" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W104" s="0" t="n">
-        <v>13000200001</v>
+        <v>12002400001</v>
       </c>
       <c r="X104" s="0" t="n">
-        <v>13000200001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="12" customHeight="1" s="3">
       <c r="A105" s="0" t="n">
-        <v>13000300001</v>
+        <v>12003100001</v>
       </c>
       <c r="C105" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D105" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H105" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I105" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J105" s="0" t="n">
-        <v>300001</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J105" s="0" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L105" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
       </c>
       <c r="O105" s="0" t="n">
-        <v>1</v>
+        <v>0.25</v>
+      </c>
+      <c r="P105" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T105" s="0" t="n">
         <v>0</v>
@@ -7031,45 +7098,52 @@
         <v>0</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>13000300001</v>
+        <v>12003100001</v>
       </c>
       <c r="X105" s="0" t="n">
-        <v>13000300001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="12" customHeight="1" s="3">
       <c r="A106" s="0" t="n">
-        <v>13000400001</v>
+        <v>12003200001</v>
       </c>
       <c r="C106" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D106" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H106" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I106" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J106" s="0" t="n">
-        <v>1</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J106" s="0" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L106" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
       </c>
       <c r="O106" s="0" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="P106" s="0" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="T106" s="0" t="n">
         <v>0</v>
@@ -7078,45 +7152,52 @@
         <v>0</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>13000400001</v>
+        <v>12003200001</v>
       </c>
       <c r="X106" s="0" t="n">
-        <v>13000400001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="12" customHeight="1" s="3">
       <c r="A107" s="0" t="n">
-        <v>13000500001</v>
+        <v>12003300001</v>
       </c>
       <c r="C107" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D107" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H107" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I107" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J107" s="0" t="n">
-        <v>1</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J107" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L107" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
       </c>
       <c r="O107" s="0" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="P107" s="0" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="T107" s="0" t="n">
         <v>0</v>
@@ -7125,39 +7206,52 @@
         <v>0</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>13000500001</v>
+        <v>12003300001</v>
       </c>
       <c r="X107" s="0" t="n">
-        <v>13000500001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="12" customHeight="1" s="3">
       <c r="A108" s="0" t="n">
-        <v>13000600001</v>
+        <v>12003400001</v>
       </c>
       <c r="C108" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D108" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H108" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadCreateCrystal</t>
+          <t>BuffEntityConditionalAttribute</t>
         </is>
       </c>
       <c r="I108" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="Q108" s="0" t="n">
-        <v>0.2</v>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="J108" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L108" s="0" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="O108" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P108" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T108" s="0" t="n">
         <v>0</v>
@@ -7166,70 +7260,48 @@
         <v>0</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>13000600001</v>
+        <v>12003400001</v>
       </c>
       <c r="X108" s="0" t="n">
-        <v>13000600001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="12" customHeight="1" s="3">
       <c r="A109" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="B109" s="0" t="inlineStr"/>
+        <v>12004100001</v>
+      </c>
       <c r="C109" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D109" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="H109" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
+          <t>BuffEntityConditionalAttributeTime</t>
         </is>
       </c>
       <c r="I109" s="0" t="inlineStr"/>
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>1,300051</t>
-        </is>
-      </c>
-      <c r="K109" s="0" t="inlineStr"/>
-      <c r="L109" s="0" t="inlineStr"/>
-      <c r="M109" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N109" s="0" t="n">
-        <v>0</v>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L109" s="0" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
       </c>
       <c r="O109" s="0" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P109" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" s="0" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="T109" s="0" t="n">
         <v>0</v>
@@ -7237,74 +7309,49 @@
       <c r="U109" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W109" s="0" t="n">
-        <v>3000500001</v>
+        <v>12004100001</v>
       </c>
       <c r="X109" s="0" t="n">
-        <v>3000500001</v>
+        <v>12004100001</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="12" customHeight="1" s="3">
       <c r="A110" s="0" t="n">
-        <v>3000500002</v>
-      </c>
-      <c r="B110" s="0" t="inlineStr"/>
+        <v>12004200001</v>
+      </c>
       <c r="C110" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D110" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D110" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="H110" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
+          <t>BuffEntityConditionalAttributeTime</t>
         </is>
       </c>
       <c r="I110" s="0" t="inlineStr"/>
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>2,300051</t>
-        </is>
-      </c>
-      <c r="K110" s="0" t="inlineStr"/>
-      <c r="L110" s="0" t="inlineStr"/>
-      <c r="M110" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N110" s="0" t="n">
-        <v>0</v>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="L110" s="0" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
       </c>
       <c r="O110" s="0" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P110" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" s="0" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="T110" s="0" t="n">
         <v>0</v>
@@ -7312,74 +7359,49 @@
       <c r="U110" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W110" s="0" t="n">
-        <v>3000500001</v>
+        <v>12004200001</v>
       </c>
       <c r="X110" s="0" t="n">
-        <v>3000500001</v>
+        <v>12004200001</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="12" customHeight="1" s="3">
       <c r="A111" s="0" t="n">
-        <v>3000500003</v>
-      </c>
-      <c r="B111" s="0" t="inlineStr"/>
+        <v>12004300001</v>
+      </c>
       <c r="C111" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D111" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="H111" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
+          <t>BuffEntityConditionalAttributeTime</t>
         </is>
       </c>
       <c r="I111" s="0" t="inlineStr"/>
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>3,300051</t>
-        </is>
-      </c>
-      <c r="K111" s="0" t="inlineStr"/>
-      <c r="L111" s="0" t="inlineStr"/>
-      <c r="M111" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N111" s="0" t="n">
-        <v>0</v>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L111" s="0" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
       </c>
       <c r="O111" s="0" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P111" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" s="0" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="T111" s="0" t="n">
         <v>0</v>
@@ -7387,74 +7409,49 @@
       <c r="U111" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W111" s="0" t="n">
-        <v>3000500001</v>
+        <v>12004300001</v>
       </c>
       <c r="X111" s="0" t="n">
-        <v>3000500001</v>
+        <v>12004300001</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>3000500004</v>
-      </c>
-      <c r="B112" s="0" t="inlineStr"/>
+        <v>12004400001</v>
+      </c>
       <c r="C112" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D112" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D112" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="H112" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
+          <t>BuffEntityConditionalAttributeTime</t>
         </is>
       </c>
       <c r="I112" s="0" t="inlineStr"/>
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>4,300051</t>
-        </is>
-      </c>
-      <c r="K112" s="0" t="inlineStr"/>
-      <c r="L112" s="0" t="inlineStr"/>
-      <c r="M112" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N112" s="0" t="n">
-        <v>0</v>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="L112" s="0" t="inlineStr">
+        <is>
+          <t>7001:300&amp;</t>
+        </is>
       </c>
       <c r="O112" s="0" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P112" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" s="0" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="T112" s="0" t="n">
         <v>0</v>
@@ -7462,93 +7459,1119 @@
       <c r="U112" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W112" s="0" t="n">
-        <v>3000500001</v>
+        <v>12004400001</v>
       </c>
       <c r="X112" s="0" t="n">
-        <v>3000500001</v>
+        <v>12004400001</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D113" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L113" s="0" t="inlineStr">
+        <is>
+          <t>2001:10&amp;</t>
+        </is>
+      </c>
+      <c r="T113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="X113" s="0" t="n">
+        <v>12010100001</v>
+      </c>
+      <c r="Y113" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I114" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L114" s="0" t="inlineStr">
+        <is>
+          <t>3001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T114" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="X114" s="0" t="n">
+        <v>12010200001</v>
+      </c>
+      <c r="Y114" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H115" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I115" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L115" s="0" t="inlineStr">
+        <is>
+          <t>4001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="X115" s="0" t="n">
+        <v>12010300001</v>
+      </c>
+      <c r="Y115" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0" t="n">
+        <v>12010400001</v>
+      </c>
+      <c r="C116" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I116" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L116" s="0" t="inlineStr">
+        <is>
+          <t>5001:500&amp;</t>
+        </is>
+      </c>
+      <c r="T116" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="0" t="n">
+        <v>12010400001</v>
+      </c>
+      <c r="X116" s="0" t="n">
+        <v>12010400001</v>
+      </c>
+      <c r="Y116" s="0" t="inlineStr">
+        <is>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0" t="n">
+        <v>12010500001</v>
+      </c>
+      <c r="C117" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H117" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I117" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_RegainHP</t>
+        </is>
+      </c>
+      <c r="L117" s="0" t="inlineStr">
+        <is>
+          <t>6001:1000&amp;</t>
+        </is>
+      </c>
+      <c r="T117" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="0" t="n">
+        <v>12010500001</v>
+      </c>
+      <c r="X117" s="0" t="n">
+        <v>12010500001</v>
+      </c>
+      <c r="Y117" s="0" t="inlineStr">
+        <is>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="C118" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H118" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I118" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L118" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
+      </c>
+      <c r="T118" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="X118" s="0" t="n">
+        <v>12011100001</v>
+      </c>
+      <c r="Y118" s="0" t="inlineStr">
+        <is>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="C119" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D119" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I119" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L119" s="0" t="inlineStr">
+        <is>
+          <t>3001:200&amp;</t>
+        </is>
+      </c>
+      <c r="T119" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="X119" s="0" t="n">
+        <v>12011200001</v>
+      </c>
+      <c r="Y119" s="0" t="inlineStr">
+        <is>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="C120" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H120" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttackAgain</t>
+        </is>
+      </c>
+      <c r="I120" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L120" s="0" t="inlineStr">
+        <is>
+          <t>4001:200&amp;</t>
+        </is>
+      </c>
+      <c r="T120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="X120" s="0" t="n">
+        <v>12011300001</v>
+      </c>
+      <c r="Y120" s="0" t="inlineStr">
+        <is>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="C121" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H121" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M121" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N121" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S121" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="X121" s="0" t="n">
+        <v>13000100001</v>
+      </c>
+      <c r="Y121" s="0" t="inlineStr">
+        <is>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="C122" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H122" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadRebirth</t>
+        </is>
+      </c>
+      <c r="I122" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="T122" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="0" t="n">
+        <v>500001</v>
+      </c>
+      <c r="W122" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="X122" s="0" t="n">
+        <v>13000200001</v>
+      </c>
+      <c r="Y122" s="0" t="inlineStr">
+        <is>
+          <t>死亡后重生</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="C123" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H123" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAttack</t>
+        </is>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J123" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O123" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="X123" s="0" t="n">
+        <v>13000300001</v>
+      </c>
+      <c r="Y123" s="0" t="inlineStr">
+        <is>
+          <t>死亡后爆炸</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="C124" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
+        </is>
+      </c>
+      <c r="I124" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J124" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O124" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P124" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T124" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="X124" s="0" t="n">
+        <v>13000400001</v>
+      </c>
+      <c r="Y124" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="C125" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D125" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H125" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J125" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O125" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P125" s="0" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="T125" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="X125" s="0" t="n">
+        <v>13000500001</v>
+      </c>
+      <c r="Y125" s="0" t="inlineStr">
+        <is>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="C126" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D126" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H126" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalDeadCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I126" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="Q126" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T126" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="X126" s="0" t="n">
+        <v>13000600001</v>
+      </c>
+      <c r="Y126" s="0" t="inlineStr">
+        <is>
+          <t>死亡后{Percentage}%生成魔晶</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="B127" s="0" t="inlineStr"/>
+      <c r="C127" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I127" s="0" t="inlineStr"/>
+      <c r="J127" s="0" t="inlineStr">
+        <is>
+          <t>1,300051</t>
+        </is>
+      </c>
+      <c r="K127" s="0" t="inlineStr"/>
+      <c r="L127" s="0" t="inlineStr"/>
+      <c r="M127" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X127" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y127" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0" t="n">
+        <v>3000500002</v>
+      </c>
+      <c r="B128" s="0" t="inlineStr"/>
+      <c r="C128" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H128" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I128" s="0" t="inlineStr"/>
+      <c r="J128" s="0" t="inlineStr">
+        <is>
+          <t>2,300051</t>
+        </is>
+      </c>
+      <c r="K128" s="0" t="inlineStr"/>
+      <c r="L128" s="0" t="inlineStr"/>
+      <c r="M128" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X128" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y128" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0" t="n">
+        <v>3000500003</v>
+      </c>
+      <c r="B129" s="0" t="inlineStr"/>
+      <c r="C129" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H129" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I129" s="0" t="inlineStr"/>
+      <c r="J129" s="0" t="inlineStr">
+        <is>
+          <t>3,300051</t>
+        </is>
+      </c>
+      <c r="K129" s="0" t="inlineStr"/>
+      <c r="L129" s="0" t="inlineStr"/>
+      <c r="M129" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X129" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y129" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0" t="n">
+        <v>3000500004</v>
+      </c>
+      <c r="B130" s="0" t="inlineStr"/>
+      <c r="C130" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H130" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I130" s="0" t="inlineStr"/>
+      <c r="J130" s="0" t="inlineStr">
+        <is>
+          <t>4,300051</t>
+        </is>
+      </c>
+      <c r="K130" s="0" t="inlineStr"/>
+      <c r="L130" s="0" t="inlineStr"/>
+      <c r="M130" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="X130" s="0" t="n">
+        <v>3000500001</v>
+      </c>
+      <c r="Y130" s="0" t="inlineStr">
+        <is>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0" t="n">
         <v>3000500005</v>
       </c>
-      <c r="B113" s="0" t="inlineStr"/>
-      <c r="C113" s="0" t="n">
+      <c r="B131" s="0" t="inlineStr"/>
+      <c r="C131" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="D113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="0" t="n">
+      <c r="D131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="H113" s="0" t="inlineStr">
+      <c r="H131" s="0" t="inlineStr">
         <is>
           <t>BuffEntityPeriodicAttackBoomerang</t>
         </is>
       </c>
-      <c r="I113" s="0" t="inlineStr"/>
-      <c r="J113" s="0" t="inlineStr">
+      <c r="I131" s="0" t="inlineStr"/>
+      <c r="J131" s="0" t="inlineStr">
         <is>
           <t>5,300051</t>
         </is>
       </c>
-      <c r="K113" s="0" t="inlineStr"/>
-      <c r="L113" s="0" t="inlineStr"/>
-      <c r="M113" s="0" t="n">
+      <c r="K131" s="0" t="inlineStr"/>
+      <c r="L131" s="0" t="inlineStr"/>
+      <c r="M131" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" s="0" t="n">
+      <c r="N131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W113" s="0" t="n">
+      <c r="T131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="X113" s="0" t="n">
+      <c r="X131" s="0" t="n">
         <v>3000500001</v>
       </c>
-      <c r="Y113" s="0" t="inlineStr">
+      <c r="Y131" s="0" t="inlineStr">
         <is>
           <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="C132" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D132" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H132" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalThorns</t>
+        </is>
+      </c>
+      <c r="I132" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O132" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P132" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="X132" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="Y132" s="0" t="inlineStr">
+        <is>
+          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="C133" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D133" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H133" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalLifeSteal</t>
+        </is>
+      </c>
+      <c r="I133" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O133" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P133" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="X133" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="Y133" s="0" t="inlineStr">
+        <is>
+          <t>造成伤害的{Percentage}%转化为自身生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0" t="n">
+        <v>13000900001</v>
+      </c>
+      <c r="C134" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D134" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H134" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalInvincible</t>
+        </is>
+      </c>
+      <c r="K134" s="0" t="inlineStr">
+        <is>
+          <t>#FFD700</t>
+        </is>
+      </c>
+      <c r="M134" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="N134" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" s="0" t="n">
+        <v>13000900001</v>
+      </c>
+      <c r="X134" s="0" t="n">
+        <v>13000900001</v>
+      </c>
+      <c r="Y134" s="0" t="inlineStr">
+        <is>
+          <t>上场后无敌{Value}秒，期间身体变为金色</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -3586,7 +3586,7 @@
         </is>
       </c>
       <c r="M41" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N41" s="0" t="n">
         <v>0</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="M42" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N42" s="0" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="M43" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N43" s="0" t="n">
         <v>0</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="M44" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N44" s="0" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="M45" s="0" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N45" s="0" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力50%,同目标1秒冷却</t>
+          <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y134"/>
+  <dimension ref="A1:Y136"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -7817,27 +7817,34 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="C121" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D121" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H121" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
-        </is>
-      </c>
-      <c r="M121" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="N121" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S121" s="0" t="n">
-        <v>3</v>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
+        </is>
+      </c>
+      <c r="I121" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L121" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
+        </is>
+      </c>
+      <c r="M121" t="n">
+        <v>20</v>
+      </c>
+      <c r="N121" t="n">
+        <v>10</v>
       </c>
       <c r="T121" s="0" t="n">
         <v>0</v>
@@ -7846,36 +7853,47 @@
         <v>0</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="X121" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="C122" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D122" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H122" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
         </is>
       </c>
       <c r="I122" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L122" s="0" t="inlineStr">
+        <is>
+          <t>3001:100&amp;</t>
+        </is>
+      </c>
+      <c r="M122" t="n">
+        <v>20</v>
+      </c>
+      <c r="N122" t="n">
+        <v>10</v>
       </c>
       <c r="T122" s="0" t="n">
         <v>0</v>
@@ -7883,24 +7901,21 @@
       <c r="U122" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W122" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="X122" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>13</v>
@@ -7910,20 +7925,18 @@
       </c>
       <c r="H123" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
-        </is>
-      </c>
-      <c r="I123" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J123" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O123" s="0" t="n">
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M123" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N123" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="S123" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="T123" s="0" t="n">
         <v>0</v>
       </c>
@@ -7931,20 +7944,20 @@
         <v>0</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="X123" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>13</v>
@@ -7954,7 +7967,7 @@
       </c>
       <c r="H124" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalDeadRebirth</t>
         </is>
       </c>
       <c r="I124" s="0" t="inlineStr">
@@ -7962,36 +7975,30 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J124" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O124" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P124" s="0" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T124" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U124" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V124" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W124" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="X124" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>死亡后重生</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>13</v>
@@ -8001,7 +8008,7 @@
       </c>
       <c r="H125" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalDeadAttack</t>
         </is>
       </c>
       <c r="I125" s="0" t="inlineStr">
@@ -8010,14 +8017,11 @@
         </is>
       </c>
       <c r="J125" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O125" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="O125" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P125" s="0" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T125" s="0" t="n">
         <v>0</v>
       </c>
@@ -8025,20 +8029,20 @@
         <v>0</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="X125" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>死亡后爆炸</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>13</v>
@@ -8048,7 +8052,7 @@
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadCreateCrystal</t>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
         </is>
       </c>
       <c r="I126" s="0" t="inlineStr">
@@ -8056,8 +8060,14 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q126" s="0" t="n">
-        <v>0.2</v>
+      <c r="J126" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O126" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P126" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="T126" s="0" t="n">
         <v>0</v>
@@ -8066,70 +8076,45 @@
         <v>0</v>
       </c>
       <c r="W126" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="X126" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="B127" s="0" t="inlineStr"/>
+        <v>13000500001</v>
+      </c>
       <c r="C127" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D127" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F127" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H127" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I127" s="0" t="inlineStr"/>
-      <c r="J127" s="0" t="inlineStr">
-        <is>
-          <t>1,300051</t>
-        </is>
-      </c>
-      <c r="K127" s="0" t="inlineStr"/>
-      <c r="L127" s="0" t="inlineStr"/>
-      <c r="M127" s="0" t="n">
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I127" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J127" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N127" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="O127" s="0" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P127" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" s="0" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="T127" s="0" t="n">
         <v>0</v>
@@ -8137,74 +8122,40 @@
       <c r="U127" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W127" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000500001</v>
       </c>
       <c r="X127" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000500001</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>3000500002</v>
-      </c>
-      <c r="B128" s="0" t="inlineStr"/>
+        <v>13000600001</v>
+      </c>
       <c r="C128" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I128" s="0" t="inlineStr"/>
-      <c r="J128" s="0" t="inlineStr">
-        <is>
-          <t>2,300051</t>
-        </is>
-      </c>
-      <c r="K128" s="0" t="inlineStr"/>
-      <c r="L128" s="0" t="inlineStr"/>
-      <c r="M128" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" s="0" t="n">
-        <v>0</v>
+          <t>BuffEntityConditionalDeadCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I128" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
       </c>
       <c r="Q128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="T128" s="0" t="n">
         <v>0</v>
@@ -8212,24 +8163,21 @@
       <c r="U128" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W128" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="X128" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000500003</v>
+        <v>3000500001</v>
       </c>
       <c r="B129" s="0" t="inlineStr"/>
       <c r="C129" s="0" t="n">
@@ -8255,7 +8203,7 @@
       <c r="I129" s="0" t="inlineStr"/>
       <c r="J129" s="0" t="inlineStr">
         <is>
-          <t>3,300051</t>
+          <t>1,300051</t>
         </is>
       </c>
       <c r="K129" s="0" t="inlineStr"/>
@@ -8298,13 +8246,13 @@
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000500004</v>
+        <v>3000500002</v>
       </c>
       <c r="B130" s="0" t="inlineStr"/>
       <c r="C130" s="0" t="n">
@@ -8330,7 +8278,7 @@
       <c r="I130" s="0" t="inlineStr"/>
       <c r="J130" s="0" t="inlineStr">
         <is>
-          <t>4,300051</t>
+          <t>2,300051</t>
         </is>
       </c>
       <c r="K130" s="0" t="inlineStr"/>
@@ -8373,13 +8321,13 @@
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000500005</v>
+        <v>3000500003</v>
       </c>
       <c r="B131" s="0" t="inlineStr"/>
       <c r="C131" s="0" t="n">
@@ -8405,7 +8353,7 @@
       <c r="I131" s="0" t="inlineStr"/>
       <c r="J131" s="0" t="inlineStr">
         <is>
-          <t>5,300051</t>
+          <t>3,300051</t>
         </is>
       </c>
       <c r="K131" s="0" t="inlineStr"/>
@@ -8448,95 +8396,163 @@
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>13000700001</v>
-      </c>
+        <v>3000500004</v>
+      </c>
+      <c r="B132" s="0" t="inlineStr"/>
       <c r="C132" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D132" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H132" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalThorns</t>
-        </is>
-      </c>
-      <c r="I132" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I132" s="0" t="inlineStr"/>
+      <c r="J132" s="0" t="inlineStr">
+        <is>
+          <t>4,300051</t>
+        </is>
+      </c>
+      <c r="K132" s="0" t="inlineStr"/>
+      <c r="L132" s="0" t="inlineStr"/>
+      <c r="M132" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O132" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P132" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T132" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W132" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="X132" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>13000800001</v>
-      </c>
+        <v>3000500005</v>
+      </c>
+      <c r="B133" s="0" t="inlineStr"/>
       <c r="C133" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D133" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H133" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalLifeSteal</t>
-        </is>
-      </c>
-      <c r="I133" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I133" s="0" t="inlineStr"/>
+      <c r="J133" s="0" t="inlineStr">
+        <is>
+          <t>5,300051</t>
+        </is>
+      </c>
+      <c r="K133" s="0" t="inlineStr"/>
+      <c r="L133" s="0" t="inlineStr"/>
+      <c r="M133" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O133" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P133" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T133" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W133" s="0" t="n">
-        <v>13000800001</v>
+        <v>3000500001</v>
       </c>
       <c r="X133" s="0" t="n">
-        <v>13000800001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>造成伤害的{Percentage}%转化为自身生命</t>
+          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000700001</v>
       </c>
       <c r="C134" s="0" t="n">
         <v>13</v>
@@ -8546,30 +8562,112 @@
       </c>
       <c r="H134" s="0" t="inlineStr">
         <is>
+          <t>BuffEntityConditionalThorns</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O134" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P134" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="X134" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="Y134" s="0" t="inlineStr">
+        <is>
+          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="C135" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D135" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H135" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalLifeSteal</t>
+        </is>
+      </c>
+      <c r="I135" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O135" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P135" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="X135" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="Y135" s="0" t="inlineStr">
+        <is>
+          <t>造成伤害的{Percentage}%转化为自身生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0" t="n">
+        <v>13000900001</v>
+      </c>
+      <c r="C136" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D136" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H136" s="0" t="inlineStr">
+        <is>
           <t>BuffEntityConditionalInvincible</t>
         </is>
       </c>
-      <c r="K134" s="0" t="inlineStr">
+      <c r="K136" s="0" t="inlineStr">
         <is>
           <t>#FFD700</t>
         </is>
       </c>
-      <c r="M134" s="0" t="n">
+      <c r="M136" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="N134" s="0" t="n">
+      <c r="N136" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" s="0" t="n">
+      <c r="T136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" s="0" t="n">
         <v>13000900001</v>
       </c>
-      <c r="X134" s="0" t="n">
+      <c r="X136" s="0" t="n">
         <v>13000900001</v>
       </c>
-      <c r="Y134" s="0" t="inlineStr">
+      <c r="Y136" s="0" t="inlineStr">
         <is>
           <t>上场后无敌{Value}秒，期间身体变为金色</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1747,7 +1747,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityBaseHPChangeByApplierATK</t>
         </is>
       </c>
       <c r="I8" s="4" t="n"/>
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="O8" s="1" t="n">
-        <v>-0.05</v>
+        <v>-0.5</v>
       </c>
       <c r="R8" s="1" t="n">
         <v>3</v>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Y8" s="1" t="inlineStr">
         <is>
-          <t>烧伤-每隔3秒扣除血量</t>
+          <t>烧伤-每隔3秒造成施加者攻击力50%伤害</t>
         </is>
       </c>
     </row>
@@ -7840,10 +7840,10 @@
           <t>2001:1&amp;</t>
         </is>
       </c>
-      <c r="M121" t="n">
+      <c r="M121" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="N121" t="n">
+      <c r="N121" s="0" t="n">
         <v>10</v>
       </c>
       <c r="T121" s="0" t="n">
@@ -7889,10 +7889,10 @@
           <t>3001:100&amp;</t>
         </is>
       </c>
-      <c r="M122" t="n">
+      <c r="M122" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="N122" t="n">
+      <c r="N122" s="0" t="n">
         <v>10</v>
       </c>
       <c r="T122" s="0" t="n">

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="O5" s="1" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="R5" s="1" t="n">
         <v>1</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityBaseHPChangeByApplierATK</t>
         </is>
       </c>
       <c r="I7" s="4" t="n"/>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="O7" s="1" t="n">
-        <v>-0.01</v>
+        <v>-0.2</v>
       </c>
       <c r="R7" s="1" t="n">
         <v>10</v>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y136"/>
+  <dimension ref="A1:Y138"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -1598,39 +1598,38 @@
       </c>
     </row>
     <row r="5" customFormat="1" s="1">
-      <c r="A5" s="1" t="n">
-        <v>1000200001</v>
-      </c>
-      <c r="C5" s="1" t="n">
+      <c r="A5" s="0" t="n">
+        <v>1000100002</v>
+      </c>
+      <c r="C5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I5" s="1" t="n"/>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>MSPD</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>#79FF6E</t>
-        </is>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="R5" s="1" t="n">
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>#54A8C8</t>
+        </is>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="R5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="S5" s="1" t="n">
-        <v>1</v>
+      <c r="S5" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="T5" s="0" t="n">
         <v>0</v>
@@ -1638,21 +1637,21 @@
       <c r="U5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="W5" s="1" t="n">
-        <v>1000200001</v>
-      </c>
-      <c r="X5" s="1" t="n">
-        <v>1000200001</v>
-      </c>
-      <c r="Y5" s="1" t="inlineStr">
-        <is>
-          <t>减速-粘液</t>
+      <c r="W5" s="0" t="n">
+        <v>1000100002</v>
+      </c>
+      <c r="X5" s="0" t="n">
+        <v>1000100002</v>
+      </c>
+      <c r="Y5" s="0" t="inlineStr">
+        <is>
+          <t>减速-冰（移速-20%）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="14.25" customFormat="1" customHeight="1" s="1">
       <c r="A6" s="1" t="n">
-        <v>1000300001</v>
+        <v>1000200001</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>1</v>
@@ -1660,15 +1659,31 @@
       <c r="D6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>BuffEntityBaseHPChange</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n"/>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="n"/>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>MSPD</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>#79FF6E</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>-0.4</v>
+      </c>
       <c r="R6" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="S6" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="T6" s="0" t="n">
         <v>0</v>
       </c>
@@ -1676,20 +1691,20 @@
         <v>0</v>
       </c>
       <c r="W6" s="1" t="n">
-        <v>1000300001</v>
+        <v>1000200001</v>
       </c>
       <c r="X6" s="1" t="n">
-        <v>1000300001</v>
+        <v>1000200001</v>
       </c>
       <c r="Y6" s="1" t="inlineStr">
         <is>
-          <t>流血</t>
+          <t>减速-粘液</t>
         </is>
       </c>
     </row>
     <row r="7" ht="14.25" customFormat="1" customHeight="1" s="1">
       <c r="A7" s="1" t="n">
-        <v>1000400001</v>
+        <v>1000300001</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>1</v>
@@ -1699,22 +1714,11 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChangeByApplierATK</t>
+          <t>BuffEntityBaseHPChange</t>
         </is>
       </c>
       <c r="I7" s="4" t="n"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>#5863D6</t>
-        </is>
-      </c>
-      <c r="O7" s="1" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="R7" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="S7" s="1" t="n">
         <v>1</v>
       </c>
       <c r="T7" s="0" t="n">
@@ -1724,20 +1728,20 @@
         <v>0</v>
       </c>
       <c r="W7" s="1" t="n">
-        <v>1000400001</v>
+        <v>1000300001</v>
       </c>
       <c r="X7" s="1" t="n">
-        <v>1000400001</v>
+        <v>1000300001</v>
       </c>
       <c r="Y7" s="1" t="inlineStr">
         <is>
-          <t>中毒</t>
+          <t>流血</t>
         </is>
       </c>
     </row>
     <row r="8" ht="14.25" customFormat="1" customHeight="1" s="1">
       <c r="A8" s="1" t="n">
-        <v>1000500001</v>
+        <v>1000400001</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>1</v>
@@ -1753,17 +1757,17 @@
       <c r="I8" s="4" t="n"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>#A92F2C</t>
+          <t>#5863D6</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="R8" s="1" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S8" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T8" s="0" t="n">
         <v>0</v>
@@ -1772,20 +1776,20 @@
         <v>0</v>
       </c>
       <c r="W8" s="1" t="n">
-        <v>1000500001</v>
+        <v>1000400001</v>
       </c>
       <c r="X8" s="1" t="n">
-        <v>1000500001</v>
+        <v>1000400001</v>
       </c>
       <c r="Y8" s="1" t="inlineStr">
         <is>
-          <t>烧伤-每隔3秒造成施加者攻击力50%伤害</t>
+          <t>中毒</t>
         </is>
       </c>
     </row>
     <row r="9" ht="14.25" customFormat="1" customHeight="1" s="1">
       <c r="A9" s="1" t="n">
-        <v>1000600001</v>
+        <v>1000500001</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>1</v>
@@ -1793,205 +1797,190 @@
       <c r="D9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="1" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>BuffEntityBaseHPChangeByApplierATK</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>#A92F2C</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1" t="n">
+        <v>1000500001</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>1000500001</v>
+      </c>
+      <c r="Y9" s="1" t="inlineStr">
+        <is>
+          <t>烧伤-每隔3秒造成施加者攻击力50%伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customFormat="1" customHeight="1" s="1">
+      <c r="A10" s="0" t="n">
+        <v>1000500002</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityBaseHPChangeByApplierATK</t>
+        </is>
+      </c>
+      <c r="K10" s="0" t="inlineStr">
+        <is>
+          <t>#A92F2C</t>
+        </is>
+      </c>
+      <c r="O10" s="0" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="R10" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="0" t="n">
+        <v>1000500002</v>
+      </c>
+      <c r="X10" s="0" t="n">
+        <v>1000500002</v>
+      </c>
+      <c r="Y10" s="0" t="inlineStr">
+        <is>
+          <t>烧伤-每隔3秒造成施加者攻击力20%伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>1000600001</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>BuffEntityAttribute</t>
         </is>
       </c>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="K9" s="1" t="inlineStr">
+      <c r="K11" s="1" t="inlineStr">
         <is>
           <t>#00BEDB</t>
         </is>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="O11" s="1" t="n">
         <v>-0.2</v>
       </c>
-      <c r="S9" s="1" t="n">
+      <c r="S11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="T9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="1" t="n">
+      <c r="T11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1" t="n">
         <v>1000600001</v>
       </c>
-      <c r="X9" s="1" t="n">
+      <c r="X11" s="1" t="n">
         <v>1000600001</v>
       </c>
-      <c r="Y9" s="1" t="inlineStr">
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>潮湿-减少攻击力</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="14.25" customFormat="1" customHeight="1" s="1">
-      <c r="A10" s="1" t="n">
+    <row r="12">
+      <c r="A12" s="1" t="n">
         <v>1000700001</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D12" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="1" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>BuffEntityAttributeAttackTime</t>
         </is>
       </c>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="1" t="n"/>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="inlineStr">
         <is>
           <t>#DDFFFF</t>
         </is>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="O12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="S10" s="1" t="n">
+      <c r="S12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="T10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="1" t="n">
+      <c r="T12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1" t="n">
         <v>1000700001</v>
       </c>
-      <c r="X10" s="1" t="n">
+      <c r="X12" s="1" t="n">
         <v>1000700001</v>
       </c>
-      <c r="Y10" s="1" t="inlineStr">
+      <c r="Y12" s="1" t="inlineStr">
         <is>
           <t>冰冻-减速</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>2000100001</v>
-      </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>EVA</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="n"/>
-      <c r="W11" s="2" t="n">
-        <v>2000100001</v>
-      </c>
-      <c r="X11" s="2" t="n">
-        <v>2000100001</v>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>闪避50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>2000200001</v>
-      </c>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>CRT</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2" t="n"/>
-      <c r="T12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="n"/>
-      <c r="W12" s="2" t="n">
-        <v>2000200001</v>
-      </c>
-      <c r="X12" s="2" t="n">
-        <v>2000200001</v>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>暴击50%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="14.25" customHeight="1" s="3">
       <c r="A13" s="2" t="n">
-        <v>2000300001</v>
+        <v>2000100001</v>
       </c>
       <c r="B13" s="2" t="n"/>
       <c r="C13" s="2" t="n">
@@ -2003,23 +1992,19 @@
       <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>EVA</t>
         </is>
       </c>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="6" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
-        </is>
-      </c>
+      <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
       <c r="N13" s="2" t="n"/>
       <c r="O13" s="2" t="n">
@@ -2037,20 +2022,20 @@
       </c>
       <c r="V13" s="2" t="n"/>
       <c r="W13" s="2" t="n">
-        <v>2000300001</v>
+        <v>2000100001</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>2000300001</v>
+        <v>2000100001</v>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>血量低于50% 攻击力提升</t>
+          <t>闪避50%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="14.25" customHeight="1" s="3">
       <c r="A14" s="2" t="n">
-        <v>2000400001</v>
+        <v>2000200001</v>
       </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n">
@@ -2062,27 +2047,23 @@
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>CRT</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
-      <c r="L14" s="6" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
-        </is>
-      </c>
+      <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
       <c r="O14" s="2" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
@@ -2096,101 +2077,138 @@
       </c>
       <c r="V14" s="2" t="n"/>
       <c r="W14" s="2" t="n">
+        <v>2000200001</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>2000200001</v>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>暴击50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>2000300001</v>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="n"/>
+      <c r="W15" s="2" t="n">
+        <v>2000300001</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>2000300001</v>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>血量低于50% 攻击力提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
         <v>2000400001</v>
       </c>
-      <c r="X14" s="2" t="n">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="n"/>
+      <c r="W16" s="2" t="n">
         <v>2000400001</v>
       </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="X16" s="2" t="n">
+        <v>2000400001</v>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>血量低于50% 攻击速度提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="n">
-        <v>3000100001</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantCloneDefenseCreature</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="n"/>
-      <c r="T15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="0" t="n">
-        <v>3000100001</v>
-      </c>
-      <c r="X15" s="0" t="n">
-        <v>3000100001</v>
-      </c>
-      <c r="Y15" s="0" t="inlineStr">
-        <is>
-          <t>增殖-随机复制一个已有的魔物</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="F16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAddDropCrystal</t>
-        </is>
-      </c>
-      <c r="I16" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadDropCrystal</t>
-        </is>
-      </c>
-      <c r="Q16" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="X16" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="Y16" s="0" t="inlineStr">
-        <is>
-          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="n">
-        <v>3000200002</v>
+        <v>3000100001</v>
       </c>
       <c r="C17" s="0" t="n">
         <v>3</v>
@@ -2198,25 +2216,12 @@
       <c r="D17" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="0" t="n">
-        <v>3000200002</v>
-      </c>
-      <c r="F17" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAddDropCrystal</t>
-        </is>
-      </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadDropCrystal</t>
-        </is>
-      </c>
-      <c r="Q17" s="0" t="n">
-        <v>0.4</v>
-      </c>
+          <t>BuffEntityInstantCloneDefenseCreature</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n"/>
       <c r="T17" s="0" t="n">
         <v>0</v>
       </c>
@@ -2224,20 +2229,20 @@
         <v>0</v>
       </c>
       <c r="W17" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="X17" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="Y17" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
+          <t>增殖-随机复制一个已有的魔物</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200001</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>3</v>
@@ -2246,10 +2251,10 @@
         <v>1</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200001</v>
       </c>
       <c r="F18" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
@@ -2262,7 +2267,7 @@
         </is>
       </c>
       <c r="Q18" s="0" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="T18" s="0" t="n">
         <v>0</v>
@@ -2278,13 +2283,13 @@
       </c>
       <c r="Y18" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
+          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>3000200004</v>
+        <v>3000200002</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>3</v>
@@ -2293,10 +2298,10 @@
         <v>1</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200002</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -2309,7 +2314,7 @@
         </is>
       </c>
       <c r="Q19" s="0" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="T19" s="0" t="n">
         <v>0</v>
@@ -2325,13 +2330,13 @@
       </c>
       <c r="Y19" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
+          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>3000200005</v>
+        <v>3000200003</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>3</v>
@@ -2343,7 +2348,7 @@
         <v>3000200003</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -2356,7 +2361,7 @@
         </is>
       </c>
       <c r="Q20" s="0" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="T20" s="0" t="n">
         <v>0</v>
@@ -2372,107 +2377,107 @@
       </c>
       <c r="Y20" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
+          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200004</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackMultiInstant</t>
-        </is>
-      </c>
-      <c r="J21" s="0" t="inlineStr">
-        <is>
-          <t>1,300031</t>
-        </is>
-      </c>
-      <c r="M21" s="0" t="n">
+      <c r="D21" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E21" s="0" t="n">
+        <v>3000200003</v>
+      </c>
+      <c r="F21" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAddDropCrystal</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadDropCrystal</t>
+        </is>
+      </c>
       <c r="Q21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="0" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="T21" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U21" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W21" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="X21" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="Y21" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
+          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="3">
       <c r="A22" s="0" t="n">
-        <v>3000300002</v>
+        <v>3000200005</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackMultiInstant</t>
-        </is>
-      </c>
-      <c r="J22" s="0" t="inlineStr">
-        <is>
-          <t>2,300032</t>
-        </is>
-      </c>
-      <c r="M22" s="0" t="n">
+      <c r="D22" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E22" s="0" t="n">
+        <v>3000200003</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAddDropCrystal</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadDropCrystal</t>
+        </is>
+      </c>
       <c r="Q22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T22" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U22" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W22" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="X22" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="Y22" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
+          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>3000300003</v>
+        <v>3000300001</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>3</v>
@@ -2487,7 +2492,7 @@
       </c>
       <c r="J23" s="0" t="inlineStr">
         <is>
-          <t>3,300033</t>
+          <t>1,300031</t>
         </is>
       </c>
       <c r="M23" s="0" t="n">
@@ -2513,13 +2518,13 @@
       </c>
       <c r="Y23" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="3">
       <c r="A24" s="0" t="n">
-        <v>3000300004</v>
+        <v>3000300002</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>3</v>
@@ -2534,7 +2539,7 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>4,300034</t>
+          <t>2,300032</t>
         </is>
       </c>
       <c r="M24" s="0" t="n">
@@ -2560,13 +2565,13 @@
       </c>
       <c r="Y24" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="0" t="n">
-        <v>3000300005</v>
+        <v>3000300003</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>3</v>
@@ -2581,7 +2586,7 @@
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>5,300035</t>
+          <t>3,300033</t>
         </is>
       </c>
       <c r="M25" s="0" t="n">
@@ -2607,13 +2612,13 @@
       </c>
       <c r="Y25" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300004</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>3</v>
@@ -2623,12 +2628,12 @@
       </c>
       <c r="H26" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRoad</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>1,300041</t>
+          <t>4,300034</t>
         </is>
       </c>
       <c r="M26" s="0" t="n">
@@ -2641,26 +2646,26 @@
         <v>0</v>
       </c>
       <c r="S26" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T26" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W26" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="X26" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="Y26" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="0" t="n">
-        <v>3000400002</v>
+        <v>3000300005</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>3</v>
@@ -2670,12 +2675,12 @@
       </c>
       <c r="H27" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRoad</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>2,300041</t>
+          <t>5,300035</t>
         </is>
       </c>
       <c r="M27" s="0" t="n">
@@ -2688,26 +2693,26 @@
         <v>0</v>
       </c>
       <c r="S27" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W27" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="X27" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="Y27" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
       <c r="A28" s="0" t="n">
-        <v>3000400003</v>
+        <v>3000400001</v>
       </c>
       <c r="C28" s="0" t="n">
         <v>3</v>
@@ -2722,7 +2727,7 @@
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>3,300041</t>
+          <t>1,300041</t>
         </is>
       </c>
       <c r="M28" s="0" t="n">
@@ -2748,13 +2753,13 @@
       </c>
       <c r="Y28" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000400004</v>
+        <v>3000400002</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>3</v>
@@ -2769,7 +2774,7 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>4,300041</t>
+          <t>2,300041</t>
         </is>
       </c>
       <c r="M29" s="0" t="n">
@@ -2795,13 +2800,13 @@
       </c>
       <c r="Y29" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000400005</v>
+        <v>3000400003</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>3</v>
@@ -2816,7 +2821,7 @@
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>5,300041</t>
+          <t>3,300041</t>
         </is>
       </c>
       <c r="M30" s="0" t="n">
@@ -2842,51 +2847,33 @@
       </c>
       <c r="Y30" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="1" s="2">
       <c r="A31" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400004</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>3</v>
-      </c>
-      <c r="D31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="G31" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H31" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBounceAxe</t>
+          <t>BuffEntityPeriodicAttackRoad</t>
         </is>
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>1,300061,1</t>
+          <t>4,300041</t>
         </is>
       </c>
       <c r="M31" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="Q31" s="0" t="n">
         <v>0</v>
       </c>
@@ -2899,65 +2886,41 @@
       <c r="T31" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="X31" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
+          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="2">
       <c r="A32" s="0" t="n">
-        <v>3000600002</v>
+        <v>3000400005</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>3</v>
-      </c>
-      <c r="D32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="G32" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H32" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBounceAxe</t>
+          <t>BuffEntityPeriodicAttackRoad</t>
         </is>
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>2,300061,2</t>
+          <t>5,300041</t>
         </is>
       </c>
       <c r="M32" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="Q32" s="0" t="n">
         <v>0</v>
       </c>
@@ -2970,27 +2933,21 @@
       <c r="T32" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="X32" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
+          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="2">
       <c r="A33" s="0" t="n">
-        <v>3000600003</v>
+        <v>3000600001</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>3</v>
@@ -3014,7 +2971,7 @@
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>3,300061,3</t>
+          <t>1,300061,1</t>
         </is>
       </c>
       <c r="M33" s="0" t="n">
@@ -3055,13 +3012,13 @@
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" s="3">
       <c r="A34" s="0" t="n">
-        <v>3000600004</v>
+        <v>3000600002</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>3</v>
@@ -3085,7 +3042,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>4,300061,4</t>
+          <t>2,300061,2</t>
         </is>
       </c>
       <c r="M34" s="0" t="n">
@@ -3126,13 +3083,13 @@
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="3">
       <c r="A35" s="0" t="n">
-        <v>3000600005</v>
+        <v>3000600003</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>3</v>
@@ -3156,7 +3113,7 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>5,300061,5</t>
+          <t>3,300061,3</t>
         </is>
       </c>
       <c r="M35" s="0" t="n">
@@ -3197,13 +3154,13 @@
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
       <c r="A36" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600004</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>3</v>
@@ -3222,16 +3179,16 @@
       </c>
       <c r="H36" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackOrbit</t>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
         </is>
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>1,300071,0.6</t>
+          <t>4,300061,4</t>
         </is>
       </c>
       <c r="M36" s="0" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N36" s="0" t="n">
         <v>0</v>
@@ -3249,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="0" t="n">
-        <v>9999</v>
+        <v>5</v>
       </c>
       <c r="T36" s="0" t="n">
         <v>0</v>
@@ -3261,20 +3218,20 @@
         <v>0</v>
       </c>
       <c r="W36" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="X36" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
       <c r="A37" s="0" t="n">
-        <v>3000700002</v>
+        <v>3000600005</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>3</v>
@@ -3293,16 +3250,16 @@
       </c>
       <c r="H37" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackOrbit</t>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
         </is>
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>2,300071,1.2</t>
+          <t>5,300061,5</t>
         </is>
       </c>
       <c r="M37" s="0" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N37" s="0" t="n">
         <v>0</v>
@@ -3320,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="0" t="n">
-        <v>9999</v>
+        <v>5</v>
       </c>
       <c r="T37" s="0" t="n">
         <v>0</v>
@@ -3332,20 +3289,20 @@
         <v>0</v>
       </c>
       <c r="W37" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="X37" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
       <c r="A38" s="0" t="n">
-        <v>3000700003</v>
+        <v>3000700001</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>3</v>
@@ -3369,7 +3326,7 @@
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>3,300071,1.8</t>
+          <t>1,300071,0.6</t>
         </is>
       </c>
       <c r="M38" s="0" t="n">
@@ -3410,13 +3367,13 @@
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
       <c r="A39" s="0" t="n">
-        <v>3000700004</v>
+        <v>3000700002</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>3</v>
@@ -3440,7 +3397,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>4,300071,2.4</t>
+          <t>2,300071,1.2</t>
         </is>
       </c>
       <c r="M39" s="0" t="n">
@@ -3481,13 +3438,13 @@
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
       <c r="A40" s="0" t="n">
-        <v>3000700005</v>
+        <v>3000700003</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>3</v>
@@ -3511,7 +3468,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>5,300071,3</t>
+          <t>3,300071,1.8</t>
         </is>
       </c>
       <c r="M40" s="0" t="n">
@@ -3552,13 +3509,13 @@
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
       <c r="A41" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700004</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>3</v>
@@ -3577,16 +3534,16 @@
       </c>
       <c r="H41" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRebound</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>1,300081</t>
+          <t>4,300071,2.4</t>
         </is>
       </c>
       <c r="M41" s="0" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N41" s="0" t="n">
         <v>0</v>
@@ -3604,7 +3561,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="0" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="T41" s="0" t="n">
         <v>0</v>
@@ -3616,20 +3573,20 @@
         <v>0</v>
       </c>
       <c r="W41" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="X41" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
       <c r="A42" s="0" t="n">
-        <v>3000800002</v>
+        <v>3000700005</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>3</v>
@@ -3648,16 +3605,16 @@
       </c>
       <c r="H42" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRebound</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>2,300082</t>
+          <t>5,300071,3</t>
         </is>
       </c>
       <c r="M42" s="0" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N42" s="0" t="n">
         <v>0</v>
@@ -3675,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="0" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="T42" s="0" t="n">
         <v>0</v>
@@ -3687,20 +3644,20 @@
         <v>0</v>
       </c>
       <c r="W42" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="X42" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
       <c r="A43" s="0" t="n">
-        <v>3000800003</v>
+        <v>3000800001</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3724,7 +3681,7 @@
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>3,300083</t>
+          <t>1,300081</t>
         </is>
       </c>
       <c r="M43" s="0" t="n">
@@ -3765,13 +3722,13 @@
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
       <c r="A44" s="0" t="n">
-        <v>3000800004</v>
+        <v>3000800002</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>3</v>
@@ -3795,7 +3752,7 @@
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>4,300084</t>
+          <t>2,300082</t>
         </is>
       </c>
       <c r="M44" s="0" t="n">
@@ -3836,13 +3793,13 @@
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
       <c r="A45" s="0" t="n">
-        <v>3000800005</v>
+        <v>3000800003</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>3</v>
@@ -3866,7 +3823,7 @@
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>5,300085</t>
+          <t>3,300083</t>
         </is>
       </c>
       <c r="M45" s="0" t="n">
@@ -3907,229 +3864,229 @@
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
+          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="14.25" customHeight="1" s="3">
+      <c r="A46" s="0" t="n">
+        <v>3000800004</v>
+      </c>
+      <c r="C46" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRebound</t>
+        </is>
+      </c>
+      <c r="J46" s="0" t="inlineStr">
+        <is>
+          <t>4,300084</t>
+        </is>
+      </c>
+      <c r="M46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="X46" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y46" s="0" t="inlineStr">
+        <is>
+          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="14.25" customHeight="1" s="3">
+      <c r="A47" s="0" t="n">
+        <v>3000800005</v>
+      </c>
+      <c r="C47" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRebound</t>
+        </is>
+      </c>
+      <c r="J47" s="0" t="inlineStr">
+        <is>
+          <t>5,300085</t>
+        </is>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="X47" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y47" s="0" t="inlineStr">
+        <is>
           <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="14.25" customHeight="1" s="3">
-      <c r="A46" s="2" t="n">
+    <row r="48" ht="14.25" customHeight="1" s="3">
+      <c r="A48" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D46" s="2" t="n">
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>BuffEntityInstantRewardMoreItem</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
-      <c r="T46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="2" t="n">
+      <c r="I48" s="2" t="n"/>
+      <c r="J48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n"/>
+      <c r="T48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="X46" s="2" t="n">
+      <c r="X48" s="2" t="n">
         <v>3000900001</v>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
+      <c r="Y48" s="2" t="inlineStr">
         <is>
           <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="14.25" customHeight="1" s="3">
-      <c r="A47" s="2" t="n">
+    <row r="49" ht="15" customHeight="1" s="3">
+      <c r="A49" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D47" s="2" t="n">
+      <c r="C49" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>BuffEntityInstantRewardMoreSelect</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n"/>
-      <c r="T47" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" s="2" t="n">
+      <c r="I49" s="2" t="n"/>
+      <c r="J49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
+      <c r="T49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="X47" s="2" t="n">
+      <c r="X49" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="Y47" s="2" t="inlineStr">
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>再来一瓶-通关奖励可选次数+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1" s="3">
-      <c r="A48" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="C48" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackShockwave</t>
-        </is>
-      </c>
-      <c r="J48" s="0" t="inlineStr">
-        <is>
-          <t>300091</t>
-        </is>
-      </c>
-      <c r="M48" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="X48" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="Y48" s="0" t="inlineStr">
-        <is>
-          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="3">
-      <c r="A49" s="0" t="n">
-        <v>3001100004</v>
-      </c>
-      <c r="C49" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H49" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackShockwave</t>
-        </is>
-      </c>
-      <c r="J49" s="0" t="inlineStr">
-        <is>
-          <t>300091</t>
-        </is>
-      </c>
-      <c r="M49" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="0" t="n">
-        <v>3001100004</v>
-      </c>
-      <c r="X49" s="0" t="n">
-        <v>3001100004</v>
-      </c>
-      <c r="Y49" s="0" t="inlineStr">
-        <is>
-          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14.25" customHeight="1" s="3">
       <c r="A50" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100005</v>
       </c>
       <c r="C50" s="0" t="n">
         <v>3</v>
@@ -4157,7 +4114,7 @@
         </is>
       </c>
       <c r="M50" s="0" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N50" s="0" t="n">
         <v>0</v>
@@ -4187,20 +4144,20 @@
         <v>0</v>
       </c>
       <c r="W50" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100005</v>
       </c>
       <c r="X50" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100005</v>
       </c>
       <c r="Y50" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
+          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="3">
       <c r="A51" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100004</v>
       </c>
       <c r="C51" s="0" t="n">
         <v>3</v>
@@ -4228,7 +4185,7 @@
         </is>
       </c>
       <c r="M51" s="0" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="N51" s="0" t="n">
         <v>0</v>
@@ -4258,20 +4215,20 @@
         <v>0</v>
       </c>
       <c r="W51" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100004</v>
       </c>
       <c r="X51" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100004</v>
       </c>
       <c r="Y51" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
+          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="3">
       <c r="A52" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100003</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>3</v>
@@ -4299,7 +4256,7 @@
         </is>
       </c>
       <c r="M52" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N52" s="0" t="n">
         <v>0</v>
@@ -4329,22 +4286,21 @@
         <v>0</v>
       </c>
       <c r="W52" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100003</v>
       </c>
       <c r="X52" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100003</v>
       </c>
       <c r="Y52" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
+          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
       <c r="A53" s="0" t="n">
-        <v>3001200001</v>
-      </c>
-      <c r="B53" s="0" t="inlineStr"/>
+        <v>3001100002</v>
+      </c>
       <c r="C53" s="0" t="n">
         <v>3</v>
       </c>
@@ -4362,19 +4318,16 @@
       </c>
       <c r="H53" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackFireBottle</t>
-        </is>
-      </c>
-      <c r="I53" s="0" t="inlineStr"/>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
       <c r="J53" s="0" t="inlineStr">
         <is>
-          <t>1,300101</t>
-        </is>
-      </c>
-      <c r="K53" s="0" t="inlineStr"/>
-      <c r="L53" s="0" t="inlineStr"/>
+          <t>300091</t>
+        </is>
+      </c>
       <c r="M53" s="0" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N53" s="0" t="n">
         <v>0</v>
@@ -4404,22 +4357,21 @@
         <v>0</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100002</v>
       </c>
       <c r="X53" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100002</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>3001200002</v>
-      </c>
-      <c r="B54" s="0" t="inlineStr"/>
+        <v>3001100001</v>
+      </c>
       <c r="C54" s="0" t="n">
         <v>3</v>
       </c>
@@ -4437,17 +4389,14 @@
       </c>
       <c r="H54" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackFireBottle</t>
-        </is>
-      </c>
-      <c r="I54" s="0" t="inlineStr"/>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
       <c r="J54" s="0" t="inlineStr">
         <is>
-          <t>2,300101</t>
-        </is>
-      </c>
-      <c r="K54" s="0" t="inlineStr"/>
-      <c r="L54" s="0" t="inlineStr"/>
+          <t>300091</t>
+        </is>
+      </c>
       <c r="M54" s="0" t="n">
         <v>0.1</v>
       </c>
@@ -4479,20 +4428,20 @@
         <v>0</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100001</v>
       </c>
       <c r="X54" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100001</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>3001200003</v>
+        <v>3001200001</v>
       </c>
       <c r="B55" s="0" t="inlineStr"/>
       <c r="C55" s="0" t="n">
@@ -4518,7 +4467,7 @@
       <c r="I55" s="0" t="inlineStr"/>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>3,300101</t>
+          <t>1,300101</t>
         </is>
       </c>
       <c r="K55" s="0" t="inlineStr"/>
@@ -4561,13 +4510,13 @@
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>3001200004</v>
+        <v>3001200002</v>
       </c>
       <c r="B56" s="0" t="inlineStr"/>
       <c r="C56" s="0" t="n">
@@ -4593,7 +4542,7 @@
       <c r="I56" s="0" t="inlineStr"/>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>4,300101</t>
+          <t>2,300101</t>
         </is>
       </c>
       <c r="K56" s="0" t="inlineStr"/>
@@ -4636,13 +4585,13 @@
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>3001200005</v>
+        <v>3001200003</v>
       </c>
       <c r="B57" s="0" t="inlineStr"/>
       <c r="C57" s="0" t="n">
@@ -4668,7 +4617,7 @@
       <c r="I57" s="0" t="inlineStr"/>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>5,300101</t>
+          <t>3,300101</t>
         </is>
       </c>
       <c r="K57" s="0" t="inlineStr"/>
@@ -4711,111 +4660,163 @@
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
+          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A58" s="0" t="n">
+        <v>3001200004</v>
+      </c>
+      <c r="B58" s="0" t="inlineStr"/>
+      <c r="C58" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I58" s="0" t="inlineStr"/>
+      <c r="J58" s="0" t="inlineStr">
+        <is>
+          <t>4,300101</t>
+        </is>
+      </c>
+      <c r="K58" s="0" t="inlineStr"/>
+      <c r="L58" s="0" t="inlineStr"/>
+      <c r="M58" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="X58" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="Y58" s="0" t="inlineStr">
+        <is>
+          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A59" s="0" t="n">
+        <v>3001200005</v>
+      </c>
+      <c r="B59" s="0" t="inlineStr"/>
+      <c r="C59" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I59" s="0" t="inlineStr"/>
+      <c r="J59" s="0" t="inlineStr">
+        <is>
+          <t>5,300101</t>
+        </is>
+      </c>
+      <c r="K59" s="0" t="inlineStr"/>
+      <c r="L59" s="0" t="inlineStr"/>
+      <c r="M59" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="X59" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="Y59" s="0" t="inlineStr">
+        <is>
           <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A58" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="X58" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="Y58" s="2" t="inlineStr">
-        <is>
-          <t>生命增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A59" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D59" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="X59" s="2" t="n">
-        <v>11000200001</v>
-      </c>
-      <c r="Y59" s="2" t="inlineStr">
-        <is>
-          <t>护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A60" s="2" t="n">
-        <v>11000300001</v>
+        <v>11000100001</v>
       </c>
       <c r="C60" s="2" t="n">
         <v>11</v>
@@ -4833,129 +4834,139 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J60" s="0" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="X60" s="2" t="n">
+        <v>11000100001</v>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>生命增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="X61" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J62" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O60" s="0" t="n">
+      <c r="O62" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="P60" s="0" t="n">
+      <c r="P62" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q60" s="2" t="n">
+      <c r="Q62" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="T60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" s="2" t="n">
+      <c r="T62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="X60" s="2" t="n">
+      <c r="X62" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="Y62" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="C61" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D61" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H61" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J61" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="O61" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="X61" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="Y61" s="0" t="inlineStr">
-        <is>
-          <t>攻击速度增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="C62" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D62" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J62" s="0" t="inlineStr">
-        <is>
-          <t>RCD</t>
-        </is>
-      </c>
-      <c r="O62" s="0" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P62" s="0" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="T62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="X62" s="0" t="n">
-        <v>11000500001</v>
-      </c>
-      <c r="Y62" s="0" t="inlineStr">
-        <is>
-          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000400001</v>
       </c>
       <c r="C63" s="0" t="n">
         <v>11</v>
@@ -4970,14 +4981,14 @@
       </c>
       <c r="J63" s="0" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="O63" s="0" t="n">
-        <v>-0.25</v>
+        <v>1</v>
       </c>
       <c r="P63" s="0" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="T63" s="0" t="n">
         <v>0</v>
@@ -4986,20 +4997,20 @@
         <v>0</v>
       </c>
       <c r="W63" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000400001</v>
       </c>
       <c r="X63" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000400001</v>
       </c>
       <c r="Y63" s="0" t="inlineStr">
         <is>
-          <t>召唤魔力消耗{Percentage}%</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000500001</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>11</v>
@@ -5007,27 +5018,21 @@
       <c r="D64" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G64" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H64" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|HP:-1</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O64" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P64" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R64" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T64" s="0" t="n">
         <v>0</v>
@@ -5036,20 +5041,20 @@
         <v>0</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000500001</v>
       </c>
       <c r="X64" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>狂战士-A</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000600001</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>11</v>
@@ -5057,27 +5062,21 @@
       <c r="D65" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G65" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H65" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J65" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|DR:-1</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O65" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P65" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R65" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T65" s="0" t="n">
         <v>0</v>
@@ -5086,20 +5085,20 @@
         <v>0</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000600001</v>
       </c>
       <c r="X65" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000600001</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>狂战士-B</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700001</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>11</v>
@@ -5117,7 +5116,7 @@
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|ASPD:-1</t>
+          <t>ATK:1|HP:-1</t>
         </is>
       </c>
       <c r="O66" s="0" t="n">
@@ -5136,20 +5135,20 @@
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700001</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700001</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>狂战士-C</t>
+          <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700002</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>11</v>
@@ -5167,7 +5166,7 @@
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|DR:-1</t>
+          <t>ATK:1|DR:-1</t>
         </is>
       </c>
       <c r="O67" s="0" t="n">
@@ -5186,20 +5185,20 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700002</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700002</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>快枪手-A</t>
+          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000700003</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>11</v>
@@ -5217,7 +5216,7 @@
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|HP:-1</t>
+          <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O68" s="0" t="n">
@@ -5236,20 +5235,20 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000700003</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000700003</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>快枪手-B</t>
+          <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800001</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>11</v>
@@ -5267,7 +5266,7 @@
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|ATK:-1</t>
+          <t>ASPD:1|DR:-1</t>
         </is>
       </c>
       <c r="O69" s="0" t="n">
@@ -5286,20 +5285,20 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800001</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800001</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>快枪手-C</t>
+          <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800002</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>11</v>
@@ -5317,7 +5316,7 @@
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t>DR:1|HP:-1</t>
+          <t>ASPD:1|HP:-1</t>
         </is>
       </c>
       <c r="O70" s="0" t="n">
@@ -5336,20 +5335,20 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800002</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800002</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-A</t>
+          <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000800003</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>11</v>
@@ -5367,7 +5366,7 @@
       </c>
       <c r="J71" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ATK:-1</t>
+          <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
       <c r="O71" s="0" t="n">
@@ -5386,20 +5385,20 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000800003</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000800003</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-B</t>
+          <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900001</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>11</v>
@@ -5417,7 +5416,7 @@
       </c>
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ASPD:-1</t>
+          <t>DR:1|HP:-1</t>
         </is>
       </c>
       <c r="O72" s="0" t="n">
@@ -5436,20 +5435,20 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900001</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900001</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-C</t>
+          <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900002</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>11</v>
@@ -5467,7 +5466,7 @@
       </c>
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ASPD:-1</t>
+          <t>DR:1|ATK:-1</t>
         </is>
       </c>
       <c r="O73" s="0" t="n">
@@ -5486,20 +5485,20 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900002</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900002</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>大块头-A</t>
+          <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000900003</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>11</v>
@@ -5517,7 +5516,7 @@
       </c>
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>HP:1|DR:-1</t>
+          <t>DR:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O74" s="0" t="n">
@@ -5536,20 +5535,20 @@
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000900003</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>11001000002</v>
+        <v>11000900003</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>大块头-B</t>
+          <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000001</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>11</v>
@@ -5567,7 +5566,7 @@
       </c>
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ATK:-1</t>
+          <t>HP:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O75" s="0" t="n">
@@ -5586,20 +5585,20 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000001</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000001</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>大块头-C</t>
+          <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000002</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>11</v>
@@ -5617,7 +5616,7 @@
       </c>
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|RCD:1</t>
+          <t>HP:1|DR:-1</t>
         </is>
       </c>
       <c r="O76" s="0" t="n">
@@ -5636,20 +5635,20 @@
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000002</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000002</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>狂战士-D</t>
+          <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>11000700005</v>
+        <v>11001000003</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>11</v>
@@ -5667,7 +5666,7 @@
       </c>
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|CMP:1</t>
+          <t>HP:1|ATK:-1</t>
         </is>
       </c>
       <c r="O77" s="0" t="n">
@@ -5686,20 +5685,20 @@
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>11000700005</v>
+        <v>11001000003</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>11000700005</v>
+        <v>11001000003</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>狂战士-E</t>
+          <t>大块头-C</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700004</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>11</v>
@@ -5717,7 +5716,7 @@
       </c>
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|RCD:1</t>
+          <t>ATK:1|RCD:1</t>
         </is>
       </c>
       <c r="O78" s="0" t="n">
@@ -5736,20 +5735,20 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700004</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700004</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>快枪手-D</t>
+          <t>狂战士-D</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000700005</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>11</v>
@@ -5767,7 +5766,7 @@
       </c>
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|CMP:1</t>
+          <t>ATK:1|CMP:1</t>
         </is>
       </c>
       <c r="O79" s="0" t="n">
@@ -5786,20 +5785,20 @@
         <v>0</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000700005</v>
       </c>
       <c r="X79" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000700005</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>快枪手-E</t>
+          <t>狂战士-E</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800004</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>11</v>
@@ -5817,7 +5816,7 @@
       </c>
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>DR:1|RCD:1</t>
+          <t>ASPD:1|RCD:1</t>
         </is>
       </c>
       <c r="O80" s="0" t="n">
@@ -5836,20 +5835,20 @@
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800004</v>
       </c>
       <c r="X80" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800004</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-D</t>
+          <t>快枪手-D</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000800005</v>
       </c>
       <c r="C81" s="0" t="n">
         <v>11</v>
@@ -5867,7 +5866,7 @@
       </c>
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>DR:1|CMP:1</t>
+          <t>ASPD:1|CMP:1</t>
         </is>
       </c>
       <c r="O81" s="0" t="n">
@@ -5886,20 +5885,20 @@
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000800005</v>
       </c>
       <c r="X81" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000800005</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-E</t>
+          <t>快枪手-E</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900004</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>11</v>
@@ -5917,7 +5916,7 @@
       </c>
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>HP:1|RCD:1</t>
+          <t>DR:1|RCD:1</t>
         </is>
       </c>
       <c r="O82" s="0" t="n">
@@ -5936,20 +5935,20 @@
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900004</v>
       </c>
       <c r="X82" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900004</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>大块头-D</t>
+          <t>铜墙铁壁-D</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>11001000005</v>
+        <v>11000900005</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>11</v>
@@ -5967,7 +5966,7 @@
       </c>
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>HP:1|CMP:1</t>
+          <t>DR:1|CMP:1</t>
         </is>
       </c>
       <c r="O83" s="0" t="n">
@@ -5986,20 +5985,20 @@
         <v>0</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>11001000005</v>
+        <v>11000900005</v>
       </c>
       <c r="X83" s="0" t="n">
-        <v>11001000005</v>
+        <v>11000900005</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>大块头-E</t>
+          <t>铜墙铁壁-E</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000004</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>11</v>
@@ -6017,14 +6016,14 @@
       </c>
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|HP:-0.5</t>
+          <t>HP:1|RCD:1</t>
         </is>
       </c>
       <c r="O84" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="P84" s="0" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R84" s="0" t="n">
         <v>0</v>
@@ -6036,20 +6035,20 @@
         <v>0</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000004</v>
       </c>
       <c r="X84" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000004</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-A</t>
+          <t>大块头-D</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001000005</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>11</v>
@@ -6067,14 +6066,14 @@
       </c>
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|DR:-0.5</t>
+          <t>HP:1|CMP:1</t>
         </is>
       </c>
       <c r="O85" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="P85" s="0" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R85" s="0" t="n">
         <v>0</v>
@@ -6086,20 +6085,20 @@
         <v>0</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001000005</v>
       </c>
       <c r="X85" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001000005</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-B</t>
+          <t>大块头-E</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100001</v>
       </c>
       <c r="C86" s="0" t="n">
         <v>11</v>
@@ -6117,7 +6116,7 @@
       </c>
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ATK:-0.5</t>
+          <t>RCD:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O86" s="0" t="n">
@@ -6136,20 +6135,20 @@
         <v>0</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100001</v>
       </c>
       <c r="X86" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100001</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-C</t>
+          <t>魂牵梦绕-A</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100002</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>11</v>
@@ -6167,7 +6166,7 @@
       </c>
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ASPD:-0.5</t>
+          <t>RCD:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O87" s="0" t="n">
@@ -6186,20 +6185,20 @@
         <v>0</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100002</v>
       </c>
       <c r="X87" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100002</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-D</t>
+          <t>魂牵梦绕-B</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100003</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>11</v>
@@ -6217,7 +6216,7 @@
       </c>
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|CMP:0.5</t>
+          <t>RCD:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O88" s="0" t="n">
@@ -6236,20 +6235,20 @@
         <v>0</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100003</v>
       </c>
       <c r="X88" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100003</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-E</t>
+          <t>魂牵梦绕-C</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100004</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>11</v>
@@ -6267,7 +6266,7 @@
       </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|HP:-0.5</t>
+          <t>RCD:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O89" s="0" t="n">
@@ -6286,20 +6285,20 @@
         <v>0</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100004</v>
       </c>
       <c r="X89" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100004</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>折上折-A</t>
+          <t>魂牵梦绕-D</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001100005</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>11</v>
@@ -6317,7 +6316,7 @@
       </c>
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|DR:-0.5</t>
+          <t>RCD:-1|CMP:0.5</t>
         </is>
       </c>
       <c r="O90" s="0" t="n">
@@ -6336,20 +6335,20 @@
         <v>0</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001100005</v>
       </c>
       <c r="X90" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001100005</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>折上折-B</t>
+          <t>魂牵梦绕-E</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200001</v>
       </c>
       <c r="C91" s="0" t="n">
         <v>11</v>
@@ -6367,7 +6366,7 @@
       </c>
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ATK:-0.5</t>
+          <t>CMP:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O91" s="0" t="n">
@@ -6386,20 +6385,20 @@
         <v>0</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200001</v>
       </c>
       <c r="X91" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200001</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>折上折-C</t>
+          <t>折上折-A</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200002</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>11</v>
@@ -6417,7 +6416,7 @@
       </c>
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ASPD:-0.5</t>
+          <t>CMP:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O92" s="0" t="n">
@@ -6436,20 +6435,20 @@
         <v>0</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200002</v>
       </c>
       <c r="X92" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200002</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>折上折-D</t>
+          <t>折上折-B</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200003</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>11</v>
@@ -6467,7 +6466,7 @@
       </c>
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|RCD:0.5</t>
+          <t>CMP:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O93" s="0" t="n">
@@ -6486,40 +6485,48 @@
         <v>0</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200003</v>
       </c>
       <c r="X93" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200003</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>折上折-E</t>
+          <t>折上折-C</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200004</v>
       </c>
       <c r="C94" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D94" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G94" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H94" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J94" s="0" t="inlineStr">
+        <is>
+          <t>CMP:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O94" s="0" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="P94" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S94" s="0" t="n">
-        <v>5</v>
+        <v>0.5</v>
+      </c>
+      <c r="R94" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T94" s="0" t="n">
         <v>0</v>
@@ -6527,44 +6534,49 @@
       <c r="U94" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W94" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200004</v>
       </c>
       <c r="X94" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200004</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>折上折-D</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>12000200001</v>
+        <v>11001200005</v>
       </c>
       <c r="C95" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D95" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G95" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H95" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J95" s="0" t="inlineStr">
+        <is>
+          <t>CMP:-1|RCD:0.5</t>
         </is>
       </c>
       <c r="O95" s="0" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="P95" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S95" s="0" t="n">
-        <v>5</v>
+        <v>0.5</v>
+      </c>
+      <c r="R95" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T95" s="0" t="n">
         <v>0</v>
@@ -6572,24 +6584,21 @@
       <c r="U95" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="0" t="n">
-        <v>500002</v>
-      </c>
       <c r="W95" s="0" t="n">
-        <v>12000200001</v>
+        <v>11001200005</v>
       </c>
       <c r="X95" s="0" t="n">
-        <v>12000200001</v>
+        <v>11001200005</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>折上折-E</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000100001</v>
       </c>
       <c r="C96" s="0" t="n">
         <v>12</v>
@@ -6599,8 +6608,14 @@
       </c>
       <c r="H96" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
+          <t>BuffEntityBaseHPChange</t>
+        </is>
+      </c>
+      <c r="O96" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P96" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="S96" s="0" t="n">
         <v>5</v>
@@ -6611,21 +6626,24 @@
       <c r="U96" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V96" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W96" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000100001</v>
       </c>
       <c r="X96" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000200001</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>12</v>
@@ -6635,29 +6653,17 @@
       </c>
       <c r="H97" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I97" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J97" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L97" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
+          <t>BuffEntityBaseDRChange</t>
         </is>
       </c>
       <c r="O97" s="0" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="P97" s="0" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
+      </c>
+      <c r="S97" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T97" s="0" t="n">
         <v>0</v>
@@ -6665,21 +6671,24 @@
       <c r="U97" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V97" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W97" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000200001</v>
       </c>
       <c r="X97" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000300001</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>12</v>
@@ -6689,29 +6698,11 @@
       </c>
       <c r="H98" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I98" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J98" s="0" t="inlineStr">
-        <is>
-          <t>DR</t>
-        </is>
-      </c>
-      <c r="L98" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O98" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P98" s="0" t="n">
-        <v>0.1</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="S98" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T98" s="0" t="n">
         <v>0</v>
@@ -6720,20 +6711,20 @@
         <v>0</v>
       </c>
       <c r="W98" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000300001</v>
       </c>
       <c r="X98" s="0" t="n">
-        <v>12001200001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001100001</v>
       </c>
       <c r="C99" s="0" t="n">
         <v>12</v>
@@ -6753,7 +6744,7 @@
       </c>
       <c r="J99" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L99" s="0" t="inlineStr">
@@ -6774,20 +6765,20 @@
         <v>0</v>
       </c>
       <c r="W99" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001100001</v>
       </c>
       <c r="X99" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001200001</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>12</v>
@@ -6807,7 +6798,7 @@
       </c>
       <c r="J100" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L100" s="0" t="inlineStr">
@@ -6828,20 +6819,20 @@
         <v>0</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001200001</v>
       </c>
       <c r="X100" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001300001</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>12</v>
@@ -6856,17 +6847,17 @@
       </c>
       <c r="I101" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J101" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O101" s="0" t="n">
@@ -6882,20 +6873,20 @@
         <v>0</v>
       </c>
       <c r="W101" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001300001</v>
       </c>
       <c r="X101" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001400001</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>12</v>
@@ -6910,17 +6901,17 @@
       </c>
       <c r="I102" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O102" s="0" t="n">
@@ -6936,20 +6927,20 @@
         <v>0</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001400001</v>
       </c>
       <c r="X102" s="0" t="n">
-        <v>12002200001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="12" customHeight="1" s="3">
       <c r="A103" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002100001</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>12</v>
@@ -6969,7 +6960,7 @@
       </c>
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
@@ -6990,20 +6981,20 @@
         <v>0</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002100001</v>
       </c>
       <c r="X103" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="12" customHeight="1" s="3">
       <c r="A104" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002200001</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>12</v>
@@ -7023,7 +7014,7 @@
       </c>
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
@@ -7044,20 +7035,20 @@
         <v>0</v>
       </c>
       <c r="W104" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002200001</v>
       </c>
       <c r="X104" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="12" customHeight="1" s="3">
       <c r="A105" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002300001</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>12</v>
@@ -7077,12 +7068,12 @@
       </c>
       <c r="J105" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L105" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O105" s="0" t="n">
@@ -7098,20 +7089,20 @@
         <v>0</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002300001</v>
       </c>
       <c r="X105" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="12" customHeight="1" s="3">
       <c r="A106" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002400001</v>
       </c>
       <c r="C106" s="0" t="n">
         <v>12</v>
@@ -7131,12 +7122,12 @@
       </c>
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O106" s="0" t="n">
@@ -7152,20 +7143,20 @@
         <v>0</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002400001</v>
       </c>
       <c r="X106" s="0" t="n">
-        <v>12003200001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="12" customHeight="1" s="3">
       <c r="A107" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003100001</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>12</v>
@@ -7185,7 +7176,7 @@
       </c>
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
@@ -7206,20 +7197,20 @@
         <v>0</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003100001</v>
       </c>
       <c r="X107" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="12" customHeight="1" s="3">
       <c r="A108" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003200001</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>12</v>
@@ -7239,7 +7230,7 @@
       </c>
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
@@ -7260,20 +7251,20 @@
         <v>0</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003200001</v>
       </c>
       <c r="X108" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="12" customHeight="1" s="3">
       <c r="A109" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003300001</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>12</v>
@@ -7283,18 +7274,22 @@
       </c>
       <c r="H109" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I109" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I109" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O109" s="0" t="n">
@@ -7310,20 +7305,20 @@
         <v>0</v>
       </c>
       <c r="W109" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003300001</v>
       </c>
       <c r="X109" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="12" customHeight="1" s="3">
       <c r="A110" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003400001</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>12</v>
@@ -7333,18 +7328,22 @@
       </c>
       <c r="H110" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I110" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I110" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O110" s="0" t="n">
@@ -7360,20 +7359,20 @@
         <v>0</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003400001</v>
       </c>
       <c r="X110" s="0" t="n">
-        <v>12004200001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="12" customHeight="1" s="3">
       <c r="A111" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004100001</v>
       </c>
       <c r="C111" s="0" t="n">
         <v>12</v>
@@ -7389,7 +7388,7 @@
       <c r="I111" s="0" t="inlineStr"/>
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
@@ -7410,20 +7409,20 @@
         <v>0</v>
       </c>
       <c r="W111" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004100001</v>
       </c>
       <c r="X111" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004100001</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004200001</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>12</v>
@@ -7439,7 +7438,7 @@
       <c r="I112" s="0" t="inlineStr"/>
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
@@ -7460,20 +7459,20 @@
         <v>0</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004200001</v>
       </c>
       <c r="X112" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004200001</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004300001</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>12</v>
@@ -7483,18 +7482,25 @@
       </c>
       <c r="H113" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I113" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I113" s="0" t="inlineStr"/>
+      <c r="J113" s="0" t="inlineStr">
+        <is>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O113" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P113" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T113" s="0" t="n">
         <v>0</v>
@@ -7503,20 +7509,20 @@
         <v>0</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004300001</v>
       </c>
       <c r="X113" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004300001</v>
       </c>
       <c r="Y113" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004400001</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>12</v>
@@ -7526,18 +7532,25 @@
       </c>
       <c r="H114" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I114" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I114" s="0" t="inlineStr"/>
+      <c r="J114" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O114" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P114" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T114" s="0" t="n">
         <v>0</v>
@@ -7546,20 +7559,20 @@
         <v>0</v>
       </c>
       <c r="W114" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004400001</v>
       </c>
       <c r="X114" s="0" t="n">
-        <v>12010200001</v>
+        <v>12004400001</v>
       </c>
       <c r="Y114" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010100001</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>12</v>
@@ -7574,12 +7587,12 @@
       </c>
       <c r="I115" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
         <is>
-          <t>4001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="T115" s="0" t="n">
@@ -7589,20 +7602,20 @@
         <v>0</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010100001</v>
       </c>
       <c r="X115" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y115" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010200001</v>
       </c>
       <c r="C116" s="0" t="n">
         <v>12</v>
@@ -7617,12 +7630,12 @@
       </c>
       <c r="I116" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
         <is>
-          <t>5001:500&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="T116" s="0" t="n">
@@ -7632,20 +7645,20 @@
         <v>0</v>
       </c>
       <c r="W116" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010200001</v>
       </c>
       <c r="X116" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010200001</v>
       </c>
       <c r="Y116" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010300001</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>12</v>
@@ -7660,12 +7673,12 @@
       </c>
       <c r="I117" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L117" s="0" t="inlineStr">
         <is>
-          <t>6001:1000&amp;</t>
+          <t>4001:1000&amp;</t>
         </is>
       </c>
       <c r="T117" s="0" t="n">
@@ -7675,20 +7688,20 @@
         <v>0</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010300001</v>
       </c>
       <c r="X117" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010300001</v>
       </c>
       <c r="Y117" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010400001</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>12</v>
@@ -7698,17 +7711,17 @@
       </c>
       <c r="H118" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_RegainHP</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
+          <t>5001:500&amp;</t>
         </is>
       </c>
       <c r="T118" s="0" t="n">
@@ -7718,20 +7731,20 @@
         <v>0</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010400001</v>
       </c>
       <c r="X118" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010400001</v>
       </c>
       <c r="Y118" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010500001</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>12</v>
@@ -7741,17 +7754,17 @@
       </c>
       <c r="H119" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I119" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_RegainHP</t>
         </is>
       </c>
       <c r="L119" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
+          <t>6001:1000&amp;</t>
         </is>
       </c>
       <c r="T119" s="0" t="n">
@@ -7761,20 +7774,20 @@
         <v>0</v>
       </c>
       <c r="W119" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010500001</v>
       </c>
       <c r="X119" s="0" t="n">
-        <v>12011200001</v>
+        <v>12010500001</v>
       </c>
       <c r="Y119" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011100001</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>12</v>
@@ -7789,12 +7802,12 @@
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L120" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="T120" s="0" t="n">
@@ -7804,20 +7817,20 @@
         <v>0</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011100001</v>
       </c>
       <c r="X120" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011100001</v>
       </c>
       <c r="Y120" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011200001</v>
       </c>
       <c r="C121" s="0" t="n">
         <v>12</v>
@@ -7827,24 +7840,18 @@
       </c>
       <c r="H121" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDemonLordMPRegain</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
-        </is>
-      </c>
-      <c r="M121" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="N121" s="0" t="n">
-        <v>10</v>
+          <t>3001:200&amp;</t>
+        </is>
       </c>
       <c r="T121" s="0" t="n">
         <v>0</v>
@@ -7853,20 +7860,20 @@
         <v>0</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011200001</v>
       </c>
       <c r="X121" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011200001</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>12012200001</v>
+        <v>12011300001</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>12</v>
@@ -7876,7 +7883,7 @@
       </c>
       <c r="H122" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDemonLordMPRegain</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I122" s="0" t="inlineStr">
@@ -7886,14 +7893,8 @@
       </c>
       <c r="L122" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
-        </is>
-      </c>
-      <c r="M122" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="N122" s="0" t="n">
-        <v>10</v>
+          <t>4001:200&amp;</t>
+        </is>
       </c>
       <c r="T122" s="0" t="n">
         <v>0</v>
@@ -7902,40 +7903,47 @@
         <v>0</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>12012200001</v>
+        <v>12011300001</v>
       </c>
       <c r="X122" s="0" t="n">
-        <v>12012200001</v>
+        <v>12011300001</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="C123" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D123" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H123" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
+        </is>
+      </c>
+      <c r="I123" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack_Dead</t>
+        </is>
+      </c>
+      <c r="L123" s="0" t="inlineStr">
+        <is>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="M123" s="0" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N123" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S123" s="0" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T123" s="0" t="n">
         <v>0</v>
@@ -7944,36 +7952,47 @@
         <v>0</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="X123" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012100001</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="C124" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D124" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H124" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
         </is>
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L124" s="0" t="inlineStr">
+        <is>
+          <t>3001:100&amp;</t>
+        </is>
+      </c>
+      <c r="M124" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N124" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="T124" s="0" t="n">
         <v>0</v>
@@ -7981,24 +8000,21 @@
       <c r="U124" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W124" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="X124" s="0" t="n">
-        <v>13000200001</v>
+        <v>12012200001</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="C125" s="0" t="n">
         <v>13</v>
@@ -8008,20 +8024,18 @@
       </c>
       <c r="H125" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
-        </is>
-      </c>
-      <c r="I125" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J125" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O125" s="0" t="n">
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M125" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N125" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="S125" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="T125" s="0" t="n">
         <v>0</v>
       </c>
@@ -8029,20 +8043,20 @@
         <v>0</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="X125" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000100001</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>13</v>
@@ -8052,7 +8066,7 @@
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalDeadRebirth</t>
         </is>
       </c>
       <c r="I126" s="0" t="inlineStr">
@@ -8060,36 +8074,30 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J126" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="O126" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P126" s="0" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T126" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U126" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V126" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W126" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="X126" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000200001</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>死亡后重生</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>13</v>
@@ -8099,7 +8107,7 @@
       </c>
       <c r="H127" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalDeadAttack</t>
         </is>
       </c>
       <c r="I127" s="0" t="inlineStr">
@@ -8108,14 +8116,11 @@
         </is>
       </c>
       <c r="J127" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O127" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="O127" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P127" s="0" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T127" s="0" t="n">
         <v>0</v>
       </c>
@@ -8123,20 +8128,20 @@
         <v>0</v>
       </c>
       <c r="W127" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="X127" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000300001</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>死亡后爆炸</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>13</v>
@@ -8146,7 +8151,7 @@
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadCreateCrystal</t>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
         </is>
       </c>
       <c r="I128" s="0" t="inlineStr">
@@ -8154,8 +8159,14 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q128" s="0" t="n">
-        <v>0.2</v>
+      <c r="J128" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O128" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P128" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="T128" s="0" t="n">
         <v>0</v>
@@ -8164,70 +8175,45 @@
         <v>0</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="X128" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000400001</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="B129" s="0" t="inlineStr"/>
+        <v>13000500001</v>
+      </c>
       <c r="C129" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D129" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H129" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I129" s="0" t="inlineStr"/>
-      <c r="J129" s="0" t="inlineStr">
-        <is>
-          <t>1,300051</t>
-        </is>
-      </c>
-      <c r="K129" s="0" t="inlineStr"/>
-      <c r="L129" s="0" t="inlineStr"/>
-      <c r="M129" s="0" t="n">
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
+        </is>
+      </c>
+      <c r="I129" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J129" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N129" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="O129" s="0" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="P129" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" s="0" t="n">
-        <v>5</v>
+        <v>0.01</v>
       </c>
       <c r="T129" s="0" t="n">
         <v>0</v>
@@ -8235,74 +8221,40 @@
       <c r="U129" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W129" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000500001</v>
       </c>
       <c r="X129" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000500001</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>3000500002</v>
-      </c>
-      <c r="B130" s="0" t="inlineStr"/>
+        <v>13000600001</v>
+      </c>
       <c r="C130" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D130" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H130" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I130" s="0" t="inlineStr"/>
-      <c r="J130" s="0" t="inlineStr">
-        <is>
-          <t>2,300051</t>
-        </is>
-      </c>
-      <c r="K130" s="0" t="inlineStr"/>
-      <c r="L130" s="0" t="inlineStr"/>
-      <c r="M130" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N130" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" s="0" t="n">
-        <v>0</v>
+          <t>BuffEntityConditionalDeadCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I130" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
       </c>
       <c r="Q130" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="T130" s="0" t="n">
         <v>0</v>
@@ -8310,24 +8262,21 @@
       <c r="U130" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W130" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="X130" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000500003</v>
+        <v>3000500001</v>
       </c>
       <c r="B131" s="0" t="inlineStr"/>
       <c r="C131" s="0" t="n">
@@ -8353,7 +8302,7 @@
       <c r="I131" s="0" t="inlineStr"/>
       <c r="J131" s="0" t="inlineStr">
         <is>
-          <t>3,300051</t>
+          <t>1,300051</t>
         </is>
       </c>
       <c r="K131" s="0" t="inlineStr"/>
@@ -8396,13 +8345,13 @@
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000500004</v>
+        <v>3000500002</v>
       </c>
       <c r="B132" s="0" t="inlineStr"/>
       <c r="C132" s="0" t="n">
@@ -8428,7 +8377,7 @@
       <c r="I132" s="0" t="inlineStr"/>
       <c r="J132" s="0" t="inlineStr">
         <is>
-          <t>4,300051</t>
+          <t>2,300051</t>
         </is>
       </c>
       <c r="K132" s="0" t="inlineStr"/>
@@ -8471,13 +8420,13 @@
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000500005</v>
+        <v>3000500003</v>
       </c>
       <c r="B133" s="0" t="inlineStr"/>
       <c r="C133" s="0" t="n">
@@ -8503,7 +8452,7 @@
       <c r="I133" s="0" t="inlineStr"/>
       <c r="J133" s="0" t="inlineStr">
         <is>
-          <t>5,300051</t>
+          <t>3,300051</t>
         </is>
       </c>
       <c r="K133" s="0" t="inlineStr"/>
@@ -8546,95 +8495,163 @@
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>13000700001</v>
-      </c>
+        <v>3000500004</v>
+      </c>
+      <c r="B134" s="0" t="inlineStr"/>
       <c r="C134" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D134" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H134" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalThorns</t>
-        </is>
-      </c>
-      <c r="I134" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I134" s="0" t="inlineStr"/>
+      <c r="J134" s="0" t="inlineStr">
+        <is>
+          <t>4,300051</t>
+        </is>
+      </c>
+      <c r="K134" s="0" t="inlineStr"/>
+      <c r="L134" s="0" t="inlineStr"/>
+      <c r="M134" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N134" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O134" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P134" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T134" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U134" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W134" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="X134" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
-          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>13000800001</v>
-      </c>
+        <v>3000500005</v>
+      </c>
+      <c r="B135" s="0" t="inlineStr"/>
       <c r="C135" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D135" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H135" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalLifeSteal</t>
-        </is>
-      </c>
-      <c r="I135" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I135" s="0" t="inlineStr"/>
+      <c r="J135" s="0" t="inlineStr">
+        <is>
+          <t>5,300051</t>
+        </is>
+      </c>
+      <c r="K135" s="0" t="inlineStr"/>
+      <c r="L135" s="0" t="inlineStr"/>
+      <c r="M135" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N135" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O135" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P135" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T135" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U135" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W135" s="0" t="n">
-        <v>13000800001</v>
+        <v>3000500001</v>
       </c>
       <c r="X135" s="0" t="n">
-        <v>13000800001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
-          <t>造成伤害的{Percentage}%转化为自身生命</t>
+          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000700001</v>
       </c>
       <c r="C136" s="0" t="n">
         <v>13</v>
@@ -8644,30 +8661,112 @@
       </c>
       <c r="H136" s="0" t="inlineStr">
         <is>
+          <t>BuffEntityConditionalThorns</t>
+        </is>
+      </c>
+      <c r="I136" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O136" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P136" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="X136" s="0" t="n">
+        <v>13000700001</v>
+      </c>
+      <c r="Y136" s="0" t="inlineStr">
+        <is>
+          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="C137" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D137" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H137" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalLifeSteal</t>
+        </is>
+      </c>
+      <c r="I137" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O137" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P137" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T137" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="X137" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="Y137" s="0" t="inlineStr">
+        <is>
+          <t>造成伤害的{Percentage}%转化为自身生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0" t="n">
+        <v>13000900001</v>
+      </c>
+      <c r="C138" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D138" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H138" s="0" t="inlineStr">
+        <is>
           <t>BuffEntityConditionalInvincible</t>
         </is>
       </c>
-      <c r="K136" s="0" t="inlineStr">
+      <c r="K138" s="0" t="inlineStr">
         <is>
           <t>#FFD700</t>
         </is>
       </c>
-      <c r="M136" s="0" t="n">
+      <c r="M138" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="N136" s="0" t="n">
+      <c r="N138" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T136" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" s="0" t="n">
+      <c r="T138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="0" t="n">
         <v>13000900001</v>
       </c>
-      <c r="X136" s="0" t="n">
+      <c r="X138" s="0" t="n">
         <v>13000900001</v>
       </c>
-      <c r="Y136" s="0" t="inlineStr">
+      <c r="Y138" s="0" t="inlineStr">
         <is>
           <t>上场后无敌{Value}秒，期间身体变为金色</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y138"/>
+  <dimension ref="A1:Y142"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -8772,6 +8772,242 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>11001300001</v>
+      </c>
+      <c r="C139" t="n">
+        <v>11</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeDecayByAllyCount</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="M139" t="n">
+        <v>50</v>
+      </c>
+      <c r="N139" t="n">
+        <v>50</v>
+      </c>
+      <c r="O139" t="n">
+        <v>3</v>
+      </c>
+      <c r="P139" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>11001300001</v>
+      </c>
+      <c r="X139" t="n">
+        <v>11001300001</v>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>独行者-A</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>11001300002</v>
+      </c>
+      <c r="C140" t="n">
+        <v>11</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeDecayByAllyCount</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="M140" t="n">
+        <v>50</v>
+      </c>
+      <c r="N140" t="n">
+        <v>50</v>
+      </c>
+      <c r="O140" t="n">
+        <v>3</v>
+      </c>
+      <c r="P140" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>11001300002</v>
+      </c>
+      <c r="X140" t="n">
+        <v>11001300002</v>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>独行者-B</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>11001300003</v>
+      </c>
+      <c r="C141" t="n">
+        <v>11</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeDecayByAllyCount</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="M141" t="n">
+        <v>50</v>
+      </c>
+      <c r="N141" t="n">
+        <v>50</v>
+      </c>
+      <c r="O141" t="n">
+        <v>3</v>
+      </c>
+      <c r="P141" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" t="n">
+        <v>11001300003</v>
+      </c>
+      <c r="X141" t="n">
+        <v>11001300003</v>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>独行者-C</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>11001300004</v>
+      </c>
+      <c r="C142" t="n">
+        <v>11</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>BuffEntityAttributeDecayByAllyCount</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="M142" t="n">
+        <v>50</v>
+      </c>
+      <c r="N142" t="n">
+        <v>50</v>
+      </c>
+      <c r="O142" t="n">
+        <v>3</v>
+      </c>
+      <c r="P142" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>11001300004</v>
+      </c>
+      <c r="X142" t="n">
+        <v>11001300004</v>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>独行者-D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1137,7 +1137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y142"/>
+  <dimension ref="A1:Y143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24.25" customWidth="1" style="3" min="1" max="1"/>
@@ -2089,67 +2089,50 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>2000300001</v>
-      </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n">
+      <c r="A15" s="0" t="n">
+        <v>2000500001</v>
+      </c>
+      <c r="C15" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>1001:0.5&amp;</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>CDMG</t>
+        </is>
+      </c>
+      <c r="O15" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n"/>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n"/>
       <c r="T15" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U15" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="2" t="n"/>
-      <c r="W15" s="2" t="n">
-        <v>2000300001</v>
-      </c>
-      <c r="X15" s="2" t="n">
-        <v>2000300001</v>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
-        <is>
-          <t>血量低于50% 攻击力提升</t>
+      <c r="V15" s="0" t="n"/>
+      <c r="W15" s="0" t="n">
+        <v>2000500001</v>
+      </c>
+      <c r="X15" s="0" t="n">
+        <v>2000500001</v>
+      </c>
+      <c r="Y15" s="0" t="inlineStr">
+        <is>
+          <t>暴击伤害100%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>2000400001</v>
+        <v>2000300001</v>
       </c>
       <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n">
@@ -2169,7 +2152,7 @@
       <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="K16" s="2" t="n"/>
@@ -2181,7 +2164,7 @@
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n"/>
@@ -2195,54 +2178,79 @@
       </c>
       <c r="V16" s="2" t="n"/>
       <c r="W16" s="2" t="n">
+        <v>2000300001</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>2000300001</v>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>血量低于50% 攻击力提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
         <v>2000400001</v>
       </c>
-      <c r="X16" s="2" t="n">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>ASPD</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1001:0.5&amp;</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="n"/>
+      <c r="W17" s="2" t="n">
         <v>2000400001</v>
       </c>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="X17" s="2" t="n">
+        <v>2000400001</v>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
         <is>
           <t>血量低于50% 攻击速度提升</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="n">
-        <v>3000100001</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantCloneDefenseCreature</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="n"/>
-      <c r="T17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="0" t="n">
-        <v>3000100001</v>
-      </c>
-      <c r="X17" s="0" t="n">
-        <v>3000100001</v>
-      </c>
-      <c r="Y17" s="0" t="inlineStr">
-        <is>
-          <t>增殖-随机复制一个已有的魔物</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="C18" s="0" t="n">
         <v>3</v>
@@ -2250,25 +2258,12 @@
       <c r="D18" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="0" t="n">
-        <v>3000200001</v>
-      </c>
-      <c r="F18" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAddDropCrystal</t>
-        </is>
-      </c>
-      <c r="I18" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadDropCrystal</t>
-        </is>
-      </c>
-      <c r="Q18" s="0" t="n">
-        <v>0.2</v>
-      </c>
+          <t>BuffEntityInstantCloneDefenseCreature</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="n"/>
       <c r="T18" s="0" t="n">
         <v>0</v>
       </c>
@@ -2276,20 +2271,20 @@
         <v>0</v>
       </c>
       <c r="W18" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="X18" s="0" t="n">
-        <v>3000200001</v>
+        <v>3000100001</v>
       </c>
       <c r="Y18" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
+          <t>增殖-随机复制一个已有的魔物</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="n">
-        <v>3000200002</v>
+        <v>3000200001</v>
       </c>
       <c r="C19" s="0" t="n">
         <v>3</v>
@@ -2298,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>3000200002</v>
+        <v>3000200001</v>
       </c>
       <c r="F19" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
@@ -2314,7 +2309,7 @@
         </is>
       </c>
       <c r="Q19" s="0" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="T19" s="0" t="n">
         <v>0</v>
@@ -2330,13 +2325,13 @@
       </c>
       <c r="Y19" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
+          <t>钱多多LV1-每一次击杀有20%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200002</v>
       </c>
       <c r="C20" s="0" t="n">
         <v>3</v>
@@ -2345,10 +2340,10 @@
         <v>1</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>3000200003</v>
+        <v>3000200002</v>
       </c>
       <c r="F20" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -2361,7 +2356,7 @@
         </is>
       </c>
       <c r="Q20" s="0" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="T20" s="0" t="n">
         <v>0</v>
@@ -2377,13 +2372,13 @@
       </c>
       <c r="Y20" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
+          <t>钱多多LV2-每一次击杀有40%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="n">
-        <v>3000200004</v>
+        <v>3000200003</v>
       </c>
       <c r="C21" s="0" t="n">
         <v>3</v>
@@ -2395,7 +2390,7 @@
         <v>3000200003</v>
       </c>
       <c r="F21" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
@@ -2408,7 +2403,7 @@
         </is>
       </c>
       <c r="Q21" s="0" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="T21" s="0" t="n">
         <v>0</v>
@@ -2424,13 +2419,13 @@
       </c>
       <c r="Y21" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
+          <t>钱多多LV3-每一次击杀有60%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="3">
       <c r="A22" s="0" t="n">
-        <v>3000200005</v>
+        <v>3000200004</v>
       </c>
       <c r="C22" s="0" t="n">
         <v>3</v>
@@ -2442,7 +2437,7 @@
         <v>3000200003</v>
       </c>
       <c r="F22" s="0" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
@@ -2455,7 +2450,7 @@
         </is>
       </c>
       <c r="Q22" s="0" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T22" s="0" t="n">
         <v>0</v>
@@ -2471,60 +2466,60 @@
       </c>
       <c r="Y22" s="0" t="inlineStr">
         <is>
-          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
+          <t>钱多多LV4-每一次击杀有80%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="3">
       <c r="A23" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200005</v>
       </c>
       <c r="C23" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackMultiInstant</t>
-        </is>
-      </c>
-      <c r="J23" s="0" t="inlineStr">
-        <is>
-          <t>1,300031</t>
-        </is>
-      </c>
-      <c r="M23" s="0" t="n">
+      <c r="D23" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="E23" s="0" t="n">
+        <v>3000200003</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>BuffEntityConditionalAddDropCrystal</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadDropCrystal</t>
+        </is>
+      </c>
       <c r="Q23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T23" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U23" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W23" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="X23" s="0" t="n">
-        <v>3000300001</v>
+        <v>3000200001</v>
       </c>
       <c r="Y23" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
+          <t>钱多多LV5-每一次击杀有100%的概率多掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="3">
       <c r="A24" s="0" t="n">
-        <v>3000300002</v>
+        <v>3000300001</v>
       </c>
       <c r="C24" s="0" t="n">
         <v>3</v>
@@ -2539,7 +2534,7 @@
       </c>
       <c r="J24" s="0" t="inlineStr">
         <is>
-          <t>2,300032</t>
+          <t>1,300031</t>
         </is>
       </c>
       <c r="M24" s="0" t="n">
@@ -2565,13 +2560,13 @@
       </c>
       <c r="Y24" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv1-每3秒1道落雷,范围0.2,单雷最多命中1个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="3">
       <c r="A25" s="0" t="n">
-        <v>3000300003</v>
+        <v>3000300002</v>
       </c>
       <c r="C25" s="0" t="n">
         <v>3</v>
@@ -2586,7 +2581,7 @@
       </c>
       <c r="J25" s="0" t="inlineStr">
         <is>
-          <t>3,300033</t>
+          <t>2,300032</t>
         </is>
       </c>
       <c r="M25" s="0" t="n">
@@ -2612,13 +2607,13 @@
       </c>
       <c r="Y25" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv2-每3秒2道落雷,范围0.4,单雷最多命中2个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="n">
-        <v>3000300004</v>
+        <v>3000300003</v>
       </c>
       <c r="C26" s="0" t="n">
         <v>3</v>
@@ -2633,7 +2628,7 @@
       </c>
       <c r="J26" s="0" t="inlineStr">
         <is>
-          <t>4,300034</t>
+          <t>3,300033</t>
         </is>
       </c>
       <c r="M26" s="0" t="n">
@@ -2659,13 +2654,13 @@
       </c>
       <c r="Y26" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv3-每3秒3道落雷,范围0.6,单雷最多命中3个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="3">
       <c r="A27" s="0" t="n">
-        <v>3000300005</v>
+        <v>3000300004</v>
       </c>
       <c r="C27" s="0" t="n">
         <v>3</v>
@@ -2680,7 +2675,7 @@
       </c>
       <c r="J27" s="0" t="inlineStr">
         <is>
-          <t>5,300035</t>
+          <t>4,300034</t>
         </is>
       </c>
       <c r="M27" s="0" t="n">
@@ -2706,13 +2701,13 @@
       </c>
       <c r="Y27" s="0" t="inlineStr">
         <is>
-          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
+          <t>闪电Lv4-每3秒4道落雷,范围0.8,单雷最多命中4个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="3">
       <c r="A28" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300005</v>
       </c>
       <c r="C28" s="0" t="n">
         <v>3</v>
@@ -2722,12 +2717,12 @@
       </c>
       <c r="H28" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRoad</t>
+          <t>BuffEntityPeriodicAttackMultiInstant</t>
         </is>
       </c>
       <c r="J28" s="0" t="inlineStr">
         <is>
-          <t>1,300041</t>
+          <t>5,300035</t>
         </is>
       </c>
       <c r="M28" s="0" t="n">
@@ -2740,26 +2735,26 @@
         <v>0</v>
       </c>
       <c r="S28" s="0" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" s="0" t="n">
         <v>0</v>
       </c>
       <c r="W28" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="X28" s="0" t="n">
-        <v>3000400001</v>
+        <v>3000300001</v>
       </c>
       <c r="Y28" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>闪电Lv5-每3秒5道落雷,范围1,单雷最多命中5个目标,伤害=魔王攻击力</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="3">
       <c r="A29" s="0" t="n">
-        <v>3000400002</v>
+        <v>3000400001</v>
       </c>
       <c r="C29" s="0" t="n">
         <v>3</v>
@@ -2774,7 +2769,7 @@
       </c>
       <c r="J29" s="0" t="inlineStr">
         <is>
-          <t>2,300041</t>
+          <t>1,300041</t>
         </is>
       </c>
       <c r="M29" s="0" t="n">
@@ -2800,13 +2795,13 @@
       </c>
       <c r="Y29" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv1-每5秒随机1条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="3">
       <c r="A30" s="0" t="n">
-        <v>3000400003</v>
+        <v>3000400002</v>
       </c>
       <c r="C30" s="0" t="n">
         <v>3</v>
@@ -2821,7 +2816,7 @@
       </c>
       <c r="J30" s="0" t="inlineStr">
         <is>
-          <t>3,300041</t>
+          <t>2,300041</t>
         </is>
       </c>
       <c r="M30" s="0" t="n">
@@ -2847,13 +2842,13 @@
       </c>
       <c r="Y30" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv2-每5秒随机2条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="31" customFormat="1" s="2">
       <c r="A31" s="0" t="n">
-        <v>3000400004</v>
+        <v>3000400003</v>
       </c>
       <c r="C31" s="0" t="n">
         <v>3</v>
@@ -2868,7 +2863,7 @@
       </c>
       <c r="J31" s="0" t="inlineStr">
         <is>
-          <t>4,300041</t>
+          <t>3,300041</t>
         </is>
       </c>
       <c r="M31" s="0" t="n">
@@ -2894,13 +2889,13 @@
       </c>
       <c r="Y31" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv3-每5秒随机3条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="32" customFormat="1" s="2">
       <c r="A32" s="0" t="n">
-        <v>3000400005</v>
+        <v>3000400004</v>
       </c>
       <c r="C32" s="0" t="n">
         <v>3</v>
@@ -2915,7 +2910,7 @@
       </c>
       <c r="J32" s="0" t="inlineStr">
         <is>
-          <t>5,300041</t>
+          <t>4,300041</t>
         </is>
       </c>
       <c r="M32" s="0" t="n">
@@ -2941,51 +2936,33 @@
       </c>
       <c r="Y32" s="0" t="inlineStr">
         <is>
-          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
+          <t>失控的矿车Lv4-每5秒随机4条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="33" customFormat="1" s="2">
       <c r="A33" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400005</v>
       </c>
       <c r="C33" s="0" t="n">
         <v>3</v>
-      </c>
-      <c r="D33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="0" t="n">
-        <v>0</v>
       </c>
       <c r="G33" s="0" t="n">
         <v>2</v>
       </c>
       <c r="H33" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBounceAxe</t>
+          <t>BuffEntityPeriodicAttackRoad</t>
         </is>
       </c>
       <c r="J33" s="0" t="inlineStr">
         <is>
-          <t>1,300061,1</t>
+          <t>5,300041</t>
         </is>
       </c>
       <c r="M33" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="Q33" s="0" t="n">
         <v>0</v>
       </c>
@@ -2998,27 +2975,21 @@
       <c r="T33" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="U33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W33" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="X33" s="0" t="n">
-        <v>3000600001</v>
+        <v>3000400001</v>
       </c>
       <c r="Y33" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
+          <t>失控的矿车Lv5-每5秒随机5条道路各出1辆矿车，第1个目标伤害=魔王攻击力，之后每撞1个减半</t>
         </is>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1" s="3">
       <c r="A34" s="0" t="n">
-        <v>3000600002</v>
+        <v>3000600001</v>
       </c>
       <c r="C34" s="0" t="n">
         <v>3</v>
@@ -3042,7 +3013,7 @@
       </c>
       <c r="J34" s="0" t="inlineStr">
         <is>
-          <t>2,300061,2</t>
+          <t>1,300061,1</t>
         </is>
       </c>
       <c r="M34" s="0" t="n">
@@ -3083,13 +3054,13 @@
       </c>
       <c r="Y34" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv1-每5秒扔出1把斧头,伤害=魔王攻击力,命中后弹跳1次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="35" ht="14.25" customHeight="1" s="3">
       <c r="A35" s="0" t="n">
-        <v>3000600003</v>
+        <v>3000600002</v>
       </c>
       <c r="C35" s="0" t="n">
         <v>3</v>
@@ -3113,7 +3084,7 @@
       </c>
       <c r="J35" s="0" t="inlineStr">
         <is>
-          <t>3,300061,3</t>
+          <t>2,300061,2</t>
         </is>
       </c>
       <c r="M35" s="0" t="n">
@@ -3154,13 +3125,13 @@
       </c>
       <c r="Y35" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv2-每5秒扔出2把斧头,命中后弹跳2次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1" s="3">
       <c r="A36" s="0" t="n">
-        <v>3000600004</v>
+        <v>3000600003</v>
       </c>
       <c r="C36" s="0" t="n">
         <v>3</v>
@@ -3184,7 +3155,7 @@
       </c>
       <c r="J36" s="0" t="inlineStr">
         <is>
-          <t>4,300061,4</t>
+          <t>3,300061,3</t>
         </is>
       </c>
       <c r="M36" s="0" t="n">
@@ -3225,13 +3196,13 @@
       </c>
       <c r="Y36" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv3-每5秒扔出3把斧头,命中后弹跳3次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="37" ht="14.25" customHeight="1" s="3">
       <c r="A37" s="0" t="n">
-        <v>3000600005</v>
+        <v>3000600004</v>
       </c>
       <c r="C37" s="0" t="n">
         <v>3</v>
@@ -3255,7 +3226,7 @@
       </c>
       <c r="J37" s="0" t="inlineStr">
         <is>
-          <t>5,300061,5</t>
+          <t>4,300061,4</t>
         </is>
       </c>
       <c r="M37" s="0" t="n">
@@ -3296,13 +3267,13 @@
       </c>
       <c r="Y37" s="0" t="inlineStr">
         <is>
-          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
+          <t>跳跳斧Lv4-每5秒扔出4把斧头,命中后弹跳4次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14.25" customHeight="1" s="3">
       <c r="A38" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600005</v>
       </c>
       <c r="C38" s="0" t="n">
         <v>3</v>
@@ -3321,16 +3292,16 @@
       </c>
       <c r="H38" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackOrbit</t>
+          <t>BuffEntityPeriodicAttackBounceAxe</t>
         </is>
       </c>
       <c r="J38" s="0" t="inlineStr">
         <is>
-          <t>1,300071,0.6</t>
+          <t>5,300061,5</t>
         </is>
       </c>
       <c r="M38" s="0" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N38" s="0" t="n">
         <v>0</v>
@@ -3348,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="0" t="n">
-        <v>9999</v>
+        <v>5</v>
       </c>
       <c r="T38" s="0" t="n">
         <v>0</v>
@@ -3360,20 +3331,20 @@
         <v>0</v>
       </c>
       <c r="W38" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="X38" s="0" t="n">
-        <v>3000700001</v>
+        <v>3000600001</v>
       </c>
       <c r="Y38" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>跳跳斧Lv5-每5秒扔出5把斧头,命中后弹跳5次,伤害逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1" s="3">
       <c r="A39" s="0" t="n">
-        <v>3000700002</v>
+        <v>3000700001</v>
       </c>
       <c r="C39" s="0" t="n">
         <v>3</v>
@@ -3397,7 +3368,7 @@
       </c>
       <c r="J39" s="0" t="inlineStr">
         <is>
-          <t>2,300071,1.2</t>
+          <t>1,300071,0.6</t>
         </is>
       </c>
       <c r="M39" s="0" t="n">
@@ -3438,13 +3409,13 @@
       </c>
       <c r="Y39" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv1-环绕1本书(半径0.75,转速0.6弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="40" ht="14.25" customHeight="1" s="3">
       <c r="A40" s="0" t="n">
-        <v>3000700003</v>
+        <v>3000700002</v>
       </c>
       <c r="C40" s="0" t="n">
         <v>3</v>
@@ -3468,7 +3439,7 @@
       </c>
       <c r="J40" s="0" t="inlineStr">
         <is>
-          <t>3,300071,1.8</t>
+          <t>2,300071,1.2</t>
         </is>
       </c>
       <c r="M40" s="0" t="n">
@@ -3509,13 +3480,13 @@
       </c>
       <c r="Y40" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv2-环绕2本书(半径0.75,转速1.2弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="14.25" customHeight="1" s="3">
       <c r="A41" s="0" t="n">
-        <v>3000700004</v>
+        <v>3000700003</v>
       </c>
       <c r="C41" s="0" t="n">
         <v>3</v>
@@ -3539,7 +3510,7 @@
       </c>
       <c r="J41" s="0" t="inlineStr">
         <is>
-          <t>4,300071,2.4</t>
+          <t>3,300071,1.8</t>
         </is>
       </c>
       <c r="M41" s="0" t="n">
@@ -3580,13 +3551,13 @@
       </c>
       <c r="Y41" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv3-环绕3本书(半径0.75,转速1.8弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1" s="3">
       <c r="A42" s="0" t="n">
-        <v>3000700005</v>
+        <v>3000700004</v>
       </c>
       <c r="C42" s="0" t="n">
         <v>3</v>
@@ -3610,7 +3581,7 @@
       </c>
       <c r="J42" s="0" t="inlineStr">
         <is>
-          <t>5,300071,3</t>
+          <t>4,300071,2.4</t>
         </is>
       </c>
       <c r="M42" s="0" t="n">
@@ -3651,13 +3622,13 @@
       </c>
       <c r="Y42" s="0" t="inlineStr">
         <is>
-          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
+          <t>知识的力量Lv4-环绕4本书(半径0.75,转速2.4弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="3">
       <c r="A43" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700005</v>
       </c>
       <c r="C43" s="0" t="n">
         <v>3</v>
@@ -3676,16 +3647,16 @@
       </c>
       <c r="H43" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackRebound</t>
+          <t>BuffEntityPeriodicAttackOrbit</t>
         </is>
       </c>
       <c r="J43" s="0" t="inlineStr">
         <is>
-          <t>1,300081</t>
+          <t>5,300071,3</t>
         </is>
       </c>
       <c r="M43" s="0" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N43" s="0" t="n">
         <v>0</v>
@@ -3703,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="S43" s="0" t="n">
-        <v>1</v>
+        <v>9999</v>
       </c>
       <c r="T43" s="0" t="n">
         <v>0</v>
@@ -3715,20 +3686,20 @@
         <v>0</v>
       </c>
       <c r="W43" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="X43" s="0" t="n">
-        <v>3000800001</v>
+        <v>3000700001</v>
       </c>
       <c r="Y43" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>知识的力量Lv5-环绕5本书(半径0.75,转速3弧度/秒),触碰伤害=魔王攻击力40%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1" s="3">
       <c r="A44" s="0" t="n">
-        <v>3000800002</v>
+        <v>3000800001</v>
       </c>
       <c r="C44" s="0" t="n">
         <v>3</v>
@@ -3752,7 +3723,7 @@
       </c>
       <c r="J44" s="0" t="inlineStr">
         <is>
-          <t>2,300082</t>
+          <t>1,300081</t>
         </is>
       </c>
       <c r="M44" s="0" t="n">
@@ -3793,13 +3764,13 @@
       </c>
       <c r="Y44" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv1-场上维持1颗永久反弹菱块(速度2),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="45" ht="14.25" customHeight="1" s="3">
       <c r="A45" s="0" t="n">
-        <v>3000800003</v>
+        <v>3000800002</v>
       </c>
       <c r="C45" s="0" t="n">
         <v>3</v>
@@ -3823,7 +3794,7 @@
       </c>
       <c r="J45" s="0" t="inlineStr">
         <is>
-          <t>3,300083</t>
+          <t>2,300082</t>
         </is>
       </c>
       <c r="M45" s="0" t="n">
@@ -3864,13 +3835,13 @@
       </c>
       <c r="Y45" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv2-场上维持2颗永久反弹菱块(速度2.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1" s="3">
       <c r="A46" s="0" t="n">
-        <v>3000800004</v>
+        <v>3000800003</v>
       </c>
       <c r="C46" s="0" t="n">
         <v>3</v>
@@ -3894,7 +3865,7 @@
       </c>
       <c r="J46" s="0" t="inlineStr">
         <is>
-          <t>4,300084</t>
+          <t>3,300083</t>
         </is>
       </c>
       <c r="M46" s="0" t="n">
@@ -3935,13 +3906,13 @@
       </c>
       <c r="Y46" s="0" t="inlineStr">
         <is>
-          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+          <t>回弹菱块Lv3-场上维持3颗永久反弹菱块(速度3),伤害=魔王攻击力100%,同目标1秒冷却</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1" s="3">
       <c r="A47" s="0" t="n">
-        <v>3000800005</v>
+        <v>3000800004</v>
       </c>
       <c r="C47" s="0" t="n">
         <v>3</v>
@@ -3965,7 +3936,7 @@
       </c>
       <c r="J47" s="0" t="inlineStr">
         <is>
-          <t>5,300085</t>
+          <t>4,300084</t>
         </is>
       </c>
       <c r="M47" s="0" t="n">
@@ -4006,50 +3977,84 @@
       </c>
       <c r="Y47" s="0" t="inlineStr">
         <is>
+          <t>回弹菱块Lv4-场上维持4颗永久反弹菱块(速度3.5),伤害=魔王攻击力100%,同目标1秒冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="14.25" customHeight="1" s="3">
+      <c r="A48" s="0" t="n">
+        <v>3000800005</v>
+      </c>
+      <c r="C48" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackRebound</t>
+        </is>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t>5,300085</t>
+        </is>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="X48" s="0" t="n">
+        <v>3000800001</v>
+      </c>
+      <c r="Y48" s="0" t="inlineStr">
+        <is>
           <t>回弹菱块Lv5-场上维持5颗永久反弹菱块(速度4),伤害=魔王攻击力100%,同目标1秒冷却</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="14.25" customHeight="1" s="3">
-      <c r="A48" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="C48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityInstantRewardMoreItem</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
-      <c r="P48" s="2" t="n"/>
-      <c r="T48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="X48" s="2" t="n">
-        <v>3000900001</v>
-      </c>
-      <c r="Y48" s="2" t="inlineStr">
-        <is>
-          <t>奖励多多-通关奖励数量+1</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="3">
       <c r="A49" s="2" t="n">
-        <v>3001000001</v>
+        <v>3000900001</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>3</v>
@@ -4059,7 +4064,7 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>BuffEntityInstantRewardMoreSelect</t>
+          <t>BuffEntityInstantRewardMoreItem</t>
         </is>
       </c>
       <c r="I49" s="2" t="n"/>
@@ -4073,91 +4078,57 @@
         <v>0</v>
       </c>
       <c r="W49" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>3000900001</v>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>奖励多多-通关奖励数量+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14.25" customHeight="1" s="3">
+      <c r="A50" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="X49" s="2" t="n">
+      <c r="C50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityInstantRewardMoreSelect</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n"/>
+      <c r="J50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
+      <c r="T50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="2" t="n">
         <v>3001000001</v>
       </c>
-      <c r="Y49" s="2" t="inlineStr">
+      <c r="X50" s="2" t="n">
+        <v>3001000001</v>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
         <is>
           <t>再来一瓶-通关奖励可选次数+1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="14.25" customHeight="1" s="3">
-      <c r="A50" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="C50" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityPeriodicAttackShockwave</t>
-        </is>
-      </c>
-      <c r="J50" s="0" t="inlineStr">
-        <is>
-          <t>300091</t>
-        </is>
-      </c>
-      <c r="M50" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="X50" s="0" t="n">
-        <v>3001100005</v>
-      </c>
-      <c r="Y50" s="0" t="inlineStr">
-        <is>
-          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
         </is>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1" s="3">
       <c r="A51" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100005</v>
       </c>
       <c r="C51" s="0" t="n">
         <v>3</v>
@@ -4185,7 +4156,7 @@
         </is>
       </c>
       <c r="M51" s="0" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="N51" s="0" t="n">
         <v>0</v>
@@ -4215,20 +4186,20 @@
         <v>0</v>
       </c>
       <c r="W51" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100005</v>
       </c>
       <c r="X51" s="0" t="n">
-        <v>3001100004</v>
+        <v>3001100005</v>
       </c>
       <c r="Y51" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
+          <t>第六次冲击Lv5-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.3</t>
         </is>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1" s="3">
       <c r="A52" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100004</v>
       </c>
       <c r="C52" s="0" t="n">
         <v>3</v>
@@ -4256,7 +4227,7 @@
         </is>
       </c>
       <c r="M52" s="0" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="N52" s="0" t="n">
         <v>0</v>
@@ -4286,20 +4257,20 @@
         <v>0</v>
       </c>
       <c r="W52" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100004</v>
       </c>
       <c r="X52" s="0" t="n">
-        <v>3001100003</v>
+        <v>3001100004</v>
       </c>
       <c r="Y52" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
+          <t>第六次冲击Lv4-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.25</t>
         </is>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1" s="3">
       <c r="A53" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100003</v>
       </c>
       <c r="C53" s="0" t="n">
         <v>3</v>
@@ -4327,7 +4298,7 @@
         </is>
       </c>
       <c r="M53" s="0" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="N53" s="0" t="n">
         <v>0</v>
@@ -4357,20 +4328,20 @@
         <v>0</v>
       </c>
       <c r="W53" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100003</v>
       </c>
       <c r="X53" s="0" t="n">
-        <v>3001100002</v>
+        <v>3001100003</v>
       </c>
       <c r="Y53" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
+          <t>第六次冲击Lv3-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.2</t>
         </is>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1" s="3">
       <c r="A54" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100002</v>
       </c>
       <c r="C54" s="0" t="n">
         <v>3</v>
@@ -4398,7 +4369,7 @@
         </is>
       </c>
       <c r="M54" s="0" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N54" s="0" t="n">
         <v>0</v>
@@ -4428,22 +4399,21 @@
         <v>0</v>
       </c>
       <c r="W54" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100002</v>
       </c>
       <c r="X54" s="0" t="n">
-        <v>3001100001</v>
+        <v>3001100002</v>
       </c>
       <c r="Y54" s="0" t="inlineStr">
         <is>
-          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
+          <t>第六次冲击Lv2-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.15</t>
         </is>
       </c>
     </row>
     <row r="55" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A55" s="0" t="n">
-        <v>3001200001</v>
-      </c>
-      <c r="B55" s="0" t="inlineStr"/>
+        <v>3001100001</v>
+      </c>
       <c r="C55" s="0" t="n">
         <v>3</v>
       </c>
@@ -4461,17 +4431,14 @@
       </c>
       <c r="H55" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackFireBottle</t>
-        </is>
-      </c>
-      <c r="I55" s="0" t="inlineStr"/>
+          <t>BuffEntityPeriodicAttackShockwave</t>
+        </is>
+      </c>
       <c r="J55" s="0" t="inlineStr">
         <is>
-          <t>1,300101</t>
-        </is>
-      </c>
-      <c r="K55" s="0" t="inlineStr"/>
-      <c r="L55" s="0" t="inlineStr"/>
+          <t>300091</t>
+        </is>
+      </c>
       <c r="M55" s="0" t="n">
         <v>0.1</v>
       </c>
@@ -4503,20 +4470,20 @@
         <v>0</v>
       </c>
       <c r="W55" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100001</v>
       </c>
       <c r="X55" s="0" t="n">
-        <v>3001200001</v>
+        <v>3001100001</v>
       </c>
       <c r="Y55" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>第六次冲击Lv1-每10秒从魔王发出冲击波，伤害=魔王攻击力x0.1</t>
         </is>
       </c>
     </row>
     <row r="56" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A56" s="0" t="n">
-        <v>3001200002</v>
+        <v>3001200001</v>
       </c>
       <c r="B56" s="0" t="inlineStr"/>
       <c r="C56" s="0" t="n">
@@ -4542,7 +4509,7 @@
       <c r="I56" s="0" t="inlineStr"/>
       <c r="J56" s="0" t="inlineStr">
         <is>
-          <t>2,300101</t>
+          <t>1,300101</t>
         </is>
       </c>
       <c r="K56" s="0" t="inlineStr"/>
@@ -4585,13 +4552,13 @@
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="57" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A57" s="0" t="n">
-        <v>3001200003</v>
+        <v>3001200002</v>
       </c>
       <c r="B57" s="0" t="inlineStr"/>
       <c r="C57" s="0" t="n">
@@ -4617,7 +4584,7 @@
       <c r="I57" s="0" t="inlineStr"/>
       <c r="J57" s="0" t="inlineStr">
         <is>
-          <t>3,300101</t>
+          <t>2,300101</t>
         </is>
       </c>
       <c r="K57" s="0" t="inlineStr"/>
@@ -4660,13 +4627,13 @@
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="58" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A58" s="0" t="n">
-        <v>3001200004</v>
+        <v>3001200003</v>
       </c>
       <c r="B58" s="0" t="inlineStr"/>
       <c r="C58" s="0" t="n">
@@ -4692,7 +4659,7 @@
       <c r="I58" s="0" t="inlineStr"/>
       <c r="J58" s="0" t="inlineStr">
         <is>
-          <t>4,300101</t>
+          <t>3,300101</t>
         </is>
       </c>
       <c r="K58" s="0" t="inlineStr"/>
@@ -4735,13 +4702,13 @@
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
         </is>
       </c>
     </row>
     <row r="59" ht="14.25" customFormat="1" customHeight="1" s="2">
       <c r="A59" s="0" t="n">
-        <v>3001200005</v>
+        <v>3001200004</v>
       </c>
       <c r="B59" s="0" t="inlineStr"/>
       <c r="C59" s="0" t="n">
@@ -4767,7 +4734,7 @@
       <c r="I59" s="0" t="inlineStr"/>
       <c r="J59" s="0" t="inlineStr">
         <is>
-          <t>5,300101</t>
+          <t>4,300101</t>
         </is>
       </c>
       <c r="K59" s="0" t="inlineStr"/>
@@ -4810,62 +4777,88 @@
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
+          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
+      <c r="A60" s="0" t="n">
+        <v>3001200005</v>
+      </c>
+      <c r="B60" s="0" t="inlineStr"/>
+      <c r="C60" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>BuffEntityPeriodicAttackFireBottle</t>
+        </is>
+      </c>
+      <c r="I60" s="0" t="inlineStr"/>
+      <c r="J60" s="0" t="inlineStr">
+        <is>
+          <t>5,300101</t>
+        </is>
+      </c>
+      <c r="K60" s="0" t="inlineStr"/>
+      <c r="L60" s="0" t="inlineStr"/>
+      <c r="M60" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="X60" s="0" t="n">
+        <v>3001200001</v>
+      </c>
+      <c r="Y60" s="0" t="inlineStr">
+        <is>
           <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="14.25" customFormat="1" customHeight="1" s="2">
-      <c r="A60" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="X60" s="2" t="n">
-        <v>11000100001</v>
-      </c>
-      <c r="Y60" s="2" t="inlineStr">
-        <is>
-          <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000100001</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>11</v>
@@ -4885,7 +4878,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="O61" s="2" t="n">
@@ -4901,20 +4894,20 @@
         <v>0</v>
       </c>
       <c r="W61" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000100001</v>
       </c>
       <c r="X61" s="2" t="n">
-        <v>11000200001</v>
+        <v>11000100001</v>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>护甲增加{Percentage}%</t>
+          <t>生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>11000300001</v>
+        <v>11000200001</v>
       </c>
       <c r="C62" s="2" t="n">
         <v>11</v>
@@ -4932,85 +4925,90 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J62" s="0" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>DR</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="X62" s="2" t="n">
+        <v>11000200001</v>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>护甲增加{Percentage}%</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>11000300001</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>BuffEntityAttribute</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
+      </c>
+      <c r="J63" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="O62" s="0" t="n">
+      <c r="O63" s="0" t="n">
         <v>0.2</v>
       </c>
-      <c r="P62" s="0" t="n">
+      <c r="P63" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q62" s="2" t="n">
+      <c r="Q63" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="T62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" s="2" t="n">
+      <c r="T63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="X62" s="2" t="n">
+      <c r="X63" s="2" t="n">
         <v>11000300001</v>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>攻击力增加{Percentage}%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="C63" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="D63" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" s="0" t="inlineStr">
-        <is>
-          <t>BuffEntityAttribute</t>
-        </is>
-      </c>
-      <c r="J63" s="0" t="inlineStr">
-        <is>
-          <t>ASPD</t>
-        </is>
-      </c>
-      <c r="O63" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="X63" s="0" t="n">
-        <v>11000400001</v>
-      </c>
-      <c r="Y63" s="0" t="inlineStr">
-        <is>
-          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000400001</v>
       </c>
       <c r="C64" s="0" t="n">
         <v>11</v>
@@ -5025,14 +5023,14 @@
       </c>
       <c r="J64" s="0" t="inlineStr">
         <is>
-          <t>RCD</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="O64" s="0" t="n">
-        <v>-0.25</v>
+        <v>1</v>
       </c>
       <c r="P64" s="0" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
       <c r="T64" s="0" t="n">
         <v>0</v>
@@ -5041,20 +5039,20 @@
         <v>0</v>
       </c>
       <c r="W64" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000400001</v>
       </c>
       <c r="X64" s="0" t="n">
-        <v>11000500001</v>
+        <v>11000400001</v>
       </c>
       <c r="Y64" s="0" t="inlineStr">
         <is>
-          <t>召唤CD{Percentage}%</t>
+          <t>攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000500001</v>
       </c>
       <c r="C65" s="0" t="n">
         <v>11</v>
@@ -5069,7 +5067,7 @@
       </c>
       <c r="J65" s="0" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>RCD</t>
         </is>
       </c>
       <c r="O65" s="0" t="n">
@@ -5085,20 +5083,20 @@
         <v>0</v>
       </c>
       <c r="W65" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000500001</v>
       </c>
       <c r="X65" s="0" t="n">
-        <v>11000600001</v>
+        <v>11000500001</v>
       </c>
       <c r="Y65" s="0" t="inlineStr">
         <is>
-          <t>召唤魔力消耗{Percentage}%</t>
+          <t>召唤CD{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000600001</v>
       </c>
       <c r="C66" s="0" t="n">
         <v>11</v>
@@ -5106,27 +5104,21 @@
       <c r="D66" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G66" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="H66" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityAttributeMulti</t>
+          <t>BuffEntityAttribute</t>
         </is>
       </c>
       <c r="J66" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|HP:-1</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="O66" s="0" t="n">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="P66" s="0" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R66" s="0" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="T66" s="0" t="n">
         <v>0</v>
@@ -5135,20 +5127,20 @@
         <v>0</v>
       </c>
       <c r="W66" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000600001</v>
       </c>
       <c r="X66" s="0" t="n">
-        <v>11000700001</v>
+        <v>11000600001</v>
       </c>
       <c r="Y66" s="0" t="inlineStr">
         <is>
-          <t>狂战士-A</t>
+          <t>召唤魔力消耗{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700001</v>
       </c>
       <c r="C67" s="0" t="n">
         <v>11</v>
@@ -5166,7 +5158,7 @@
       </c>
       <c r="J67" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|DR:-1</t>
+          <t>ATK:1|HP:-1</t>
         </is>
       </c>
       <c r="O67" s="0" t="n">
@@ -5185,20 +5177,20 @@
         <v>0</v>
       </c>
       <c r="W67" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700001</v>
       </c>
       <c r="X67" s="0" t="n">
-        <v>11000700002</v>
+        <v>11000700001</v>
       </c>
       <c r="Y67" s="0" t="inlineStr">
         <is>
-          <t>狂战士-B</t>
+          <t>狂战士-A</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700002</v>
       </c>
       <c r="C68" s="0" t="n">
         <v>11</v>
@@ -5216,7 +5208,7 @@
       </c>
       <c r="J68" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|ASPD:-1</t>
+          <t>ATK:1|DR:-1</t>
         </is>
       </c>
       <c r="O68" s="0" t="n">
@@ -5235,20 +5227,20 @@
         <v>0</v>
       </c>
       <c r="W68" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700002</v>
       </c>
       <c r="X68" s="0" t="n">
-        <v>11000700003</v>
+        <v>11000700002</v>
       </c>
       <c r="Y68" s="0" t="inlineStr">
         <is>
-          <t>狂战士-C</t>
+          <t>狂战士-B</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" s="3">
       <c r="A69" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700003</v>
       </c>
       <c r="C69" s="0" t="n">
         <v>11</v>
@@ -5266,7 +5258,7 @@
       </c>
       <c r="J69" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|DR:-1</t>
+          <t>ATK:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O69" s="0" t="n">
@@ -5285,20 +5277,20 @@
         <v>0</v>
       </c>
       <c r="W69" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700003</v>
       </c>
       <c r="X69" s="0" t="n">
-        <v>11000800001</v>
+        <v>11000700003</v>
       </c>
       <c r="Y69" s="0" t="inlineStr">
         <is>
-          <t>快枪手-A</t>
+          <t>狂战士-C</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" s="3">
       <c r="A70" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800001</v>
       </c>
       <c r="C70" s="0" t="n">
         <v>11</v>
@@ -5316,7 +5308,7 @@
       </c>
       <c r="J70" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|HP:-1</t>
+          <t>ASPD:1|DR:-1</t>
         </is>
       </c>
       <c r="O70" s="0" t="n">
@@ -5335,20 +5327,20 @@
         <v>0</v>
       </c>
       <c r="W70" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800001</v>
       </c>
       <c r="X70" s="0" t="n">
-        <v>11000800002</v>
+        <v>11000800001</v>
       </c>
       <c r="Y70" s="0" t="inlineStr">
         <is>
-          <t>快枪手-B</t>
+          <t>快枪手-A</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="3">
       <c r="A71" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800002</v>
       </c>
       <c r="C71" s="0" t="n">
         <v>11</v>
@@ -5366,7 +5358,7 @@
       </c>
       <c r="J71" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|ATK:-1</t>
+          <t>ASPD:1|HP:-1</t>
         </is>
       </c>
       <c r="O71" s="0" t="n">
@@ -5385,20 +5377,20 @@
         <v>0</v>
       </c>
       <c r="W71" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800002</v>
       </c>
       <c r="X71" s="0" t="n">
-        <v>11000800003</v>
+        <v>11000800002</v>
       </c>
       <c r="Y71" s="0" t="inlineStr">
         <is>
-          <t>快枪手-C</t>
+          <t>快枪手-B</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800003</v>
       </c>
       <c r="C72" s="0" t="n">
         <v>11</v>
@@ -5416,7 +5408,7 @@
       </c>
       <c r="J72" s="0" t="inlineStr">
         <is>
-          <t>DR:1|HP:-1</t>
+          <t>ASPD:1|ATK:-1</t>
         </is>
       </c>
       <c r="O72" s="0" t="n">
@@ -5435,20 +5427,20 @@
         <v>0</v>
       </c>
       <c r="W72" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800003</v>
       </c>
       <c r="X72" s="0" t="n">
-        <v>11000900001</v>
+        <v>11000800003</v>
       </c>
       <c r="Y72" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-A</t>
+          <t>快枪手-C</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900001</v>
       </c>
       <c r="C73" s="0" t="n">
         <v>11</v>
@@ -5466,7 +5458,7 @@
       </c>
       <c r="J73" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ATK:-1</t>
+          <t>DR:1|HP:-1</t>
         </is>
       </c>
       <c r="O73" s="0" t="n">
@@ -5485,20 +5477,20 @@
         <v>0</v>
       </c>
       <c r="W73" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900001</v>
       </c>
       <c r="X73" s="0" t="n">
-        <v>11000900002</v>
+        <v>11000900001</v>
       </c>
       <c r="Y73" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-B</t>
+          <t>铜墙铁壁-A</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900002</v>
       </c>
       <c r="C74" s="0" t="n">
         <v>11</v>
@@ -5516,7 +5508,7 @@
       </c>
       <c r="J74" s="0" t="inlineStr">
         <is>
-          <t>DR:1|ASPD:-1</t>
+          <t>DR:1|ATK:-1</t>
         </is>
       </c>
       <c r="O74" s="0" t="n">
@@ -5535,20 +5527,20 @@
         <v>0</v>
       </c>
       <c r="W74" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900002</v>
       </c>
       <c r="X74" s="0" t="n">
-        <v>11000900003</v>
+        <v>11000900002</v>
       </c>
       <c r="Y74" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-C</t>
+          <t>铜墙铁壁-B</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900003</v>
       </c>
       <c r="C75" s="0" t="n">
         <v>11</v>
@@ -5566,7 +5558,7 @@
       </c>
       <c r="J75" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ASPD:-1</t>
+          <t>DR:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O75" s="0" t="n">
@@ -5585,20 +5577,20 @@
         <v>0</v>
       </c>
       <c r="W75" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900003</v>
       </c>
       <c r="X75" s="0" t="n">
-        <v>11001000001</v>
+        <v>11000900003</v>
       </c>
       <c r="Y75" s="0" t="inlineStr">
         <is>
-          <t>大块头-A</t>
+          <t>铜墙铁壁-C</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000001</v>
       </c>
       <c r="C76" s="0" t="n">
         <v>11</v>
@@ -5616,7 +5608,7 @@
       </c>
       <c r="J76" s="0" t="inlineStr">
         <is>
-          <t>HP:1|DR:-1</t>
+          <t>HP:1|ASPD:-1</t>
         </is>
       </c>
       <c r="O76" s="0" t="n">
@@ -5635,20 +5627,20 @@
         <v>0</v>
       </c>
       <c r="W76" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000001</v>
       </c>
       <c r="X76" s="0" t="n">
-        <v>11001000002</v>
+        <v>11001000001</v>
       </c>
       <c r="Y76" s="0" t="inlineStr">
         <is>
-          <t>大块头-B</t>
+          <t>大块头-A</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000002</v>
       </c>
       <c r="C77" s="0" t="n">
         <v>11</v>
@@ -5666,7 +5658,7 @@
       </c>
       <c r="J77" s="0" t="inlineStr">
         <is>
-          <t>HP:1|ATK:-1</t>
+          <t>HP:1|DR:-1</t>
         </is>
       </c>
       <c r="O77" s="0" t="n">
@@ -5685,20 +5677,20 @@
         <v>0</v>
       </c>
       <c r="W77" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000002</v>
       </c>
       <c r="X77" s="0" t="n">
-        <v>11001000003</v>
+        <v>11001000002</v>
       </c>
       <c r="Y77" s="0" t="inlineStr">
         <is>
-          <t>大块头-C</t>
+          <t>大块头-B</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000003</v>
       </c>
       <c r="C78" s="0" t="n">
         <v>11</v>
@@ -5716,7 +5708,7 @@
       </c>
       <c r="J78" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|RCD:1</t>
+          <t>HP:1|ATK:-1</t>
         </is>
       </c>
       <c r="O78" s="0" t="n">
@@ -5735,20 +5727,20 @@
         <v>0</v>
       </c>
       <c r="W78" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000003</v>
       </c>
       <c r="X78" s="0" t="n">
-        <v>11000700004</v>
+        <v>11001000003</v>
       </c>
       <c r="Y78" s="0" t="inlineStr">
         <is>
-          <t>狂战士-D</t>
+          <t>大块头-C</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000700004</v>
       </c>
       <c r="C79" s="0" t="n">
         <v>11</v>
@@ -5766,7 +5758,7 @@
       </c>
       <c r="J79" s="0" t="inlineStr">
         <is>
-          <t>ATK:1|CMP:1</t>
+          <t>ATK:1|RCD:1</t>
         </is>
       </c>
       <c r="O79" s="0" t="n">
@@ -5785,20 +5777,20 @@
         <v>0</v>
       </c>
       <c r="W79" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000700004</v>
       </c>
       <c r="X79" s="0" t="n">
-        <v>11000700005</v>
+        <v>11000700004</v>
       </c>
       <c r="Y79" s="0" t="inlineStr">
         <is>
-          <t>狂战士-E</t>
+          <t>狂战士-D</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700005</v>
       </c>
       <c r="C80" s="0" t="n">
         <v>11</v>
@@ -5816,7 +5808,7 @@
       </c>
       <c r="J80" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|RCD:1</t>
+          <t>ATK:1|CMP:1</t>
         </is>
       </c>
       <c r="O80" s="0" t="n">
@@ -5835,20 +5827,20 @@
         <v>0</v>
       </c>
       <c r="W80" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700005</v>
       </c>
       <c r="X80" s="0" t="n">
-        <v>11000800004</v>
+        <v>11000700005</v>
       </c>
       <c r="Y80" s="0" t="inlineStr">
         <is>
-          <t>快枪手-D</t>
+          <t>狂战士-E</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000800004</v>
       </c>
       <c r="C81" s="0" t="n">
         <v>11</v>
@@ -5866,7 +5858,7 @@
       </c>
       <c r="J81" s="0" t="inlineStr">
         <is>
-          <t>ASPD:1|CMP:1</t>
+          <t>ASPD:1|RCD:1</t>
         </is>
       </c>
       <c r="O81" s="0" t="n">
@@ -5885,20 +5877,20 @@
         <v>0</v>
       </c>
       <c r="W81" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000800004</v>
       </c>
       <c r="X81" s="0" t="n">
-        <v>11000800005</v>
+        <v>11000800004</v>
       </c>
       <c r="Y81" s="0" t="inlineStr">
         <is>
-          <t>快枪手-E</t>
+          <t>快枪手-D</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800005</v>
       </c>
       <c r="C82" s="0" t="n">
         <v>11</v>
@@ -5916,7 +5908,7 @@
       </c>
       <c r="J82" s="0" t="inlineStr">
         <is>
-          <t>DR:1|RCD:1</t>
+          <t>ASPD:1|CMP:1</t>
         </is>
       </c>
       <c r="O82" s="0" t="n">
@@ -5935,20 +5927,20 @@
         <v>0</v>
       </c>
       <c r="W82" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800005</v>
       </c>
       <c r="X82" s="0" t="n">
-        <v>11000900004</v>
+        <v>11000800005</v>
       </c>
       <c r="Y82" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-D</t>
+          <t>快枪手-E</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000900004</v>
       </c>
       <c r="C83" s="0" t="n">
         <v>11</v>
@@ -5966,7 +5958,7 @@
       </c>
       <c r="J83" s="0" t="inlineStr">
         <is>
-          <t>DR:1|CMP:1</t>
+          <t>DR:1|RCD:1</t>
         </is>
       </c>
       <c r="O83" s="0" t="n">
@@ -5985,20 +5977,20 @@
         <v>0</v>
       </c>
       <c r="W83" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000900004</v>
       </c>
       <c r="X83" s="0" t="n">
-        <v>11000900005</v>
+        <v>11000900004</v>
       </c>
       <c r="Y83" s="0" t="inlineStr">
         <is>
-          <t>铜墙铁壁-E</t>
+          <t>铜墙铁壁-D</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900005</v>
       </c>
       <c r="C84" s="0" t="n">
         <v>11</v>
@@ -6016,7 +6008,7 @@
       </c>
       <c r="J84" s="0" t="inlineStr">
         <is>
-          <t>HP:1|RCD:1</t>
+          <t>DR:1|CMP:1</t>
         </is>
       </c>
       <c r="O84" s="0" t="n">
@@ -6035,20 +6027,20 @@
         <v>0</v>
       </c>
       <c r="W84" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900005</v>
       </c>
       <c r="X84" s="0" t="n">
-        <v>11001000004</v>
+        <v>11000900005</v>
       </c>
       <c r="Y84" s="0" t="inlineStr">
         <is>
-          <t>大块头-D</t>
+          <t>铜墙铁壁-E</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001000004</v>
       </c>
       <c r="C85" s="0" t="n">
         <v>11</v>
@@ -6066,7 +6058,7 @@
       </c>
       <c r="J85" s="0" t="inlineStr">
         <is>
-          <t>HP:1|CMP:1</t>
+          <t>HP:1|RCD:1</t>
         </is>
       </c>
       <c r="O85" s="0" t="n">
@@ -6085,20 +6077,20 @@
         <v>0</v>
       </c>
       <c r="W85" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001000004</v>
       </c>
       <c r="X85" s="0" t="n">
-        <v>11001000005</v>
+        <v>11001000004</v>
       </c>
       <c r="Y85" s="0" t="inlineStr">
         <is>
-          <t>大块头-E</t>
+          <t>大块头-D</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000005</v>
       </c>
       <c r="C86" s="0" t="n">
         <v>11</v>
@@ -6116,14 +6108,14 @@
       </c>
       <c r="J86" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|HP:-0.5</t>
+          <t>HP:1|CMP:1</t>
         </is>
       </c>
       <c r="O86" s="0" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="P86" s="0" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="R86" s="0" t="n">
         <v>0</v>
@@ -6135,20 +6127,20 @@
         <v>0</v>
       </c>
       <c r="W86" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000005</v>
       </c>
       <c r="X86" s="0" t="n">
-        <v>11001100001</v>
+        <v>11001000005</v>
       </c>
       <c r="Y86" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-A</t>
+          <t>大块头-E</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100001</v>
       </c>
       <c r="C87" s="0" t="n">
         <v>11</v>
@@ -6166,7 +6158,7 @@
       </c>
       <c r="J87" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|DR:-0.5</t>
+          <t>RCD:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O87" s="0" t="n">
@@ -6185,20 +6177,20 @@
         <v>0</v>
       </c>
       <c r="W87" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100001</v>
       </c>
       <c r="X87" s="0" t="n">
-        <v>11001100002</v>
+        <v>11001100001</v>
       </c>
       <c r="Y87" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-B</t>
+          <t>魂牵梦绕-A</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100002</v>
       </c>
       <c r="C88" s="0" t="n">
         <v>11</v>
@@ -6216,7 +6208,7 @@
       </c>
       <c r="J88" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ATK:-0.5</t>
+          <t>RCD:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O88" s="0" t="n">
@@ -6235,20 +6227,20 @@
         <v>0</v>
       </c>
       <c r="W88" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100002</v>
       </c>
       <c r="X88" s="0" t="n">
-        <v>11001100003</v>
+        <v>11001100002</v>
       </c>
       <c r="Y88" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-C</t>
+          <t>魂牵梦绕-B</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100003</v>
       </c>
       <c r="C89" s="0" t="n">
         <v>11</v>
@@ -6266,7 +6258,7 @@
       </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|ASPD:-0.5</t>
+          <t>RCD:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O89" s="0" t="n">
@@ -6285,20 +6277,20 @@
         <v>0</v>
       </c>
       <c r="W89" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100003</v>
       </c>
       <c r="X89" s="0" t="n">
-        <v>11001100004</v>
+        <v>11001100003</v>
       </c>
       <c r="Y89" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-D</t>
+          <t>魂牵梦绕-C</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100004</v>
       </c>
       <c r="C90" s="0" t="n">
         <v>11</v>
@@ -6316,7 +6308,7 @@
       </c>
       <c r="J90" s="0" t="inlineStr">
         <is>
-          <t>RCD:-1|CMP:0.5</t>
+          <t>RCD:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O90" s="0" t="n">
@@ -6335,20 +6327,20 @@
         <v>0</v>
       </c>
       <c r="W90" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100004</v>
       </c>
       <c r="X90" s="0" t="n">
-        <v>11001100005</v>
+        <v>11001100004</v>
       </c>
       <c r="Y90" s="0" t="inlineStr">
         <is>
-          <t>魂牵梦绕-E</t>
+          <t>魂牵梦绕-D</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100005</v>
       </c>
       <c r="C91" s="0" t="n">
         <v>11</v>
@@ -6366,7 +6358,7 @@
       </c>
       <c r="J91" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|HP:-0.5</t>
+          <t>RCD:-1|CMP:0.5</t>
         </is>
       </c>
       <c r="O91" s="0" t="n">
@@ -6385,20 +6377,20 @@
         <v>0</v>
       </c>
       <c r="W91" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100005</v>
       </c>
       <c r="X91" s="0" t="n">
-        <v>11001200001</v>
+        <v>11001100005</v>
       </c>
       <c r="Y91" s="0" t="inlineStr">
         <is>
-          <t>折上折-A</t>
+          <t>魂牵梦绕-E</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200001</v>
       </c>
       <c r="C92" s="0" t="n">
         <v>11</v>
@@ -6416,7 +6408,7 @@
       </c>
       <c r="J92" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|DR:-0.5</t>
+          <t>CMP:-1|HP:-0.5</t>
         </is>
       </c>
       <c r="O92" s="0" t="n">
@@ -6435,20 +6427,20 @@
         <v>0</v>
       </c>
       <c r="W92" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200001</v>
       </c>
       <c r="X92" s="0" t="n">
-        <v>11001200002</v>
+        <v>11001200001</v>
       </c>
       <c r="Y92" s="0" t="inlineStr">
         <is>
-          <t>折上折-B</t>
+          <t>折上折-A</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200002</v>
       </c>
       <c r="C93" s="0" t="n">
         <v>11</v>
@@ -6466,7 +6458,7 @@
       </c>
       <c r="J93" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ATK:-0.5</t>
+          <t>CMP:-1|DR:-0.5</t>
         </is>
       </c>
       <c r="O93" s="0" t="n">
@@ -6485,20 +6477,20 @@
         <v>0</v>
       </c>
       <c r="W93" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200002</v>
       </c>
       <c r="X93" s="0" t="n">
-        <v>11001200003</v>
+        <v>11001200002</v>
       </c>
       <c r="Y93" s="0" t="inlineStr">
         <is>
-          <t>折上折-C</t>
+          <t>折上折-B</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200003</v>
       </c>
       <c r="C94" s="0" t="n">
         <v>11</v>
@@ -6516,7 +6508,7 @@
       </c>
       <c r="J94" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|ASPD:-0.5</t>
+          <t>CMP:-1|ATK:-0.5</t>
         </is>
       </c>
       <c r="O94" s="0" t="n">
@@ -6535,20 +6527,20 @@
         <v>0</v>
       </c>
       <c r="W94" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200003</v>
       </c>
       <c r="X94" s="0" t="n">
-        <v>11001200004</v>
+        <v>11001200003</v>
       </c>
       <c r="Y94" s="0" t="inlineStr">
         <is>
-          <t>折上折-D</t>
+          <t>折上折-C</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200004</v>
       </c>
       <c r="C95" s="0" t="n">
         <v>11</v>
@@ -6566,7 +6558,7 @@
       </c>
       <c r="J95" s="0" t="inlineStr">
         <is>
-          <t>CMP:-1|RCD:0.5</t>
+          <t>CMP:-1|ASPD:-0.5</t>
         </is>
       </c>
       <c r="O95" s="0" t="n">
@@ -6585,40 +6577,48 @@
         <v>0</v>
       </c>
       <c r="W95" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200004</v>
       </c>
       <c r="X95" s="0" t="n">
-        <v>11001200005</v>
+        <v>11001200004</v>
       </c>
       <c r="Y95" s="0" t="inlineStr">
         <is>
-          <t>折上折-E</t>
+          <t>折上折-D</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200005</v>
       </c>
       <c r="C96" s="0" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D96" s="0" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="G96" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="H96" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseHPChange</t>
+          <t>BuffEntityAttributeMulti</t>
+        </is>
+      </c>
+      <c r="J96" s="0" t="inlineStr">
+        <is>
+          <t>CMP:-1|RCD:0.5</t>
         </is>
       </c>
       <c r="O96" s="0" t="n">
-        <v>0.05</v>
+        <v>0.75</v>
       </c>
       <c r="P96" s="0" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="S96" s="0" t="n">
-        <v>5</v>
+        <v>0.5</v>
+      </c>
+      <c r="R96" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="T96" s="0" t="n">
         <v>0</v>
@@ -6626,24 +6626,21 @@
       <c r="U96" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W96" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200005</v>
       </c>
       <c r="X96" s="0" t="n">
-        <v>12000100001</v>
+        <v>11001200005</v>
       </c>
       <c r="Y96" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
+          <t>折上折-E</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000100001</v>
       </c>
       <c r="C97" s="0" t="n">
         <v>12</v>
@@ -6653,7 +6650,7 @@
       </c>
       <c r="H97" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityBaseDRChange</t>
+          <t>BuffEntityBaseHPChange</t>
         </is>
       </c>
       <c r="O97" s="0" t="n">
@@ -6672,23 +6669,23 @@
         <v>0</v>
       </c>
       <c r="V97" s="0" t="n">
-        <v>500002</v>
+        <v>500001</v>
       </c>
       <c r="W97" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000100001</v>
       </c>
       <c r="X97" s="0" t="n">
-        <v>12000200001</v>
+        <v>12000100001</v>
       </c>
       <c r="Y97" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%生命</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000200001</v>
       </c>
       <c r="C98" s="0" t="n">
         <v>12</v>
@@ -6698,8 +6695,14 @@
       </c>
       <c r="H98" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackAgain</t>
-        </is>
+          <t>BuffEntityBaseDRChange</t>
+        </is>
+      </c>
+      <c r="O98" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P98" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="S98" s="0" t="n">
         <v>5</v>
@@ -6710,21 +6713,24 @@
       <c r="U98" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V98" s="0" t="n">
+        <v>500002</v>
+      </c>
       <c r="W98" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000200001</v>
       </c>
       <c r="X98" s="0" t="n">
-        <v>12000300001</v>
+        <v>12000200001</v>
       </c>
       <c r="Y98" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒立即攻击一次</t>
+          <t>每隔{Time_S}秒恢复{Percentage}%护甲</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000300001</v>
       </c>
       <c r="C99" s="0" t="n">
         <v>12</v>
@@ -6734,29 +6740,11 @@
       </c>
       <c r="H99" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttribute</t>
-        </is>
-      </c>
-      <c r="I99" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
-        </is>
-      </c>
-      <c r="J99" s="0" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="L99" s="0" t="inlineStr">
-        <is>
-          <t>2001:10&amp;</t>
-        </is>
-      </c>
-      <c r="O99" s="0" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P99" s="0" t="n">
-        <v>0.1</v>
+          <t>BuffEntityPeriodicAttackAgain</t>
+        </is>
+      </c>
+      <c r="S99" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T99" s="0" t="n">
         <v>0</v>
@@ -6765,20 +6753,20 @@
         <v>0</v>
       </c>
       <c r="W99" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000300001</v>
       </c>
       <c r="X99" s="0" t="n">
-        <v>12001100001</v>
+        <v>12000300001</v>
       </c>
       <c r="Y99" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
+          <t>每隔{Time_S}秒立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001100001</v>
       </c>
       <c r="C100" s="0" t="n">
         <v>12</v>
@@ -6798,7 +6786,7 @@
       </c>
       <c r="J100" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L100" s="0" t="inlineStr">
@@ -6819,20 +6807,20 @@
         <v>0</v>
       </c>
       <c r="W100" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001100001</v>
       </c>
       <c r="X100" s="0" t="n">
-        <v>12001200001</v>
+        <v>12001100001</v>
       </c>
       <c r="Y100" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001200001</v>
       </c>
       <c r="C101" s="0" t="n">
         <v>12</v>
@@ -6852,7 +6840,7 @@
       </c>
       <c r="J101" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L101" s="0" t="inlineStr">
@@ -6873,20 +6861,20 @@
         <v>0</v>
       </c>
       <c r="W101" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001200001</v>
       </c>
       <c r="X101" s="0" t="n">
-        <v>12001300001</v>
+        <v>12001200001</v>
       </c>
       <c r="Y101" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001300001</v>
       </c>
       <c r="C102" s="0" t="n">
         <v>12</v>
@@ -6906,7 +6894,7 @@
       </c>
       <c r="J102" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L102" s="0" t="inlineStr">
@@ -6927,20 +6915,20 @@
         <v>0</v>
       </c>
       <c r="W102" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001300001</v>
       </c>
       <c r="X102" s="0" t="n">
-        <v>12001400001</v>
+        <v>12001300001</v>
       </c>
       <c r="Y102" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="103" ht="12" customHeight="1" s="3">
       <c r="A103" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001400001</v>
       </c>
       <c r="C103" s="0" t="n">
         <v>12</v>
@@ -6955,17 +6943,17 @@
       </c>
       <c r="I103" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="J103" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L103" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="O103" s="0" t="n">
@@ -6981,20 +6969,20 @@
         <v>0</v>
       </c>
       <c r="W103" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001400001</v>
       </c>
       <c r="X103" s="0" t="n">
-        <v>12002100001</v>
+        <v>12001400001</v>
       </c>
       <c r="Y103" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
+          <t>击杀{KillNum}次生物，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="104" ht="12" customHeight="1" s="3">
       <c r="A104" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002100001</v>
       </c>
       <c r="C104" s="0" t="n">
         <v>12</v>
@@ -7014,7 +7002,7 @@
       </c>
       <c r="J104" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L104" s="0" t="inlineStr">
@@ -7035,20 +7023,20 @@
         <v>0</v>
       </c>
       <c r="W104" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002100001</v>
       </c>
       <c r="X104" s="0" t="n">
-        <v>12002200001</v>
+        <v>12002100001</v>
       </c>
       <c r="Y104" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="105" ht="12" customHeight="1" s="3">
       <c r="A105" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002200001</v>
       </c>
       <c r="C105" s="0" t="n">
         <v>12</v>
@@ -7068,7 +7056,7 @@
       </c>
       <c r="J105" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L105" s="0" t="inlineStr">
@@ -7089,20 +7077,20 @@
         <v>0</v>
       </c>
       <c r="W105" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002200001</v>
       </c>
       <c r="X105" s="0" t="n">
-        <v>12002300001</v>
+        <v>12002200001</v>
       </c>
       <c r="Y105" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="106" ht="12" customHeight="1" s="3">
       <c r="A106" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002300001</v>
       </c>
       <c r="C106" s="0" t="n">
         <v>12</v>
@@ -7122,7 +7110,7 @@
       </c>
       <c r="J106" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L106" s="0" t="inlineStr">
@@ -7143,20 +7131,20 @@
         <v>0</v>
       </c>
       <c r="W106" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002300001</v>
       </c>
       <c r="X106" s="0" t="n">
-        <v>12002400001</v>
+        <v>12002300001</v>
       </c>
       <c r="Y106" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="107" ht="12" customHeight="1" s="3">
       <c r="A107" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002400001</v>
       </c>
       <c r="C107" s="0" t="n">
         <v>12</v>
@@ -7176,12 +7164,12 @@
       </c>
       <c r="J107" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L107" s="0" t="inlineStr">
         <is>
-          <t>1001:0.5&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="O107" s="0" t="n">
@@ -7197,20 +7185,20 @@
         <v>0</v>
       </c>
       <c r="W107" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002400001</v>
       </c>
       <c r="X107" s="0" t="n">
-        <v>12003100001</v>
+        <v>12002400001</v>
       </c>
       <c r="Y107" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
+          <t>受到{UnderAttackDamage}点伤害，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="108" ht="12" customHeight="1" s="3">
       <c r="A108" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003100001</v>
       </c>
       <c r="C108" s="0" t="n">
         <v>12</v>
@@ -7230,7 +7218,7 @@
       </c>
       <c r="J108" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L108" s="0" t="inlineStr">
@@ -7251,20 +7239,20 @@
         <v>0</v>
       </c>
       <c r="W108" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003100001</v>
       </c>
       <c r="X108" s="0" t="n">
-        <v>12003200001</v>
+        <v>12003100001</v>
       </c>
       <c r="Y108" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="109" ht="12" customHeight="1" s="3">
       <c r="A109" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003200001</v>
       </c>
       <c r="C109" s="0" t="n">
         <v>12</v>
@@ -7284,7 +7272,7 @@
       </c>
       <c r="J109" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L109" s="0" t="inlineStr">
@@ -7305,20 +7293,20 @@
         <v>0</v>
       </c>
       <c r="W109" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003200001</v>
       </c>
       <c r="X109" s="0" t="n">
-        <v>12003300001</v>
+        <v>12003200001</v>
       </c>
       <c r="Y109" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="110" ht="12" customHeight="1" s="3">
       <c r="A110" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003300001</v>
       </c>
       <c r="C110" s="0" t="n">
         <v>12</v>
@@ -7338,7 +7326,7 @@
       </c>
       <c r="J110" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L110" s="0" t="inlineStr">
@@ -7359,20 +7347,20 @@
         <v>0</v>
       </c>
       <c r="W110" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003300001</v>
       </c>
       <c r="X110" s="0" t="n">
-        <v>12003400001</v>
+        <v>12003300001</v>
       </c>
       <c r="Y110" s="0" t="inlineStr">
         <is>
-          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="111" ht="12" customHeight="1" s="3">
       <c r="A111" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003400001</v>
       </c>
       <c r="C111" s="0" t="n">
         <v>12</v>
@@ -7382,18 +7370,22 @@
       </c>
       <c r="H111" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttributeTime</t>
-        </is>
-      </c>
-      <c r="I111" s="0" t="inlineStr"/>
+          <t>BuffEntityConditionalAttribute</t>
+        </is>
+      </c>
+      <c r="I111" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
       <c r="J111" s="0" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L111" s="0" t="inlineStr">
         <is>
-          <t>7001:300&amp;</t>
+          <t>1001:0.5&amp;</t>
         </is>
       </c>
       <c r="O111" s="0" t="n">
@@ -7409,20 +7401,20 @@
         <v>0</v>
       </c>
       <c r="W111" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003400001</v>
       </c>
       <c r="X111" s="0" t="n">
-        <v>12004100001</v>
+        <v>12003400001</v>
       </c>
       <c r="Y111" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
+          <t>血量少于{HPRateLess}%，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004100001</v>
       </c>
       <c r="C112" s="0" t="n">
         <v>12</v>
@@ -7438,7 +7430,7 @@
       <c r="I112" s="0" t="inlineStr"/>
       <c r="J112" s="0" t="inlineStr">
         <is>
-          <t>DR</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="L112" s="0" t="inlineStr">
@@ -7459,20 +7451,20 @@
         <v>0</v>
       </c>
       <c r="W112" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004100001</v>
       </c>
       <c r="X112" s="0" t="n">
-        <v>12004200001</v>
+        <v>12004100001</v>
       </c>
       <c r="Y112" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，生命增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004200001</v>
       </c>
       <c r="C113" s="0" t="n">
         <v>12</v>
@@ -7488,7 +7480,7 @@
       <c r="I113" s="0" t="inlineStr"/>
       <c r="J113" s="0" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>DR</t>
         </is>
       </c>
       <c r="L113" s="0" t="inlineStr">
@@ -7509,20 +7501,20 @@
         <v>0</v>
       </c>
       <c r="W113" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004200001</v>
       </c>
       <c r="X113" s="0" t="n">
-        <v>12004300001</v>
+        <v>12004200001</v>
       </c>
       <c r="Y113" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，护甲增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004300001</v>
       </c>
       <c r="C114" s="0" t="n">
         <v>12</v>
@@ -7538,7 +7530,7 @@
       <c r="I114" s="0" t="inlineStr"/>
       <c r="J114" s="0" t="inlineStr">
         <is>
-          <t>ASPD</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="L114" s="0" t="inlineStr">
@@ -7559,20 +7551,20 @@
         <v>0</v>
       </c>
       <c r="W114" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004300001</v>
       </c>
       <c r="X114" s="0" t="n">
-        <v>12004400001</v>
+        <v>12004300001</v>
       </c>
       <c r="Y114" s="0" t="inlineStr">
         <is>
-          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击力增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004400001</v>
       </c>
       <c r="C115" s="0" t="n">
         <v>12</v>
@@ -7582,18 +7574,25 @@
       </c>
       <c r="H115" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalCreateCrystal</t>
-        </is>
-      </c>
-      <c r="I115" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>BuffEntityConditionalAttributeTime</t>
+        </is>
+      </c>
+      <c r="I115" s="0" t="inlineStr"/>
+      <c r="J115" s="0" t="inlineStr">
+        <is>
+          <t>ASPD</t>
         </is>
       </c>
       <c r="L115" s="0" t="inlineStr">
         <is>
-          <t>2001:10&amp;</t>
-        </is>
+          <t>7001:300&amp;</t>
+        </is>
+      </c>
+      <c r="O115" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P115" s="0" t="n">
+        <v>0.1</v>
       </c>
       <c r="T115" s="0" t="n">
         <v>0</v>
@@ -7602,20 +7601,20 @@
         <v>0</v>
       </c>
       <c r="W115" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004400001</v>
       </c>
       <c r="X115" s="0" t="n">
-        <v>12010100001</v>
+        <v>12004400001</v>
       </c>
       <c r="Y115" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
+          <t>在场存活超过{OnFieldTime}秒后，攻击速度增加{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010100001</v>
       </c>
       <c r="C116" s="0" t="n">
         <v>12</v>
@@ -7630,12 +7629,12 @@
       </c>
       <c r="I116" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L116" s="0" t="inlineStr">
         <is>
-          <t>3001:1000&amp;</t>
+          <t>2001:10&amp;</t>
         </is>
       </c>
       <c r="T116" s="0" t="n">
@@ -7645,20 +7644,20 @@
         <v>0</v>
       </c>
       <c r="W116" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010100001</v>
       </c>
       <c r="X116" s="0" t="n">
-        <v>12010200001</v>
+        <v>12010100001</v>
       </c>
       <c r="Y116" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
+          <t>击杀{KillNum}次生物，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010200001</v>
       </c>
       <c r="C117" s="0" t="n">
         <v>12</v>
@@ -7678,7 +7677,7 @@
       </c>
       <c r="L117" s="0" t="inlineStr">
         <is>
-          <t>4001:1000&amp;</t>
+          <t>3001:1000&amp;</t>
         </is>
       </c>
       <c r="T117" s="0" t="n">
@@ -7688,20 +7687,20 @@
         <v>0</v>
       </c>
       <c r="W117" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010200001</v>
       </c>
       <c r="X117" s="0" t="n">
-        <v>12010300001</v>
+        <v>12010200001</v>
       </c>
       <c r="Y117" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
+          <t>受到{UnderAttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010300001</v>
       </c>
       <c r="C118" s="0" t="n">
         <v>12</v>
@@ -7716,12 +7715,12 @@
       </c>
       <c r="I118" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_RegainHP</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L118" s="0" t="inlineStr">
         <is>
-          <t>5001:500&amp;</t>
+          <t>4001:1000&amp;</t>
         </is>
       </c>
       <c r="T118" s="0" t="n">
@@ -7731,20 +7730,20 @@
         <v>0</v>
       </c>
       <c r="W118" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010300001</v>
       </c>
       <c r="X118" s="0" t="n">
-        <v>12010400001</v>
+        <v>12010300001</v>
       </c>
       <c r="Y118" s="0" t="inlineStr">
         <is>
-          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
+          <t>造成{AttackDamage}点伤害，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010400001</v>
       </c>
       <c r="C119" s="0" t="n">
         <v>12</v>
@@ -7764,7 +7763,7 @@
       </c>
       <c r="L119" s="0" t="inlineStr">
         <is>
-          <t>6001:1000&amp;</t>
+          <t>5001:500&amp;</t>
         </is>
       </c>
       <c r="T119" s="0" t="n">
@@ -7774,20 +7773,20 @@
         <v>0</v>
       </c>
       <c r="W119" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010400001</v>
       </c>
       <c r="X119" s="0" t="n">
-        <v>12010500001</v>
+        <v>12010400001</v>
       </c>
       <c r="Y119" s="0" t="inlineStr">
         <is>
-          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
+          <t>累计被治疗{RegainHPReceived}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010500001</v>
       </c>
       <c r="C120" s="0" t="n">
         <v>12</v>
@@ -7797,17 +7796,17 @@
       </c>
       <c r="H120" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalAttackAgain</t>
+          <t>BuffEntityConditionalCreateCrystal</t>
         </is>
       </c>
       <c r="I120" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_RegainHP</t>
         </is>
       </c>
       <c r="L120" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
+          <t>6001:1000&amp;</t>
         </is>
       </c>
       <c r="T120" s="0" t="n">
@@ -7817,20 +7816,20 @@
         <v>0</v>
       </c>
       <c r="W120" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010500001</v>
       </c>
       <c r="X120" s="0" t="n">
-        <v>12011100001</v>
+        <v>12010500001</v>
       </c>
       <c r="Y120" s="0" t="inlineStr">
         <is>
-          <t>击杀{KillNum}次生物，立即攻击一次</t>
+          <t>累计治疗{RegainHPCast}点，掉落一次魔晶</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011100001</v>
       </c>
       <c r="C121" s="0" t="n">
         <v>12</v>
@@ -7845,12 +7844,12 @@
       </c>
       <c r="I121" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L121" s="0" t="inlineStr">
         <is>
-          <t>3001:200&amp;</t>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="T121" s="0" t="n">
@@ -7860,20 +7859,20 @@
         <v>0</v>
       </c>
       <c r="W121" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011100001</v>
       </c>
       <c r="X121" s="0" t="n">
-        <v>12011200001</v>
+        <v>12011100001</v>
       </c>
       <c r="Y121" s="0" t="inlineStr">
         <is>
-          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
+          <t>击杀{KillNum}次生物，立即攻击一次</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011200001</v>
       </c>
       <c r="C122" s="0" t="n">
         <v>12</v>
@@ -7893,7 +7892,7 @@
       </c>
       <c r="L122" s="0" t="inlineStr">
         <is>
-          <t>4001:200&amp;</t>
+          <t>3001:200&amp;</t>
         </is>
       </c>
       <c r="T122" s="0" t="n">
@@ -7903,20 +7902,20 @@
         <v>0</v>
       </c>
       <c r="W122" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011200001</v>
       </c>
       <c r="X122" s="0" t="n">
-        <v>12011300001</v>
+        <v>12011200001</v>
       </c>
       <c r="Y122" s="0" t="inlineStr">
         <is>
-          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
+          <t>受到{UnderAttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011300001</v>
       </c>
       <c r="C123" s="0" t="n">
         <v>12</v>
@@ -7926,24 +7925,18 @@
       </c>
       <c r="H123" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDemonLordMPRegain</t>
+          <t>BuffEntityConditionalAttackAgain</t>
         </is>
       </c>
       <c r="I123" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack_Dead</t>
+          <t>GameFightLogic_UnderAttack</t>
         </is>
       </c>
       <c r="L123" s="0" t="inlineStr">
         <is>
-          <t>2001:1&amp;</t>
-        </is>
-      </c>
-      <c r="M123" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="N123" s="0" t="n">
-        <v>10</v>
+          <t>4001:200&amp;</t>
+        </is>
       </c>
       <c r="T123" s="0" t="n">
         <v>0</v>
@@ -7952,20 +7945,20 @@
         <v>0</v>
       </c>
       <c r="W123" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011300001</v>
       </c>
       <c r="X123" s="0" t="n">
-        <v>12012100001</v>
+        <v>12011300001</v>
       </c>
       <c r="Y123" s="0" t="inlineStr">
         <is>
-          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
+          <t>造成{AttackDamage}点伤害，秒再攻击一次</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="n">
-        <v>12012200001</v>
+        <v>12012100001</v>
       </c>
       <c r="C124" s="0" t="n">
         <v>12</v>
@@ -7980,12 +7973,12 @@
       </c>
       <c r="I124" s="0" t="inlineStr">
         <is>
-          <t>GameFightLogic_UnderAttack</t>
+          <t>GameFightLogic_UnderAttack_Dead</t>
         </is>
       </c>
       <c r="L124" s="0" t="inlineStr">
         <is>
-          <t>3001:100&amp;</t>
+          <t>2001:1&amp;</t>
         </is>
       </c>
       <c r="M124" s="0" t="n">
@@ -8001,40 +7994,47 @@
         <v>0</v>
       </c>
       <c r="W124" s="0" t="n">
-        <v>12012200001</v>
+        <v>12012100001</v>
       </c>
       <c r="X124" s="0" t="n">
-        <v>12012200001</v>
+        <v>12012100001</v>
       </c>
       <c r="Y124" s="0" t="inlineStr">
         <is>
-          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
+          <t>每击杀{KillNum}个生物，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012200001</v>
       </c>
       <c r="C125" s="0" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D125" s="0" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H125" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicPickupCrystal</t>
+          <t>BuffEntityConditionalDemonLordMPRegain</t>
+        </is>
+      </c>
+      <c r="I125" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="L125" s="0" t="inlineStr">
+        <is>
+          <t>3001:100&amp;</t>
         </is>
       </c>
       <c r="M125" s="0" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N125" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S125" s="0" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T125" s="0" t="n">
         <v>0</v>
@@ -8043,20 +8043,20 @@
         <v>0</v>
       </c>
       <c r="W125" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012200001</v>
       </c>
       <c r="X125" s="0" t="n">
-        <v>13000100001</v>
+        <v>12012200001</v>
       </c>
       <c r="Y125" s="0" t="inlineStr">
         <is>
-          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
+          <t>累计受到{UnderAttackDamage}点伤害，魔王回复{Value}点魔力</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000100001</v>
       </c>
       <c r="C126" s="0" t="n">
         <v>13</v>
@@ -8066,13 +8066,17 @@
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadRebirth</t>
-        </is>
-      </c>
-      <c r="I126" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_CreatureDeadEnd</t>
-        </is>
+          <t>BuffEntityPeriodicPickupCrystal</t>
+        </is>
+      </c>
+      <c r="M126" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N126" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="S126" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="T126" s="0" t="n">
         <v>0</v>
@@ -8080,24 +8084,21 @@
       <c r="U126" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="0" t="n">
-        <v>500001</v>
-      </c>
       <c r="W126" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000100001</v>
       </c>
       <c r="X126" s="0" t="n">
-        <v>13000200001</v>
+        <v>13000100001</v>
       </c>
       <c r="Y126" s="0" t="inlineStr">
         <is>
-          <t>死亡后重生</t>
+          <t>每隔{Time_S}秒自动拾取附近魔晶</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="C127" s="0" t="n">
         <v>13</v>
@@ -8107,7 +8108,7 @@
       </c>
       <c r="H127" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAttack</t>
+          <t>BuffEntityConditionalDeadRebirth</t>
         </is>
       </c>
       <c r="I127" s="0" t="inlineStr">
@@ -8115,33 +8116,30 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="J127" s="0" t="n">
-        <v>300001</v>
-      </c>
-      <c r="O127" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="T127" s="0" t="n">
         <v>0</v>
       </c>
       <c r="U127" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="V127" s="0" t="n">
+        <v>500001</v>
+      </c>
       <c r="W127" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="X127" s="0" t="n">
-        <v>13000300001</v>
+        <v>13000200001</v>
       </c>
       <c r="Y127" s="0" t="inlineStr">
         <is>
-          <t>死亡后爆炸</t>
+          <t>死亡后重生</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="C128" s="0" t="n">
         <v>13</v>
@@ -8151,7 +8149,7 @@
       </c>
       <c r="H128" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaHPChange</t>
+          <t>BuffEntityConditionalDeadAttack</t>
         </is>
       </c>
       <c r="I128" s="0" t="inlineStr">
@@ -8160,14 +8158,11 @@
         </is>
       </c>
       <c r="J128" s="0" t="n">
+        <v>300001</v>
+      </c>
+      <c r="O128" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="O128" s="0" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="P128" s="0" t="n">
-        <v>0.01</v>
-      </c>
       <c r="T128" s="0" t="n">
         <v>0</v>
       </c>
@@ -8175,20 +8170,20 @@
         <v>0</v>
       </c>
       <c r="W128" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="X128" s="0" t="n">
-        <v>13000400001</v>
+        <v>13000300001</v>
       </c>
       <c r="Y128" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
+          <t>死亡后爆炸</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="C129" s="0" t="n">
         <v>13</v>
@@ -8198,7 +8193,7 @@
       </c>
       <c r="H129" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadAreaDRChange</t>
+          <t>BuffEntityConditionalDeadAreaHPChange</t>
         </is>
       </c>
       <c r="I129" s="0" t="inlineStr">
@@ -8222,20 +8217,20 @@
         <v>0</v>
       </c>
       <c r="W129" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="X129" s="0" t="n">
-        <v>13000500001</v>
+        <v>13000400001</v>
       </c>
       <c r="Y129" s="0" t="inlineStr">
         <is>
-          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
+          <t>死亡后恢复附近友军生命，恢复量:自身生命上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="C130" s="0" t="n">
         <v>13</v>
@@ -8245,7 +8240,7 @@
       </c>
       <c r="H130" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalDeadCreateCrystal</t>
+          <t>BuffEntityConditionalDeadAreaDRChange</t>
         </is>
       </c>
       <c r="I130" s="0" t="inlineStr">
@@ -8253,8 +8248,14 @@
           <t>GameFightLogic_CreatureDeadEnd</t>
         </is>
       </c>
-      <c r="Q130" s="0" t="n">
-        <v>0.2</v>
+      <c r="J130" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="O130" s="0" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P130" s="0" t="n">
+        <v>0.01</v>
       </c>
       <c r="T130" s="0" t="n">
         <v>0</v>
@@ -8263,70 +8264,39 @@
         <v>0</v>
       </c>
       <c r="W130" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="X130" s="0" t="n">
-        <v>13000600001</v>
+        <v>13000500001</v>
       </c>
       <c r="Y130" s="0" t="inlineStr">
         <is>
-          <t>死亡后{Percentage}%生成魔晶</t>
+          <t>死亡后恢复附近友军护甲，恢复量:自身护甲上限的{Percentage}%</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="n">
-        <v>3000500001</v>
-      </c>
-      <c r="B131" s="0" t="inlineStr"/>
+        <v>13000600001</v>
+      </c>
       <c r="C131" s="0" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H131" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityPeriodicAttackBoomerang</t>
-        </is>
-      </c>
-      <c r="I131" s="0" t="inlineStr"/>
-      <c r="J131" s="0" t="inlineStr">
-        <is>
-          <t>1,300051</t>
-        </is>
-      </c>
-      <c r="K131" s="0" t="inlineStr"/>
-      <c r="L131" s="0" t="inlineStr"/>
-      <c r="M131" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="N131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="0" t="n">
-        <v>0</v>
+          <t>BuffEntityConditionalDeadCreateCrystal</t>
+        </is>
+      </c>
+      <c r="I131" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_CreatureDeadEnd</t>
+        </is>
       </c>
       <c r="Q131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" s="0" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="T131" s="0" t="n">
         <v>0</v>
@@ -8334,24 +8304,21 @@
       <c r="U131" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="W131" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="X131" s="0" t="n">
-        <v>3000500001</v>
+        <v>13000600001</v>
       </c>
       <c r="Y131" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡后{Percentage}%生成魔晶</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="n">
-        <v>3000500002</v>
+        <v>3000500001</v>
       </c>
       <c r="B132" s="0" t="inlineStr"/>
       <c r="C132" s="0" t="n">
@@ -8377,7 +8344,7 @@
       <c r="I132" s="0" t="inlineStr"/>
       <c r="J132" s="0" t="inlineStr">
         <is>
-          <t>2,300051</t>
+          <t>1,300051</t>
         </is>
       </c>
       <c r="K132" s="0" t="inlineStr"/>
@@ -8420,13 +8387,13 @@
       </c>
       <c r="Y132" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv1-每5秒发射1枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="n">
-        <v>3000500003</v>
+        <v>3000500002</v>
       </c>
       <c r="B133" s="0" t="inlineStr"/>
       <c r="C133" s="0" t="n">
@@ -8452,7 +8419,7 @@
       <c r="I133" s="0" t="inlineStr"/>
       <c r="J133" s="0" t="inlineStr">
         <is>
-          <t>3,300051</t>
+          <t>2,300051</t>
         </is>
       </c>
       <c r="K133" s="0" t="inlineStr"/>
@@ -8495,13 +8462,13 @@
       </c>
       <c r="Y133" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv2-每5秒发射2枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="n">
-        <v>3000500004</v>
+        <v>3000500003</v>
       </c>
       <c r="B134" s="0" t="inlineStr"/>
       <c r="C134" s="0" t="n">
@@ -8527,7 +8494,7 @@
       <c r="I134" s="0" t="inlineStr"/>
       <c r="J134" s="0" t="inlineStr">
         <is>
-          <t>4,300051</t>
+          <t>3,300051</t>
         </is>
       </c>
       <c r="K134" s="0" t="inlineStr"/>
@@ -8570,13 +8537,13 @@
       </c>
       <c r="Y134" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv3-每5秒发射3枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="n">
-        <v>3000500005</v>
+        <v>3000500004</v>
       </c>
       <c r="B135" s="0" t="inlineStr"/>
       <c r="C135" s="0" t="n">
@@ -8602,7 +8569,7 @@
       <c r="I135" s="0" t="inlineStr"/>
       <c r="J135" s="0" t="inlineStr">
         <is>
-          <t>5,300051</t>
+          <t>4,300051</t>
         </is>
       </c>
       <c r="K135" s="0" t="inlineStr"/>
@@ -8645,54 +8612,88 @@
       </c>
       <c r="Y135" s="0" t="inlineStr">
         <is>
-          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
+          <t>死亡回旋Lv4-每5秒发射4枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="n">
-        <v>13000700001</v>
-      </c>
+        <v>3000500005</v>
+      </c>
+      <c r="B136" s="0" t="inlineStr"/>
       <c r="C136" s="0" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D136" s="0" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="E136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="H136" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalThorns</t>
-        </is>
-      </c>
-      <c r="I136" s="0" t="inlineStr">
-        <is>
-          <t>GameFightLogic_UnderAttack</t>
-        </is>
+          <t>BuffEntityPeriodicAttackBoomerang</t>
+        </is>
+      </c>
+      <c r="I136" s="0" t="inlineStr"/>
+      <c r="J136" s="0" t="inlineStr">
+        <is>
+          <t>5,300051</t>
+        </is>
+      </c>
+      <c r="K136" s="0" t="inlineStr"/>
+      <c r="L136" s="0" t="inlineStr"/>
+      <c r="M136" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="N136" s="0" t="n">
+        <v>0</v>
       </c>
       <c r="O136" s="0" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="P136" s="0" t="n">
-        <v>0.1</v>
+        <v>0</v>
+      </c>
+      <c r="Q136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="T136" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="U136" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" s="0" t="n">
+        <v>0</v>
+      </c>
       <c r="W136" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="X136" s="0" t="n">
-        <v>13000700001</v>
+        <v>3000500001</v>
       </c>
       <c r="Y136" s="0" t="inlineStr">
         <is>
-          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
+          <t>死亡回旋Lv5-每5秒发射5枚回旋镖,伤害=魔王攻击力,逐目标减半保底1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000700001</v>
       </c>
       <c r="C137" s="0" t="n">
         <v>13</v>
@@ -8702,7 +8703,7 @@
       </c>
       <c r="H137" s="0" t="inlineStr">
         <is>
-          <t>BuffEntityConditionalLifeSteal</t>
+          <t>BuffEntityConditionalThorns</t>
         </is>
       </c>
       <c r="I137" s="0" t="inlineStr">
@@ -8720,20 +8721,20 @@
         <v>0</v>
       </c>
       <c r="W137" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000700001</v>
       </c>
       <c r="X137" s="0" t="n">
-        <v>13000800001</v>
+        <v>13000700001</v>
       </c>
       <c r="Y137" s="0" t="inlineStr">
         <is>
-          <t>造成伤害的{Percentage}%转化为自身生命</t>
+          <t>受到攻击时，反弹承伤的{Percentage}%给攻击者（上限为自身当前生命值）</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="n">
-        <v>13000900001</v>
+        <v>13000800001</v>
       </c>
       <c r="C138" s="0" t="n">
         <v>13</v>
@@ -8743,266 +8744,307 @@
       </c>
       <c r="H138" s="0" t="inlineStr">
         <is>
+          <t>BuffEntityConditionalLifeSteal</t>
+        </is>
+      </c>
+      <c r="I138" s="0" t="inlineStr">
+        <is>
+          <t>GameFightLogic_UnderAttack</t>
+        </is>
+      </c>
+      <c r="O138" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P138" s="0" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="X138" s="0" t="n">
+        <v>13000800001</v>
+      </c>
+      <c r="Y138" s="0" t="inlineStr">
+        <is>
+          <t>造成伤害的{Percentage}%转化为自身生命</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0" t="n">
+        <v>13000900001</v>
+      </c>
+      <c r="C139" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="D139" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H139" s="0" t="inlineStr">
+        <is>
           <t>BuffEntityConditionalInvincible</t>
         </is>
       </c>
-      <c r="K138" s="0" t="inlineStr">
+      <c r="K139" s="0" t="inlineStr">
         <is>
           <t>#FFD700</t>
         </is>
       </c>
-      <c r="M138" s="0" t="n">
+      <c r="M139" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="N138" s="0" t="n">
+      <c r="N139" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="T138" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="W138" s="0" t="n">
+      <c r="T139" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" s="0" t="n">
         <v>13000900001</v>
       </c>
-      <c r="X138" s="0" t="n">
+      <c r="X139" s="0" t="n">
         <v>13000900001</v>
       </c>
-      <c r="Y138" s="0" t="inlineStr">
+      <c r="Y139" s="0" t="inlineStr">
         <is>
           <t>上场后无敌{Value}秒，期间身体变为金色</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="n">
+    <row r="140">
+      <c r="A140" s="0" t="n">
         <v>11001300001</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C140" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D140" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G139" t="n">
+      <c r="G140" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H140" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeDecayByAllyCount</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J140" s="0" t="inlineStr">
         <is>
           <t>ATK</t>
         </is>
       </c>
-      <c r="M139" t="n">
+      <c r="M140" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="N139" t="n">
+      <c r="N140" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="O139" t="n">
-        <v>3</v>
-      </c>
-      <c r="P139" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="T139" t="n">
-        <v>0</v>
-      </c>
-      <c r="U139" t="n">
-        <v>0</v>
-      </c>
-      <c r="W139" t="n">
+      <c r="O140" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P140" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q140" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" s="0" t="n">
         <v>11001300001</v>
       </c>
-      <c r="X139" t="n">
+      <c r="X140" s="0" t="n">
         <v>11001300001</v>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Y140" s="0" t="inlineStr">
         <is>
           <t>独行者-A</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="n">
+    <row r="141">
+      <c r="A141" s="0" t="n">
         <v>11001300002</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C141" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D141" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G140" t="n">
+      <c r="G141" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H141" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeDecayByAllyCount</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="J141" s="0" t="inlineStr">
         <is>
           <t>ASPD</t>
         </is>
       </c>
-      <c r="M140" t="n">
+      <c r="M141" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="N140" t="n">
+      <c r="N141" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="O140" t="n">
-        <v>3</v>
-      </c>
-      <c r="P140" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
+      <c r="O141" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P141" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q141" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U141" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W141" s="0" t="n">
         <v>11001300002</v>
       </c>
-      <c r="X140" t="n">
+      <c r="X141" s="0" t="n">
         <v>11001300002</v>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Y141" s="0" t="inlineStr">
         <is>
           <t>独行者-B</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="n">
+    <row r="142">
+      <c r="A142" s="0" t="n">
         <v>11001300003</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C142" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D142" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G141" t="n">
+      <c r="G142" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H142" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeDecayByAllyCount</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J142" s="0" t="inlineStr">
         <is>
           <t>DR</t>
         </is>
       </c>
-      <c r="M141" t="n">
+      <c r="M142" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="N141" t="n">
+      <c r="N142" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="O141" t="n">
-        <v>3</v>
-      </c>
-      <c r="P141" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="T141" t="n">
-        <v>0</v>
-      </c>
-      <c r="U141" t="n">
-        <v>0</v>
-      </c>
-      <c r="W141" t="n">
+      <c r="O142" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P142" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" s="0" t="n">
         <v>11001300003</v>
       </c>
-      <c r="X141" t="n">
+      <c r="X142" s="0" t="n">
         <v>11001300003</v>
       </c>
-      <c r="Y141" t="inlineStr">
+      <c r="Y142" s="0" t="inlineStr">
         <is>
           <t>独行者-C</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="n">
+    <row r="143">
+      <c r="A143" s="0" t="n">
         <v>11001300004</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C143" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D143" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="G142" t="n">
+      <c r="G143" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H143" s="0" t="inlineStr">
         <is>
           <t>BuffEntityAttributeDecayByAllyCount</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J143" s="0" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="M142" t="n">
+      <c r="M143" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="N142" t="n">
+      <c r="N143" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="O142" t="n">
-        <v>3</v>
-      </c>
-      <c r="P142" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="W142" t="n">
+      <c r="O143" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="P143" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q143" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="0" t="n">
         <v>11001300004</v>
       </c>
-      <c r="X142" t="n">
+      <c r="X143" s="0" t="n">
         <v>11001300004</v>
       </c>
-      <c r="Y142" t="inlineStr">
+      <c r="Y143" s="0" t="inlineStr">
         <is>
           <t>独行者-D</t>
         </is>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -4515,7 +4515,7 @@
       <c r="K56" s="0" t="inlineStr"/>
       <c r="L56" s="0" t="inlineStr"/>
       <c r="M56" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N56" s="0" t="n">
         <v>0</v>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="Y56" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv1-每10秒向1个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       <c r="K57" s="0" t="inlineStr"/>
       <c r="L57" s="0" t="inlineStr"/>
       <c r="M57" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N57" s="0" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Y57" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv2-每10秒向2个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
@@ -4665,7 +4665,7 @@
       <c r="K58" s="0" t="inlineStr"/>
       <c r="L58" s="0" t="inlineStr"/>
       <c r="M58" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N58" s="0" t="n">
         <v>0</v>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="Y58" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv3-每10秒向3个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       <c r="K59" s="0" t="inlineStr"/>
       <c r="L59" s="0" t="inlineStr"/>
       <c r="M59" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N59" s="0" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="Y59" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv4-每10秒向4个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       <c r="K60" s="0" t="inlineStr"/>
       <c r="L60" s="0" t="inlineStr"/>
       <c r="M60" s="0" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="N60" s="0" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="Y60" s="0" t="inlineStr">
         <is>
-          <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力10%伤害,持续5秒</t>
+          <t>瓶装炼狱火Lv5-每10秒向5个敌人投掷炼狱火瓶,落地燃放地形火焰,每1秒对半径1.2内敌人造成魔王攻击力20%伤害,持续5秒</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_buff_info[buff信息].xlsx
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>BuffEntityAttribute</t>
+          <t>BuffEntityAttributeDurationByApplierATK</t>
         </is>
       </c>
       <c r="I6" s="1" t="n"/>
@@ -1682,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="T6" s="0" t="n">
         <v>0</v>
